--- a/price.xlsx
+++ b/price.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ПРОЕКТ AI\ЛИЧНЫЕ НАРАБОТКИ\AI Skin Lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0A0FA8-FC6C-4286-ADF1-DD79E041E0B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF242B31-3E9A-4895-9F11-BC1309E0508C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="777">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="790">
   <si>
     <t>Артикул</t>
   </si>
@@ -4186,6 +4186,149 @@
 Вік: 25+, 30+, 40+, 50+
 Країна виробництва: 🇺🇦 Україна
 🌟 Illumination Quadro C Elixir – твій must-have для сяючої, рівної та молодої шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>Освітлювальний молекулярний тонік з ніацинамідом та глутатіоном Smart4Derma N-glutation Tonic Molecular Glow 250 мл</t>
+  </si>
+  <si>
+    <t>856</t>
+  </si>
+  <si>
+    <t>✨ Illuminating Toner – твій щоденний крок до рівного тону та сяйва! ✨
+🌿 Потужна формула:
+💎 Освітлює сліди постакне та рубці
+🌸 Зміцнює захисний бар’єр шкіри
+💧 Інтенсивно зволожує та робить шкіру м’якою
+🛡️ Захищає від вільних радикалів та зовнішніх факторів
+🌟 Запобігає появі пігментних плям і вирівнює колір обличчя
+💚 Результат – гладка, сяюча та здорова шкіра без недоліків!
+📌 Ключові активні компоненти:
+🌱 Арбутин – освітлення та профілактика пігментації
+☀️ Вітамін C – антиоксидантний захист та вирівнювання тону
+💎 Глутатіон – потужний антиоксидант, підтримує баланс шкіри
+🌸 Диглюкозид галової кислоти – зміцнює та відновлює
+🌼 Екстракт маргаритки та толокнянки – природне освітлення та регенерація
+🌿 Олія Шуінко – живлення та захист
+⚡ Папаїн – м’яке відлущення та оновлення
+📌 Як застосовувати:  
+Нанеси тонік на очищену шкіру обличчя вранці та ввечері за допомогою ватного диска.
+М’яко масажуй круговими рухами для кращого проникнення активних компонентів.
+✔️ Характеристики продукту:
+Тип: Освітлювальний тонік
+Призначення: Вирівнювання тону, усунення пігментації, покращення тургору, зміцнення бар’єру
+Тип шкіри: Нормальна, суха, комбінована, чутлива
+Вік: 25+, 30+, 40+, 50+
+Країна виробництва: 🇺🇦 Україна
+🌟 Illuminating Toner – твій must-have для рівного, сяючого та доглянутого обличчя! 🌟</t>
+  </si>
+  <si>
+    <t>Зміцнювальний Нічний крем для чутливої шкіри та куперозом 50 мл</t>
+  </si>
+  <si>
+    <t>✨ Therapeutic Night Cream – нічний догляд для чутливої та куперозної шкіри! ✨
+🌙 Потужна формула для відновлення:
+💎 Зміцнює судини та капіляри
+🌸 Знімає подразнення, почервоніння та набряки
+💧 Інтенсивно зволожує та підтримує ліпідний баланс
+🛡️ Освітлює пігментацію та захищає від зовнішніх факторів
+🌟 Відновлює мікроциркуляцію та дарує комфорт
+💚 Результат – спокійна, рівна та доглянута шкіра щоранку!
+📌 Ключові активні компоненти:
+🌺 Екстракт магнолії – протизапальна дія, зменшення подразнень
+🌱 Поліпептидний комплекс – активізує обмін речовин та зміцнює тканини
+💧 Гіалуронова кислота – глибоке зволоження та еластичність
+🥑 Олія авокадо та жожоба – живлення та відновлення бар’єру
+📌 Показання до застосування:
+Купероз та розацеа
+Судинна сітка та почервоніння
+Реактивна та суха шкіра
+Порушення мікроциркуляції
+📌 Як застосовувати:  
+Нанеси крем на очищену шкіру обличчя перед сном. Рівномірно розподіли по всій поверхні для максимального ефекту.
+✔️ Характеристики продукту:
+Тип: Нічний крем для чутливої шкіри
+Призначення: Зміцнення судин, зволоження, освітлення пігментації, зняття подразнень
+Тип шкіри: Чутлива, суха, куперозна
+Об’єм: 50 мл
+Країна виробництва: 🇺🇦 Україна
+🌟 Therapeutic Night Cream – твій must-have для міцних капілярів та спокійної шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>802</t>
+  </si>
+  <si>
+    <t>Освітлювальна пінка з вітаміном C та глутатіоном Smart4Derma C-glutation Mousse Glow Cleanser 80мл</t>
+  </si>
+  <si>
+    <t>80 мл</t>
+  </si>
+  <si>
+    <t>854</t>
+  </si>
+  <si>
+    <t>✨ C-Glutation Mousse Glow Cleanser – сила вітаміну С та глутатіону! ✨
+🌿 Інноваційна формула:
+💧 Дбайливо очищує від макіяжу, забруднень та себуму
+🌸 Освітлює пігментні плями та сліди постакне
+💎 Забезпечує потужний антиоксидантний захист
+🛡️ Звужує пори та вирівнює мікрорельєф шкіри
+🌟 Дарує здорове сяйво та свіжість
+💚 Результат – чиста, сяюча та доглянута шкіра без подразнень!
+📌 Ключові активні компоненти:
+🌱 Арбутин – освітлення та профілактика пігментації
+☀️ Вітамін C – антиоксидантний захист та вирівнювання тону
+💎 Глутатіон – потужний антиоксидант, зволоження та еластичність
+🌸 Диглюкозид галової кислоти – регенерація та зміцнення
+💧 Пантенол – інтенсивне зволоження та заспокоєння
+📌 Як застосовувати:  
+Нанеси невелику кількість пінки на вологу шкіру, легко помасажуй та змий теплою водою. Використовуй регулярно для максимального ефекту.
+✔️ Характеристики продукту:
+Бренд: Smart4Derma
+Тип: Освітлювальна пінка для вмивання
+Призначення: Очищення, освітлення, зволоження, антиоксидантний захист, себорегуляція
+Тип шкіри: Нормальна, жирна, комбінована, проблемна
+Вік: 20+, 30+, 40+, 50+
+Країна виробництва: 🇺🇦 Україна
+🌟 Smart4Derma C-Glutation Mousse – твій must-have для сяючої та рівної шкіри щодня! 🌟</t>
+  </si>
+  <si>
+    <t>Зміцнювальний Денний крем для чутливої, куперозної шкіри SPF 20 - 50 мл</t>
+  </si>
+  <si>
+    <t>800</t>
+  </si>
+  <si>
+    <t>✨ Strengthening Day Cream SPF 20 – щоденний захист і комфорт для чутливої шкіри! ✨
+🌿 Професійна формула:
+☀️ Захист від UVA/UVB-променів завдяки SPF 20
+💎 Зміцнює капіляри та судини
+🌸 Зменшує почервоніння та подразнення
+💧 Підтримує ліпідний баланс і зволоження
+🌟 Освітлює пігментацію та вирівнює тон
+💚 Результат – спокійна, рівна та доглянута шкіра протягом дня!
+📌 Ключові активні компоненти:
+🌺 Екстракт магнолії – протизапальна дія, зменшення подразнень
+🌸 Екстракт шафрану – освітлення та антиоксидантний захист
+🥑 Олії ши, аргани та нони – живлення та відновлення бар’єру
+🌿 Escin ß-Sitosterol Phtosome®, ескулін, рутин – зміцнення судинної системи
+💧 Гіалуронова кислота та пептиди – зволоження та підвищення еластичності
+⚡ Кофеїн та CM-Naringenin-Chalcone – стимуляція мікроциркуляції
+📌 Показання до застосування:
+Купероз та розацеа
+Судинні сітки та зірочки
+Реактивна та суха шкіра
+Приливний рум’янець
+Порушення мікроциркуляції
+Локальні запалення
+📌 Як застосовувати:  
+Нанеси крем на очищену шкіру обличчя щоранку. Рівномірно розподіли по всій поверхні, уникаючи зони навколо очей.
+✔️ Характеристики продукту:
+Тип: Денний крем для чутливої шкіри
+Об’єм: 50 мл
+Призначення: Зміцнення судин, зменшення почервонінь, освітлення пігментації, захист SPF 20
+Тип шкіри: Чутлива, суха, куперозна
+Країна виробництва: 🇺🇦 Україна
+🌟 Strengthening Day Cream SPF 20 – твій must-have для щоденного захисту та здорової шкіри! 🌟</t>
   </si>
 </sst>
 </file>
@@ -5934,72 +6077,128 @@
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A42" s="12"/>
-      <c r="B42" s="8"/>
+      <c r="A42" s="12" t="s">
+        <v>778</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>777</v>
+      </c>
       <c r="C42" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D42" s="8"/>
+      <c r="D42" s="8">
+        <v>860</v>
+      </c>
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="8"/>
+      <c r="G42" s="8">
+        <v>16</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>672</v>
+      </c>
       <c r="I42" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J42" s="8"/>
-      <c r="K42" s="18"/>
+      <c r="J42" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="K42" s="18" t="s">
+        <v>778</v>
+      </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A43" s="12"/>
-      <c r="B43" s="8"/>
+      <c r="A43" s="12" t="s">
+        <v>782</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>780</v>
+      </c>
       <c r="C43" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D43" s="8"/>
+      <c r="D43" s="8">
+        <v>740</v>
+      </c>
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
+      <c r="G43" s="8">
+        <v>26</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="I43" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J43" s="8"/>
-      <c r="K43" s="18"/>
+      <c r="J43" s="8" t="s">
+        <v>781</v>
+      </c>
+      <c r="K43" s="18" t="s">
+        <v>782</v>
+      </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A44" s="12"/>
-      <c r="B44" s="8"/>
+      <c r="A44" s="12" t="s">
+        <v>785</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>783</v>
+      </c>
       <c r="C44" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D44" s="8"/>
+      <c r="D44" s="8">
+        <v>540</v>
+      </c>
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="8"/>
+      <c r="G44" s="8">
+        <v>17</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>784</v>
+      </c>
       <c r="I44" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J44" s="8"/>
-      <c r="K44" s="18"/>
+      <c r="J44" s="8" t="s">
+        <v>786</v>
+      </c>
+      <c r="K44" s="18" t="s">
+        <v>785</v>
+      </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A45" s="12"/>
-      <c r="B45" s="8"/>
+      <c r="A45" s="12" t="s">
+        <v>788</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>787</v>
+      </c>
       <c r="C45" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D45" s="8"/>
+      <c r="D45" s="8">
+        <v>740</v>
+      </c>
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
+      <c r="G45" s="8">
+        <v>19</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="I45" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J45" s="8"/>
-      <c r="K45" s="18"/>
+      <c r="J45" s="8" t="s">
+        <v>789</v>
+      </c>
+      <c r="K45" s="18" t="s">
+        <v>788</v>
+      </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="12"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ПРОЕКТ AI\ЛИЧНЫЕ НАРАБОТКИ\AI Skin Lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF242B31-3E9A-4895-9F11-BC1309E0508C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55CF0113-EC32-4FDB-875D-560D72D5D3F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1861" uniqueCount="814">
   <si>
     <t>Артикул</t>
   </si>
@@ -3395,9 +3395,6 @@
 🌟 CEF Lab Intensive Retinol Serum – твій must-have для глибокого антивікового догляду та сяючої шкіри! 🌟</t>
   </si>
   <si>
-    <t>Ретинолова старт-сироватка Ceramide CEF Lab 30мл</t>
-  </si>
-  <si>
     <t>1403</t>
   </si>
   <si>
@@ -4329,6 +4326,292 @@
 Тип шкіри: Чутлива, суха, куперозна
 Країна виробництва: 🇺🇦 Україна
 🌟 Strengthening Day Cream SPF 20 – твій must-have для щоденного захисту та здорової шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>🌸 Інтенсивна зміцнювальна маска «Розкішна Магнолія» 50 мл 🌸
+✨ Маска з екстрактом магнолії – справжня розкіш для чутливої та схильної до почервоніння шкіри! Вона дарує комфорт, ніжність та силу, допомагаючи твоїй шкірі сяяти здоров’ям.
+💎 Основні переваги:
+🌿 Заспокоює реактивну та подразнену шкіру
+💖 Зміцнює судини та зменшує їхню реактивність
+🛡️ Відновлює захисний бар’єр шкіри
+💧 Глибоко зволожує та тонізує
+🌸 Сприяє загоєнню дрібних тріщин
+🔥 Показання: купероз, розацеа, судинна сітка, почервоніння, сухість та чутливість.
+🌟 Склад – твій секрет краси: MAXnolia, гамамеліс, рутин, кофеїн, екстракти імбиру, лакриці, алое, пептиди та інші активи для гармонії та сяйва.
+💚 Відчуй ніжність магнолії та подаруй своїй шкірі розкішний догляд!</t>
+  </si>
+  <si>
+    <t>805</t>
+  </si>
+  <si>
+    <t>803</t>
+  </si>
+  <si>
+    <t>✨ SOS Serum for Sensitive &amp; Couperose Skin – миттєве заспокоєння та зміцнення! ✨
+🌿 Потужна терапевтична дія:
+💧 Глибоко зволожує та відновлює бар’єр шкіри
+🌸 Знімає подразнення, свербіж та запалення
+💎 Зміцнює стінки судин і капілярів
+🛡️ Корегує прояви куперозу та розацеа
+🌟 Освітлює пігментацію та вирівнює тон
+⚡ Підвищує поріг чутливості шкіри
+💚 Результат – спокійна, рівна та доглянута шкіра без почервонінь!
+📌 Ключові активні компоненти:
+🌺 Екстракт кори магнолії – протизапальна дія, зменшення подразнень
+☀️ Токоферол (вітамін Е) – антиоксидантний захист
+🍇 Виноградна вода – тонізація та відновлення
+🌱 Рутин та пептиди – зміцнення судин та підвищення еластичності
+💧 Гіалуронова кислота – глибоке зволоження та комфорт
+📌 Показання до застосування:
+Купероз та розацеа
+Судинна сітка та почервоніння
+Реактивна та суха шкіра
+Приливний рум’янець
+Локальні запалення
+Порушення мікроциркуляції
+📌 Як застосовувати:  
+Нанеси невелику кількість сироватки на очищену шкіру обличчя. Використовуй щодня, особливо ввечері для інтенсивного відновлення.
+✔️ Характеристики продукту:
+Тип: Інтенсивна SOS-сироватка
+Об’єм: 50 мл
+Призначення: Зміцнення судин, зволоження, освітлення пігментації, зняття подразнень
+Тип шкіри: Чутлива, суха, куперозна
+Країна виробництва: 🇺🇦 Україна
+🌟 SOS Serum – твій must-have для миттєвого заспокоєння та здорової шкіри без куперозу! 🌟</t>
+  </si>
+  <si>
+    <t>Нейроседативна заспокійлива маска SOS-терапія 50 мл</t>
+  </si>
+  <si>
+    <t>Інтенсивна SOS сиворотка для куперозної шкіри 50 мл</t>
+  </si>
+  <si>
+    <t>Інтенсивна зміцнювальний маска "розкішна магнолія" 50 мл</t>
+  </si>
+  <si>
+    <t>806</t>
+  </si>
+  <si>
+    <t>✨ Neuro-SOS Calming Mask – миттєве заспокоєння та комфорт для чутливої шкіри! ✨
+🌿 Інноваційна формула з пептидним комплексом моментальної дії:
+💎 Зменшує нервову реакцію на зовнішні подразники
+🌸 Заспокоює нейрогенне запалення та почервоніння
+💧 Підвищує поріг толерантності шкіри
+🛡️ Зміцнює капіляри та зменшує реактивність
+🌟 Відновлює баланс і дарує відчуття комфорту
+💚 Результат – спокійна, рівна та доглянута шкіра вже після першого застосування!
+📌 Ключові активні компоненти:
+🌺 Екстракт кораліни, каштану та амбора – протизапальна та зміцнювальна дія
+🥥 Олії таману, Моної де Таїті та андіроба – живлення та відновлення бар’єру
+🌸 MAXnolia та олія сливових кісточок – антиоксидантний захист і заспокоєння
+🌿 Escin ß-Sitosterol Phtosome®, ескулін, рутин – зміцнення судинної системи
+💧 Бета-глюкан та пептиди (ацетил-тетрапептид-40, трипептид-8, гексапептид-1) – зволоження та відновлення
+⚡ PINOLUMIN PWD та CM-Naringenin-Chalcone – зменшення реактивності та подразнень
+📌 Показання до застосування:
+Почервоніння та роздратування
+Купероз та розацеа
+Судинна сітка та зірочки
+Приливний рум’янець
+Порушення мікроциркуляції
+Чутлива та суха шкіра
+✔️ Характеристики продукту:
+Тип: Заспокійлива нейроседативна маска
+Об’єм: 50 мл
+Призначення: Заспокоєння, зміцнення судин, зменшення реактивності, зволоження
+Тип шкіри: Чутлива, суха, куперозна
+Країна виробництва: 🇺🇦 Україна
+🌟 Neuro-SOS Mask – твій must-have для миттєвого заспокоєння та здорової шкіри без подразнень! 🌟</t>
+  </si>
+  <si>
+    <t>Зміцнювалиний 2х-фазний Тонер для чутливої та куперозної шкіри 250 мл</t>
+  </si>
+  <si>
+    <t>811</t>
+  </si>
+  <si>
+    <t>✨ Strengthening 2-Phase Toner – щоденний догляд для чутливої та куперозної шкіри! ✨
+🌿 Формула без спирту:
+💧 Швидко заспокоює подразнення та знімає почервоніння
+🌸 Зменшує набряки та відновлює бар’єр шкіри
+💎 Зміцнює судини та капіляри
+🛡️ Вирівнює тон та підтримує баланс мікробіому
+💚 Результат – свіжа, спокійна та доглянута шкіра щодня!
+📌 Ключові активні компоненти:
+🌱 Гідролізат гамамелісу + квіткова вода – заспокоює та звужує пори
+⚡ Есцин + кофеїн – покращують мікроциркуляцію та знімають набряки
+💧 Пантенол + бісаболол – зволоження та відновлення
+🌸 Ніацинамід – вирівнює тон шкіри
+🌿 Пребіотики – підтримують баланс мікробіому
+🌺 Екстракт камелії – додаткове заспокоєння
+📌 Переваги:
+Зміцнення судин та зменшення куперозу
+Усунення набряків та почервонінь
+Відновлення захисного бар’єру
+📌 Як застосовувати:  
+Перед використанням струсити. Нанести тонер на ватний диск та протерти обличчя вранці й ввечері після очищення.
+✔️ Характеристики продукту:
+Тип: Двофазний тонер для чутливої та куперозної шкіри
+Об’єм: 250 мл
+Призначення: Заспокоєння, зміцнення судин, зменшення почервонінь, відновлення бар’єру
+Тип шкіри: Чутлива, суха, куперозна
+Країна виробництва: 🇺🇦 Україна
+🌟 Strengthening 2-Phase Toner – твій must-have для щоденного комфорту та здорової шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>Міцелярний очищувальний крем-гель для чутливої, куперозної шкіри 250 мл</t>
+  </si>
+  <si>
+    <t>809</t>
+  </si>
+  <si>
+    <t>✨ Micellar Cleansing Cream-Gel – ніжне очищення та захист для чутливої шкіри! ✨
+🌿 Формула для щоденного комфорту:
+💧 Делікатно очищує та видаляє макіяж без подразнень
+🌸 Заспокоює та зменшує почервоніння
+💎 Зміцнює судини та підтримує мікроциркуляцію
+🛡️ Захищає від окислювального стресу
+🌟 Підтримує синтез колагену та покращує загальний стан шкіри
+💚 Результат – чиста, свіжа та доглянута шкіра без відчуття сухості!
+📌 Ключові активні компоненти:
+🌺 Водорозчинна арганова олія – м’яке очищення без порушення гідроліпідного балансу
+🌸 Екстракт магнолії (Maxnolia) – антиоксидантний захист та заспокоєння
+🌱 Пептид Skinasensyl – зменшення чутливості та реактивності
+☕ Кофеїн – стимуляція мікроциркуляції та тонус шкіри
+🌼 Екстракти женьшеню, ромашки та інші фітоекстракти – живлення та відновлення
+💧 Вітамін Е та гліцерин – зволоження та еластичність
+📌 Переваги:
+М’яке очищення та видалення макіяжу
+Заспокійлива дія та антиоксидантний захист
+Стимуляція синтезу колагену
+Підтримка природного балансу шкіри
+📌 Як застосовувати:  
+Нанеси невелику кількість крем-гелю на вологу шкіру, легко помасажуй та змий водою. Використовуй вранці та ввечері.
+✔️ Характеристики продукту:
+Бренд: Smart4Derma
+Тип: Міцелярний очищувальний крем-гель
+Об’єм: 250 мл
+Призначення: Очищення, заспокоєння, зміцнення судин, антиоксидантний захист
+Тип шкіри: Чутлива, суха, куперозна
+Країна виробництва: 🇺🇦 Україна
+🌟 Smart4Derma Micellar Cream-Gel – твій must-have для ніжного очищення та здорової шкіри щодня! 🌟</t>
+  </si>
+  <si>
+    <t>Вдосконалений денний крем SPF 30 - 50 мл</t>
+  </si>
+  <si>
+    <t>730</t>
+  </si>
+  <si>
+    <t>✨ Advanced Day Cream SPF 30 – інтелектуальний догляд та захист! ✨
+🌿 Високотехнологічна формула:
+☀️ Захист від UVA/UVB-променів завдяки SPF 30
+💎 Активізує природні процеси регенерації
+🌸 Стимулює утворення нових клітин
+💧 Відновлює пружність та еластичність
+🌟 Формує овал обличчя та розгладжує зморшки
+💚 Результат – сяюча, підтягнута та захищена шкіра щодня!
+📌 Показання до застосування:
+Фото- та хроностаріння
+Зморшки та тьмяний колір обличчя
+Гіперпігментація
+Знижений тонус шкіри
+Профілактика біостаріння
+Догляд після інвазивних процедур
+📌 Ключові активні компоненти:
+🌱 Комплекс UVA/UVB-фільтрів – захист від сонця
+🥥 Олії ши, кіноа, бабасу та макадамії – живлення та відновлення
+💧 X50 Hyalufiller та гіалуронат натрію – глибоке зволоження та заповнення зморшок
+🌸 Lipobelle Soyaglycone – стимуляція синтезу колагену
+⚡ X50 Photoglow Powder – сяйво та рівний тон
+🌿 Phytopresome та ПДРН – регенерація та ревіталізація
+🥕 Олія моркви та олія ему – антиоксидантний захист
+📌 Як застосовувати:  
+Нанеси крем на очищену шкіру обличчя щоранку. Рівномірно розподіли по всій поверхні, уникаючи зони навколо очей.
+✔️ Характеристики продукту:
+Тип: Денний крем для зрілої шкіри
+Об’єм: 50 мл
+Призначення: Захист SPF 30, омолодження, відновлення пружності, освітлення пігментації
+Тип шкіри: Зріла, суха, комбінована
+Країна виробництва: 🇺🇦 Україна
+🌟 Advanced Day Cream SPF 30 – твій must-have для щоденного захисту та молодої шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>Ретинолова старт-сироватка Ceramide CEF Lab 30 мл</t>
+  </si>
+  <si>
+    <t>Вдосконалювальний Крем з ретинолом та церамідами 50 мл</t>
+  </si>
+  <si>
+    <t>✨ Advanced Retinol &amp; Ceramide Cream – нічний антивіковий догляд! ✨
+🌿 Передова формула:
+💎 Мікрокапсульований ретинол – контрольована нічна ексфоліація без подразнень
+🌸 Цераміди – відновлення епідермального бар’єру та захист від втрати вологи
+💧 Гіалуронат натрію – глибоке зволоження та еластичність
+🛡️ ПДРН та Lipobelle Soyaglycone – стимуляція регенерації та синтезу колагену
+🌟 Рослинні олії (камелії, макадамії, амли, Моной де Таїті) – живлення та антиоксидантний захист
+💚 Результат – пружна, гладка та сяюча шкіра щоранку!
+📌 Дія крему:
+Розгладжує статичні та мімічні зморшки
+Відновлює пружність та еластичність
+Покращує колір обличчя та коригує постакне
+Забезпечує оптимальне зволоження
+Зміцнює дерма-епідермальне сполучення
+📌 Показання до застосування:
+Фото- та хроностаріння
+Зморшки та знижений тонус
+Тьмяний колір та гіперпігментація
+Профілактика біостаріння
+Догляд після інвазивних процедур
+📌 Як застосовувати:  
+Нанеси крем на очищену шкіру обличчя ввечері перед сном. Використовуй регулярно для максимального ефекту.
+✔️ Характеристики продукту:
+Тип: Антивіковий нічний крем
+Об’єм: 50 мл
+Призначення: Омолодження, освітлення, зволоження, відновлення бар’єру
+Тип шкіри: Зріла, суха, комбінована
+Країна виробництва: 🇺🇦 Україна
+🌟 Advanced Retinol &amp; Ceramide Cream – твій must-have для молодої та сяючої шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>731</t>
+  </si>
+  <si>
+    <t>Вдосконалювальний Пептидний крем для періорбітальної зони очей 30 мл</t>
+  </si>
+  <si>
+    <t>734</t>
+  </si>
+  <si>
+    <t>✨ Advanced Peptide Eye Cream – інноваційний догляд для зони навколо очей! ✨
+🌿 Високотехнологічна формула з технологією «рідких пептидів»:
+💎 Ефективно розгладжує тонкі лінії та зморшки
+🌸 Забезпечує миттєвий ліфтинг і моделювання контуру
+💧 Синхронізує природні процеси відновлення шкіри
+🛡️ Запобігає антиоксидантному стресу
+⚡ Потужні провідникові системи доставляють активні комплекси безпосередньо до клітин
+💚 Результат – сяючий, свіжий та молодий погляд!
+📌 Ключові активні компоненти:
+🌱 Декапептиди та олігопептиди – стимуляція синтезу колагену, омолодження
+💧 Гіалуронат натрію – глибоке зволоження та еластичність
+🥭 Олія манго та макадамії – живлення та відновлення бар’єру
+🌊 Екстракт фукуса – антиоксидантний захист та тонізація
+⚡ Аргирелін та нанопептиди – зменшення мімічних зморшок
+🌸 Shadownyl та Agefinity – освітлення та ревіталізація
+📌 Показання до застосування:
+Фото- та хроностаріння
+Зморшки та знижений тонус шкіри
+Гіперпігментація
+Профілактика біостаріння
+Догляд після інвазивних процедур
+📌 Як застосовувати:  
+Нанеси невелику кількість крему на чисту шкіру навколо очей. Використовуй щодня вранці та/або ввечері.
+✔️ Характеристики продукту:
+Тип: Пептидний крем для періорбітальної зони
+Об’єм: 30 мл
+Призначення: Ліфтинг, омолодження, освітлення, зволоження
+Тип шкіри: Чутлива, суха, зріла
+Країна виробництва: 🇺🇦 Україна
+🌟 Advanced Peptide Eye Cream – твій must-have для сяючого та молодого погляду! 🌟</t>
   </si>
 </sst>
 </file>
@@ -5396,10 +5679,10 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>710</v>
+        <v>807</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>658</v>
@@ -5419,18 +5702,18 @@
         <v>657</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="K20" s="18" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>658</v>
@@ -5450,18 +5733,18 @@
         <v>657</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="K21" s="18" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>658</v>
@@ -5481,18 +5764,18 @@
         <v>657</v>
       </c>
       <c r="J22" s="8" t="s">
+        <v>716</v>
+      </c>
+      <c r="K22" s="18" t="s">
         <v>717</v>
-      </c>
-      <c r="K22" s="18" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>658</v>
@@ -5512,18 +5795,18 @@
         <v>657</v>
       </c>
       <c r="J23" s="8" t="s">
+        <v>719</v>
+      </c>
+      <c r="K23" s="18" t="s">
         <v>720</v>
-      </c>
-      <c r="K23" s="18" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>658</v>
@@ -5543,18 +5826,18 @@
         <v>657</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="K24" s="18" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>658</v>
@@ -5574,18 +5857,18 @@
         <v>657</v>
       </c>
       <c r="J25" s="8" t="s">
+        <v>725</v>
+      </c>
+      <c r="K25" s="18" t="s">
         <v>726</v>
-      </c>
-      <c r="K25" s="18" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>658</v>
@@ -5605,18 +5888,18 @@
         <v>657</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K26" s="18" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>658</v>
@@ -5636,18 +5919,18 @@
         <v>657</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="K27" s="18" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>658</v>
@@ -5667,18 +5950,18 @@
         <v>657</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K28" s="18" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>658</v>
@@ -5698,18 +5981,18 @@
         <v>657</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="K29" s="18" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>653</v>
@@ -5729,18 +6012,18 @@
         <v>657</v>
       </c>
       <c r="J30" s="8" t="s">
+        <v>740</v>
+      </c>
+      <c r="K30" s="18" t="s">
         <v>741</v>
-      </c>
-      <c r="K30" s="18" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>653</v>
@@ -5760,18 +6043,18 @@
         <v>657</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="K31" s="18" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>653</v>
@@ -5791,18 +6074,18 @@
         <v>657</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="K32" s="18" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>653</v>
@@ -5822,18 +6105,18 @@
         <v>657</v>
       </c>
       <c r="J33" s="8" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="K33" s="18" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>653</v>
@@ -5853,18 +6136,18 @@
         <v>657</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="K34" s="18" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>653</v>
@@ -5884,18 +6167,18 @@
         <v>657</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K35" s="18" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="12" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>653</v>
@@ -5915,18 +6198,18 @@
         <v>657</v>
       </c>
       <c r="J36" s="8" t="s">
+        <v>759</v>
+      </c>
+      <c r="K36" s="18" t="s">
         <v>760</v>
-      </c>
-      <c r="K36" s="18" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="12" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>653</v>
@@ -5946,18 +6229,18 @@
         <v>657</v>
       </c>
       <c r="J37" s="8" t="s">
+        <v>762</v>
+      </c>
+      <c r="K37" s="18" t="s">
         <v>763</v>
-      </c>
-      <c r="K37" s="18" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>653</v>
@@ -5977,18 +6260,18 @@
         <v>657</v>
       </c>
       <c r="J38" s="8" t="s">
+        <v>765</v>
+      </c>
+      <c r="K38" s="18" t="s">
         <v>766</v>
-      </c>
-      <c r="K38" s="18" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="12" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>653</v>
@@ -6008,18 +6291,18 @@
         <v>657</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K39" s="18" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="12" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>653</v>
@@ -6039,18 +6322,18 @@
         <v>657</v>
       </c>
       <c r="J40" s="8" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="K40" s="18" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="12" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>653</v>
@@ -6070,18 +6353,18 @@
         <v>657</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="K41" s="18" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="12" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>653</v>
@@ -6101,18 +6384,18 @@
         <v>657</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="K42" s="18" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="12" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>653</v>
@@ -6132,18 +6415,18 @@
         <v>657</v>
       </c>
       <c r="J43" s="8" t="s">
+        <v>780</v>
+      </c>
+      <c r="K43" s="18" t="s">
         <v>781</v>
-      </c>
-      <c r="K43" s="18" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="12" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>653</v>
@@ -6157,24 +6440,24 @@
         <v>17</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="I44" s="8" t="s">
         <v>657</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="K44" s="18" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>653</v>
@@ -6194,227 +6477,395 @@
         <v>657</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="K45" s="18" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A46" s="12"/>
-      <c r="B46" s="8"/>
+      <c r="A46" s="12" t="s">
+        <v>790</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>795</v>
+      </c>
       <c r="C46" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D46" s="8"/>
+      <c r="D46" s="8">
+        <v>640</v>
+      </c>
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
-      <c r="I46" s="8"/>
-      <c r="J46" s="8"/>
-      <c r="K46" s="18"/>
+      <c r="G46" s="8">
+        <v>29</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>789</v>
+      </c>
+      <c r="K46" s="18" t="s">
+        <v>790</v>
+      </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A47" s="12"/>
-      <c r="B47" s="8"/>
+      <c r="A47" s="12" t="s">
+        <v>791</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>794</v>
+      </c>
       <c r="C47" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D47" s="8"/>
+      <c r="D47" s="8">
+        <v>1460</v>
+      </c>
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="18"/>
+      <c r="G47" s="8">
+        <v>17</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J47" s="8" t="s">
+        <v>792</v>
+      </c>
+      <c r="K47" s="18" t="s">
+        <v>791</v>
+      </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A48" s="12"/>
-      <c r="B48" s="8"/>
+      <c r="A48" s="12" t="s">
+        <v>796</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>793</v>
+      </c>
       <c r="C48" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D48" s="8"/>
+      <c r="D48" s="8">
+        <v>800</v>
+      </c>
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
-      <c r="H48" s="8"/>
-      <c r="I48" s="8"/>
-      <c r="J48" s="8"/>
-      <c r="K48" s="18"/>
+      <c r="G48" s="8">
+        <v>19</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>797</v>
+      </c>
+      <c r="K48" s="18" t="s">
+        <v>796</v>
+      </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A49" s="12"/>
-      <c r="B49" s="8"/>
+      <c r="A49" s="12" t="s">
+        <v>799</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>798</v>
+      </c>
       <c r="C49" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D49" s="8"/>
+      <c r="D49" s="8">
+        <v>860</v>
+      </c>
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8"/>
-      <c r="I49" s="8"/>
-      <c r="J49" s="8"/>
-      <c r="K49" s="18"/>
+      <c r="G49" s="8">
+        <v>22</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J49" s="8" t="s">
+        <v>800</v>
+      </c>
+      <c r="K49" s="18" t="s">
+        <v>799</v>
+      </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A50" s="12"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="8"/>
+      <c r="A50" s="12" t="s">
+        <v>802</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>801</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="D50" s="8">
+        <v>800</v>
+      </c>
       <c r="E50" s="8"/>
       <c r="F50" s="8"/>
-      <c r="G50" s="8"/>
-      <c r="H50" s="8"/>
-      <c r="I50" s="8"/>
-      <c r="J50" s="9"/>
-      <c r="K50" s="15"/>
+      <c r="G50" s="8">
+        <v>25</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>803</v>
+      </c>
+      <c r="K50" s="18" t="s">
+        <v>802</v>
+      </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A51" s="12"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="8"/>
+      <c r="A51" s="12" t="s">
+        <v>805</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="D51" s="8">
+        <v>1400</v>
+      </c>
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
-      <c r="H51" s="8"/>
-      <c r="I51" s="8"/>
-      <c r="J51" s="9"/>
-      <c r="K51" s="15"/>
+      <c r="G51" s="8">
+        <v>18</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J51" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="K51" s="18" t="s">
+        <v>805</v>
+      </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A52" s="12"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="8"/>
+      <c r="A52" s="12" t="s">
+        <v>810</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="D52" s="8">
+        <v>1260</v>
+      </c>
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
-      <c r="G52" s="8"/>
-      <c r="H52" s="8"/>
-      <c r="I52" s="8"/>
-      <c r="J52" s="9"/>
-      <c r="K52" s="15"/>
+      <c r="G52" s="8">
+        <v>26</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J52" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="K52" s="18" t="s">
+        <v>810</v>
+      </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A53" s="12"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="8"/>
+      <c r="A53" s="12" t="s">
+        <v>812</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>811</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="D53" s="8">
+        <v>800</v>
+      </c>
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
-      <c r="G53" s="8"/>
-      <c r="H53" s="8"/>
-      <c r="I53" s="8"/>
-      <c r="J53" s="9"/>
-      <c r="K53" s="15"/>
+      <c r="G53" s="8">
+        <v>24</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>664</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J53" s="8" t="s">
+        <v>813</v>
+      </c>
+      <c r="K53" s="18" t="s">
+        <v>812</v>
+      </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="12"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8" t="s">
+        <v>653</v>
+      </c>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
       <c r="G54" s="8"/>
       <c r="H54" s="8"/>
-      <c r="I54" s="8"/>
-      <c r="J54" s="9"/>
-      <c r="K54" s="15"/>
+      <c r="I54" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J54" s="8"/>
+      <c r="K54" s="18"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="12"/>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
+      <c r="B55" s="8"/>
+      <c r="C55" s="8" t="s">
+        <v>653</v>
+      </c>
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
-      <c r="I55" s="8"/>
-      <c r="J55" s="9"/>
-      <c r="K55" s="15"/>
+      <c r="I55" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J55" s="8"/>
+      <c r="K55" s="18"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="12"/>
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
+      <c r="B56" s="8"/>
+      <c r="C56" s="8" t="s">
+        <v>653</v>
+      </c>
       <c r="D56" s="8"/>
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
       <c r="G56" s="8"/>
       <c r="H56" s="8"/>
-      <c r="I56" s="8"/>
-      <c r="J56" s="9"/>
-      <c r="K56" s="15"/>
+      <c r="I56" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J56" s="8"/>
+      <c r="K56" s="18"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="12"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
+      <c r="B57" s="8"/>
+      <c r="C57" s="8" t="s">
+        <v>653</v>
+      </c>
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
-      <c r="I57" s="8"/>
-      <c r="J57" s="9"/>
-      <c r="K57" s="15"/>
+      <c r="I57" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J57" s="8"/>
+      <c r="K57" s="18"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="12"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
+      <c r="B58" s="8"/>
+      <c r="C58" s="8" t="s">
+        <v>653</v>
+      </c>
       <c r="D58" s="8"/>
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
       <c r="G58" s="8"/>
       <c r="H58" s="8"/>
-      <c r="I58" s="8"/>
-      <c r="J58" s="9"/>
-      <c r="K58" s="15"/>
+      <c r="I58" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J58" s="8"/>
+      <c r="K58" s="18"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="12"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
+      <c r="B59" s="8"/>
+      <c r="C59" s="8" t="s">
+        <v>653</v>
+      </c>
       <c r="D59" s="8"/>
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
       <c r="G59" s="8"/>
       <c r="H59" s="8"/>
-      <c r="I59" s="8"/>
-      <c r="J59" s="9"/>
-      <c r="K59" s="15"/>
+      <c r="I59" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J59" s="8"/>
+      <c r="K59" s="18"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="12"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
+      <c r="B60" s="8"/>
+      <c r="C60" s="8" t="s">
+        <v>653</v>
+      </c>
       <c r="D60" s="8"/>
       <c r="E60" s="8"/>
       <c r="F60" s="8"/>
       <c r="G60" s="8"/>
       <c r="H60" s="8"/>
-      <c r="I60" s="8"/>
-      <c r="J60" s="9"/>
-      <c r="K60" s="15"/>
+      <c r="I60" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J60" s="8"/>
+      <c r="K60" s="18"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="12"/>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
+      <c r="B61" s="8"/>
+      <c r="C61" s="8" t="s">
+        <v>653</v>
+      </c>
       <c r="D61" s="8"/>
       <c r="E61" s="8"/>
       <c r="F61" s="8"/>
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
-      <c r="I61" s="8"/>
-      <c r="J61" s="9"/>
-      <c r="K61" s="15"/>
+      <c r="I61" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J61" s="8"/>
+      <c r="K61" s="18"/>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="12"/>
@@ -6425,7 +6876,9 @@
       <c r="F62" s="8"/>
       <c r="G62" s="8"/>
       <c r="H62" s="8"/>
-      <c r="I62" s="8"/>
+      <c r="I62" s="8" t="s">
+        <v>657</v>
+      </c>
       <c r="J62" s="9"/>
       <c r="K62" s="15"/>
     </row>

--- a/price.xlsx
+++ b/price.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ПРОЕКТ AI\ЛИЧНЫЕ НАРАБОТКИ\AI Skin Lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55CF0113-EC32-4FDB-875D-560D72D5D3F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2845FEF-0906-4AA1-80F0-30CDEDD8980B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Зручна таблиця" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1861" uniqueCount="814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1922" uniqueCount="841">
   <si>
     <t>Артикул</t>
   </si>
@@ -4612,6 +4612,340 @@
 Тип шкіри: Чутлива, суха, зріла
 Країна виробництва: 🇺🇦 Україна
 🌟 Advanced Peptide Eye Cream – твій must-have для сяючого та молодого погляду! 🌟</t>
+  </si>
+  <si>
+    <t>Рестарт-сиворотка з ретинолом та PDNA - 30 мл</t>
+  </si>
+  <si>
+    <t>✨ Restart Retinol &amp; PDNA Serum – революційний нічний догляд! ✨
+🌙 Інноваційна формула з охолоджуючим ефектом:
+💎 Зменшує тонкі лінії та зморшки
+🌸 Вирівнює та зміцнює шкіру
+💧 Оновлює текстуру та пом’якшує
+🛡️ Мінімізує прояви акне та постакне
+⚡ Працює без лущення та подразнень завдяки технології Slow Release Retinol
+💚 Результат – гладка, пружна та сяюча шкіра щоранку!
+📌 Ключові інновації:
+🌱 Ретиноїди + полінуклеотиди (PDNA) – подвійна дія для відновлення та омолодження
+🌸 Фіторелаксанти – підвищують толерантність чутливої шкіри
+⚡ SLOW RELEASE RETINOL – контрольоване нічне вивільнення без подразнень
+💧 Гіалуронат натрію та олії кіноа, баобаба – глибоке зволоження та живлення
+🌟 ПДРН, Lipobelle Soyaglycone, Suberlift – стимуляція регенерації та пружності
+🛡️ RADICARE-GOLD та альфа-ліпоєва кислота – потужний антиоксидантний захист
+📌 Показання до застосування:
+Фото- та хроностаріння
+Зморшки та знижений тонус
+Гіперпігментація
+Постакне та нерівна текстура
+Догляд після інвазивних процедур
+📌 Як застосовувати:  
+Нанеси сироватку ввечері на очищену шкіру обличчя. Використовуй регулярно для максимального ефекту омолодження та відновлення.
+✔️ Характеристики продукту:
+Тип: Нічна антивікова сироватка
+Об’єм: 50 мл
+Призначення: Омолодження, освітлення, відновлення, антиоксидантний захист
+Тип шкіри: Зріла, комбінована, проблемна
+Країна виробництва: 🇺🇦 Україна
+🌟 Restart Serum – твій must-have для нічного відновлення та сяючої шкіри без ознак старіння! 🌟</t>
+  </si>
+  <si>
+    <t>732</t>
+  </si>
+  <si>
+    <t>Омолоджуюча маска "Едельвейс" 50 мл</t>
+  </si>
+  <si>
+    <t>737</t>
+  </si>
+  <si>
+    <t>✨ Edelweiss Stem Cell Mask – інтелектуальне омолодження для твоєї шкіри! ✨
+🌿 Концентрована формула зі стовбуровими клітинами едельвейсу:
+💎 Розгладжує тонкі лінії та зморшки
+🌸 Забезпечує виражений ліфтинг-ефект
+💧 Стимулює оновлення клітин та підтримує їх структуру
+🛡️ Укріплює дерма-епідермальне сполучення
+🌟 Має потужну цитопротекторну дію
+💚 Результат – пружна, сяюча та оновлена шкіра з ефектом перетворення!
+📌 Ключові активні компоненти:
+🌱 PhytoStem Cells Edelweiss – стовбурові клітини едельвейсу для омолодження
+🌸 Екстракт Ambiaty – регенерація та захист
+💧 Гіалуронат натрію – глибоке зволоження
+🌿 ПДРН – стимуляція відновлення клітин
+🌺 Alpine Rose Active та екстракт рису – антиоксидантний захист та ревіталізація
+📌 Показання до застосування:
+Фото- та хроностаріння
+Зморшки та тьмяний колір обличчя
+Гіперпігментація
+Знижений тонус шкіри
+Профілактика біостаріння
+Догляд після інвазивних процедур
+✔️ Характеристики продукту:
+Тип: Омолоджуюча концентрована маска
+Об’єм: 50 мл
+Призначення: Ліфтинг, омолодження, освітлення, зволоження, захист
+Тип шкіри: Зріла, суха, комбінована
+Країна виробництва: 🇺🇦 Україна
+🌟 Edelweiss Stem Cell Mask – твій must-have для миттєвого омолодження та сяючої шкіри!</t>
+  </si>
+  <si>
+    <t>Розкішна ліфтинг-сироватка з ботокс-ефектом Smart4Derma Luxurious Lifting Serum with Botox Effect 50 ml</t>
+  </si>
+  <si>
+    <t>✨ Luxury Lifting Serum – інтелектуальний догляд з ботокс-ефектом! ✨
+🌿 Інноваційна формула:
+💎 Розгладжує мімічні зморшки та зменшує їх вираженість
+💧 Забезпечує глибоке зволоження та відновлення бар’єру
+🌸 Підвищує тонус та пружність шкіри
+🛡️ Бореться з фото- та хроностарінням
+🌟 Пролонгує ефект ін’єкційних методик
+💚 Результат – гладка, підтягнута та сяюча шкіра без ознак втоми!
+📌 Ключові активні компоненти:
+🌱 ПДРН – стимуляція регенерації та відновлення клітин
+💧 Гіалуронат натрію – глибоке зволоження та еластичність
+🌸 Рослинний ретинол – омолодження та вирівнювання текстури
+🌺 Екстракт гібіскуса – антиоксидантний захист та тонізація
+⚡ Інші інноваційні комплекси – для максимального ефекту ліфтингу
+📌 Показання до застосування:
+Зморшки та тьмяний колір обличчя
+Гіперпігментація та знижений тонус
+Профілактика біостаріння
+Догляд після інвазивних процедур
+📌 Як застосовувати:  
+Нанеси кілька крапель сироватки на очищену шкіру обличчя та шиї. Використовуй щодня для досягнення стійкого ефекту омолодження.
+✔️ Характеристики продукту:
+Тип: Ліфтинг-сироватка з ботокс-ефектом
+Об’єм: 50 мл
+Призначення: Омолодження, ліфтинг, зволоження, відновлення бар’єру
+Тип шкіри: Зріла, суха, комбінована
+Країна виробництва: 🇺🇦 Україна
+🌟 Luxury Lifting Serum – твій must-have для розкішного догляду та молодої шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>735</t>
+  </si>
+  <si>
+    <t>Хронобіологічний енергетичний ліфтінг-крем 50 мл</t>
+  </si>
+  <si>
+    <t>✨ ChronoBio Energy Lifting Cream – нічне перезавантаження для твоєї шкіри! ✨
+🌙 Інноваційна хронобіологічна формула з комплексами Chronodyn та DermCom:
+⚡ Максимально стимулює енергообмін у клітинах
+💎 Забезпечує активне відновлення та видимий ліфтинг обличчя, шиї та підборіддя
+🌸 Усуває обвисання та в’ялість (птоз)
+💧 Підвищує пружність і відновлює тонус
+🛡️ Захищає від фото- та хроностаріння
+💚 Результат – підтягнута, сяюча та енергійна шкіра щоранку!
+📌 Ключові активні компоненти:
+🌱 Chronodyn + DermCom – стимуляція клітинного обміну та регенерації
+🥥 Олії сезаму, пасіфлори, моної де Таїті, макадамії – живлення та відновлення бар’єру
+💧 Гіалуронат натрію + Hyaluronic Filling Spheres™ – глибоке зволоження та заповнення зморшок
+🌸 Juveleven™ peptide solution, Replexium, Agefinity™ – омолодження та ревіталізація
+🌿 Фукогель, екстракт цикорію, камедь акації – тонізація та захист
+⚡ Кофеїн та сквален – енергія та антиоксидантний захист
+📌 Показання до застосування:
+Уповільнення старіння без радикальних методів
+Запобігання динамічним та статичним зморшкам
+Фото- та хроностаріння
+Тьмяний колір обличчя
+Гіперпігментація
+Знижений тонус та вікова шкіра
+Догляд після інвазивних процедур
+📌 Як застосовувати:  
+Нанеси крем на очищену шкіру обличчя, шиї та підборіддя перед сном. Використовуй регулярно для максимального ефекту ліфтингу та відновлення.
+✔️ Характеристики продукту:
+Тип: Нічний хронобіологічний ліфтинг-крем
+Об’єм: 50 мл
+Призначення: Ліфтинг, омолодження, відновлення тонусу, зволоження
+Тип шкіри: Зріла, суха, комбінована
+Країна виробництва: 🇺🇦 Україна
+🌟 ChronoBio Energy Lifting Cream – твій must-have для нічного відновлення та сяючої шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>708</t>
+  </si>
+  <si>
+    <t>Заповнювальна маска-біоміметик з вітаміном С, 50 мл</t>
+  </si>
+  <si>
+    <t>✨ Biomimetic Vitamin C Mask – інноваційне омолодження та сяйво! ✨
+🌿 Ультрасучасна формула з багатоформним вітаміном С та 8 пептидами:
+💎 Помітно омолоджує та коригує всі прояви вікових змін
+🌸 Освітлює пігментні плями та вирівнює тон
+💧 Інтенсивно зволожує завдяки гіалуроновій кислоті
+🛡️ Глибоко ревіталізує та відновлює структуру шкіри
+🌟 Пом’якшує видимість ліній і зморшок
+💚 Результат – гладка, сяюча та оновлена шкіра з ефектом перетворення!
+📌 Ключові активні компоненти:
+☀️ Вітамін С у кількох формах – антиоксидантний захист та освітлення
+🌱 8 пептидів (Replexium, Juveleven™, Collalift® 18 та ін.) – стимуляція синтезу колагену та омолодження
+💧 Гіалуронат натрію + Hyaluronic Filling Spheres™ – глибоке зволоження та заповнення зморшок
+🌸 Ceramosides™ Hp та олія насіння квітки Алтеї – відновлення бар’єру та захист від втрати вологи
+⚡ Agefinity™, Easyliance, Collamung® Onp – ревіталізація та ліфтинг
+🌿 Екстракт цикорію, амінокислоти (лізин, серин, валін), пантенол – живлення та відновлення
+📌 Показання до застосування:
+Щоденний догляд для уповільнення старіння
+Запобігання динамічним та статичним зморшкам
+Фото- та хроностаріння
+Тьмяний колір обличчя
+Гіперпігментація
+Знижений тонус шкіри
+Догляд після інвазивних процедур
+✔️ Характеристики продукту:
+Тип: Заповнювальна маска-біоміметик
+Об’єм: 50 мл
+Призначення: Омолодження, освітлення, ревіталізація, зволоження
+Тип шкіри: Зріла, суха, комбінована
+Країна виробництва: 🇺🇦 Україна
+🌟 Biomimetic Vitamin C Mask – твій must-have для сяючої та молодої шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>712</t>
+  </si>
+  <si>
+    <t>Ліпосомальна антиоксидантна ліфтинг-сироватка Age Performance Smart4Derma 50 мл</t>
+  </si>
+  <si>
+    <t>✨ Liposomal Antioxidant Lifting Serum – інноваційний догляд 35+! ✨
+🌿 Високотехнологічна формула з ліпосомальними пептидами:
+💎 Освітлює тон шкіри та усуває тьмяність
+💧 Ефективно зволожує та живить
+🌸 Розгладжує тонкі лінії та зморшки
+🛡️ Захищає від фотостаріння та оксидативного стресу
+🌟 Покращує текстуру та підвищує тонус
+⚡ Запобігає появі динамічних і статичних зморшок
+💚 Ідеальний догляд після інвазивних процедур, контурної пластики чи хірургії
+Результат – сяюча, підтягнута та здорова шкіра вже після перших застосувань!
+📌 Показання до застосування:
+Фото- та хроностаріння
+Зморшки та знижений тонус
+Тьмяний колір обличчя
+Гіперпігментація
+Догляд після інвазивних процедур
+Щоденний догляд для шкіри 35+
+✔️ Характеристики продукту:
+Тип: Антиоксидантна ліфтинг-сироватка
+Об’єм: 50 мл
+Призначення: Омолодження, освітлення, зволоження, захист від фотостаріння
+Тип шкіри: Всі типи
+Країна виробництва: 🇺🇦 Україна
+🌟 Liposomal Antioxidant Lifting Serum – твій must-have для сяючої та молодої шкіри після 35! 🌟</t>
+  </si>
+  <si>
+    <t>717</t>
+  </si>
+  <si>
+    <t>Пептидний ліфтинг-флюїд для зони навколо очей Білосніжна лілія Smart4Derma Age Performance P-LIFT EYE FLUID WHITENESS LILI 30 мл</t>
+  </si>
+  <si>
+    <t>✨ Peptide Eye Lifting Fluid – інноваційний догляд для сяючого погляду! ✨
+🌿 Передова транс-дермальна формула з 14 пептидами:
+💎 Активно бореться з проявами старіння у періорбітальній зоні
+🌸 Зменшує темні кола та освітлює шкіру навколо очей
+💧 Забезпечує виражену протинабрякову дію
+🛡️ Зміцнює судини та покращує мікроциркуляцію
+🌟 Містить рідкісні олії та антиоксиданти останнього покоління
+💚 Результат – свіжий, відпочилий та молодий погляд щодня!
+📌 Ключові активні компоненти:
+🌺 Екстракт білої лілії та CERNILYS® – освітлення та зменшення темних кіл
+🌱 Екстракти чорної лободи, мальви, каштану, гамамелісу, іглиці та арніки – протизапальна та зміцнювальна дія
+☀️ Гесперидин метилхалкон, рутин, есцин, ескулін – зміцнення капілярів та протинабряковий ефект
+🥥 Олія Аннато, масло Ши, олія маракуї – живлення та антиоксидантний захист
+💧 Shadownyl™, Agefinity™, бета-глюкан, фосфоліпіди – ревіталізація та зволоження
+⚡ Кофеїн та наргідринхалкон – стимуляція мікроциркуляції та тонус шкіри
+📌 Показання до застосування:
+Щоденний догляд для уповільнення старіння
+Запобігання динамічним та статичним зморшкам
+Фото- та хроностаріння
+Гіперпігментація та знижений тонус
+Догляд після інвазивних процедур
+📌 Як застосовувати:  
+Нанеси невелику кількість флюїду на чисту шкіру навколо очей. Використовуй щодня вранці та ввечері для максимального ефекту.
+✔️ Характеристики продукту:
+Тип: Пептидний ліфтинг-флюїд для зони навколо очей
+Об’єм: 30 мл
+Призначення: Ліфтинг, освітлення, протинабрякова дія, омолодження
+Тип шкіри: Чутлива, суха, зріла
+Країна виробництва: 🇺🇦 Україна
+🌟 Peptide Eye Lifting Fluid – твій must-have для сяючого та молодого погляду! 🌟</t>
+  </si>
+  <si>
+    <t>711</t>
+  </si>
+  <si>
+    <t>Пептидна ліфтинг сироватка для періорбітальної зони Age Performance Smart4Derma 30 мл</t>
+  </si>
+  <si>
+    <t>✨ Peptide Eye Lifting Serum – інтенсивне омолодження для сяючого погляду! ✨
+🌿 Німецька розробка з передовими sh-поліпептидами:
+💎 Оновлює клітини та відновлює тургор шкіри
+🌸 Уповільнює старіння та попереджає появу зморшок
+💧 Вирівнює тон і мікрорельєф епідермісу
+🛡️ Посилює бар’єрну функцію та стійкість до подразників
+⚡ Забезпечує інтенсивну регенерацію та антиоксидантний захист
+💚 Результат – гладка, пружна та сяюча шкіра навколо очей!
+📌 Ключові активні компоненти:
+🌱 ПДРН – стимуляція клітинного відновлення
+⚡ Argireline – зменшення мімічних зморшок
+🌿 Екстракт кінського каштану та есцин – зміцнення судин та протинабрякова дія
+🌸 Алое та гіалуронат натрію – зволоження та заспокоєння
+💧 Hydagen Aquaporin – підтримка водного балансу
+🛡️ Вітамін Е та бета-ситостерол – антиоксидантний захист
+📌 Показання до застосування:
+Фото- та хроностаріння
+Зморшки та знижений тонус
+Тьмяний колір та гіперпігментація
+Профілактика біостаріння
+Догляд після інвазивних процедур
+📌 Як застосовувати:  
+Наноси сироватку двічі на день на чисту шкіру навколо очей. Використовуй регулярно для максимального ефекту.
+✔️ Характеристики продукту:
+Тип: Пептидна ліфтинг-сироватка для очей
+Об’єм: 30 мл
+Призначення: Омолодження, регенерація, освітлення, протинабрякова дія
+Тип шкіри: Чутлива, зріла, суха
+Країна виробництва: 🇩🇪 Німеччина
+🌟 Peptide Eye Lifting Serum – твій must-have для молодого та сяючого погляду! 🌟</t>
+  </si>
+  <si>
+    <t>716</t>
+  </si>
+  <si>
+    <t>Реструктурирующая маска для зони навколо очей з екстрактом кави арабіка Smart4Derma Arabica eye mask contour relief 50 мл</t>
+  </si>
+  <si>
+    <t>709</t>
+  </si>
+  <si>
+    <t>✨ Arabica Coffee Eye Mask – реструктуруючий догляд для сяючого погляду! ✨
+🌿 Потужний комплекс активних інгредієнтів:
+💎 Бореться з набряками та темними колами
+🌸 Активує мікроциркуляцію та зменшує зморшки
+💧 Стимулює синтез колагену I типу
+🛡️ Знімає запалення в періорбітальній зоні
+💚 Результат – свіжий, відпочилий та молодий погляд без ознак втоми!
+📌 Ключові активні компоненти:
+☕ Екстракт кави арабіка та зеленої кави – тонізація та антиоксидантний захист
+🌱 Гіалуронова кислота та бета-глюкан – глибоке зволоження та відновлення
+🌸 Олії ши, авокадо, журавлини, чіа – живлення та захист від втрати вологи
+⚡ Кофеїн, есцин, ескулін, рутин – протинабрякова дія та зміцнення судин
+🌿 Shadownyl™, Argireline®, Biopeptide El™, Rubixyl® – омолодження та розгладження зморшок
+🛡️ Nano-Lipobelle™ DN, Inoveol EGCG – антиоксидантний щит нового покоління
+📌 Показання до застосування:
+Щоденний догляд для уповільнення старіння
+Профілактика зморшок
+Фото- та хроностаріння
+Тьмяний колір обличчя
+Гіперпігментація
+Знижений тонус та вікова шкіра
+Догляд після інвазивних процедур
+✔️ Характеристики продукту:
+Тип: Реструктуруюча маска для очей
+Об’єм: 30–50 мл (залежно від упаковки)
+Призначення: Освітлення, протинабрякова дія, омолодження, зволоження
+Тип шкіри: Чутлива, зріла, суха
+Бренд: SMART DERMA
+Країна виробництва: 🇺🇦 Україна
+🌟 Arabica Coffee Eye Mask – твій must-have для сяючого та молодого погляду без темних кіл і набряків! 🌟</t>
   </si>
 </sst>
 </file>
@@ -6732,259 +7066,417 @@
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A54" s="12"/>
-      <c r="B54" s="8"/>
+      <c r="A54" s="12" t="s">
+        <v>816</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>814</v>
+      </c>
       <c r="C54" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D54" s="8"/>
+      <c r="D54" s="8">
+        <v>1380</v>
+      </c>
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="8"/>
+      <c r="G54" s="8">
+        <v>17</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>664</v>
+      </c>
       <c r="I54" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J54" s="8"/>
-      <c r="K54" s="18"/>
+      <c r="J54" s="8" t="s">
+        <v>815</v>
+      </c>
+      <c r="K54" s="18" t="s">
+        <v>816</v>
+      </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A55" s="12"/>
-      <c r="B55" s="8"/>
+      <c r="A55" s="12" t="s">
+        <v>818</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>817</v>
+      </c>
       <c r="C55" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D55" s="8"/>
+      <c r="D55" s="8">
+        <v>840</v>
+      </c>
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
-      <c r="G55" s="8"/>
-      <c r="H55" s="8"/>
+      <c r="G55" s="8">
+        <v>18</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="I55" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J55" s="8"/>
-      <c r="K55" s="18"/>
+      <c r="J55" s="8" t="s">
+        <v>819</v>
+      </c>
+      <c r="K55" s="18" t="s">
+        <v>818</v>
+      </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A56" s="12"/>
-      <c r="B56" s="8"/>
+      <c r="A56" s="12" t="s">
+        <v>822</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>820</v>
+      </c>
       <c r="C56" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D56" s="8"/>
+      <c r="D56" s="8">
+        <v>1680</v>
+      </c>
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
-      <c r="G56" s="8"/>
-      <c r="H56" s="8"/>
+      <c r="G56" s="8">
+        <v>25</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="I56" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J56" s="8"/>
-      <c r="K56" s="18"/>
+      <c r="J56" s="8" t="s">
+        <v>821</v>
+      </c>
+      <c r="K56" s="18" t="s">
+        <v>822</v>
+      </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A57" s="12"/>
-      <c r="B57" s="8"/>
+      <c r="A57" s="12" t="s">
+        <v>825</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>823</v>
+      </c>
       <c r="C57" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D57" s="8"/>
+      <c r="D57" s="8">
+        <v>1200</v>
+      </c>
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
-      <c r="G57" s="8"/>
-      <c r="H57" s="8"/>
+      <c r="G57" s="8">
+        <v>21</v>
+      </c>
+      <c r="H57" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="I57" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J57" s="8"/>
-      <c r="K57" s="18"/>
+      <c r="J57" s="8" t="s">
+        <v>824</v>
+      </c>
+      <c r="K57" s="18" t="s">
+        <v>825</v>
+      </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A58" s="12"/>
-      <c r="B58" s="8"/>
+      <c r="A58" s="12" t="s">
+        <v>828</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>826</v>
+      </c>
       <c r="C58" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D58" s="8"/>
+      <c r="D58" s="8">
+        <v>1100</v>
+      </c>
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8"/>
+      <c r="G58" s="8">
+        <v>14</v>
+      </c>
+      <c r="H58" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="I58" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J58" s="8"/>
-      <c r="K58" s="18"/>
+      <c r="J58" s="8" t="s">
+        <v>827</v>
+      </c>
+      <c r="K58" s="18" t="s">
+        <v>828</v>
+      </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A59" s="12"/>
-      <c r="B59" s="8"/>
+      <c r="A59" s="12" t="s">
+        <v>831</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>829</v>
+      </c>
       <c r="C59" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D59" s="8"/>
+      <c r="D59" s="8">
+        <v>1700</v>
+      </c>
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
-      <c r="G59" s="8"/>
-      <c r="H59" s="8"/>
+      <c r="G59" s="8">
+        <v>21</v>
+      </c>
+      <c r="H59" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="I59" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J59" s="8"/>
-      <c r="K59" s="18"/>
+      <c r="J59" s="8" t="s">
+        <v>830</v>
+      </c>
+      <c r="K59" s="18" t="s">
+        <v>831</v>
+      </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A60" s="12"/>
-      <c r="B60" s="8"/>
+      <c r="A60" s="12" t="s">
+        <v>834</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>832</v>
+      </c>
       <c r="C60" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D60" s="8"/>
+      <c r="D60" s="8">
+        <v>1060</v>
+      </c>
       <c r="E60" s="8"/>
       <c r="F60" s="8"/>
-      <c r="G60" s="8"/>
-      <c r="H60" s="8"/>
+      <c r="G60" s="8">
+        <v>14</v>
+      </c>
+      <c r="H60" s="8" t="s">
+        <v>664</v>
+      </c>
       <c r="I60" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J60" s="8"/>
-      <c r="K60" s="18"/>
+      <c r="J60" s="8" t="s">
+        <v>833</v>
+      </c>
+      <c r="K60" s="18" t="s">
+        <v>834</v>
+      </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A61" s="12"/>
-      <c r="B61" s="8"/>
+      <c r="A61" s="12" t="s">
+        <v>837</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>835</v>
+      </c>
       <c r="C61" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D61" s="8"/>
+      <c r="D61" s="8">
+        <v>1200</v>
+      </c>
       <c r="E61" s="8"/>
       <c r="F61" s="8"/>
-      <c r="G61" s="8"/>
-      <c r="H61" s="8"/>
+      <c r="G61" s="8">
+        <v>18</v>
+      </c>
+      <c r="H61" s="8" t="s">
+        <v>664</v>
+      </c>
       <c r="I61" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J61" s="8"/>
-      <c r="K61" s="18"/>
+      <c r="J61" s="8" t="s">
+        <v>836</v>
+      </c>
+      <c r="K61" s="18" t="s">
+        <v>837</v>
+      </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A62" s="12"/>
-      <c r="B62" s="9"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="8"/>
+      <c r="A62" s="12" t="s">
+        <v>839</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>838</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="D62" s="8">
+        <v>1440</v>
+      </c>
       <c r="E62" s="8"/>
       <c r="F62" s="8"/>
-      <c r="G62" s="8"/>
-      <c r="H62" s="8"/>
+      <c r="G62" s="8">
+        <v>17</v>
+      </c>
+      <c r="H62" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="I62" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J62" s="9"/>
-      <c r="K62" s="15"/>
+      <c r="J62" s="8" t="s">
+        <v>840</v>
+      </c>
+      <c r="K62" s="18" t="s">
+        <v>839</v>
+      </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="12"/>
-      <c r="B63" s="9"/>
-      <c r="C63" s="9"/>
+      <c r="B63" s="8"/>
+      <c r="C63" s="8" t="s">
+        <v>653</v>
+      </c>
       <c r="D63" s="8"/>
       <c r="E63" s="8"/>
       <c r="F63" s="8"/>
       <c r="G63" s="8"/>
       <c r="H63" s="8"/>
-      <c r="I63" s="8"/>
-      <c r="J63" s="9"/>
-      <c r="K63" s="15"/>
+      <c r="I63" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J63" s="8"/>
+      <c r="K63" s="18"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="12"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
+      <c r="B64" s="8"/>
+      <c r="C64" s="8" t="s">
+        <v>653</v>
+      </c>
       <c r="D64" s="8"/>
       <c r="E64" s="8"/>
       <c r="F64" s="8"/>
       <c r="G64" s="8"/>
       <c r="H64" s="8"/>
-      <c r="I64" s="8"/>
-      <c r="J64" s="9"/>
-      <c r="K64" s="15"/>
+      <c r="I64" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J64" s="8"/>
+      <c r="K64" s="18"/>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="12"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8" t="s">
+        <v>653</v>
+      </c>
       <c r="D65" s="8"/>
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
       <c r="G65" s="8"/>
       <c r="H65" s="8"/>
-      <c r="I65" s="8"/>
-      <c r="J65" s="9"/>
-      <c r="K65" s="15"/>
+      <c r="I65" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J65" s="8"/>
+      <c r="K65" s="18"/>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="12"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
+      <c r="B66" s="8"/>
+      <c r="C66" s="8" t="s">
+        <v>653</v>
+      </c>
       <c r="D66" s="8"/>
       <c r="E66" s="8"/>
       <c r="F66" s="8"/>
       <c r="G66" s="8"/>
       <c r="H66" s="8"/>
-      <c r="I66" s="8"/>
-      <c r="J66" s="9"/>
-      <c r="K66" s="15"/>
+      <c r="I66" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J66" s="8"/>
+      <c r="K66" s="18"/>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="12"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
+      <c r="B67" s="8"/>
+      <c r="C67" s="8" t="s">
+        <v>653</v>
+      </c>
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
       <c r="F67" s="8"/>
       <c r="G67" s="8"/>
       <c r="H67" s="8"/>
-      <c r="I67" s="8"/>
-      <c r="J67" s="9"/>
-      <c r="K67" s="15"/>
+      <c r="I67" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J67" s="8"/>
+      <c r="K67" s="18"/>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="12"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
+      <c r="B68" s="8"/>
+      <c r="C68" s="8" t="s">
+        <v>653</v>
+      </c>
       <c r="D68" s="8"/>
       <c r="E68" s="8"/>
       <c r="F68" s="8"/>
       <c r="G68" s="8"/>
       <c r="H68" s="8"/>
-      <c r="I68" s="8"/>
-      <c r="J68" s="9"/>
-      <c r="K68" s="15"/>
+      <c r="I68" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J68" s="8"/>
+      <c r="K68" s="18"/>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="12"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
+      <c r="B69" s="8"/>
+      <c r="C69" s="8" t="s">
+        <v>653</v>
+      </c>
       <c r="D69" s="8"/>
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
       <c r="G69" s="8"/>
       <c r="H69" s="8"/>
-      <c r="I69" s="8"/>
-      <c r="J69" s="9"/>
-      <c r="K69" s="15"/>
+      <c r="I69" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J69" s="8"/>
+      <c r="K69" s="18"/>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="12"/>
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
+      <c r="B70" s="8"/>
+      <c r="C70" s="8" t="s">
+        <v>653</v>
+      </c>
       <c r="D70" s="8"/>
       <c r="E70" s="8"/>
       <c r="F70" s="8"/>
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
-      <c r="J70" s="9"/>
-      <c r="K70" s="15"/>
+      <c r="J70" s="8"/>
+      <c r="K70" s="18"/>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="12"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ПРОЕКТ AI\ЛИЧНЫЕ НАРАБОТКИ\AI Skin Lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2845FEF-0906-4AA1-80F0-30CDEDD8980B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A7EA4F-C085-4AEC-8F07-75BE160892B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1922" uniqueCount="841">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1932" uniqueCount="847">
   <si>
     <t>Артикул</t>
   </si>
@@ -4946,6 +4946,78 @@
 Бренд: SMART DERMA
 Країна виробництва: 🇺🇦 Україна
 🌟 Arabica Coffee Eye Mask – твій must-have для сяючого та молодого погляду без темних кіл і набряків! 🌟</t>
+  </si>
+  <si>
+    <t>Інтелектуальна сироватка-елексир "БІОПЛАЗМА" з мультипептидами - 50 мл</t>
+  </si>
+  <si>
+    <t>✨ Bioplasma Peptide Elixir – концентрований інтелектуальний догляд! ✨
+🌿 Високотехнологічна формула для комплексного омолодження:
+💎 Відновлює пружність та еластичність завдяки комплексу пептидів
+💧 Забезпечує глибоке зволоження гіалуроновою кислотою
+🌸 Омега-насичена лляна олія живить та розгладжує
+🛡️ Активізує регенераційні процеси та захищає від стресу
+🌟 Дарує шкірі гладкість, сяйво та молодість
+💚 Результат – тонкі лінії та зморшки розгладжуються, шкіра виглядає здоровою та оновленою!
+📌 Ключові активні компоненти:
+🌱 Bioplasma™ FA та комплекс пептидів (Replexium, CAPS2GO™, Argireline, Agefinity™) – стимуляція синтезу колагену та регенерація
+💧 Гіалуронат натрію, Hyalurosmooth PW LS 8997, Hydagen® Aquaporin – глибоке зволоження та підтримка водного балансу
+🥥 Лляна олія, масла ши та авокадо – живлення та відновлення бар’єру
+🌸 Антарктицин, Easyliance, біотин трипептид-1 – ревіталізація та зміцнення шкіри
+⚡ Ацетил тетрапептид-2, ацетил гексапептид-1, олігопептиди та поліпептиди – омолодження та корекція зморшок
+📌 Показання до застосування:
+Щоденний догляд для уповільнення старіння
+Запобігання зморшкам
+Фото- та хроностаріння
+Тьмяний колір обличчя
+Гіперпігментація та знижений тонус
+Догляд після інвазивних процедур
+Вікова шкіра
+📌 Як застосовувати:  
+Нанеси кілька крапель еліксиру на очищену шкіру обличчя та шиї. Використовуй щодня для максимального ефекту омолодження.
+✔️ Характеристики продукту:
+Тип: Інтелектуальна антивікова сироватка-еліксир
+Об’єм: 50 мл
+Призначення: Омолодження, зволоження, відновлення, живлення
+Тип шкіри: Зріла, суха, комбінована
+Країна виробництва: 🇺🇦 Україна
+🌟 Bioplasma Peptide Elixir – твій must-have для молодої та сяючої шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>704</t>
+  </si>
+  <si>
+    <t>Інтелектуального заповнювального Гідромісту – 250 мл</t>
+  </si>
+  <si>
+    <t>✨ Intelligent HydroMist – багатофункціональне зволоження та anti-age догляд! ✨
+🌿 Інноваційна формула для щоденного відновлення:
+💧 Миттєве та пролонговане зволоження
+🌸 Нормалізація pH та вирівнювання тону шкіри
+💎 Зменшення глибини зморшок та профілактика їх появи
+🛡️ Захист від сухості та еритеми
+🌟 Ефект сяйва зсередини
+💚 Результат – свіжа, гладка та сяюча шкіра щодня!
+📌 Ключові активні компоненти:
+❄️ Antarcticine® – морський інгредієнт із криопротекторними властивостями
+💧 Гіалуронат натрію та Hydagen® Aquaporin – глибоке зволоження та підтримка водного балансу
+🌱 SPAR'AGE™ та морські мінерали – ревіталізація та захист
+🌸 Амінокислоти та пантенол – живлення, відновлення та зміцнення шкіри
+📌 Показання до застосування:
+Щоденний догляд за віковою шкірою
+Профілактика старіння
+Відновлення після косметологічних процедур
+Борьба з гіперпігментацією та зниженим тонусом
+✔️ Характеристики продукту:
+Тип: Інтелектуальний заповнювальний гідроміст
+Об’єм: 250 мл
+Призначення: Зволоження, омолодження, захист, сяйво
+Тип шкіри: Всі типи, особливо суха та зріла
+Країна виробництва: 🇺🇦 Україна
+🌟 Intelligent HydroMist – твій must-have для миттєвого зволоження та сяючої шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>703</t>
   </si>
 </sst>
 </file>
@@ -7345,38 +7417,66 @@
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A63" s="12"/>
-      <c r="B63" s="8"/>
+      <c r="A63" s="12" t="s">
+        <v>843</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>841</v>
+      </c>
       <c r="C63" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D63" s="8"/>
+      <c r="D63" s="8">
+        <v>1140</v>
+      </c>
       <c r="E63" s="8"/>
       <c r="F63" s="8"/>
-      <c r="G63" s="8"/>
-      <c r="H63" s="8"/>
+      <c r="G63" s="8">
+        <v>16</v>
+      </c>
+      <c r="H63" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="I63" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J63" s="8"/>
-      <c r="K63" s="18"/>
+      <c r="J63" s="8" t="s">
+        <v>842</v>
+      </c>
+      <c r="K63" s="18" t="s">
+        <v>843</v>
+      </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A64" s="12"/>
-      <c r="B64" s="8"/>
+      <c r="A64" s="12" t="s">
+        <v>846</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>844</v>
+      </c>
       <c r="C64" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D64" s="8"/>
+      <c r="D64" s="8">
+        <v>1000</v>
+      </c>
       <c r="E64" s="8"/>
       <c r="F64" s="8"/>
-      <c r="G64" s="8"/>
-      <c r="H64" s="8"/>
+      <c r="G64" s="8">
+        <v>19</v>
+      </c>
+      <c r="H64" s="8" t="s">
+        <v>672</v>
+      </c>
       <c r="I64" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J64" s="8"/>
-      <c r="K64" s="18"/>
+      <c r="J64" s="8" t="s">
+        <v>845</v>
+      </c>
+      <c r="K64" s="18" t="s">
+        <v>846</v>
+      </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="12"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ПРОЕКТ AI\ЛИЧНЫЕ НАРАБОТКИ\AI Skin Lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A7EA4F-C085-4AEC-8F07-75BE160892B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD68DCB2-8C38-491A-B141-9C853EA50B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1932" uniqueCount="847">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2006" uniqueCount="878">
   <si>
     <t>Артикул</t>
   </si>
@@ -5018,6 +5018,339 @@
   </si>
   <si>
     <t>703</t>
+  </si>
+  <si>
+    <t>Гель для вмивання "Активатор Енергії" з кислотами - 250 мл</t>
+  </si>
+  <si>
+    <t>✨ Energy Activator Cleansing Gel – перезарядка для твоєї шкіри! ✨
+🌿 Інноваційна формула з кислотами та ензимами:
+⚡ Перезаряджає клітини шкіри на 27%
+💧 Відновлює pH-баланс та підтримує оптимальний рівень зволоження
+🌸 Комплекс із трьох кислот у розчині електролітів – м’яке, але ефективне очищення
+🛡️ Компонент OXY 229 PF активує мітохондріальне дихання для енергії клітин
+💎 Дарує свіжість, сяйво та рівний тон
+💚 Результат – чиста, енергійна та сяюча шкіра після кожного вмивання!
+📌 Ключові активні компоненти:
+🌱 Гліколева, піруватна та ферулова кислоти – ексфоліація та вирівнювання тону
+⚡ OXY 229 PF – активація клітинної енергії
+💧 Гіалуронат натрію, сечовина, Д-пантенол – глибоке зволоження та відновлення
+🌸 Екстракт гібіскуса, морські мінерали – антиоксидантний захист та тонізація
+🌟 Hydagen® Aquaporin, Lys'lastine™ V, Perlaura® – підтримка водного балансу та пружності
+📌 Показання до застосування:
+Уповільнення старіння без радикальних методів
+Запобігання появі зморшок
+Фото- та хроностаріння
+Тьмяний колір обличчя
+Гіперпігментація
+Знижений тонус шкіри
+Догляд після інвазивних процедур
+📌 Як застосовувати:  
+Нанеси невелику кількість гелю на вологу шкіру, розподіли по масажних лініях, легко промасажуй та змий теплою водою. Використовуй щодня для максимального ефекту.
+✔️ Характеристики продукту:
+Тип: Інноваційний гель для вмивання
+Об’єм: 250 мл
+Призначення: Очищення, омолодження, відновлення енергії клітин
+Тип шкіри: Вікова, комбінована, проблемна
+Країна виробництва: 🇺🇦 Україна
+🌟 Energy Activator Cleansing Gel – твій must-have для щоденного енергетичного догляду! 🌟</t>
+  </si>
+  <si>
+    <t>700</t>
+  </si>
+  <si>
+    <t>SMART4DERMA Aquagen - Двоетапна система інтенсивного зволоження 2х75</t>
+  </si>
+  <si>
+    <t>2х75 мл</t>
+  </si>
+  <si>
+    <t>✨ SMART4DERMA Aquagen – інноваційна система догляду з урахуванням циркадних ритмів! ✨
+🌿 Двоетапна формула для глибокого зволоження, живлення та ревіталізації:
+💧 Відновлює баланс вологи та мікробіом шкіри
+🌸 Стимулює синтез колагену та забезпечує ліфтинг
+💎 Освітлює пігментацію та повертає природне сяйво
+🛡️ Захищає від зовнішніх факторів та фотостаріння
+💚 Результат – пружна, сяюча та здорова шкіра з ефектом перетворення!
+📌 Система включає дві маски:
+1️⃣ 4D Aqua Mask Vita C &amp; Probiotic (75 мл)
+Збагачена вітамінами та пребіотиками
+Містить чотири види гіалуронової кислоти
+Відновлює мікробіом, покращує тон та тургор
+Захищає від зовнішніх факторів
+2️⃣ Bakuchiol Mask Ceramides &amp; AA2G (75 мл)
+Глибоко зволожує та оздоровлює шкіру
+Розгладжує зморшки та освітлює пігментацію
+Повертає природне сяйво та еластичність
+📌 Активні інгредієнти:
+🌱 Крок 1: Сік алое, Hydagen® Aquaporin, 4D гіалуронова кислота, пребіотики, Д-пантенол, вітаміни В3 і С, кофеїн, біотин, Amitose 3GA
+🌸 Крок 2: Олії ши та оливки, бакухіол, сквалан, BIO CERAMIDYL PURE, гідролізовані протеїни пшениці, вівса, шовку та рису
+✔️ Характеристики продукту:
+Тип: Двоетапна система інтенсивного зволоження
+Об’єм: 2×75 мл
+Призначення: Зволоження, живлення, ліфтинг, освітлення
+Тип шкіри: Всі типи, особливо суха та зріла
+Бренд: SMART4DERMA
+Країна виробництва: 🇺🇦 Україна
+🌟 SMART4DERMA Aquagen – твій must-have для глибокого зволоження та сяючої шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>520</t>
+  </si>
+  <si>
+    <t>Розкішний живильний крем з церамідами 50 мл</t>
+  </si>
+  <si>
+    <t>✨ Luxury Ceramide Nourishing Cream – глибоке живлення та сяйво! ✨
+🌿 Інноваційна формула для щоденного догляду:
+💧 Технологія подвійного зволоження – миттєвий та тривалий ефект
+🌸 Церамиди зміцнюють захисний бар’єр шкіри
+🥥 Комплекс Multifeel забезпечує інтенсивне живлення
+🌟 Пантенол заспокоює та відновлює
+💎 Зменшує глибину зморшок, підвищує пружність та еластичність
+💚 Результат – гладка, сяюча та здорова шкіра щодня!
+📌 Показання до застосування:
+Суха та зневоднена шкіра
+Зріла та чутлива шкіра
+Всі типи шкіри для щоденного догляду
+Відновлення після косметичних процедур
+✔️ Характеристики продукту:
+Тип: Живильний крем з церамідами
+Об’єм: 50 мл / 100 мл (залежно від упаковки)
+Призначення: Зволоження, живлення, відновлення, омолодження
+Тип шкіри: Всі типи, особливо суха та зріла
+Країна виробництва: 🇺🇦 Україна
+🌟 Luxury Ceramide Nourishing Cream – твій must-have для глибокого живлення та сяючої шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>Невагомий Крем-гель SPF 50 - 50 мл</t>
+  </si>
+  <si>
+    <t>✨ Weightless SPF 50 Gel-Cream – щоденний захист та зволоження! ✨
+🌿 Інноваційна формула для комфортного щоденного догляду:
+☀️ Потужний УФ-захист: комплекс PolyFructol Plus та X50 Skin Barrier запобігає фотостарінню та передчасним зморшкам
+💧 Глибоке зволоження: технологія PatcH2O та Hydagen® Aquaporine працюють на клітинному рівні
+🛡️ Антиоксидантний захист: DN-Age нейтралізує вільні радикали та стрес
+🌸 Легка текстура: миттєво вбирається без липкості, даруючи комфорт
+💚 Результат – пружна, гладка та захищена шкіра з ефектом свіжості після кожного нанесення!
+📌 Показання до застосування:
+Щоденний догляд для всіх типів шкіри
+Захист від фото- та хроностаріння
+Профілактика зморшок та пігментації
+Зволоження та підтримка клітинного балансу
+📌 Як застосовувати:  
+Наносити на чисту, суху шкіру обличчя за 20 хвилин до виходу на сонце. Використовувати щодня для максимального захисту.
+✔️ Характеристики продукту:
+Тип: Крем-гель з SPF
+Об’єм: 50 мл / 230 мл
+Рівень захисту: SPF 50+ PA++++
+Призначення: Захист, зволоження, антиоксидантний догляд
+Тип шкіри: Всі типи
+Країна виробництва: 🇺🇦 Україна
+🌟 Weightless SPF 50 Gel-Cream – твій must-have для щоденного захисту та сяючої шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>524</t>
+  </si>
+  <si>
+    <t>Постпроцедурний захисний регенерувальний спрей SPF50, 150 мл</t>
+  </si>
+  <si>
+    <t>518</t>
+  </si>
+  <si>
+    <t>✨ Post-Procedure Protective Spray SPF 50 – професійний догляд та відновлення! ✨
+🌿 Інноваційна формула для чутливої та пошкодженої шкіри:
+☀️ Максимальний захист SPF 50 від UVA/UVB-випромінювання
+💧 Відновлює оптимальний рівень зволоження без відчуття важкості
+🌸 Заспокоює подразнення та зменшує сухість
+🛡️ Сприяє регенерації та відновленню бар’єрної функції
+⚡ Зручний формат спрею для рівномірного нанесення
+💚 Результат – захищена, зволожена та відновлена шкіра після процедур!
+📌 Показання до застосування:
+Догляд після пілінгів, лазерних процедур, шліфування
+Суха та чутлива шкіра
+Роздратування та зневоднення
+Зниження тонусу та перші ознаки старіння
+Відновлення бар’єрної функції
+✔️ Характеристики продукту:
+Тип: Захисний регенерувальний спрей
+Об’єм: 150 мл
+Фактор захисту: SPF 50
+Спектр: UVA/UVB
+Водостійкий, гіпоалергенний
+Без вікових обмежень
+Країна виробництва: 🇺🇦 Україна
+🌟 Post-Procedure Protective Spray SPF 50 – твій must-have для безпечного та комфортного відновлення шкіри після процедур! 🌟</t>
+  </si>
+  <si>
+    <t>Сонцезахисний ультразволожувальний крем SPF50 з олією канабісу 50 мл</t>
+  </si>
+  <si>
+    <t>✨ Cannabis Ultra-Hydrating Sunscreen SPF 50 – повний спектр захисту та сяйво! ✨
+🌿 Інноваційна формула для щоденного догляду:
+☀️ SPF50 + широкоспектральний UVA/UVB-захист – профілактика фотостаріння та збереження колагену
+💧 Гіалуронова кислота + PolyFructol Plus – глибоке зволоження та підтримка водного балансу
+🌸 Екстракт азіатської центелли – заспокоює та відновлює бар’єрні функції
+🛡️ Токоферол ацетат та аскорбіл глюкозид – антиоксидантний захист від стресу та вільних радикалів
+🌟 Легка текстура з матуючим ефектом – без відчуття тяжкості
+💚 Результат – пружна, сяюча та захищена шкіра щодня!
+📌 Показання до застосування:
+Суха та чутлива шкіра
+Подразнення та зневоднення
+Перші ознаки старіння
+Зниження бар’єрної функції
+📌 Як застосовувати:  
+Наносити на очищену шкіру обличчя вранці, за 20 хвилин до виходу на сонце. Використовувати щодня для максимального ефекту.
+✔️ Характеристики продукту:
+Тип: Сонцезахисний крем з SPF
+Об’єм: 50 мл
+Рівень захисту: SPF 50+ PA++++
+Призначення: Захист, зволоження, антиоксидантний догляд
+Тип шкіри: Суха, чутлива, зріла
+Країна виробництва: 🇺🇦 Україна
+🌟 Cannabis Ultra-Hydrating Sunscreen SPF 50 – твій must-have для щоденного захисту та сяйва шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>517</t>
+  </si>
+  <si>
+    <t>Ультразволожуючий бустер х50 "Поліфруктол", 30 мл</t>
+  </si>
+  <si>
+    <t>510</t>
+  </si>
+  <si>
+    <t>✨ Polyfructol x50 Ultra-Hydrating Booster – інноваційна енергія зволоження! ✨
+🌿 Передова дрон-молекулярна система доставки:
+💧 Миттєва, глибока та пролонгована гідратація
+🌸 Стимулює природне продукування гіалуронової кислоти
+🛡️ Відновлює водний баланс та бар’єрні функції шкіри
+⚡ Зменшує запальні процеси та подразнення
+🌟 Покращує текстуру та еластичність
+💚 Результат – шкіра стає свіжою, пружною та сяючою вже після першого застосування!
+📌 Ключові активні компоненти:
+🌱 Skin Barrier та Polyfructol Plus – захист та пролонговане зволоження
+🌿 Олія коноплі та екстракт зеленого чаю – антиоксидантний щит та живлення
+💧 Бета-глюкан, трегалоза, альгін – глибоке зволоження та відновлення
+🌸 Purisoft™ LS 9836 – детокс та захист від зовнішніх факторів
+📌 Показання до застосування:
+Суха та чутлива шкіра
+Подразнення та зневоднення
+Зниження тонусу та перші ознаки старіння
+Відновлення бар’єрної функції
+✔️ Характеристики продукту:
+Тип: Антиоксидантний ультразволожуючий бустер
+Об’єм: 30 мл
+Призначення: Зволоження, живлення, антиоксидантний захист
+Тип шкіри: Суха, чутлива, зріла
+Країна виробництва: 🇺🇦 Україна
+🌟 Polyfructol x50 Booster – твій must-have для екстра зволоження та сяйва шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>Удосконалювало ний зволожувальний СС КРЕМ SPF30 - 50 мл</t>
+  </si>
+  <si>
+    <t>✨ Advanced Moisturizing CC Cream SPF 30 – ідеальний тон та захист! ✨
+🌿 Мультифункціональна формула для щоденного догляду:
+💎 Пігменти в мікрокапсулах адаптуються до відтінку шкіри
+🌸 Вирівнює тон та дарує миттєвий ефект свіжості
+☀️ Захист від ультрафіолету завдяки SPF 30
+💧 Легка текстура – не забиває пори та забезпечує комфорт
+💚 Результат – рівний тон, сяйво та захищена шкіра щодня!
+📌 Ключові активні компоненти:
+🥥 Масло насіння жожоба та ши – живлення та м’якість
+🌿 Екстракт камелії – стимуляція регенерації
+💧 Гіалуронат натрію – інтенсивне зволоження
+🛡️ Оксид цинку – захист від UVA/UVB-променів
+🌸 Пчелиний віск – заспокоює та утримує вологу
+⚡ Ацетил гексапептид-8 – зменшення зморшок
+🌟 Вітамін Е та лецитин – антиоксидантний захист та баланс
+📌 Як застосовувати:  
+Нанеси крем на чисту шкіру обличчя, шиї та декольте масажними рухами. Використовуй щодня для рівного тону та захисту від сонця.
+✔️ Характеристики продукту:
+Тип: Зволожувальний СС крем з SPF
+Об’єм: 50 мл
+Рівень захисту: SPF 30
+Призначення: Тонування, зволоження, захист, омолодження
+Тип шкіри: Всі типи, особливо суха та чутлива
+Країна виробництва: 🇺🇦 Україна
+🌟 Advanced CC Cream SPF 30 – твій must-have для ідеального тону та щоденного захисту! 🌟</t>
+  </si>
+  <si>
+    <t>519</t>
+  </si>
+  <si>
+    <t>Екстразволожувальний крем із церамідами SPF30 суха та нормальна шкіра</t>
+  </si>
+  <si>
+    <t>✨ Ceramide Extra-Hydrating Cream SPF 30 – подвійний захист та зволоження! ✨
+🌿 Інноваційна формула для щоденного догляду:
+💧 Комплекс церамідів I–IV, VI – відновлює бар’єрну функцію та зміцнює шкіру
+🌸 Гіалуронова кислота + гліцерил глюкозид – пролонговане зволоження на клітинному рівні
+🛡️ Антиоксидантний щит – ферулова кислота, токоферол ацетат та екстракт зеленого чаю нейтралізують вільні радикали
+☀️ SPF 30 широкого спектру – невидимий сонцезахисний щит проти UVA/UVB
+🌟 PatcH20 та Hydagen® Aquaporin – підтримка водного балансу та пружності
+💚 Результат – гладка, сяюча та захищена шкіра без сухості та подразнень!
+📌 Показання до застосування:
+Суха та чутлива шкіра
+Подразнення та зневоднення
+Зниження тонусу та перші ознаки старіння
+Відновлення та захист бар’єрної функції
+📌 Активні компоненти:
+🌱 Оливкова олія, екстракт ромашки, центелла азіатська
+💧 Hydagen® Aquaporin, PatcH20, Д-пантенол
+🛡️ iActive Ceramide, X50 Skin Barrier, Phytosoothe LS 9766
+🌸 Токоферол ацетат, натрій аскорбіл фосфат, ферулова кислота, бісаболол
+✔️ Характеристики продукту:
+Тип: Екстразволожувальний крем із SPF
+Об’єм: 50 мл
+Рівень захисту: SPF 30
+Призначення: Зволоження, живлення, антиоксидантний захист, сонцезахист
+Тип шкіри: Суха, нормальна, чутлива
+Країна виробництва: 🇺🇦 Україна
+🌟 Ceramide Extra-Hydrating Cream SPF 30 – твій must-have для щоденного зволоження та захисту шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>506</t>
+  </si>
+  <si>
+    <t>Крем-маска глибоке зволоження 50 мл</t>
+  </si>
+  <si>
+    <t>✨ Deep Moisture Cream-Mask – миттєве та пролонговане зволоження! ✨
+🌿 Легка пептидна формула з системою доставки X50:
+💧 Створює депо вологи в шкірі для подвійного ефекту гідратації
+🌸 Відновлює бар’єрні функції завдяки комплексу церамідів
+🛡️ Заспокоює подразнення та зменшує сухість
+⚡ Підвищує тонус та еластичність шкіри
+🌟 Дарує свіжість і сяйво вже після першого застосування
+💚 Результат – шкіра стає пружною, гладкою та сяючою!
+📌 Показання до застосування:
+Суха та чутлива шкіра
+Подразнення та зневоднення
+Зниження тонусу
+Перші ознаки старіння
+Відновлення та захист шкіри
+📌 Ключові активні компоненти:
+💧 Hydagen® Aquaporin, гіалуронат натрію, PolyFructol Plus – інтенсивне зволоження
+🌱 Олія авокадо, примули, екстракт центелли – живлення та відновлення
+🌸 Д-пантенол, ніацинамід, бета-глюкан – заспокійливий та регенеруючий ефект
+🛡️ iActive Ceramide, X50 Skin Barrier, токоферол, ферулова кислота, убіхінон – антиоксидантний захист та зміцнення бар’єру
+⚡ Амінокислоти та магнезіум аскорбіл фосфат – стимуляція клітинного оновлення
+✔️ Характеристики продукту:
+Тип: Крем-маска для глибокого зволоження
+Об’єм: 300 мл
+Призначення: Зволоження, живлення, відновлення, антиоксидантний захист
+Тип шкіри: Суха, чутлива, зріла
+Країна виробництва: 🇺🇦 Україна
+🌟 Deep Moisture Cream-Mask – твій must-have для миттєвого та тривалого зволоження! 🌟</t>
+  </si>
+  <si>
+    <t>514</t>
   </si>
 </sst>
 </file>
@@ -7479,260 +7812,448 @@
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A65" s="12"/>
-      <c r="B65" s="8"/>
+      <c r="A65" s="12" t="s">
+        <v>849</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>847</v>
+      </c>
       <c r="C65" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D65" s="8"/>
+      <c r="D65" s="8">
+        <v>780</v>
+      </c>
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
-      <c r="G65" s="8"/>
-      <c r="H65" s="8"/>
+      <c r="G65" s="8">
+        <v>16</v>
+      </c>
+      <c r="H65" s="8" t="s">
+        <v>672</v>
+      </c>
       <c r="I65" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J65" s="8"/>
-      <c r="K65" s="18"/>
+      <c r="J65" s="8" t="s">
+        <v>848</v>
+      </c>
+      <c r="K65" s="18" t="s">
+        <v>849</v>
+      </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A66" s="12"/>
-      <c r="B66" s="8"/>
+      <c r="A66" s="12" t="s">
+        <v>853</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>850</v>
+      </c>
       <c r="C66" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D66" s="8"/>
+      <c r="D66" s="8">
+        <v>1320</v>
+      </c>
       <c r="E66" s="8"/>
       <c r="F66" s="8"/>
-      <c r="G66" s="8"/>
-      <c r="H66" s="8"/>
+      <c r="G66" s="8">
+        <v>19</v>
+      </c>
+      <c r="H66" s="8" t="s">
+        <v>851</v>
+      </c>
       <c r="I66" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J66" s="8"/>
-      <c r="K66" s="18"/>
+      <c r="J66" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="K66" s="18" t="s">
+        <v>853</v>
+      </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A67" s="12"/>
-      <c r="B67" s="8"/>
+      <c r="A67" s="12" t="s">
+        <v>856</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>854</v>
+      </c>
       <c r="C67" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D67" s="8"/>
+      <c r="D67" s="8">
+        <v>680</v>
+      </c>
       <c r="E67" s="8"/>
       <c r="F67" s="8"/>
-      <c r="G67" s="8"/>
-      <c r="H67" s="8"/>
+      <c r="G67" s="8">
+        <v>25</v>
+      </c>
+      <c r="H67" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="I67" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J67" s="8"/>
-      <c r="K67" s="18"/>
+      <c r="J67" s="8" t="s">
+        <v>855</v>
+      </c>
+      <c r="K67" s="18" t="s">
+        <v>856</v>
+      </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A68" s="12"/>
-      <c r="B68" s="8"/>
+      <c r="A68" s="12" t="s">
+        <v>859</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>857</v>
+      </c>
       <c r="C68" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D68" s="8"/>
+      <c r="D68" s="8">
+        <v>980</v>
+      </c>
       <c r="E68" s="8"/>
       <c r="F68" s="8"/>
-      <c r="G68" s="8"/>
-      <c r="H68" s="8"/>
+      <c r="G68" s="8">
+        <v>17</v>
+      </c>
+      <c r="H68" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="I68" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J68" s="8"/>
-      <c r="K68" s="18"/>
+      <c r="J68" s="8" t="s">
+        <v>858</v>
+      </c>
+      <c r="K68" s="18" t="s">
+        <v>859</v>
+      </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A69" s="12"/>
-      <c r="B69" s="8"/>
+      <c r="A69" s="12" t="s">
+        <v>861</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>860</v>
+      </c>
       <c r="C69" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D69" s="8"/>
+      <c r="D69" s="8">
+        <v>1260</v>
+      </c>
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
-      <c r="G69" s="8"/>
-      <c r="H69" s="8"/>
+      <c r="G69" s="8">
+        <v>21</v>
+      </c>
+      <c r="H69" s="8" t="s">
+        <v>695</v>
+      </c>
       <c r="I69" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J69" s="8"/>
-      <c r="K69" s="18"/>
+      <c r="J69" s="8" t="s">
+        <v>862</v>
+      </c>
+      <c r="K69" s="18" t="s">
+        <v>861</v>
+      </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A70" s="12"/>
-      <c r="B70" s="8"/>
+      <c r="A70" s="12" t="s">
+        <v>865</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>863</v>
+      </c>
       <c r="C70" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D70" s="8"/>
+      <c r="D70" s="8">
+        <v>1020</v>
+      </c>
       <c r="E70" s="8"/>
       <c r="F70" s="8"/>
-      <c r="G70" s="8"/>
-      <c r="H70" s="8"/>
-      <c r="I70" s="8"/>
-      <c r="J70" s="8"/>
-      <c r="K70" s="18"/>
+      <c r="G70" s="8">
+        <v>26</v>
+      </c>
+      <c r="H70" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J70" s="8" t="s">
+        <v>864</v>
+      </c>
+      <c r="K70" s="18" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A71" s="12"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="8"/>
+      <c r="A71" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>866</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="D71" s="8">
+        <v>980</v>
+      </c>
       <c r="E71" s="8"/>
       <c r="F71" s="8"/>
-      <c r="G71" s="8"/>
-      <c r="H71" s="8"/>
-      <c r="I71" s="8"/>
-      <c r="J71" s="9"/>
-      <c r="K71" s="15"/>
+      <c r="G71" s="8">
+        <v>16</v>
+      </c>
+      <c r="H71" s="8" t="s">
+        <v>664</v>
+      </c>
+      <c r="I71" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J71" s="8" t="s">
+        <v>868</v>
+      </c>
+      <c r="K71" s="18" t="s">
+        <v>867</v>
+      </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A72" s="12"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="8"/>
+      <c r="A72" s="12" t="s">
+        <v>871</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="D72" s="8">
+        <v>1220</v>
+      </c>
       <c r="E72" s="8"/>
       <c r="F72" s="8"/>
-      <c r="G72" s="8"/>
-      <c r="H72" s="8"/>
-      <c r="I72" s="8"/>
-      <c r="J72" s="9"/>
-      <c r="K72" s="15"/>
+      <c r="G72" s="8">
+        <v>17</v>
+      </c>
+      <c r="H72" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I72" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J72" s="8" t="s">
+        <v>870</v>
+      </c>
+      <c r="K72" s="18" t="s">
+        <v>871</v>
+      </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A73" s="12"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="8"/>
+      <c r="A73" s="12" t="s">
+        <v>874</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>872</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="D73" s="8">
+        <v>1140</v>
+      </c>
       <c r="E73" s="8"/>
       <c r="F73" s="8"/>
-      <c r="G73" s="8"/>
-      <c r="H73" s="8"/>
-      <c r="I73" s="8"/>
-      <c r="J73" s="9"/>
-      <c r="K73" s="15"/>
+      <c r="G73" s="8">
+        <v>21</v>
+      </c>
+      <c r="H73" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I73" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J73" s="8" t="s">
+        <v>873</v>
+      </c>
+      <c r="K73" s="18" t="s">
+        <v>874</v>
+      </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A74" s="12"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="8"/>
+      <c r="A74" s="12" t="s">
+        <v>877</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>875</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="D74" s="8">
+        <v>780</v>
+      </c>
       <c r="E74" s="8"/>
       <c r="F74" s="8"/>
-      <c r="G74" s="8"/>
-      <c r="H74" s="8"/>
-      <c r="I74" s="8"/>
-      <c r="J74" s="9"/>
-      <c r="K74" s="15"/>
+      <c r="G74" s="8">
+        <v>24</v>
+      </c>
+      <c r="H74" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I74" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J74" s="8" t="s">
+        <v>876</v>
+      </c>
+      <c r="K74" s="18" t="s">
+        <v>877</v>
+      </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="12"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
+      <c r="B75" s="8"/>
+      <c r="C75" s="8" t="s">
+        <v>653</v>
+      </c>
       <c r="D75" s="8"/>
       <c r="E75" s="8"/>
       <c r="F75" s="8"/>
       <c r="G75" s="8"/>
       <c r="H75" s="8"/>
-      <c r="I75" s="8"/>
-      <c r="J75" s="9"/>
-      <c r="K75" s="15"/>
+      <c r="I75" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J75" s="8"/>
+      <c r="K75" s="18"/>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="12"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
+      <c r="B76" s="8"/>
+      <c r="C76" s="8" t="s">
+        <v>653</v>
+      </c>
       <c r="D76" s="8"/>
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
       <c r="G76" s="8"/>
       <c r="H76" s="8"/>
-      <c r="I76" s="8"/>
-      <c r="J76" s="9"/>
-      <c r="K76" s="15"/>
+      <c r="I76" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J76" s="8"/>
+      <c r="K76" s="18"/>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="12"/>
-      <c r="B77" s="9"/>
-      <c r="C77" s="9"/>
+      <c r="B77" s="8"/>
+      <c r="C77" s="8" t="s">
+        <v>653</v>
+      </c>
       <c r="D77" s="8"/>
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
       <c r="G77" s="8"/>
       <c r="H77" s="8"/>
-      <c r="I77" s="8"/>
-      <c r="J77" s="9"/>
-      <c r="K77" s="15"/>
+      <c r="I77" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J77" s="8"/>
+      <c r="K77" s="18"/>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="12"/>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
+      <c r="B78" s="8"/>
+      <c r="C78" s="8" t="s">
+        <v>653</v>
+      </c>
       <c r="D78" s="8"/>
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
       <c r="G78" s="8"/>
       <c r="H78" s="8"/>
-      <c r="I78" s="8"/>
-      <c r="J78" s="9"/>
-      <c r="K78" s="15"/>
+      <c r="I78" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J78" s="8"/>
+      <c r="K78" s="18"/>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="12"/>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8" t="s">
+        <v>653</v>
+      </c>
       <c r="D79" s="8"/>
       <c r="E79" s="8"/>
       <c r="F79" s="8"/>
       <c r="G79" s="8"/>
       <c r="H79" s="8"/>
-      <c r="I79" s="8"/>
-      <c r="J79" s="9"/>
-      <c r="K79" s="15"/>
+      <c r="I79" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J79" s="8"/>
+      <c r="K79" s="18"/>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="12"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
+      <c r="B80" s="8"/>
+      <c r="C80" s="8" t="s">
+        <v>653</v>
+      </c>
       <c r="D80" s="8"/>
       <c r="E80" s="8"/>
       <c r="F80" s="8"/>
       <c r="G80" s="8"/>
       <c r="H80" s="8"/>
-      <c r="I80" s="8"/>
-      <c r="J80" s="9"/>
-      <c r="K80" s="15"/>
+      <c r="I80" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J80" s="8"/>
+      <c r="K80" s="18"/>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="12"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="9"/>
+      <c r="B81" s="8"/>
+      <c r="C81" s="8" t="s">
+        <v>653</v>
+      </c>
       <c r="D81" s="8"/>
       <c r="E81" s="8"/>
       <c r="F81" s="8"/>
       <c r="G81" s="8"/>
       <c r="H81" s="8"/>
-      <c r="I81" s="8"/>
-      <c r="J81" s="9"/>
-      <c r="K81" s="15"/>
+      <c r="I81" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J81" s="8"/>
+      <c r="K81" s="18"/>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="12"/>
-      <c r="B82" s="9"/>
-      <c r="C82" s="9"/>
+      <c r="B82" s="8"/>
+      <c r="C82" s="8"/>
       <c r="D82" s="8"/>
       <c r="E82" s="8"/>
       <c r="F82" s="8"/>
       <c r="G82" s="8"/>
       <c r="H82" s="8"/>
-      <c r="I82" s="8"/>
-      <c r="J82" s="9"/>
-      <c r="K82" s="15"/>
+      <c r="I82" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J82" s="8"/>
+      <c r="K82" s="18"/>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="12"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ПРОЕКТ AI\ЛИЧНЫЕ НАРАБОТКИ\AI Skin Lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD68DCB2-8C38-491A-B141-9C853EA50B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81592AE-E6FD-4959-B8DD-B468DE8D66AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2006" uniqueCount="878">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2016" uniqueCount="884">
   <si>
     <t>Артикул</t>
   </si>
@@ -5351,6 +5351,76 @@
   </si>
   <si>
     <t>514</t>
+  </si>
+  <si>
+    <t>Зволожувальний дренажний крем від темних кіл та набряків 30 мл</t>
+  </si>
+  <si>
+    <t>✨ Drainage Moisturizing Eye Cream – свіжий та сяючий погляд! ✨
+🌿 Активна формула для зони навколо очей:
+💧 Інтенсивне зволоження та відновлення бар’єрної функції
+🌸 Освітлення темних кіл завдяки екстракту водоростей
+🛡️ Зменшення набряків завдяки рутину та ескуліну
+⚡ Комплекс інкапсульованих пептидів – стимуляція синтезу білків для пружності
+🌟 Живлення та захист завдяки олії авокадо та примули
+💚 Результат – зменшені набряки, світліший тон та пружна шкіра навколо очей!
+📌 Активні компоненти:
+🌱 Екстракт водоростей – покращує кровообіг та освітлює темні кола
+🌸 Рутин + ескулін – протинабрякова дія
+💧 Інулін – підвищує пружність та еластичність
+⚡ Інкапсульовані пептиди – стимулюють синтез кератину, філагрину та лорекину
+🥥 Олія авокадо та примули вечірньої – живлення та захист
+🌟 Токоферол + магнезіум аскорбіл фосфат – антиоксидантний щит
+📌 Показання до застосування:
+Суха та чутлива шкіра навколо очей
+Подразнення та зневоднення
+Зниження тонусу
+Перші ознаки старіння
+Відновлення бар’єрної функції
+✔️ Характеристики продукту:
+Тип: Зволожувальний дренажний крем для очей
+Об’єм: 30 мл
+Призначення: Зволоження, протинабрякова дія, освітлення темних кіл
+Тип шкіри: Суха, чутлива, зріла
+Країна виробництва: 🇺🇦 Україна
+🌟 Drainage Moisturizing Eye Cream – твій must-have для сяючого та відпочилого погляду! 🌟</t>
+  </si>
+  <si>
+    <t>508</t>
+  </si>
+  <si>
+    <t>Дренажна освітлююча маска Глабрідин для очей 50 мл</t>
+  </si>
+  <si>
+    <t>✨ Smart4Derma Glabridin Eye Mask – професійний догляд для сяючого погляду! ✨
+🌿 Інноваційна формула для переорбітальної зони:
+💧 Зволожує та підвищує еластичність шкіри
+🌸 Освітлює темні кола та зменшує набряки нижніх повік
+🛡️ Зміцнює судини та покращує мікроциркуляцію
+⚡ Активізує виведення заліза та білірубіну, зменшуючи тьмяність
+🌟 Відновлює бар’єрну функцію та захищає від стресових факторів
+💚 Результат – свіжий, відпочилий та сяючий погляд!
+📌 Активні компоненти:
+🌱 Shadownyl, Рутин, Ескулін – зміцнення судин та протинабрякова дія
+🌸 Inoveol EGCG, екстракт зеленого чаю та каштана – антиоксидантний захист та покращення кровообігу
+💧 PolyFructol Plus, Hydagen® Aquaporin, інулін – глибоке зволоження та підтримка водного балансу
+🛡️ X50® Skin Barrier та комплекс пептидів – стимуляція синтезу кератину та філагрину, відновлення бар’єру
+📌 Показання до застосування:
+Суха та чутлива шкіра навколо очей
+Подразнення та зневоднення
+Зниження тонусу
+Перші ознаки старіння
+Відновлення та захист
+✔️ Характеристики продукту:
+Тип: Дренажна освітлююча маска для очей
+Об’єм: 50 мл
+Призначення: Зволоження, освітлення, протинабрякова дія, відновлення
+Бренд: Smart4Derma (Україна + Німеччина)
+Країна виробництва: 🇺🇦 Україна / 🇩🇪 Німеччина
+🌟 Smart4Derma Glabridin Eye Mask – твій must-have для сяючого та відпочилого погляду! 🌟</t>
+  </si>
+  <si>
+    <t>512</t>
   </si>
 </sst>
 </file>
@@ -8122,38 +8192,66 @@
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A75" s="12"/>
-      <c r="B75" s="8"/>
+      <c r="A75" s="12" t="s">
+        <v>880</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>878</v>
+      </c>
       <c r="C75" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D75" s="8"/>
+      <c r="D75" s="8">
+        <v>660</v>
+      </c>
       <c r="E75" s="8"/>
       <c r="F75" s="8"/>
-      <c r="G75" s="8"/>
-      <c r="H75" s="8"/>
+      <c r="G75" s="8">
+        <v>13</v>
+      </c>
+      <c r="H75" s="8" t="s">
+        <v>664</v>
+      </c>
       <c r="I75" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J75" s="8"/>
-      <c r="K75" s="18"/>
+      <c r="J75" s="8" t="s">
+        <v>879</v>
+      </c>
+      <c r="K75" s="18" t="s">
+        <v>880</v>
+      </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A76" s="12"/>
-      <c r="B76" s="8"/>
+      <c r="A76" s="12" t="s">
+        <v>883</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>881</v>
+      </c>
       <c r="C76" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D76" s="8"/>
+      <c r="D76" s="8">
+        <v>1000</v>
+      </c>
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
-      <c r="G76" s="8"/>
-      <c r="H76" s="8"/>
+      <c r="G76" s="8">
+        <v>14</v>
+      </c>
+      <c r="H76" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="I76" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J76" s="8"/>
-      <c r="K76" s="18"/>
+      <c r="J76" s="8" t="s">
+        <v>882</v>
+      </c>
+      <c r="K76" s="18" t="s">
+        <v>883</v>
+      </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="12"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ПРОЕКТ AI\ЛИЧНЫЕ НАРАБОТКИ\AI Skin Lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81592AE-E6FD-4959-B8DD-B468DE8D66AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98587DFA-14EC-468C-B9CD-64BE232C5C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2016" uniqueCount="884">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2041" uniqueCount="899">
   <si>
     <t>Артикул</t>
   </si>
@@ -5421,6 +5421,169 @@
   </si>
   <si>
     <t>512</t>
+  </si>
+  <si>
+    <t>Екстразволожувальна Антиоксидантна сиворотка з центеллою 50 мл</t>
+  </si>
+  <si>
+    <t>✨ Smart4Derma Glabridin Eye Mask – професійний догляд для сяючого погляду! ✨
+🌿 Комплексне рішення для делікатної переорбітальної зони:
+💧 Інтенсивне зволоження та підвищення еластичності
+🌸 Освітлення темних кіл та зменшення набряків нижніх повік
+🛡️ Зміцнення судин та покращення мікроциркуляції
+⚡ Активізація процесів виведення заліза та білірубіну для рівного тону
+🌟 Відновлення бар’єрної функції та захист від стресових факторів
+💚 Результат – свіжий, відпочилий та сяючий погляд без ознак втоми!
+📌 Активні компоненти:
+🌱 Shadownyl, Рутин, Ескулін – протинабрякова дія та зміцнення судин
+🌸 Inoveol EGCG, екстракти зеленого чаю та каштана – антиоксидантний захист і покращення кровообігу
+💧 PolyFructol Plus, Hydagen® Aquaporin, інулін – глибоке та пролонговане зволоження
+🛡️ X50® Skin Barrier та комплекс пептидів – стимуляція синтезу кератину та філагрину, відновлення бар’єру
+📌 Показання до застосування:
+Суха та чутлива шкіра навколо очей
+Подразнення та зневоднення
+Зниження тонусу
+Перші ознаки старіння
+Відновлення та захист
+✔️ Характеристики продукту:
+Тип: Дренажна освітлююча маска для очей
+Об’єм: 50 мл
+Призначення: Зволоження, освітлення, протинабрякова дія, відновлення
+Бренд: Smart4Derma (🇺🇦 Україна + 🇩🇪 Німеччина)
+🌟 Smart4Derma Glabridin Eye Mask – твій must-have для сяючого та відпочилого погляду! 🌟</t>
+  </si>
+  <si>
+    <t>509</t>
+  </si>
+  <si>
+    <t>Зволожуючий гель-тонер для сіяння шкіри 250 мл</t>
+  </si>
+  <si>
+    <t>✨ Polyfructol Toner Bright Skin – професійне сяйво та зволоження! ✨
+🌿 Інноваційна формула для атонічної та зневодненої шкіри:
+💧 Hydagen® Aquaporin + PatcH2O – інтенсивне зволоження та утримання вологи
+🌸 Екстракти ромашки та шавлії – заспокоюють, знімають почервоніння та дискомфорт
+🌟 Ніацинамід – вирівнює тон та додає природне сяйво
+🛡️ Puricare POE LS 9727 + PolyFructol Plus – захист від негативного впливу навколишнього середовища
+⚡ Д-пантенол та натрій гіалуронат – пружність та відчуття свіжості
+💚 Результат – тривале зволоження до 24 годин, свіжий вигляд та сяюча шкіра!
+📌 Результати використання:
+Тривале зволоження на 24 години
+Свіжий та сяючий вигляд шкіри
+Активація процесів оновлення клітин та синтезу колагену
+Захист та покращення бар’єрної функції
+✔️ Характеристики продукту:
+Тип: Зволожуючий гель-тонер
+Об’єм: 250 мл
+Призначення: Зволоження, сяйво, захист
+Тип шкіри: Суха, тьмяна, атонічна
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Polyfructol Toner Bright Skin – твій must-have для сяючої та зволоженої шкіри щодня! 🌟</t>
+  </si>
+  <si>
+    <t>505</t>
+  </si>
+  <si>
+    <t>Пінка для сухої та чутливої шкіри з канабісом Hydro Aloe Mousse 80 мл</t>
+  </si>
+  <si>
+    <t>✨ Luxury Gentle Cleansing Foam – делікатне очищення та зволоження! ✨
+🌿 Спеціальна формула для щоденного догляду:
+💧 Легка текстура ефективно видаляє забруднення та макіяж
+🌸 Вирівнює поверхню шкіри без відчуття стягнутості
+🛡️ Заспокоює подразнення та зменшує запалення
+🌟 Відновлює бар’єрні функції та дарує відчуття комфорту
+💚 Результат – чиста, м’яка та сяюча шкіра після кожного очищення!
+📌 Активні компоненти:
+🌱 Олія коноплі та чіа – насичені омега-кислотами, зменшують подразнення
+🌸 Екстракт ромашки – заспокоює чутливу шкіру
+💧 Інулін та Hydagen® Aquaporin – глибоке зволоження та еластичність
+🛡️ Д-пантенол та бетаїн – відновлення та захист бар’єру
+📌 Показання до застосування:
+Суха та чутлива шкіра
+Подразнення та зневоднення
+Зниження тонусу
+Перші ознаки старіння
+Відновлення бар’єрної функції
+✔️ Характеристики продукту:
+Тип: Очищувальна піна для обличчя
+Об’єм: 150 мл / 200 мл (залежно від упаковки)
+Призначення: Делікатне очищення, зволоження, відновлення
+Тип шкіри: Суха, чутлива
+Країна виробництва: 🇺🇦 Україна
+🌟 Luxury Gentle Cleansing Foam – твій must-have для щоденного ніжного очищення та сяйва шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>504</t>
+  </si>
+  <si>
+    <t>Розкішне молочко для вмивання ОМЕГА Smart Derma 250 мл ніжне очищення</t>
+  </si>
+  <si>
+    <t>✨ Gentle Omega Cleansing – делікатне очищення та регенерація! ✨
+🌿 Багатофункціональна формула для щоденного догляду:
+💧 Ефективно видаляє макіяж та всі типи забруднень (водо- і жиророзчинні)
+🌸 Відновлює та інтенсивно регенерує шкіру
+🛡️ Попереджає подразнення та зневоднення
+⚡ Підтримує водно-ліпідний баланс
+🌟 Активізує кровообіг та покращує тургор
+💚 Результат – чиста, свіжа та сяюча шкіра без відчуття сухості!
+📌 Активні компоненти:
+🌱 Олія коноплі та чіа – насичені омега-кислотами, живлення та протизапальна дія
+🌸 Екстракт ромашки та центелли азіатської – заспокоюють та відновлюють
+💧 Hydagen® Aquaporin, PatcH2O, сечовина – інтенсивне зволоження та утримання вологи
+🛡️ Д-пантенол та натрій аскорбіл фосфат – антиоксидантний захист та регенерація
+📌 Показання до застосування:
+Суха та чутлива шкіра
+Подразнення та зневоднення
+Зниження тонусу
+Перші ознаки старіння
+Відновлення та захист бар’єрної функції
+✔️ Характеристики продукту:
+Тип: Очищуючий засіб для обличчя
+Об’єм: 150 мл / 200 мл (залежно від упаковки)
+Призначення: Очищення, регенерація, зволоження
+Тип шкіри: Суха, чутлива
+Країна виробництва: 🇺🇦 Україна
+🌟 Gentle Omega Cleansing – твій must-have для щоденного делікатного очищення та сяйва шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>Мультикислотна локальна присушка 50 мл</t>
+  </si>
+  <si>
+    <t>✨ LOCAL SOS Lotion – точковий удар по акне! ✨
+🌿 Високоефективна мультикислотна формула для проблемної шкіри:
+💧 Сірка та камфора – антибактеріальна та протизапальна дія
+🌸 Саліцилова кислота – глибоке очищення пор
+🛡️ Нікотинамід та оксид цинку – заспокоюють, відновлюють та створюють захисний бар’єр
+⚡ Азелаїнова, мигдальна та молочна кислоти – вирівнюють тон та борються з постакне
+🌟 Bix'Activ + екстракт каштана – зменшують почервоніння та регулюють себум
+💚 Результат – зменшення запалень, швидке підсушування висипань та відновлена шкіра!
+📌 Показання до застосування:
+Акне 1–3 ступеня
+Постакне та розширені пори
+Нерівний тон шкіри
+Атопічний дерматит, псоріаз, екзема
+Подразнення та свербіж
+📌 Додаткові активні компоненти:
+🌱 Д-пантенол – заспокоює та регенерує
+💧 Гліцерин – підтримує зволоження
+⚡ Кофеїн – активізує мікроциркуляцію
+✔️ Характеристики продукту:
+Тип: Локальний засіб для проблемної шкіри
+Об’єм: 50 мл
+Призначення: Підсушування, протизапальна дія, відновлення
+Тип шкіри: Проблемна, жирна, комбінована
+Лінія: Акнедерм
+Країна виробництва: 🇺🇦 Україна
+🌟 LOCAL SOS Lotion – твій must-have для швидкої допомоги при акне та подразненнях! 🌟</t>
+  </si>
+  <si>
+    <t>410</t>
   </si>
 </sst>
 </file>
@@ -6032,9 +6195,11 @@
         <v>658</v>
       </c>
       <c r="D5" s="8">
+        <v>1300</v>
+      </c>
+      <c r="E5" s="8">
         <v>1100</v>
       </c>
-      <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8">
         <v>31</v>
@@ -6063,9 +6228,11 @@
         <v>658</v>
       </c>
       <c r="D6" s="8">
+        <v>1200</v>
+      </c>
+      <c r="E6" s="8">
         <v>1100</v>
       </c>
-      <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8">
         <v>15</v>
@@ -8254,89 +8421,159 @@
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A77" s="12"/>
-      <c r="B77" s="8"/>
+      <c r="A77" s="12" t="s">
+        <v>886</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>884</v>
+      </c>
       <c r="C77" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D77" s="8"/>
+      <c r="D77" s="8">
+        <v>1280</v>
+      </c>
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8"/>
+      <c r="G77" s="8">
+        <v>19</v>
+      </c>
+      <c r="H77" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="I77" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J77" s="8"/>
-      <c r="K77" s="18"/>
+      <c r="J77" s="8" t="s">
+        <v>885</v>
+      </c>
+      <c r="K77" s="18" t="s">
+        <v>886</v>
+      </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A78" s="12"/>
-      <c r="B78" s="8"/>
+      <c r="A78" s="12" t="s">
+        <v>889</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>887</v>
+      </c>
       <c r="C78" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D78" s="8"/>
+      <c r="D78" s="8">
+        <v>940</v>
+      </c>
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
-      <c r="G78" s="8"/>
-      <c r="H78" s="8"/>
+      <c r="G78" s="8">
+        <v>26</v>
+      </c>
+      <c r="H78" s="8" t="s">
+        <v>672</v>
+      </c>
       <c r="I78" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J78" s="8"/>
-      <c r="K78" s="18"/>
+      <c r="J78" s="8" t="s">
+        <v>888</v>
+      </c>
+      <c r="K78" s="18" t="s">
+        <v>889</v>
+      </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A79" s="12"/>
-      <c r="B79" s="8"/>
+      <c r="A79" s="12" t="s">
+        <v>892</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>890</v>
+      </c>
       <c r="C79" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D79" s="8"/>
+      <c r="D79" s="8">
+        <v>480</v>
+      </c>
       <c r="E79" s="8"/>
       <c r="F79" s="8"/>
-      <c r="G79" s="8"/>
-      <c r="H79" s="8"/>
+      <c r="G79" s="8">
+        <v>15</v>
+      </c>
+      <c r="H79" s="8" t="s">
+        <v>783</v>
+      </c>
       <c r="I79" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J79" s="8"/>
-      <c r="K79" s="18"/>
+      <c r="J79" s="8" t="s">
+        <v>891</v>
+      </c>
+      <c r="K79" s="18" t="s">
+        <v>892</v>
+      </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A80" s="12"/>
-      <c r="B80" s="8"/>
+      <c r="A80" s="12" t="s">
+        <v>895</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>893</v>
+      </c>
       <c r="C80" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D80" s="8"/>
+      <c r="D80" s="8">
+        <v>700</v>
+      </c>
       <c r="E80" s="8"/>
       <c r="F80" s="8"/>
-      <c r="G80" s="8"/>
-      <c r="H80" s="8"/>
+      <c r="G80" s="8">
+        <v>12</v>
+      </c>
+      <c r="H80" s="8" t="s">
+        <v>672</v>
+      </c>
       <c r="I80" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J80" s="8"/>
-      <c r="K80" s="18"/>
+      <c r="J80" s="8" t="s">
+        <v>894</v>
+      </c>
+      <c r="K80" s="18" t="s">
+        <v>895</v>
+      </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A81" s="12"/>
-      <c r="B81" s="8"/>
+      <c r="A81" s="12" t="s">
+        <v>898</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>896</v>
+      </c>
       <c r="C81" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="D81" s="8"/>
+      <c r="D81" s="8">
+        <v>620</v>
+      </c>
       <c r="E81" s="8"/>
       <c r="F81" s="8"/>
-      <c r="G81" s="8"/>
-      <c r="H81" s="8"/>
+      <c r="G81" s="8">
+        <v>24</v>
+      </c>
+      <c r="H81" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="I81" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J81" s="8"/>
-      <c r="K81" s="18"/>
+      <c r="J81" s="8" t="s">
+        <v>897</v>
+      </c>
+      <c r="K81" s="18" t="s">
+        <v>898</v>
+      </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="12"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ПРОЕКТ AI\ЛИЧНЫЕ НАРАБОТКИ\AI Skin Lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98587DFA-14EC-468C-B9CD-64BE232C5C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B16B6B9B-0AC8-4E74-847B-DDFC89E7B5DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2041" uniqueCount="899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2291" uniqueCount="1014">
   <si>
     <t>Артикул</t>
   </si>
@@ -5423,6 +5423,9 @@
     <t>512</t>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t>Екстразволожувальна Антиоксидантна сиворотка з центеллою 50 мл</t>
   </si>
   <si>
@@ -5584,6 +5587,1180 @@
   </si>
   <si>
     <t>410</t>
+  </si>
+  <si>
+    <t>Порозвужувальна себорегулювальна маска «босвелія» 50 мл</t>
+  </si>
+  <si>
+    <t>✨ Boswellia Clay Mask Herbal Pore Control – чиста та збалансована шкіра! ✨
+🌿 Активна формула для проблемної шкіри:
+💧 Зменшує пори та контролює себум
+🌸 Знижує запалення, подразнення та почервоніння
+🛡️ Нормалізує мікробіом шкіри та створює антисептичний бар’єр
+⚡ Має тонізуючу та регенеруючу дію
+🌟 Покращує стан проблемної шкіри та дарує відчуття свіжості
+💚 Результат – матова, рівна та здорова шкіра без надлишку себуму!
+📌 Показання до застосування:
+Акне 1–3 ступеня, постакне
+Розширені пори, нерівний тон
+Атопічний дерматит, екзема, псоріаз
+Подразнення та свербіж
+📌 Активні компоненти:
+🌱 Олії виноградних та персикових кісточок – живлення та відновлення
+🌸 Каолін – глибоке очищення та себорегуляція
+💧 Д-пантенол, гліцерин, ніацинамід – зволоження та регенерація
+🛡️ Екстракти епілобіуму, прополісу, каштану та календули – протизапальна дія
+⚡ Кофеїн, Bosexil, Bix'Activ – контроль себуму та тонізуючий ефект
+🌟 Бісаболол, алантоїн, ацетил тетрапептид-15 – заспокоюють та відновлюють
+✔️ Характеристики продукту:
+Тип: Себорегулююча порозвужуюча маска
+Об’єм: 50 мл
+Призначення: Очищення, себорегуляція, протизапальна дія
+Тип шкіри: Проблемна, жирна, комбінована
+Країна виробництва: 🇺🇦 Україна
+🌟 Boswellia Clay Mask – твій must-have для чистої та збалансованої шкіри без недоліків! 🌟</t>
+  </si>
+  <si>
+    <t>408-1</t>
+  </si>
+  <si>
+    <t>Нічний себорегулювальний флюїд «азеламід» 50 мл</t>
+  </si>
+  <si>
+    <t>✨ Azelamid Night Fluid – нічна терапія проти акне! ✨
+🌿 Лікувальна формула для проблемної шкіри:
+💧 Глибоко очищає пори та зменшує виділення себуму
+🌸 Усуває запалення та почервоніння
+🛡️ Відновлює баланс мікробіому та бар’єрні функції
+⚡ Заспокоює подразнення та прискорює регенерацію
+🌟 Дарує рівний тон та здоровий вигляд шкіри
+💚 Результат – чиста, матова та спокійна шкіра вже після кількох застосувань!
+📌 Активні компоненти:
+🌱 Bix'Activ та прополіс – пригнічують P.Acne, забезпечують антибактеріальний ефект
+🌸 Екстракт епілобіуму – регулює активність сальних залоз та мікробіом
+💧 Азелаїнова та саліцилова кислоти – відлущують та очищають пори
+🛡️ Босвелія – покращує мікроциркуляцію та зменшує почервоніння
+🌟 Ніацинамід та D-пантенол – заспокоюють та стимулюють відновлення
+🌸 Екстракти ромашки, шавлії та каштана – протизапальна та тонізуюча дія
+📌 Показання до застосування:
+Акне 1–3 ступеня
+Постакне та розширені пори
+Нерівний тон шкіри
+Атопічний дерматит, псоріаз, екзема
+Подразнення та свербіж
+✔️ Характеристики продукту:
+Тип: Нічний себорегулюючий флюїд
+Об’єм: 50 мл
+Призначення: Лікування акне, себорегуляція, протизапальна дія
+Тип шкіри: Проблемна, жирна, комбінована
+Країна виробництва: 🇺🇦 Україна
+🌟 Azelamid Night Fluid – твій must-have для нічного догляду та боротьби з акне! 🌟</t>
+  </si>
+  <si>
+    <t>409</t>
+  </si>
+  <si>
+    <t>Трансдермальний санблок ꜱᴘꜰ 𝟥𝟢, 50 мл</t>
+  </si>
+  <si>
+    <t>407</t>
+  </si>
+  <si>
+    <t>✨ Therapeutic Sunscreen SPF 30 – комплексний догляд та захист! ✨
+🌿 Формула спеціально для проблемної шкіри з акне та себореєю:
+☀️ SPF 30 широкого спектру – надійний захист від UVA/UVB
+💧 Зменшує пори та контролює себум
+🌸 Лікує акне 1–3 ступеня та постакне
+🛡️ Бореться з дерматитом, псоріазом та екземою
+⚡ Вирівнює тон та зменшує почервоніння
+💚 Результат – здорова, матова та захищена шкіра без недоліків!
+📌 Активні компоненти:
+🌱 Ніацинамід – відновлює мікробіом та регулює себум
+🌸 Екстракт епілобіуму флешері – протизапальна дія
+💧 Бета-глюкан – відновлює та заспокоює
+🛡️ Екстракт бікс орлеана – зменшує пори та жирність
+🌟 Бісаболол, Д-пантенол, пантеніл триацетат – знімають подразнення та почервоніння
+⚡ Екстракт босвелії – ефективний при дерматиті та екземі
+🌸 Додатково: екстракти шавлії, алое, ромашки, прополіс, олії льону та винограду, токоферол ацетат
+📌 Показання до застосування:
+Акне 1–3 ступеня, постакне
+Себорея та розширені пори
+Атопічний дерматит, псоріаз, екзема
+Подразнення та свербіж
+Нерівний тон шкіри
+✔️ Характеристики продукту:
+Тип: Лікувальний сонцезахисний крем
+Об’єм: 50 мл
+Рівень захисту: SPF 30
+Призначення: Захист, лікування акне, себорегуляція, відновлення
+Тип шкіри: Проблемна, жирна, комбінована
+Країна виробництва: 🇺🇦 Україна
+🌟 Therapeutic Sunscreen SPF 30 – твій must-have для комплексного догляду та захисту проблемної шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>Мінеральний себорегулювальний тонер 250 мл</t>
+  </si>
+  <si>
+    <t>403</t>
+  </si>
+  <si>
+    <t>✨ MINERAL BHA-TONER DE-BLEMISH SOLUTION – твій мінеральний секрет чистої та сяючої шкіри! ✨
+🌿 Активний тонік-ексфоліант із мультимінеральним комплексом:
+🔄 Стимулює оновлення клітин та контролює себум
+⚖️ Балансує мікрофлору шкіри
+💎 Прискорює регенерацію та відновлення тканин
+💧 Глибоко зволожує та дарує еластичність
+💚 Показання:
+🌟 Акне 1–3 ступеня
+🌟 Постакне та розширені пори
+🌟 Нерівний тон шкіри
+🌟 Атопічний дерматит, псоріаз, екзема
+🌟 Подразнення та свербіж
+🌸 Активні компоненти:
+🔥 Азелаїнова та саліцилова кислоти
+✨ Ніацинамід та глюконолактон
+🌼 Екстракти ромашки, шавлії, епілобіуму
+🍯 Прополіс та Bosexil
+🪨 Мінерали: магній, калій, цинк, натрій, кальцій
+💎 Результат – чиста, свіжа та збалансована шкіра без недоліків! 🌟</t>
+  </si>
+  <si>
+    <t>Iнтенсивний очищувальний гель з босвелією 250 мл</t>
+  </si>
+  <si>
+    <t>✨ Boswellia Pro-Gel Deep Cleanse – твій ритуал чистоти та комфорту! ✨
+🌿 Інтенсивний очищаючий гель з босвелією – універсальний засіб для проблемної шкіри. 💎 Поєднання кислот, прополісу та екстракту босвелії дарує глибоке очищення та відновлення.
+🔥 Основні дії:
+✨ Усунення жирного блиску та гіперкератозу
+⚖️ Регуляція вироблення себуму
+🌸 Заспокоює та знімає подразнення
+🛡️ Відновлює бар’єрні функції епідермісу
+💚 Корегує прояви себореї та екземи
+🌟 Показання:
+🌿 Акне 1–3 ступеня та постакне
+🔍 Розширені пори
+🎨 Нерівний тон обличчя
+🧴 Атопічний дерматит, псоріаз, екзема
+😌 Подразнення та свербіж
+💧 Активні компоненти:
+🌼 Екстракт ромашки, 🌱 екстракт шавлії, 💎 сечовина, 🌿 Д-пантенол, 🌟 Bosexil, 🍯 прополіс, ⚡ азелаїнова кислота, 🌊 саліцилова кислота, ✨ ніацинамід, 🌰 екстракт кінського каштана.
+💚 Boswellia Pro-Gel Deep Cleanse – твій секрет чистої та здорової шкіри!</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>✨ Нічний крем CutiBiome Extra Regeneration 50 мл ✨
+🌙 Інтенсивний догляд для жирної та комбінованої шкіри з проявами акне!
+💎 Ліпосомальна формула забезпечує глибоке проникнення активних компонентів, даруючи шкірі відновлення та баланс.
+🔹 Показання до застосування:
+🌿 Жирна та комбінована шкіра
+🌸 Корекція акне 1–2 ступеня
+🌟 Зменшення слідів постакне
+✨ Вирівнювання тону обличчя
+🔍 Зменшення розширених пор
+💧 Заспокоєння запальних процесів
+💚 Основні переваги:
+⚖️ Нормалізація мікробіому шкіри
+🌿 Себорегуляція
+🌸 Зменшення слідів постакне
+🛡️ Антибактеріальна та протизапальна дія
+💦 Інтенсивне зволоження
+🌞 Матуючий ефект
+🌟 Активні компоненти:
+Олія виноградних та персикових кісточок, Д-пантенол, гліцерин, ніацинамід, Sebaryl FL LS 9088, екстракти лайма, зеленого чаю та чайного дерева, лактобіонова кислота, CutiBiome CLR™, Skinasensyl, алантоїн.
+📦 Об’єм: 50 мл
+🏢 Виробник: Smart4Derma</t>
+  </si>
+  <si>
+    <t>Нічний крем Кутибіом Extra Regeneration 50 мл для жирної шкіри</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>✨ Smart Derma Total Protect BB Cream SPF 30 – матовість та захист! ✨
+🌿 Багатофункціональна формула для жирної та комбінованої шкіри:
+☀️ SPF 30 UVA/UVB-захист – профілактика фотопошкоджень
+💧 Матуючий ефект без жирного блиску
+🌸 Вирівнює тон та зменшує сліди постакне
+🛡️ CutiBiome CLR – нормалізація мікробіому та протизапальна дія
+⚡ Довготривала гідратація та себорегуляція
+💚 Результат – рівний тон, матова та здорова шкіра щодня!
+📌 Активні компоненти:
+🌱 Олія виноградних та персикових кісточок – живлення та відновлення
+🌸 Екстракти зеленого чаю, лайма та чайного дерева – антибактеріальна дія
+💧 Ніацинамід та Д-пантенол – зволоження та регенерація
+🛡️ Лактобіонова кислота – м’яке відлущення та вирівнювання тону
+🌟 Алантоїн – заспокоює та знімає подразнення
+📌 Показання до застосування:
+Жирна та комбінована шкіра
+Акне 1–2 ступеня та постакне
+Нерівний тон обличчя
+Розширені пори
+Запальні процеси
+✔️ Характеристики продукту:
+Тип: Матуючий BB крем з SPF
+Об’єм: 50 мл
+Рівень захисту: SPF 30
+Призначення: Матування, тонування, захист, себорегуляція
+Тип шкіри: Жирна, комбінована, проблемна
+Бренд: Smart Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Smart Derma Total Protect BB Cream SPF 30 – твій must-have для матової та доглянутої шкіри щодня! 🌟</t>
+  </si>
+  <si>
+    <t>Матуючий ВВ крем SPF 30 Smart Derma Total Protect</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>✨ Sebo-Mask Manuka – контроль себуму та чиста шкіра! ✨
+🌿 Спеціалізована формула для жирної та комбінованої шкіри:
+💧 Нормалізує роботу сальних залоз та зменшує секрецію себуму
+🌸 Пригнічує розмноження бактерій Propionibacterium acnes
+🛡️ Заспокоює запальні процеси та зменшує почервоніння
+⚡ Вирівнює тон та зменшує сліди постакне
+🌟 Дарує матовість без жирного блиску
+💚 Результат – чиста, матова та здорова шкіра без недоліків!
+📌 Основні переваги:
+Нормалізація мікробіому шкіри
+Себорегуляція та матуючий ефект
+Зменшення слідів постакне
+Антибактеріальна та протизапальна дія
+Зволоження без жирного блиску
+Звуження пор
+📌 Активні компоненти:
+🌱 Олія персика та кокоса – живлення та відновлення
+🌸 Екстракти зеленого чаю, календули та кропиви – антиоксидантна та заспокійлива дія
+💧 Ніацинамід – контроль себуму та вирівнювання тону
+🛡️ Sebaryl – регуляція роботи сальних залоз
+⚡ Гідролат лайма – тонізуючий ефект
+🌟 Екстракт чайного дерева – антибактеріальна дія
+✔️ Характеристики продукту:
+Тип: Себорегулююча маска для жирної шкіри
+Об’єм: 50 мл
+Призначення: Контроль себуму, лікування акне, матування
+Тип шкіри: Жирна, комбінована, проблемна
+Країна виробництва: 🇺🇦 Україна
+🌟 Sebo-Mask Manuka – твій must-have для догляду за жирною та проблемною шкірою! 🌟</t>
+  </si>
+  <si>
+    <t>Манукі маска для жирної шкіри та акне Sebo-Mask 50 мл</t>
+  </si>
+  <si>
+    <t>306-1</t>
+  </si>
+  <si>
+    <t>Ліпосомальна сироватка з феруловою кислотою BHA-PHA Control 50 мл</t>
+  </si>
+  <si>
+    <t>✨ BHA-PHA Control Serum – інтенсивна терапія для проблемної шкіри! ✨
+🌿 Спеціалізована формула для жирної та комбінованої шкіри:
+💧 Нормалізує мікробіом та пригнічує ріст бактерій P. Acnes
+🌸 Зменшує сліди постакне та вирівнює тон
+🛡️ Забезпечує себорегуляцію та матуючий ефект
+⚡ Має антибактеріальну та протизапальну дію
+🌟 Дарує зволоження без жирного блиску
+💚 Результат – чиста, матова та здорова шкіра з рівним тоном!
+📌 Основні активні компоненти:
+🌱 Азелаїнова кислота – потужна антибактеріальна дія
+🌸 Ферулова кислота – антиоксидантний захист
+💧 Ніацинамід – себорегуляція та зволоження
+🛡️ Лактобіонова кислота – делікатне відлущування
+🌟 Екстракти алоє, ромашки, чайного дерева та зеленого чаю – заспокоюють та знімають запалення
+📌 Показання до застосування:
+Жирна та комбінована шкіра
+Акне 1–2 ступеня
+Постакне та розширені пори
+Нерівний тон обличчя
+Запальні процеси
+✔️ Характеристики продукту:
+Тип: Ліпосомальна сироватка для проблемної шкіри
+Об’єм: 50 мл
+Призначення: Лікування акне, себорегуляція, антиоксидантний захист
+Тип шкіри: Жирна, комбінована, проблемна
+Країна виробництва: 🇺🇦 Україна
+🌟 BHA-PHA Control Serum – твій must-have для догляду за проблемною шкірою та контролю акне! 🌟</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>Манукі маска для жирної шкіри та акне Sebo-Mask 230 мл</t>
+  </si>
+  <si>
+    <t>230 мл</t>
+  </si>
+  <si>
+    <t>✨ Sebo-Mask Manuka – контроль себуму та чиста шкіра! ✨
+🌿 Спеціалізована формула для жирної та комбінованої шкіри:
+💧 Нормалізує роботу сальних залоз та зменшує секрецію себуму
+🌸 Пригнічує розмноження бактерій Propionibacterium acnes
+🛡️ Заспокоює запальні процеси та зменшує почервоніння
+⚡ Вирівнює тон та зменшує сліди постакне
+🌟 Дарує матовість без жирного блиску
+💚 Результат – чиста, матова та здорова шкіра без недоліків!
+📌 Основні переваги:
+Нормалізація мікробіому шкіри
+Себорегуляція та матуючий ефект
+Зменшення слідів постакне
+Антибактеріальна та протизапальна дія
+Зволоження без жирного блиску
+Звуження пор
+📌 Активні компоненти:
+🌱 Олія персика та кокоса – живлення та відновлення
+🌸 Екстракти зеленого чаю, календули та кропиви – антиоксидантна та заспокійлива дія
+💧 Ніацинамід – контроль себуму та вирівнювання тону
+🛡️ Sebaryl – регуляція роботи сальних залоз
+⚡ Гідролат лайма – тонізуючий ефект
+🌟 Екстракт чайного дерева – антибактеріальна дія
+✔️ Характеристики продукту:
+Тип: Себорегулююча маска для жирної шкіри
+Об’єм: 230 мл
+Призначення: Контроль себуму, лікування акне, матування
+Тип шкіри: Жирна, комбінована, проблемна
+Країна виробництва: 🇺🇦 Україна
+🌟 Sebo-Mask Manuka – твій must-have для догляду за жирною та проблемною шкірою! 🌟</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>Ензимна пудра Smart4Derma з вулканічним пилом для жирної шкіри 120 г</t>
+  </si>
+  <si>
+    <t>120 г</t>
+  </si>
+  <si>
+    <t>✨ Smart4Derma Enzyme Powder – глибоке очищення та контроль себуму! ✨
+🌿 Професійна формула для жирної та комбінованої шкіри:
+💧 Ефективно розчиняє сальні пробки та очищає пори
+🌸 Зменшує їх розмір та нормалізує себорегуляцію
+🛡️ Має антибактеріальну та протизапальну дію
+⚡ Дарує матуючий ефект без пересушування
+🌟 Стимулює регенерацію та вирівнює тон шкіри
+💚 Результат – чиста, матова та здорова шкіра з рівним тоном!
+📌 Активні компоненти:
+🌱 Ніацинамід – контроль роботи сальних залоз
+🌸 Комплекс кислот (лактобіонова, винна) – делікатне відлущування
+💧 Папаїн – ензимне очищення
+🛡️ Вулканічний пил – регуляція себуму та глибоке очищення
+⚡ Цинк глюканат – протизапальна дія
+🌟 Кофеїн – тонізує та активізує мікроциркуляцію
+📌 Показання до застосування:
+Жирна та комбінована шкіра
+Акне 1–2 ступеня
+Постакне та нерівний тон
+Розширені пори
+Запальні процеси
+✔️ Характеристики продукту:
+Тип: Ензимна пудра для очищення
+Об’єм: 120 г
+Лінійка: Acne Balance
+Призначення: Глибоке очищення, себорегуляція, матування
+Тип шкіри: Жирна, комбінована, проблемна
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Smart4Derma Enzyme Powder – твій must-have для глибокого очищення та сяючої шкіри без недоліків! 🌟</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>Себорегулюючий мультикислотний тонер CUTIBIOME TONER BHA-PHA CONTROL</t>
+  </si>
+  <si>
+    <t>✨ CUTIBIOME TONER – контроль себуму та рівний тон! ✨
+🌿 Інтенсивна терапія для проблемної шкіри:
+💧 Зволожує та нормалізує рН
+🌸 Вирівнює тон та зменшує сліди постакне
+🛡️ Має виражену антибактеріальну та протизапальну дію
+⚡ Нормалізує мікробіом та регулює роботу сальних залоз
+🌟 Дарує матуючий ефект без пересушування
+💚 Результат – чиста, матова та здорова шкіра з рівним тоном!
+📌 Показання до застосування:
+Жирна та комбінована шкіра
+Акне 1–2 ступеня
+Постакне та розширені пори
+Нерівний тон обличчя
+Запальні процеси
+📌 Активні компоненти:
+🌱 Кислотний комплекс BHA + PHA (саліцилова та лактобіонова кислоти) – очищення та делікатне відлущування
+🌸 Азелаїнова кислота – протизапальна та антибактеріальна дія
+💧 Ніацинамід та цинк глюканат – себорегуляція та зволоження
+🛡️ Екстракти алоє та ромашки – заспокоюють та знімають подразнення
+⚡ Кофеїн – тонізує та активізує мікроциркуляцію
+🌟 Ефірні олії чайного дерева та лайма, CutiBiome CLR – нормалізація мікробіому та антисептичний ефект
+✔️ Характеристики продукту:
+Тип: Себорегулюючий мультикислотний тонер
+Об’єм: 100 мл
+Призначення: Зволоження, себорегуляція, антибактеріальна дія
+Тип шкіри: Жирна, комбінована, проблемна
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 CUTIBIOME TONER – твій must-have для догляду за проблемною шкірою та контролю акне!</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>Очищающая мультикислотная пенка для жирной, комбинированной и кожи из акне 80 мл</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>✨ Smart4Derma AHA-BHA-PHA Foam – глибоке очищення та контроль акне! ✨
+🌿 Спеціальна формула для жирної та проблемної шкіри:
+💧 Делікатно, але ефективно видаляє забруднення, себум та залишки макіяжу
+🌸 Регулює вироблення себуму та зменшує пори
+🛡️ Має антибактеріальну та заспокійливу дію
+⚡ Підтримує мікробіом шкіри завдяки PHA-кислотам
+🌟 Робить шкіру гладкою, матовою та свіжою
+💚 Результат – чиста, матова та здорова шкіра без недоліків!
+📌 Основні властивості:
+Регуляція себуму та зменшення пор (ніацинамід, азелаїнова та гліколева кислоти)
+Антибактеріальна та заспокійлива дія (олії чайного дерева та лайма)
+Підтримка мікробіому (PHA-кислоти)
+📌 Активні компоненти:
+🌱 AHA, BHA, PHA кислоти (гліколева, молочна, винна, яблучна, лактобіонова, саліцилова)
+🌸 Азелаїнова кислота – протизапальна дія
+💧 Ніацинамід – себорегуляція та зволоження
+🛡️ Олії лайма та чайного дерева – антисептичний ефект
+⚡ Кофеїн та цинк – тонізуюча та протизапальна дія
+📌 Застосування:  
+Нанести на вологу шкіру, помасажувати 1–2 хвилини та змити. Використовувати двічі на день.
+✔️ Характеристики продукту:
+Тип: Очищувальна пінка для обличчя
+Призначення: Очищення, себорегуляція, антибактеріальна дія
+Тип шкіри: Жирна, комбінована, проблемна
+Лінійка: Acne Balance
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Smart4Derma AHA-BHA-PHA Foam – твій must-have для щоденного контролю акне та сяючої шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>Маска-гоммаж Smart4Derma з молочними протеїнами та ферментами 100 мл</t>
+  </si>
+  <si>
+    <t>240-1</t>
+  </si>
+  <si>
+    <t>✨ Smart4Derma Enzyme Gommage – м’яке відлущування та сяйво! ✨
+🌿 Унікальна формула для делікатного догляду:
+💧 Дбайливо видаляє відмерлі клітини та сальні пробки
+🌸 Вирівнює текстуру та дарує гладкість
+🛡️ Зберігає гідроліпідний баланс шкіри
+⚡ Стимулює регенерацію та оновлення клітин
+🌟 Робить шкіру сяючою та свіжою після кожного застосування
+💚 Результат – м’яка, рівна та сяюча шкіра без подразнень!
+📌 Активні інгредієнти:
+🌱 Молочні протеїни та ферменти (актинідин, бромелайн, трипсин, хримотрипсин, фіцин, сутілайн) – ензимне очищення та ексфоліація
+🌸 Екстракти розмарину, ламінарії, кори верби, обліпихи та горобини – антиоксидантна та протизапальна дія
+💧 Олії пінника лугового, солодкого мигдалю та грецького горіха – живлення та відновлення
+🛡️ Prozymex® та X-pressin – стимуляція регенерації та оновлення клітин
+📌 Спосіб застосування:  
+Нанести на чисту вологу шкіру, легкими масажними рухами скочувати засіб, видаляючи відмерлі клітини. Змити водою.
+✔️ Характеристики продукту:
+Тип: Очищувальна маска-гоммаж
+Об’єм: 100 мл
+Призначення: Ексфоліація, очищення, сяйво
+Тип шкіри: Усі типи, особливо тьмяна та проблемна
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Smart4Derma Enzyme Gommage – твій must-have для м’якого відлущування та сяйва шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>Освітлювальний пілінг для делікатних зон Smart4Derma Intimate Harmony Peel 30 мл</t>
+  </si>
+  <si>
+    <t>✨ Intimate Harmony Peel – ніжне освітлення та догляд! ✨
+🌿 Спеціально створений для делікатних зон:
+💧 Освітлює та вирівнює тон шкіри
+🌸 Зменшує пігментацію та нерівності текстури
+🛡️ Уповільнює ріст волосся та запобігає його вростанню
+⚡ Підтримує пружність та еластичність
+🌟 Дарує гладку, світлу та доглянуту шкіру навіть у найчутливіших ділянках
+💚 Результат – бездоганна шкіра без дискомфорту!
+📌 Активні інгредієнти та їх дія:
+🌱 Мигдальна кислота (20%) – м’яке відлущування та освітлення
+🌸 Транексамова кислота (15%) – боротьба з пігментними плямами
+💧 Молочна кислота (10%) – зволоження та вирівнювання текстури
+🛡️ Лактобіонова кислота (7%) – антиоксидантна та омолоджуюча дія
+⚡ Лимонна кислота та папаїн – посилюють освітлення та очищають пори
+🌟 Саліцилова кислота – запобігає вростанню волосся
+📌 Спосіб використання:  
+Нанести 1–2 мл засобу на чисту, суху шкіру делікатних зон (пахви, зона бікіні, внутрішня поверхня стегон, ареоли), уникаючи слизових оболонок.
+Залишити на 5–10 хвилин, після чого ретельно змити теплою водою.
+Рекомендований курс: 6–8 процедур з інтервалом 7–10 днів.
+✔️ Характеристики продукту:
+Тип: Освітлювальний пілінг для делікатних зон
+Об’єм: 50 мл
+Призначення: Освітлення, вирівнювання тону, профілактика вростання волосся
+Тип шкіри: Усі типи, особливо чутлива та схильна до пігментації
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Intimate Harmony Peel – твій must-have для ніжного догляду та рівного тону шкіри у делікатних зонах! 🌟</t>
+  </si>
+  <si>
+    <t>681</t>
+  </si>
+  <si>
+    <t>681(1)</t>
+  </si>
+  <si>
+    <t>Антиоксидантний ультразахисний крем SPF 80 для жирної шкіри Smart4Derma QC Sunblock Oil-Free 230 мл</t>
+  </si>
+  <si>
+    <t>✨ QC Sunblock Oil-Free SPF 80 – ультра-захист та молодість шкіри! ✨
+🌿 Формула для щоденного використання:
+☀️ SPF 80 широкого спектра UVA/UVB – максимальний захист від сонячних променів
+🌸 Коензим Q10 та вітамін С – потужний антиоксидантний комплекс проти вільних радикалів
+🛡️ Запобігає появі зморшок та пігментних плям
+💧 Некомедогенна формула – зволожує без жирного блиску
+⚡ Створює рівномірне та гладке покриття
+💚 Результат – захищена, свіжа та доглянута шкіра щодня!
+📌 Переваги:
+Максимальний сонцезахисний ефект
+Антиоксидантний захист
+Некомедогенна формула
+Зволоження та протизапальна дія
+📌 Активні компоненти:
+🌱 Емоленти – живлення та м’якість
+🌸 Бісаболол – заспокоює та знімає подразнення
+💧 Вітамін С – антиоксидантний захист
+🛡️ Коензим Q10 – уповільнює старіння
+☀️ Сонцезахисні фільтри – UVA/UVB-захист
+📌 Спосіб використання:  
+Нанести тонким рівномірним шаром на очищену шкіру обличчя за 15–20 хвилин до виходу на сонце.
+Для тривалого перебування на сонці – оновлювати кожні 2–3 години.
+✔️ Характеристики продукту:
+Тип: Сонцезахисний крем
+Об’єм: 50 мл / 100 мл (залежно від упаковки)
+Рівень захисту: SPF 80
+Призначення: Захист, антиоксидантний догляд, профілактика старіння
+Тип шкіри: Усі типи, особливо схильна до фотостаріння
+Бренд: QC
+Країна виробництва: 🇺🇦 Україна
+🌟 QC Sunblock Oil-Free SPF 80 – твій must-have для щоденного ультра-захисту та молодості шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>849(1)</t>
+  </si>
+  <si>
+    <t>849</t>
+  </si>
+  <si>
+    <t>Денний крем SPF 35 проти пігментації для всіх типів шкіри Smart4Derma Marguerite Cream Power Defence SPF 35 - 230 мл</t>
+  </si>
+  <si>
+    <t>841</t>
+  </si>
+  <si>
+    <t>841(1)</t>
+  </si>
+  <si>
+    <t>✨ Marguerite Cream Power Defence SPF 35 – освітлення та захист! ✨
+🌿 Універсальна формула для всіх типів шкіри:
+☀️ SPF 35 – надійний захист від UVA/UVB
+🌸 Освітлює та вирівнює тон, зменшує пігментацію
+🛡️ Знижує продукування меланіну та запобігає появі нових плям
+⚡ Коригує вже наявні дефекти шкіри
+🌟 Заспокоює подразнення та зменшує запальні реакції
+💚 Результат – рівний, світлий та здоровий тон шкіри щодня!
+📌 Переваги:
+Висококонцентрована формула
+Сонцезахисний ефект
+Вирівнювання тону та зменшення гіперпігментації
+Антиоксидантна дія
+Зволоження та живлення
+📌 Активні компоненти:
+🌱 Амарантова олія, арбутин, бісаболол
+🌸 Вітамін C, глутатіон, токоферол
+💧 Екстракти маргаритки, солодки, ячменю, гадючника в’язолистого, кресу
+🛡️ Ізофлавони сої, лецитин, ліноленова кислота
+⚡ Олії бабассу, бораго, виноградної кісточки
+🌟 Пептиди та освітлюючий комплекс
+☀️ Сонцезахисні фільтри
+📌 Спосіб використання:  
+Щоранку нанести невелику кількість крему на очищену шкіру обличчя та шиї.
+Рівномірно розподілити легкими рухами до повного вбирання.
+Для максимального ефекту – використовувати щоденно.
+✔️ Характеристики продукту:
+Тип: Освітлювальний сонцезахисний крем
+Об’єм: 50 мл
+Рівень захисту: SPF 35
+Призначення: Освітлення, захист, антиоксидантний догляд
+Тип шкіри: Усі типи, включно з чутливою
+Бренд: Marguerite
+Країна виробництва: 🇺🇦 Україна
+🌟 Marguerite Cream Power Defence SPF 35 – твій must-have для рівного тону та захисту шкіри від сонця! 🌟</t>
+  </si>
+  <si>
+    <t>Освітлюючий крем SPF 15 «Сяючий погляд» Smart4Derma Eye Cream B-White Contour SPF 15 - 100 мл</t>
+  </si>
+  <si>
+    <t>844</t>
+  </si>
+  <si>
+    <t>844(1)</t>
+  </si>
+  <si>
+    <t>✨ B-White Eye Cream SPF 15 – сяйво та молодість погляду! ✨
+🌿 Формула для ніжної шкіри навколо очей:
+💧 Освітлює темні кола та зменшує набряки
+🌸 Вирівнює тон та усуває пігментацію
+🛡️ Захищає від фотостаріння та оксидативного стресу
+⚡ Заспокоює подразнення та знижує запальні процеси
+🌟 Підтримує пружність та еластичність шкіри
+💚 Результат – сяючий, свіжий та молодий погляд щодня!
+📌 Переваги:
+Зволоження та живлення
+Поліпшення мікроциркуляції
+Антиоксидантний захист
+Освітлення та вирівнювання тону
+Захист від UVA/UVB (SPF 15)
+📌 Активні компоненти:
+🌱 Shadownyl – антивіковий комплекс для зменшення темних кіл
+🌸 EGCG детокс-комплекс – антиоксидантна дія
+💧 β‑White пептид та арбутин – освітлення та контроль меланіну
+🛡️ Вітамін С та Brightenyl – боротьба з пігментацією
+⚡ Гіалуронова кислота, Aquaporin комплекс – інтенсивне зволоження
+🌟 Ескулін, есцин, рутина, пептиди Rubixyl – покращення мікроциркуляції та тонусу
+🌸 Олії авокадо та пасіфлори – живлення та відновлення
+📌 Спосіб використання:  
+Наносити щодня вранці та ввечері на очищену шкіру навколо очей легкими рухами по масажних лініях до повного поглинання.
+Підходить для всіх типів шкіри, особливо схильної до пігментації та втрати тонусу.
+✔️ Характеристики продукту:
+Тип: Освітлювальний антивіковий крем для очей
+Об’єм: 30 мл
+Рівень захисту: SPF 15
+Призначення: Освітлення, антиоксидантний захист, зволоження
+Тип шкіри: Усі типи, особливо делікатна та схильна до пігментації
+Бренд: B-White
+Країна виробництва: 🇺🇦 Україна
+🌟 Eye Cream B-White Contour SPF 15 – твій must-have для сяючого та молодого погляду без темних кіл! 🌟</t>
+  </si>
+  <si>
+    <t>Оптично-відбілююча реепітелізуюча маска Smart4Derma Opti-White Mask DGA Re-Epithelium 300 мл</t>
+  </si>
+  <si>
+    <t>300 мл</t>
+  </si>
+  <si>
+    <t>847</t>
+  </si>
+  <si>
+    <t>847(1)</t>
+  </si>
+  <si>
+    <t>✨ Opti-White Mask – сяйво та рівний тон! ✨
+🌿 Висококонцентрована формула для боротьби з пігментацією:
+💧 Зменшує вираженість постакне, вікових та пігментних плям
+🌸 Усуває тьмяність та неоднорідний тон
+🛡️ Нейтралізує вільні радикали та захищає від оксидативного стресу
+⚡ Інтенсивно зволожує, усуває сухість та стягнутість
+🌟 Відновлює пружність, еластичність та природне сяйво
+💚 Результат – гладка, свіжа та сяюча шкіра без недоліків!
+📌 Властивості:
+Освітлення та вирівнювання тону
+Висококонцентрований склад
+Антиоксидантний захист
+Поліпшення тургору та пружності
+Інтенсивне зволоження
+📌 Активні компоненти:
+🌱 Вітамін С (3 стабільні форми) – освітлення та антиоксидантна дія
+🌸 Нанопептид-1 – повертає сяйво та вдосконалює мікрорельєф
+💧 Гіалуронова кислота – глибоке зволоження
+🛡️ Бісаболол – заспокоює та знімає подразнення
+🌟 Лецитин та пептиди – відновлення та зміцнення шкіри
+📌 Спосіб використання:  
+Нанести маску на чисту шкіру обличчя, рівномірно розподілити та залишити для дії. Використовувати регулярно для максимального ефекту освітлення та відновлення.
+✔️ Характеристики продукту:
+Тип: Освітлювальна концентрована маска
+Призначення: Освітлення, зволоження, антиоксидантний захист
+Тип шкіри: Нормальна, суха, комбінована, чутлива
+Вік: 25+, 30+, 40+, 50+
+Країна виробництва: 🇺🇦 Україна
+🌟 Opti-White Mask – твій must-have для сяючої та доглянутої шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>Интеллектуальный осветляющий Бустер-Концентрат тройного действия Smart Booster 3D Whitening Smart4Derma 10 ml</t>
+  </si>
+  <si>
+    <t>10 ml</t>
+  </si>
+  <si>
+    <t>843</t>
+  </si>
+  <si>
+    <t>843(1)</t>
+  </si>
+  <si>
+    <t>✨ Brightenyl Concentrate – рівний тон та сяйво шкіри! ✨
+🌿 Інноваційна формула для щоденного догляду:
+💧 Коригує меланогенез за трьома напрямками:
+• зменшує утворення ендотеліну-1 (ЕТ-1)
+• скорочує біосинтез меланіну, індукований УФ-випромінюванням
+• регулює активність тирозинази та α-MSH
+🌸 Освітлює пігментні плями різного генезу
+🛡️ Запобігає фотостарінню та оксидативному стресу клітин
+⚡ Вирівнює тон та текстуру шкіри
+🌟 Дарує сяйво та здоровий вигляд
+💚 Результат – світла, рівна та доглянута шкіра без пігментації!
+📌 Показання:
+Пігментні плями різного походження (сонячні, вікові, постакне, післязапальні)
+Нерівний тон та тьмяність
+Профілактика фотостаріння
+Лікування будь-якої гіперхромії
+📌 Активні інгредієнти:
+🌱 Екстракт маргаритки та кресу садового – освітлення та регуляція меланогенезу
+🌸 Гіалуронова кислота – глибоке зволоження
+💧 Лецитин та ізофлавони сої – відновлення та антиоксидантний захист
+🛡️ Аміноетилфосфінова кислота – контроль пігментації
+⚡ Екстракт софори японської та бурої водорості – протизапальна дія
+🌟 BRIGHTENYL®, арбутин, глутатіон, аскорбіл пальмітат – потужний освітлюючий комплекс
+✨ Нанопептид-1 – відновлення сяйва та пружності
+📌 Спосіб застосування:  
+Нанести невелику кількість препарату на очищену шкіру обличчя, шиї та декольте.
+Масажувати круговими рухами до повного поглинання.
+Рекомендується щоденне використання.
+✔️ Характеристики продукту:
+Тип: Освітлюючий концентрат для корекції пігментації
+Об’єм: 30 мл
+Призначення: Освітлення, профілактика фотостаріння, антиоксидантний захист
+Тип шкіри: Усі типи, особливо схильна до пігментації
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Brightenyl Concentrate – твій must-have для рівного тону та сяйва шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>Освітлювальний молекулярний тонік з ніацинамідом та глутатіоном Smart4Derma N-glutation Tonic Molecular Glow 500 мл</t>
+  </si>
+  <si>
+    <t>500 мл</t>
+  </si>
+  <si>
+    <t>855</t>
+  </si>
+  <si>
+    <t>855(1)</t>
+  </si>
+  <si>
+    <t>✨ Illuminating Toner – рівний тон та сяйво! ✨
+🌿 Формула для щоденного догляду:
+💧 Освітлює сліди постакне та рубці
+🌸 Зміцнює захисний бар’єр та протидіє вільним радикалам
+🛡️ Запобігає появі пігментних плям
+⚡ Гідратує та робить шкіру м’якою й гладкою
+🌟 Вирівнює колір та текстуру шкіри
+💚 Результат – здорова, сяюча та доглянута шкіра без недоліків!
+📌 Переваги:
+Вирівнювання тону
+Усунення пігментації
+Покращення тургору
+Зміцнення захисної функції
+📌 Активні компоненти:
+🌱 Арбутин – освітлення та профілактика пігментації
+🌸 Вітамін C та глутатіон – антиоксидантний захист
+💧 Диглюкозид галової кислоти – відновлення та зміцнення
+🌼 Екстракти маргаритки та толокнянки – природне освітлення
+🌿 Олія Шуінко – живлення та захист
+⚡ Папаїн – м’яке відлущування та оновлення
+📌 Спосіб використання:  
+Нанести тонік на очищену шкіру обличчя вранці та ввечері за допомогою ватного диска.
+М’яко масажувати круговими рухами для кращого проникнення активних компонентів.
+✔️ Характеристики продукту:
+Тип: Освітлювальний тонік
+Об’єм: 150 мл
+Призначення: Освітлення, вирівнювання тону, антиоксидантний захист
+Тип шкіри: Нормальна, комбінована, проблемна
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Illuminating Toner – твій must-have для сяючої та доглянутої шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>Освітлювальна ензимна пудра Smart4Derma Glow Enzyme Powder 10% Vitamin C &amp; Q10 120 грам</t>
+  </si>
+  <si>
+    <t>120 грам</t>
+  </si>
+  <si>
+    <t>852</t>
+  </si>
+  <si>
+    <t>852(1)</t>
+  </si>
+  <si>
+    <t>✨ Smart4Derma Enzyme Powder – сяйво та рівний тон! ✨
+🌿 Формула для боротьби з пігментацією та тьмяністю:
+💧 Видаляє ороговілі клітини та сальні пробки
+🌸 Освітлює пігментні плями та сліди постакне
+🛡️ Зміцнює захисний бар’єр та протидіє вільним радикалам
+⚡ Вирівнює тон та текстуру шкіри
+🌟 Дарує свіжість, гладкість та сяйво
+💚 Результат – чиста, світла та доглянута шкіра без недоліків!
+📌 Переваги продукту:
+Ефективне видалення ороговілих клітин
+Освітлення пігментації та постакне
+Звуження пор та вирівнювання тону
+Підтримка шкіри в ідеальному стані
+📌 Активні компоненти:
+🌱 Арбутин та койєва кислота – освітлення та профілактика пігментації
+🌸 Вітамін С та коензим Q10 – антиоксидантний захист
+💧 Алантоїн та фолієва кислота – зволоження та відновлення
+🛡️ Бромелайн, папаїн, протеаза – ензимне очищення та ексфоліація
+⚡ Аргінін та винна кислота – регенерація та вирівнювання текстури
+📌 Спосіб використання:  
+Змішати невелику кількість пудри з водою до утворення піни.
+Нанести на вологу шкіру, м’яко масажувати та змити водою.
+Рекомендується використовувати 2–3 рази на тиждень.
+✔️ Характеристики продукту:
+Тип: Освітлювальна ензимна пудра
+Об’єм: 100 г
+Призначення: Освітлення, ексфоліація, антиоксидантний захист
+Тип шкіри: Усі типи, особливо схильна до пігментації та постакне
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Smart4Derma Enzyme Powder – твій must-have для сяючої та рівної шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>480 мл</t>
+  </si>
+  <si>
+    <t>Освітлювальна пінка з вітаміном C та глутатіоном Smart4Derma C-glutation Mousse Glow Cleanser 480 мл</t>
+  </si>
+  <si>
+    <t>853(1)</t>
+  </si>
+  <si>
+    <t>853</t>
+  </si>
+  <si>
+    <t>✨ Сила вітаміну С та глутатіону – сяюча шкіра щодня! ✨
+🌿 Інноваційна формула для комплексного догляду:
+💧 Дбайливо видаляє макіяж, забруднення та надлишки себуму
+🌸 Освітлює пігментні плями та сліди постакне
+🛡️ Забезпечує потужний антиоксидантний захист
+⚡ Інтенсивно гідратує та зберігає еластичність
+🌟 Звужує пори, вирівнює мікрорельєф та запобігає висипанням
+💚 Результат – чиста, сяюча та доглянута шкіра без подразнень!
+📌 Переваги:
+Ефективне очищення
+Освітлення пігментних плям
+Гідратування та захист
+Себорегуляція
+📌 Активні компоненти:
+🌱 Арбутин – освітлення та профілактика пігментації
+☀️ Вітамін C – антиоксидантний захист та вирівнювання тону
+💎 Глутатіон – потужний антиоксидант, зволоження та еластичність
+🌸 Диглюкозид галової кислоти – регенерація та зміцнення
+💧 Пантенол – інтенсивне зволоження та заспокоєння
+📌 Спосіб використання:  
+Нанести невелику кількість пінки на вологу шкіру, легко помасажувати та змити теплою водою.
+Використовувати регулярно для максимального ефекту.
+✔️ Характеристики продукту:
+Тип: Освітлювальна пінка для вмивання
+Призначення: Очищення, освітлення, антиоксидантний захист
+Тип шкіри: Нормальна, жирна, комбінована, проблемна
+Вік: 20+, 30+, 40+, 50+
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Smart4Derma C-Glutation Mousse – твій must-have для сяючої та рівної шкіри щодня! 🌟</t>
+  </si>
+  <si>
+    <t>Зміцнювальний Нічний крем для чутливої шкіри та куперозом 230 мл</t>
+  </si>
+  <si>
+    <t>✨ Therapeutic Night Cream – нічний догляд для міцних капілярів! ✨
+🌿 Формула для чутливої та куперозної шкіри:
+💧 Зміцнює судини та капіляри
+🌸 Підтримує стабільну циркуляцію крові
+🛡️ Освітлює пігментацію та знімає подразнення
+⚡ Зменшує набряки та реактивність шкіри
+🌟 Відновлює ліпідний баланс та дарує комфорт
+💚 Результат – спокійна, рівна та доглянута шкіра щоранку!
+📌 Активні компоненти:
+🌺 Екстракт магнолії – протизапальна дія, зменшення подразнень
+🌱 Поліпептидний комплекс – активізує обмін речовин та зміцнює тканини
+💧 Гіалуронова кислота – глибоке зволоження та еластичність
+🥑 Олія авокадо та жожоба – живлення та відновлення бар’єру
+📌 Показання до застосування:
+Купероз та розацеа
+Судинна сітка та почервоніння
+Реактивна та суха шкіра
+Порушення мікроциркуляції
+📌 Спосіб використання:  
+Нанести крем на очищену шкіру обличчя перед сном. Рівномірно розподілити по всій поверхні для максимального ефекту.
+✔️ Характеристики продукту:
+Тип: Нічний крем для чутливої шкіри
+Об’єм: 230 мл
+Призначення: Зміцнення судин, зволоження, освітлення пігментації, зняття подразнень
+Тип шкіри: Чутлива, суха, куперозна
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Therapeutic Night Cream – твій must-have для міцних капілярів та спокійної шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>802-1</t>
+  </si>
+  <si>
+    <t>802-1(1)</t>
+  </si>
+  <si>
+    <t>Зміцнювальний Денний крем для чутливої, куперозної шкіри SPF 20 - 230 мл</t>
+  </si>
+  <si>
+    <t>✨ Strengthening Day Cream SPF 20 – щоденний захист та комфорт! ✨
+🌿 Професійна формула для проблемної шкіри:
+☀️ Захист від UVA/UVB-променів завдяки SPF 20
+🌸 Зміцнює капіляри та судини
+💧 Зменшує почервоніння та подразнення
+🛡️ Натуральні екстракти магнолії та шафрану для комплексного догляду
+⚡ Відновлює ліпідний баланс та підтримує мікроциркуляцію
+💚 Результат – спокійна, рівна та доглянута шкіра протягом дня!
+📌 Показання до застосування:
+Купероз та розацеа
+Судинні сітки та зірочки
+Реактивна та суха шкіра
+Приливний рум’янець
+Порушення мікроциркуляції
+Локальні запалення
+📌 Активні компоненти:
+🌺 Екстракт магнолії та шафрану – протизапальна та освітлююча дія
+☀️ Комплекс UVA/UVB-фільтрів – сонцезахисний ефект
+🥑 Олії ши, аргани та нони – живлення та відновлення бар’єру
+🌿 Escin ß-Sitosterol Phtosome®, ескулін, рутин – зміцнення судинної системи
+💧 Гіалуронова кислота та пептиди – зволоження та підвищення еластичності
+⚡ Кофеїн та CM-Naringenin-Chalcone – стимуляція мікроциркуляції
+📌 Спосіб використання:  
+Нанести крем на очищену шкіру обличчя щоранку. Рівномірно розподілити по всій поверхні, уникаючи зони навколо очей.
+✔️ Характеристики продукту:
+Тип: Денний крем для чутливої шкіри
+Об’єм: 230 мл
+Призначення: Зміцнення судин, зменшення почервонінь, освітлення пігментації, захист SPF 20
+Тип шкіри: Чутлива, суха, куперозна
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Strengthening Day Cream SPF 20 – твій must-have для щоденного захисту та здорової шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>801</t>
+  </si>
+  <si>
+    <t>801(1)</t>
+  </si>
+  <si>
+    <t>Інтенсивна зміцнювальний маска "розкішна магнолія" 300 мл</t>
+  </si>
+  <si>
+    <t>807(1)</t>
+  </si>
+  <si>
+    <t>807</t>
+  </si>
+  <si>
+    <t>✨ Luxury Magnolia Mask – інтенсивне зміцнення та комфорт! ✨
+🌿 Формула для чутливої та схильної до почервоніння шкіри:
+💧 Заспокоює реактивну та роздратовану шкіру
+🌸 Зміцнює судинну стінку та знижує їх реактивність
+🛡️ Відновлює гідроліпідну мантію та бар’єрні функції
+⚡ Виражено зволожує та тонізує
+🌟 Сприяє загоєнню дрібних тріщин та мікропошкоджень
+💚 Результат – спокійна, міцна та сяюча шкіра після кожного застосування!
+📌 Показання до застосування:
+Купероз та розацеа
+Судинна сітка та зірочки
+Почервоніння та приливний рум’янець
+Порушення мікроциркуляції
+Суха та чутлива шкіра
+📌 Активні компоненти:
+🌺 MAXnolia та гідролат гамамелісу – протизапальна та заспокійлива дія
+🌱 Escin ß-Sitosterol Phtosome, ескулін, рутин – зміцнення судин
+💧 Unisooth ST-32, бета-глюкан, д-пантеніл триацетат – зволоження та відновлення
+🌸 Ацетил-тетрапептиди та пальмітол трипептид-8 – регенерація та підвищення еластичності
+🛡️ Екстракти імбиру, лакриці та гарпагофітуму – антиоксидантна та протизапальна дія
+⚡ PINOLUMIN PWD, CM-Naringenin-Chalcone – освітлення та вирівнювання тону
+📌 Спосіб використання:  
+Нанести маску на чисту шкіру обличчя, залишити на 10–15 хвилин, після чого змити теплою водою. Використовувати 1–2 рази на тиждень.
+✔️ Характеристики продукту:
+Тип: Зміцнювальна маска для обличчя
+Об’єм: 300 мл
+Призначення: Зміцнення судин, зволоження, заспокоєння, освітлення
+Тип шкіри: Чутлива, суха, куперозна
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Luxury Magnolia Mask – твій must-have для міцної та сяючої шкіри без почервонінь! 🌟</t>
+  </si>
+  <si>
+    <t>Нейроседативний бустер для чутливої та куперозної шкіри 10 мл</t>
+  </si>
+  <si>
+    <t>10 мл</t>
+  </si>
+  <si>
+    <t>804</t>
+  </si>
+  <si>
+    <t>804(1)</t>
+  </si>
+  <si>
+    <t>✨ Neuro-Calm Booster – інтенсивна підтримка судин та спокій шкіри! ✨
+🌿 Висококонцентрована формула для проблемної та реактивної шкіри:
+💧 Зменшує нервову реакцію на зовнішні подразники
+🌸 Усуває нейрогенне запалення та почервоніння
+🛡️ Зміцнює стінки судин та зменшує їх проникність
+⚡ Покращує мікроциркуляцію крові та лімфовідтік
+🌟 Відновлює еластичність та міцність судин
+💚 Результат – спокійна, рівна та доглянута шкіра без судинних проявів!
+📌 Показання до застосування:
+Купероз та розацеа
+Судинна сітка та зірочки
+Почервоніння та роздратована шкіра
+Реактивна та чутлива шкіра
+Приливний рум’янець
+Порушення мікроциркуляції
+📌 Активні компоненти:
+🌺 MAXnolia та Anasensyl LS 9322 – заспокійлива та протизапальна дія
+🌱 Escin ß-Sitosterol Phtosome, ескулін, рутин – зміцнення судинної системи
+💧 Гіалуронова кислота та бета-глюкан – глибоке зволоження та відновлення
+⚡ Endothelyol та кофеїн – стимуляція мікроциркуляції
+🌸 Ацетил-тетрапептиди та пальмітол трипептид-8 – регенерація та підвищення еластичності
+🌟 CM-Naringenin-Chalcone та PINOLUMIN PWD – зменшення реактивності та освітлення тону
+📌 Спосіб використання:  
+Нанести кілька крапель бустера на очищену шкіру обличчя, особливо на ділянки з судинними проявами. Використовувати щодня перед нанесенням крему.
+✔️ Характеристики продукту:
+Тип: Інтенсивна сироватка-бустер
+Об’єм: 10 мл
+Призначення: Зміцнення судин, зменшення почервонінь, заспокоєння
+Тип шкіри: Чутлива, куперозна, реактивна
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Neuro-Calm Booster – твій must-have для боротьби з куперозом та відновлення спокою шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>Зміцнювалиний 2х-фазний Тонер для чутливої та куперозної шкіри 500 мл</t>
+  </si>
+  <si>
+    <t>✨ Strengthening 2-Phase Toner – щоденний догляд та комфорт! ✨
+🌿 Формула без спирту для делікатної шкіри:
+💧 Швидко заспокоює подразнення та зменшує почервоніння
+🌸 Знімає набряки та відновлює бар’єр шкіри
+🛡️ Зміцнює судини та капіляри
+⚡ Вирівнює тон та підтримує баланс мікробіому
+🌟 Дарує свіжість та здоровий вигляд щодня
+💚 Результат – спокійна, рівна та доглянута шкіра без куперозу!
+📌 Ключові компоненти:
+🌱 Гідролізат гамамелісу + квіткова вода – заспокоює та звужує пори
+⚡ Есцин + кофеїн – покращують мікроциркуляцію та знімають набряки
+💧 Пантенол + бісаболол – зволоження та відновлення
+🌸 Ніацинамід – вирівнює тон шкіри
+🌿 Пребіотики – підтримують баланс мікробіому
+🌺 Екстракт камелії – додаткове заспокоєння
+📌 Переваги:
+Зміцнення судин та зменшення куперозу
+Усунення набряків та почервонінь
+Відновлення захисного бар’єру
+📌 Спосіб використання:  
+Перед застосуванням струсити. Нанести тонер на ватний диск та протерти обличчя вранці й ввечері після очищення.
+✔️ Характеристики продукту:
+Тип: Двофазний тонер для обличчя
+Об’єм: 500 мл
+Призначення: Заспокоєння, зміцнення судин, зменшення почервонінь
+Тип шкіри: Чутлива, суха, куперозна
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Strengthening 2-Phase Toner – твій must-have для щоденного комфорту та здорової шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>810</t>
+  </si>
+  <si>
+    <t>810(1)</t>
+  </si>
+  <si>
+    <t>Міцелярний очищувальний крем-гель для чутливої, куперозної шкіри 500 мл</t>
+  </si>
+  <si>
+    <t>✨ Smart4Derma Micellar Cream-Gel – ніжне очищення та захист! ✨
+🌿 Формула для делікатного догляду:
+💧 Дбайливо очищує та видаляє макіяж без подразнень
+🌸 Заспокоює та зменшує почервоніння
+🛡️ Захищає від окислювального стресу
+⚡ Стимулює синтез колагену та підтримує пружність
+🌟 Зберігає природний гідроліпідний баланс
+💚 Результат – чиста, свіжа та доглянута шкіра щодня!
+📌 Переваги:
+М’яке очищення та видалення макіяжу
+Заспокійлива та антиоксидантна дія
+Стимуляція синтезу колагену
+Підтримка природного балансу шкіри
+📌 Активні компоненти:
+🌺 Водорозчинна арганова олія – делікатне очищення
+🌸 Екстракт магнолії (Maxnolia) – антиоксидантний захист
+🌱 Пептид Skinasensyl – зменшення чутливості
+☕ Кофеїн – стимуляція мікроциркуляції
+🌼 Екстракти женьшеню, ромашки та інші фітоекстракти – живлення та відновлення
+💧 Вітамін Е та гліцерин – зволоження та еластичність
+📌 Спосіб використання:  
+Нанести на вологу шкіру, легко помасажувати та змити водою. Використовувати вранці та ввечері.
+✔️ Характеристики продукту:
+Тип: Міцелярний очищувальний крем-гель
+Об’єм: 500 мл
+Призначення: Очищення, заспокоєння, зміцнення судин, антиоксидантний захист
+Тип шкіри: Чутлива, суха, куперозна
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Smart4Derma Micellar Cream-Gel – твій must-have для ніжного очищення та здорової шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>808</t>
+  </si>
+  <si>
+    <t>808(1)</t>
+  </si>
+  <si>
+    <t>Вдосконалювальний Крем з ретинолом та церамідами 230 мл</t>
+  </si>
+  <si>
+    <t>✨ Advanced Retinol &amp; Ceramide Cream – нічне відновлення та омолодження! ✨
+🌿 Передова антивікова формула:
+💎 Мікрокапсульований ретинол – контрольована нічна ексфоліація без подразнень
+🌸 Цераміди – відновлення епідермального бар’єру та захист від втрати вологи
+💧 Гіалуронат натрію та рослинні олії – глибоке зволоження та живлення
+🛡️ ПДРН та Lipobelle Soyaglycone – стимуляція регенерації та синтезу колагену
+🌟 RetiSTAR та рослинний ретинол – потужна антивікова дія
+💚 Результат – пружна, гладка та сяюча шкіра щоранку!
+📌 Дія крему:
+Розгладжує статичні та мімічні зморшки
+Відновлює пружність та еластичність
+Покращує колір обличчя та коригує постакне
+Забезпечує оптимальне зволоження
+Зміцнює дерма-епідермальне сполучення
+📌 Показання:
+Фото- та хроностаріння
+Зморшки та знижений тонус
+Тьмяний колір та гіперпігментація
+Профілактика біостаріння
+Догляд після інвазивних процедур
+📌 Спосіб використання:  
+Рекомендовано для нічного застосування на віковій шкірі. Нанести на очищене обличчя та шию перед сном, рівномірно розподілити легкими рухами.
+✔️ Характеристики продукту:
+Тип: Антивіковий нічний крем
+Об’єм: 230 мл
+Призначення: Омолодження, освітлення, зволоження, відновлення бар’єру
+Тип шкіри: Зріла, суха, комбінована
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Advanced Retinol &amp; Ceramide Cream – твій must-have для молодої та сяючої шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>731-1</t>
+  </si>
+  <si>
+    <t>731-1(1)</t>
   </si>
 </sst>
 </file>
@@ -5717,9 +6894,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5731,9 +6905,6 @@
     <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5743,12 +6914,186 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Відсотковий" xfId="1" builtinId="5"/>
     <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -6033,25 +7378,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K158"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" style="13" customWidth="1"/>
-    <col min="2" max="2" width="74.77734375" style="10" customWidth="1"/>
-    <col min="3" max="3" width="16" style="10" customWidth="1"/>
-    <col min="4" max="4" width="14.88671875" style="10" customWidth="1"/>
-    <col min="5" max="5" width="20.5546875" style="10" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" style="10" customWidth="1"/>
-    <col min="7" max="7" width="12" style="10" customWidth="1"/>
-    <col min="8" max="8" width="18.88671875" style="10" customWidth="1"/>
-    <col min="9" max="9" width="21.109375" style="10" customWidth="1"/>
-    <col min="10" max="10" width="44" style="10" customWidth="1"/>
-    <col min="11" max="11" width="18" style="13" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="10"/>
+    <col min="1" max="1" width="12" style="12" customWidth="1"/>
+    <col min="2" max="2" width="37.44140625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="16" style="9" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" style="9" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" style="9" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" style="9" customWidth="1"/>
+    <col min="7" max="7" width="12" style="9" customWidth="1"/>
+    <col min="8" max="8" width="18.88671875" style="9" customWidth="1"/>
+    <col min="9" max="9" width="21.109375" style="9" customWidth="1"/>
+    <col min="10" max="10" width="56" style="9" customWidth="1"/>
+    <col min="11" max="11" width="18" style="12" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="7" customFormat="1" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
@@ -6081,18 +7426,18 @@
       <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="13" t="s">
         <v>649</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="14" t="s">
         <v>650</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="14" t="s">
         <v>653</v>
       </c>
       <c r="D2" s="8">
@@ -6105,27 +7450,27 @@
       <c r="G2" s="8">
         <v>10</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="14" t="s">
         <v>652</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="14" t="s">
         <v>657</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="J2" s="14" t="s">
         <v>651</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="K2" s="15" t="s">
         <v>649</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>655</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="14" t="s">
         <v>654</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="14" t="s">
         <v>658</v>
       </c>
       <c r="D3" s="8">
@@ -6138,27 +7483,27 @@
       <c r="G3" s="8">
         <v>25</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="14" t="s">
         <v>657</v>
       </c>
-      <c r="J3" s="16" t="s">
+      <c r="J3" s="14" t="s">
         <v>656</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="K3" s="15" t="s">
         <v>655</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="13" t="s">
         <v>660</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="14" t="s">
         <v>659</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="14" t="s">
         <v>658</v>
       </c>
       <c r="D4" s="8">
@@ -6171,27 +7516,27 @@
       <c r="G4" s="8">
         <v>35</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="H4" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="14" t="s">
         <v>657</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="J4" s="14" t="s">
         <v>661</v>
       </c>
-      <c r="K4" s="17" t="s">
+      <c r="K4" s="15" t="s">
         <v>660</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="13" t="s">
         <v>663</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="14" t="s">
         <v>662</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="14" t="s">
         <v>658</v>
       </c>
       <c r="D5" s="8">
@@ -6204,21 +7549,21 @@
       <c r="G5" s="8">
         <v>31</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="14" t="s">
         <v>664</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="I5" s="14" t="s">
         <v>657</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" s="14" t="s">
         <v>665</v>
       </c>
-      <c r="K5" s="17" t="s">
+      <c r="K5" s="15" t="s">
         <v>663</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>668</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -6246,12 +7591,12 @@
       <c r="J6" s="8" t="s">
         <v>667</v>
       </c>
-      <c r="K6" s="18" t="s">
+      <c r="K6" s="16" t="s">
         <v>668</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="11" t="s">
         <v>670</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -6277,12 +7622,12 @@
       <c r="J7" s="8" t="s">
         <v>671</v>
       </c>
-      <c r="K7" s="18" t="s">
+      <c r="K7" s="16" t="s">
         <v>670</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="11" t="s">
         <v>674</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -6308,12 +7653,12 @@
       <c r="J8" s="8" t="s">
         <v>675</v>
       </c>
-      <c r="K8" s="18" t="s">
+      <c r="K8" s="16" t="s">
         <v>674</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="11" t="s">
         <v>677</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -6339,12 +7684,12 @@
       <c r="J9" s="8" t="s">
         <v>678</v>
       </c>
-      <c r="K9" s="18" t="s">
+      <c r="K9" s="16" t="s">
         <v>677</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="11" t="s">
         <v>680</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -6370,12 +7715,12 @@
       <c r="J10" s="8" t="s">
         <v>681</v>
       </c>
-      <c r="K10" s="18" t="s">
+      <c r="K10" s="16" t="s">
         <v>680</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="11" t="s">
         <v>683</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -6401,12 +7746,12 @@
       <c r="J11" s="8" t="s">
         <v>684</v>
       </c>
-      <c r="K11" s="18" t="s">
+      <c r="K11" s="16" t="s">
         <v>683</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="11" t="s">
         <v>687</v>
       </c>
       <c r="B12" s="8" t="s">
@@ -6432,12 +7777,12 @@
       <c r="J12" s="8" t="s">
         <v>686</v>
       </c>
-      <c r="K12" s="18" t="s">
+      <c r="K12" s="16" t="s">
         <v>687</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="11" t="s">
         <v>689</v>
       </c>
       <c r="B13" s="8" t="s">
@@ -6463,12 +7808,12 @@
       <c r="J13" s="8" t="s">
         <v>690</v>
       </c>
-      <c r="K13" s="18" t="s">
+      <c r="K13" s="16" t="s">
         <v>689</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="11" t="s">
         <v>693</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -6494,12 +7839,12 @@
       <c r="J14" s="8" t="s">
         <v>692</v>
       </c>
-      <c r="K14" s="18" t="s">
+      <c r="K14" s="16" t="s">
         <v>693</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="11" t="s">
         <v>696</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -6525,12 +7870,12 @@
       <c r="J15" s="8" t="s">
         <v>697</v>
       </c>
-      <c r="K15" s="18" t="s">
+      <c r="K15" s="16" t="s">
         <v>696</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="11" t="s">
         <v>699</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -6556,12 +7901,12 @@
       <c r="J16" s="8" t="s">
         <v>700</v>
       </c>
-      <c r="K16" s="18" t="s">
+      <c r="K16" s="16" t="s">
         <v>699</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="11" t="s">
         <v>702</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -6587,12 +7932,12 @@
       <c r="J17" s="8" t="s">
         <v>703</v>
       </c>
-      <c r="K17" s="18" t="s">
+      <c r="K17" s="16" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="11" t="s">
         <v>705</v>
       </c>
       <c r="B18" s="8" t="s">
@@ -6618,12 +7963,12 @@
       <c r="J18" s="8" t="s">
         <v>706</v>
       </c>
-      <c r="K18" s="18" t="s">
+      <c r="K18" s="16" t="s">
         <v>705</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="11" t="s">
         <v>708</v>
       </c>
       <c r="B19" s="8" t="s">
@@ -6649,12 +7994,12 @@
       <c r="J19" s="8" t="s">
         <v>709</v>
       </c>
-      <c r="K19" s="18" t="s">
+      <c r="K19" s="16" t="s">
         <v>708</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="11" t="s">
         <v>710</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -6680,12 +8025,12 @@
       <c r="J20" s="8" t="s">
         <v>711</v>
       </c>
-      <c r="K20" s="18" t="s">
+      <c r="K20" s="16" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="11" t="s">
         <v>713</v>
       </c>
       <c r="B21" s="8" t="s">
@@ -6711,12 +8056,12 @@
       <c r="J21" s="8" t="s">
         <v>714</v>
       </c>
-      <c r="K21" s="18" t="s">
+      <c r="K21" s="16" t="s">
         <v>713</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="11" t="s">
         <v>717</v>
       </c>
       <c r="B22" s="8" t="s">
@@ -6742,12 +8087,12 @@
       <c r="J22" s="8" t="s">
         <v>716</v>
       </c>
-      <c r="K22" s="18" t="s">
+      <c r="K22" s="16" t="s">
         <v>717</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="11" t="s">
         <v>720</v>
       </c>
       <c r="B23" s="8" t="s">
@@ -6773,12 +8118,12 @@
       <c r="J23" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="K23" s="18" t="s">
+      <c r="K23" s="16" t="s">
         <v>720</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="11" t="s">
         <v>722</v>
       </c>
       <c r="B24" s="8" t="s">
@@ -6804,12 +8149,12 @@
       <c r="J24" s="8" t="s">
         <v>723</v>
       </c>
-      <c r="K24" s="18" t="s">
+      <c r="K24" s="16" t="s">
         <v>722</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="11" t="s">
         <v>726</v>
       </c>
       <c r="B25" s="8" t="s">
@@ -6835,12 +8180,12 @@
       <c r="J25" s="8" t="s">
         <v>725</v>
       </c>
-      <c r="K25" s="18" t="s">
+      <c r="K25" s="16" t="s">
         <v>726</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="11" t="s">
         <v>728</v>
       </c>
       <c r="B26" s="8" t="s">
@@ -6866,12 +8211,12 @@
       <c r="J26" s="8" t="s">
         <v>729</v>
       </c>
-      <c r="K26" s="18" t="s">
+      <c r="K26" s="16" t="s">
         <v>728</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="11" t="s">
         <v>731</v>
       </c>
       <c r="B27" s="8" t="s">
@@ -6897,12 +8242,12 @@
       <c r="J27" s="8" t="s">
         <v>732</v>
       </c>
-      <c r="K27" s="18" t="s">
+      <c r="K27" s="16" t="s">
         <v>731</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="11" t="s">
         <v>734</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -6928,12 +8273,12 @@
       <c r="J28" s="8" t="s">
         <v>735</v>
       </c>
-      <c r="K28" s="18" t="s">
+      <c r="K28" s="16" t="s">
         <v>734</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="11" t="s">
         <v>737</v>
       </c>
       <c r="B29" s="8" t="s">
@@ -6959,12 +8304,12 @@
       <c r="J29" s="8" t="s">
         <v>738</v>
       </c>
-      <c r="K29" s="18" t="s">
+      <c r="K29" s="16" t="s">
         <v>737</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="11" t="s">
         <v>741</v>
       </c>
       <c r="B30" s="8" t="s">
@@ -6990,12 +8335,12 @@
       <c r="J30" s="8" t="s">
         <v>740</v>
       </c>
-      <c r="K30" s="18" t="s">
+      <c r="K30" s="16" t="s">
         <v>741</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="11" t="s">
         <v>743</v>
       </c>
       <c r="B31" s="8" t="s">
@@ -7021,12 +8366,12 @@
       <c r="J31" s="8" t="s">
         <v>744</v>
       </c>
-      <c r="K31" s="18" t="s">
+      <c r="K31" s="16" t="s">
         <v>743</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="11" t="s">
         <v>746</v>
       </c>
       <c r="B32" s="8" t="s">
@@ -7052,12 +8397,12 @@
       <c r="J32" s="8" t="s">
         <v>747</v>
       </c>
-      <c r="K32" s="18" t="s">
+      <c r="K32" s="16" t="s">
         <v>746</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="12" t="s">
+      <c r="A33" s="11" t="s">
         <v>749</v>
       </c>
       <c r="B33" s="8" t="s">
@@ -7083,12 +8428,12 @@
       <c r="J33" s="8" t="s">
         <v>750</v>
       </c>
-      <c r="K33" s="18" t="s">
+      <c r="K33" s="16" t="s">
         <v>749</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A34" s="12" t="s">
+      <c r="A34" s="11" t="s">
         <v>753</v>
       </c>
       <c r="B34" s="8" t="s">
@@ -7114,12 +8459,12 @@
       <c r="J34" s="8" t="s">
         <v>752</v>
       </c>
-      <c r="K34" s="18" t="s">
+      <c r="K34" s="16" t="s">
         <v>754</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="11" t="s">
         <v>756</v>
       </c>
       <c r="B35" s="8" t="s">
@@ -7145,12 +8490,12 @@
       <c r="J35" s="8" t="s">
         <v>757</v>
       </c>
-      <c r="K35" s="18" t="s">
+      <c r="K35" s="16" t="s">
         <v>756</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A36" s="12" t="s">
+      <c r="A36" s="11" t="s">
         <v>760</v>
       </c>
       <c r="B36" s="8" t="s">
@@ -7176,12 +8521,12 @@
       <c r="J36" s="8" t="s">
         <v>759</v>
       </c>
-      <c r="K36" s="18" t="s">
+      <c r="K36" s="16" t="s">
         <v>760</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="11" t="s">
         <v>763</v>
       </c>
       <c r="B37" s="8" t="s">
@@ -7207,12 +8552,12 @@
       <c r="J37" s="8" t="s">
         <v>762</v>
       </c>
-      <c r="K37" s="18" t="s">
+      <c r="K37" s="16" t="s">
         <v>763</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="11" t="s">
         <v>766</v>
       </c>
       <c r="B38" s="8" t="s">
@@ -7238,12 +8583,12 @@
       <c r="J38" s="8" t="s">
         <v>765</v>
       </c>
-      <c r="K38" s="18" t="s">
+      <c r="K38" s="16" t="s">
         <v>766</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A39" s="12" t="s">
+      <c r="A39" s="11" t="s">
         <v>768</v>
       </c>
       <c r="B39" s="8" t="s">
@@ -7269,12 +8614,12 @@
       <c r="J39" s="8" t="s">
         <v>769</v>
       </c>
-      <c r="K39" s="18" t="s">
+      <c r="K39" s="16" t="s">
         <v>768</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="11" t="s">
         <v>771</v>
       </c>
       <c r="B40" s="8" t="s">
@@ -7300,12 +8645,12 @@
       <c r="J40" s="8" t="s">
         <v>772</v>
       </c>
-      <c r="K40" s="18" t="s">
+      <c r="K40" s="16" t="s">
         <v>771</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="11" t="s">
         <v>774</v>
       </c>
       <c r="B41" s="8" t="s">
@@ -7331,12 +8676,12 @@
       <c r="J41" s="8" t="s">
         <v>775</v>
       </c>
-      <c r="K41" s="18" t="s">
+      <c r="K41" s="16" t="s">
         <v>774</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="11" t="s">
         <v>777</v>
       </c>
       <c r="B42" s="8" t="s">
@@ -7362,12 +8707,12 @@
       <c r="J42" s="8" t="s">
         <v>778</v>
       </c>
-      <c r="K42" s="18" t="s">
+      <c r="K42" s="16" t="s">
         <v>777</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A43" s="12" t="s">
+      <c r="A43" s="11" t="s">
         <v>781</v>
       </c>
       <c r="B43" s="8" t="s">
@@ -7393,12 +8738,12 @@
       <c r="J43" s="8" t="s">
         <v>780</v>
       </c>
-      <c r="K43" s="18" t="s">
+      <c r="K43" s="16" t="s">
         <v>781</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A44" s="12" t="s">
+      <c r="A44" s="11" t="s">
         <v>784</v>
       </c>
       <c r="B44" s="8" t="s">
@@ -7424,12 +8769,12 @@
       <c r="J44" s="8" t="s">
         <v>785</v>
       </c>
-      <c r="K44" s="18" t="s">
+      <c r="K44" s="16" t="s">
         <v>784</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A45" s="12" t="s">
+      <c r="A45" s="11" t="s">
         <v>787</v>
       </c>
       <c r="B45" s="8" t="s">
@@ -7455,12 +8800,12 @@
       <c r="J45" s="8" t="s">
         <v>788</v>
       </c>
-      <c r="K45" s="18" t="s">
+      <c r="K45" s="16" t="s">
         <v>787</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A46" s="12" t="s">
+      <c r="A46" s="11" t="s">
         <v>790</v>
       </c>
       <c r="B46" s="8" t="s">
@@ -7486,12 +8831,12 @@
       <c r="J46" s="8" t="s">
         <v>789</v>
       </c>
-      <c r="K46" s="18" t="s">
+      <c r="K46" s="16" t="s">
         <v>790</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A47" s="12" t="s">
+      <c r="A47" s="11" t="s">
         <v>791</v>
       </c>
       <c r="B47" s="8" t="s">
@@ -7517,12 +8862,12 @@
       <c r="J47" s="8" t="s">
         <v>792</v>
       </c>
-      <c r="K47" s="18" t="s">
+      <c r="K47" s="16" t="s">
         <v>791</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A48" s="12" t="s">
+      <c r="A48" s="11" t="s">
         <v>796</v>
       </c>
       <c r="B48" s="8" t="s">
@@ -7548,12 +8893,12 @@
       <c r="J48" s="8" t="s">
         <v>797</v>
       </c>
-      <c r="K48" s="18" t="s">
+      <c r="K48" s="16" t="s">
         <v>796</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A49" s="12" t="s">
+      <c r="A49" s="11" t="s">
         <v>799</v>
       </c>
       <c r="B49" s="8" t="s">
@@ -7579,12 +8924,12 @@
       <c r="J49" s="8" t="s">
         <v>800</v>
       </c>
-      <c r="K49" s="18" t="s">
+      <c r="K49" s="16" t="s">
         <v>799</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A50" s="12" t="s">
+      <c r="A50" s="11" t="s">
         <v>802</v>
       </c>
       <c r="B50" s="8" t="s">
@@ -7610,12 +8955,12 @@
       <c r="J50" s="8" t="s">
         <v>803</v>
       </c>
-      <c r="K50" s="18" t="s">
+      <c r="K50" s="16" t="s">
         <v>802</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A51" s="12" t="s">
+      <c r="A51" s="11" t="s">
         <v>805</v>
       </c>
       <c r="B51" s="8" t="s">
@@ -7641,12 +8986,12 @@
       <c r="J51" s="8" t="s">
         <v>806</v>
       </c>
-      <c r="K51" s="18" t="s">
+      <c r="K51" s="16" t="s">
         <v>805</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A52" s="12" t="s">
+      <c r="A52" s="11" t="s">
         <v>810</v>
       </c>
       <c r="B52" s="8" t="s">
@@ -7672,12 +9017,12 @@
       <c r="J52" s="8" t="s">
         <v>809</v>
       </c>
-      <c r="K52" s="18" t="s">
+      <c r="K52" s="16" t="s">
         <v>810</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A53" s="12" t="s">
+      <c r="A53" s="11" t="s">
         <v>812</v>
       </c>
       <c r="B53" s="8" t="s">
@@ -7703,12 +9048,12 @@
       <c r="J53" s="8" t="s">
         <v>813</v>
       </c>
-      <c r="K53" s="18" t="s">
+      <c r="K53" s="16" t="s">
         <v>812</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A54" s="12" t="s">
+      <c r="A54" s="11" t="s">
         <v>816</v>
       </c>
       <c r="B54" s="8" t="s">
@@ -7734,12 +9079,12 @@
       <c r="J54" s="8" t="s">
         <v>815</v>
       </c>
-      <c r="K54" s="18" t="s">
+      <c r="K54" s="16" t="s">
         <v>816</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A55" s="12" t="s">
+      <c r="A55" s="11" t="s">
         <v>818</v>
       </c>
       <c r="B55" s="8" t="s">
@@ -7765,12 +9110,12 @@
       <c r="J55" s="8" t="s">
         <v>819</v>
       </c>
-      <c r="K55" s="18" t="s">
+      <c r="K55" s="16" t="s">
         <v>818</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A56" s="12" t="s">
+      <c r="A56" s="11" t="s">
         <v>822</v>
       </c>
       <c r="B56" s="8" t="s">
@@ -7796,12 +9141,12 @@
       <c r="J56" s="8" t="s">
         <v>821</v>
       </c>
-      <c r="K56" s="18" t="s">
+      <c r="K56" s="16" t="s">
         <v>822</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A57" s="12" t="s">
+      <c r="A57" s="11" t="s">
         <v>825</v>
       </c>
       <c r="B57" s="8" t="s">
@@ -7827,12 +9172,12 @@
       <c r="J57" s="8" t="s">
         <v>824</v>
       </c>
-      <c r="K57" s="18" t="s">
+      <c r="K57" s="16" t="s">
         <v>825</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A58" s="12" t="s">
+      <c r="A58" s="11" t="s">
         <v>828</v>
       </c>
       <c r="B58" s="8" t="s">
@@ -7858,12 +9203,12 @@
       <c r="J58" s="8" t="s">
         <v>827</v>
       </c>
-      <c r="K58" s="18" t="s">
+      <c r="K58" s="16" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A59" s="12" t="s">
+      <c r="A59" s="11" t="s">
         <v>831</v>
       </c>
       <c r="B59" s="8" t="s">
@@ -7889,12 +9234,12 @@
       <c r="J59" s="8" t="s">
         <v>830</v>
       </c>
-      <c r="K59" s="18" t="s">
+      <c r="K59" s="16" t="s">
         <v>831</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A60" s="12" t="s">
+      <c r="A60" s="11" t="s">
         <v>834</v>
       </c>
       <c r="B60" s="8" t="s">
@@ -7920,12 +9265,12 @@
       <c r="J60" s="8" t="s">
         <v>833</v>
       </c>
-      <c r="K60" s="18" t="s">
+      <c r="K60" s="16" t="s">
         <v>834</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A61" s="12" t="s">
+      <c r="A61" s="11" t="s">
         <v>837</v>
       </c>
       <c r="B61" s="8" t="s">
@@ -7951,12 +9296,12 @@
       <c r="J61" s="8" t="s">
         <v>836</v>
       </c>
-      <c r="K61" s="18" t="s">
+      <c r="K61" s="16" t="s">
         <v>837</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A62" s="12" t="s">
+      <c r="A62" s="11" t="s">
         <v>839</v>
       </c>
       <c r="B62" s="8" t="s">
@@ -7982,12 +9327,12 @@
       <c r="J62" s="8" t="s">
         <v>840</v>
       </c>
-      <c r="K62" s="18" t="s">
+      <c r="K62" s="16" t="s">
         <v>839</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A63" s="12" t="s">
+      <c r="A63" s="11" t="s">
         <v>843</v>
       </c>
       <c r="B63" s="8" t="s">
@@ -8013,12 +9358,12 @@
       <c r="J63" s="8" t="s">
         <v>842</v>
       </c>
-      <c r="K63" s="18" t="s">
+      <c r="K63" s="16" t="s">
         <v>843</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A64" s="12" t="s">
+      <c r="A64" s="11" t="s">
         <v>846</v>
       </c>
       <c r="B64" s="8" t="s">
@@ -8044,12 +9389,12 @@
       <c r="J64" s="8" t="s">
         <v>845</v>
       </c>
-      <c r="K64" s="18" t="s">
+      <c r="K64" s="16" t="s">
         <v>846</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A65" s="12" t="s">
+      <c r="A65" s="11" t="s">
         <v>849</v>
       </c>
       <c r="B65" s="8" t="s">
@@ -8075,12 +9420,12 @@
       <c r="J65" s="8" t="s">
         <v>848</v>
       </c>
-      <c r="K65" s="18" t="s">
+      <c r="K65" s="16" t="s">
         <v>849</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A66" s="12" t="s">
+      <c r="A66" s="11" t="s">
         <v>853</v>
       </c>
       <c r="B66" s="8" t="s">
@@ -8106,12 +9451,12 @@
       <c r="J66" s="8" t="s">
         <v>852</v>
       </c>
-      <c r="K66" s="18" t="s">
+      <c r="K66" s="16" t="s">
         <v>853</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A67" s="12" t="s">
+      <c r="A67" s="11" t="s">
         <v>856</v>
       </c>
       <c r="B67" s="8" t="s">
@@ -8137,12 +9482,12 @@
       <c r="J67" s="8" t="s">
         <v>855</v>
       </c>
-      <c r="K67" s="18" t="s">
+      <c r="K67" s="16" t="s">
         <v>856</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A68" s="12" t="s">
+      <c r="A68" s="11" t="s">
         <v>859</v>
       </c>
       <c r="B68" s="8" t="s">
@@ -8168,12 +9513,12 @@
       <c r="J68" s="8" t="s">
         <v>858</v>
       </c>
-      <c r="K68" s="18" t="s">
+      <c r="K68" s="16" t="s">
         <v>859</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A69" s="12" t="s">
+      <c r="A69" s="11" t="s">
         <v>861</v>
       </c>
       <c r="B69" s="8" t="s">
@@ -8199,12 +9544,12 @@
       <c r="J69" s="8" t="s">
         <v>862</v>
       </c>
-      <c r="K69" s="18" t="s">
+      <c r="K69" s="16" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A70" s="12" t="s">
+      <c r="A70" s="11" t="s">
         <v>865</v>
       </c>
       <c r="B70" s="8" t="s">
@@ -8230,12 +9575,12 @@
       <c r="J70" s="8" t="s">
         <v>864</v>
       </c>
-      <c r="K70" s="18" t="s">
+      <c r="K70" s="16" t="s">
         <v>865</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A71" s="12" t="s">
+      <c r="A71" s="11" t="s">
         <v>867</v>
       </c>
       <c r="B71" s="8" t="s">
@@ -8261,12 +9606,12 @@
       <c r="J71" s="8" t="s">
         <v>868</v>
       </c>
-      <c r="K71" s="18" t="s">
+      <c r="K71" s="16" t="s">
         <v>867</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A72" s="12" t="s">
+      <c r="A72" s="11" t="s">
         <v>871</v>
       </c>
       <c r="B72" s="8" t="s">
@@ -8292,12 +9637,12 @@
       <c r="J72" s="8" t="s">
         <v>870</v>
       </c>
-      <c r="K72" s="18" t="s">
+      <c r="K72" s="16" t="s">
         <v>871</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A73" s="12" t="s">
+      <c r="A73" s="11" t="s">
         <v>874</v>
       </c>
       <c r="B73" s="8" t="s">
@@ -8323,12 +9668,12 @@
       <c r="J73" s="8" t="s">
         <v>873</v>
       </c>
-      <c r="K73" s="18" t="s">
+      <c r="K73" s="16" t="s">
         <v>874</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A74" s="12" t="s">
+      <c r="A74" s="11" t="s">
         <v>877</v>
       </c>
       <c r="B74" s="8" t="s">
@@ -8354,12 +9699,12 @@
       <c r="J74" s="8" t="s">
         <v>876</v>
       </c>
-      <c r="K74" s="18" t="s">
+      <c r="K74" s="16" t="s">
         <v>877</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A75" s="12" t="s">
+      <c r="A75" s="11" t="s">
         <v>880</v>
       </c>
       <c r="B75" s="8" t="s">
@@ -8385,12 +9730,12 @@
       <c r="J75" s="8" t="s">
         <v>879</v>
       </c>
-      <c r="K75" s="18" t="s">
+      <c r="K75" s="16" t="s">
         <v>880</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A76" s="12" t="s">
+      <c r="A76" s="11" t="s">
         <v>883</v>
       </c>
       <c r="B76" s="8" t="s">
@@ -8416,16 +9761,16 @@
       <c r="J76" s="8" t="s">
         <v>882</v>
       </c>
-      <c r="K76" s="18" t="s">
+      <c r="K76" s="16" t="s">
         <v>883</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A77" s="12" t="s">
-        <v>886</v>
+      <c r="A77" s="11" t="s">
+        <v>887</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C77" s="8" t="s">
         <v>653</v>
@@ -8445,18 +9790,18 @@
         <v>657</v>
       </c>
       <c r="J77" s="8" t="s">
-        <v>885</v>
-      </c>
-      <c r="K77" s="18" t="s">
         <v>886</v>
       </c>
+      <c r="K77" s="16" t="s">
+        <v>887</v>
+      </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A78" s="12" t="s">
-        <v>889</v>
+      <c r="A78" s="11" t="s">
+        <v>890</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>653</v>
@@ -8476,18 +9821,18 @@
         <v>657</v>
       </c>
       <c r="J78" s="8" t="s">
-        <v>888</v>
-      </c>
-      <c r="K78" s="18" t="s">
         <v>889</v>
       </c>
+      <c r="K78" s="16" t="s">
+        <v>890</v>
+      </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A79" s="12" t="s">
-        <v>892</v>
+      <c r="A79" s="11" t="s">
+        <v>893</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>653</v>
@@ -8507,18 +9852,18 @@
         <v>657</v>
       </c>
       <c r="J79" s="8" t="s">
-        <v>891</v>
-      </c>
-      <c r="K79" s="18" t="s">
         <v>892</v>
       </c>
+      <c r="K79" s="16" t="s">
+        <v>893</v>
+      </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A80" s="12" t="s">
-        <v>895</v>
+      <c r="A80" s="11" t="s">
+        <v>896</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C80" s="8" t="s">
         <v>653</v>
@@ -8538,18 +9883,18 @@
         <v>657</v>
       </c>
       <c r="J80" s="8" t="s">
-        <v>894</v>
-      </c>
-      <c r="K80" s="18" t="s">
         <v>895</v>
       </c>
+      <c r="K80" s="16" t="s">
+        <v>896</v>
+      </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A81" s="12" t="s">
-        <v>898</v>
+      <c r="A81" s="11" t="s">
+        <v>899</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>653</v>
@@ -8569,173 +9914,1517 @@
         <v>657</v>
       </c>
       <c r="J81" s="8" t="s">
-        <v>897</v>
-      </c>
-      <c r="K81" s="18" t="s">
         <v>898</v>
       </c>
+      <c r="K81" s="16" t="s">
+        <v>899</v>
+      </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A82" s="12"/>
-      <c r="B82" s="8"/>
-      <c r="C82" s="8"/>
-      <c r="D82" s="8"/>
+      <c r="A82" s="11" t="s">
+        <v>902</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>900</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="D82" s="8">
+        <v>680</v>
+      </c>
       <c r="E82" s="8"/>
       <c r="F82" s="8"/>
-      <c r="G82" s="8"/>
-      <c r="H82" s="8"/>
+      <c r="G82" s="8">
+        <v>12</v>
+      </c>
+      <c r="H82" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="I82" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J82" s="8"/>
-      <c r="K82" s="18"/>
+      <c r="J82" s="8" t="s">
+        <v>901</v>
+      </c>
+      <c r="K82" s="16" t="s">
+        <v>902</v>
+      </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A83" s="12"/>
-      <c r="B83" s="9"/>
-      <c r="C83" s="9"/>
-      <c r="D83" s="8"/>
+      <c r="A83" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>903</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="D83" s="8">
+        <v>700</v>
+      </c>
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
-      <c r="G83" s="8"/>
-      <c r="H83" s="8"/>
-      <c r="I83" s="8"/>
-      <c r="J83" s="9"/>
-      <c r="K83" s="15"/>
+      <c r="G83" s="8">
+        <v>16</v>
+      </c>
+      <c r="H83" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I83" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J83" s="8" t="s">
+        <v>904</v>
+      </c>
+      <c r="K83" s="16" t="s">
+        <v>905</v>
+      </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A84" s="12"/>
-      <c r="B84" s="9"/>
-      <c r="C84" s="9"/>
-      <c r="D84" s="8"/>
+      <c r="A84" s="11" t="s">
+        <v>907</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>906</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="D84" s="8">
+        <v>700</v>
+      </c>
       <c r="E84" s="8"/>
       <c r="F84" s="8"/>
-      <c r="G84" s="8"/>
-      <c r="H84" s="8"/>
-      <c r="I84" s="8"/>
-      <c r="J84" s="9"/>
-      <c r="K84" s="15"/>
+      <c r="G84" s="8">
+        <v>21</v>
+      </c>
+      <c r="H84" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I84" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J84" s="8" t="s">
+        <v>908</v>
+      </c>
+      <c r="K84" s="16" t="s">
+        <v>907</v>
+      </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A85" s="12"/>
-      <c r="B85" s="9"/>
-      <c r="C85" s="9"/>
-      <c r="D85" s="8"/>
+      <c r="A85" s="11" t="s">
+        <v>910</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>909</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="D85" s="8">
+        <v>860</v>
+      </c>
       <c r="E85" s="8"/>
       <c r="F85" s="8"/>
-      <c r="G85" s="8"/>
-      <c r="H85" s="8"/>
-      <c r="I85" s="8"/>
-      <c r="J85" s="9"/>
-      <c r="K85" s="15"/>
+      <c r="G85" s="8">
+        <v>23</v>
+      </c>
+      <c r="H85" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="I85" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J85" s="8" t="s">
+        <v>911</v>
+      </c>
+      <c r="K85" s="16" t="s">
+        <v>910</v>
+      </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A86" s="12"/>
-      <c r="B86" s="9"/>
-      <c r="C86" s="9"/>
-      <c r="D86" s="8"/>
+      <c r="A86" s="11" t="s">
+        <v>914</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>912</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="D86" s="8">
+        <v>720</v>
+      </c>
       <c r="E86" s="8"/>
       <c r="F86" s="8"/>
-      <c r="G86" s="8"/>
-      <c r="H86" s="8"/>
-      <c r="I86" s="8"/>
-      <c r="J86" s="9"/>
-      <c r="K86" s="15"/>
+      <c r="G86" s="8">
+        <v>24</v>
+      </c>
+      <c r="H86" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="I86" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J86" s="8" t="s">
+        <v>913</v>
+      </c>
+      <c r="K86" s="16" t="s">
+        <v>914</v>
+      </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A87" s="12"/>
-      <c r="B87" s="9"/>
-      <c r="C87" s="9"/>
-      <c r="D87" s="8"/>
+      <c r="A87" s="11" t="s">
+        <v>917</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>916</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="D87" s="8">
+        <v>1160</v>
+      </c>
       <c r="E87" s="8"/>
       <c r="F87" s="8"/>
-      <c r="G87" s="8"/>
-      <c r="H87" s="8"/>
-      <c r="I87" s="8"/>
-      <c r="J87" s="9"/>
-      <c r="K87" s="15"/>
+      <c r="G87" s="8">
+        <v>17</v>
+      </c>
+      <c r="H87" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I87" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J87" s="8" t="s">
+        <v>915</v>
+      </c>
+      <c r="K87" s="16" t="s">
+        <v>917</v>
+      </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A88" s="12"/>
-      <c r="B88" s="9"/>
-      <c r="C88" s="9"/>
-      <c r="D88" s="8"/>
+      <c r="A88" s="11" t="s">
+        <v>920</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>919</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="D88" s="8">
+        <v>680</v>
+      </c>
       <c r="E88" s="8"/>
       <c r="F88" s="8"/>
-      <c r="G88" s="8"/>
-      <c r="H88" s="8"/>
-      <c r="I88" s="8"/>
-      <c r="J88" s="9"/>
-      <c r="K88" s="15"/>
+      <c r="G88" s="8">
+        <v>15</v>
+      </c>
+      <c r="H88" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I88" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J88" s="8" t="s">
+        <v>918</v>
+      </c>
+      <c r="K88" s="16" t="s">
+        <v>920</v>
+      </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A89" s="12"/>
-      <c r="B89" s="9"/>
-      <c r="C89" s="9"/>
-      <c r="D89" s="8"/>
+      <c r="A89" s="11" t="s">
+        <v>923</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>922</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="D89" s="8">
+        <v>780</v>
+      </c>
       <c r="E89" s="8"/>
       <c r="F89" s="8"/>
-      <c r="G89" s="8"/>
-      <c r="H89" s="8"/>
-      <c r="I89" s="8"/>
-      <c r="J89" s="9"/>
-      <c r="K89" s="15"/>
+      <c r="G89" s="8">
+        <v>25</v>
+      </c>
+      <c r="H89" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I89" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J89" s="8" t="s">
+        <v>921</v>
+      </c>
+      <c r="K89" s="16" t="s">
+        <v>923</v>
+      </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A90" s="12"/>
-      <c r="B90" s="9"/>
-      <c r="C90" s="9"/>
-      <c r="D90" s="8"/>
+      <c r="A90" s="11" t="s">
+        <v>926</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>924</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="D90" s="8">
+        <v>1100</v>
+      </c>
       <c r="E90" s="8"/>
       <c r="F90" s="8"/>
-      <c r="G90" s="8"/>
-      <c r="H90" s="8"/>
-      <c r="I90" s="8"/>
-      <c r="J90" s="9"/>
-      <c r="K90" s="15"/>
+      <c r="G90" s="8">
+        <v>21</v>
+      </c>
+      <c r="H90" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I90" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J90" s="8" t="s">
+        <v>925</v>
+      </c>
+      <c r="K90" s="16" t="s">
+        <v>926</v>
+      </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A91" s="12"/>
-      <c r="B91" s="9"/>
-      <c r="C91" s="9"/>
-      <c r="D91" s="8"/>
+      <c r="A91" s="11" t="s">
+        <v>930</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>927</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="D91" s="8">
+        <v>1440</v>
+      </c>
       <c r="E91" s="8"/>
       <c r="F91" s="8"/>
-      <c r="G91" s="8"/>
-      <c r="H91" s="8"/>
-      <c r="I91" s="8"/>
-      <c r="J91" s="9"/>
-      <c r="K91" s="15"/>
+      <c r="G91" s="8">
+        <v>16</v>
+      </c>
+      <c r="H91" s="8" t="s">
+        <v>928</v>
+      </c>
+      <c r="I91" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J91" s="8" t="s">
+        <v>929</v>
+      </c>
+      <c r="K91" s="16" t="s">
+        <v>930</v>
+      </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A92" s="12"/>
-      <c r="B92" s="9"/>
-      <c r="C92" s="9"/>
-      <c r="D92" s="8"/>
+      <c r="A92" s="11" t="s">
+        <v>934</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>931</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="D92" s="8">
+        <v>680</v>
+      </c>
       <c r="E92" s="8"/>
       <c r="F92" s="8"/>
-      <c r="G92" s="8"/>
-      <c r="H92" s="8"/>
-      <c r="I92" s="8"/>
-      <c r="J92" s="9"/>
-      <c r="K92" s="15"/>
+      <c r="G92" s="8">
+        <v>17</v>
+      </c>
+      <c r="H92" s="8" t="s">
+        <v>932</v>
+      </c>
+      <c r="I92" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J92" s="8" t="s">
+        <v>933</v>
+      </c>
+      <c r="K92" s="16" t="s">
+        <v>934</v>
+      </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A93" s="12"/>
-      <c r="B93" s="9"/>
-      <c r="C93" s="9"/>
-      <c r="D93" s="8"/>
+      <c r="A93" s="11" t="s">
+        <v>937</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>935</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="D93" s="8">
+        <v>900</v>
+      </c>
       <c r="E93" s="8"/>
-      <c r="F93" s="8"/>
-      <c r="G93" s="8"/>
-      <c r="H93" s="8"/>
-      <c r="I93" s="8"/>
-      <c r="J93" s="9"/>
-      <c r="K93" s="15"/>
+      <c r="F93" s="8" t="s">
+        <v>884</v>
+      </c>
+      <c r="G93" s="8">
+        <v>19</v>
+      </c>
+      <c r="H93" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="I93" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J93" s="8" t="s">
+        <v>936</v>
+      </c>
+      <c r="K93" s="16" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A94" s="17" t="s">
+        <v>939</v>
+      </c>
+      <c r="B94" s="18" t="s">
+        <v>938</v>
+      </c>
+      <c r="C94" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D94" s="18">
+        <v>480</v>
+      </c>
+      <c r="E94" s="18"/>
+      <c r="F94" s="18"/>
+      <c r="G94" s="8">
+        <v>16</v>
+      </c>
+      <c r="H94" s="18" t="s">
+        <v>783</v>
+      </c>
+      <c r="I94" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="J94" s="18" t="s">
+        <v>940</v>
+      </c>
+      <c r="K94" s="17" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A95" s="17" t="s">
+        <v>942</v>
+      </c>
+      <c r="B95" s="18" t="s">
+        <v>941</v>
+      </c>
+      <c r="C95" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D95" s="18">
+        <v>1060</v>
+      </c>
+      <c r="E95" s="18"/>
+      <c r="F95" s="18"/>
+      <c r="G95" s="8">
+        <v>15</v>
+      </c>
+      <c r="H95" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="I95" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J95" s="18" t="s">
+        <v>943</v>
+      </c>
+      <c r="K95" s="17" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A96" s="17" t="s">
+        <v>946</v>
+      </c>
+      <c r="B96" s="18" t="s">
+        <v>944</v>
+      </c>
+      <c r="C96" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D96" s="18">
+        <v>1400</v>
+      </c>
+      <c r="E96" s="18">
+        <v>1100</v>
+      </c>
+      <c r="F96" s="18"/>
+      <c r="G96" s="8">
+        <v>25</v>
+      </c>
+      <c r="H96" s="18" t="s">
+        <v>664</v>
+      </c>
+      <c r="I96" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J96" s="18" t="s">
+        <v>945</v>
+      </c>
+      <c r="K96" s="17" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A97" s="17" t="s">
+        <v>951</v>
+      </c>
+      <c r="B97" s="18" t="s">
+        <v>948</v>
+      </c>
+      <c r="C97" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D97" s="18">
+        <v>2500</v>
+      </c>
+      <c r="E97" s="18">
+        <v>2200</v>
+      </c>
+      <c r="F97" s="18"/>
+      <c r="G97" s="8">
+        <v>15</v>
+      </c>
+      <c r="H97" s="18" t="s">
+        <v>928</v>
+      </c>
+      <c r="I97" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J97" s="18" t="s">
+        <v>949</v>
+      </c>
+      <c r="K97" s="17" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A98" s="17" t="s">
+        <v>953</v>
+      </c>
+      <c r="B98" s="18" t="s">
+        <v>952</v>
+      </c>
+      <c r="C98" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D98" s="18">
+        <v>1600</v>
+      </c>
+      <c r="E98" s="18">
+        <v>1460</v>
+      </c>
+      <c r="F98" s="18"/>
+      <c r="G98" s="8">
+        <v>21</v>
+      </c>
+      <c r="H98" s="18" t="s">
+        <v>928</v>
+      </c>
+      <c r="I98" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J98" s="18" t="s">
+        <v>955</v>
+      </c>
+      <c r="K98" s="17" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A99" s="17" t="s">
+        <v>957</v>
+      </c>
+      <c r="B99" s="18" t="s">
+        <v>956</v>
+      </c>
+      <c r="C99" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D99" s="18">
+        <v>1650</v>
+      </c>
+      <c r="E99" s="18">
+        <v>1430</v>
+      </c>
+      <c r="F99" s="18"/>
+      <c r="G99" s="8">
+        <v>26</v>
+      </c>
+      <c r="H99" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="I99" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J99" s="18" t="s">
+        <v>959</v>
+      </c>
+      <c r="K99" s="17" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A100" s="17" t="s">
+        <v>962</v>
+      </c>
+      <c r="B100" s="18" t="s">
+        <v>960</v>
+      </c>
+      <c r="C100" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D100" s="18">
+        <v>2300</v>
+      </c>
+      <c r="E100" s="18">
+        <v>1900</v>
+      </c>
+      <c r="F100" s="18"/>
+      <c r="G100" s="8">
+        <v>17</v>
+      </c>
+      <c r="H100" s="18" t="s">
+        <v>961</v>
+      </c>
+      <c r="I100" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J100" s="18" t="s">
+        <v>964</v>
+      </c>
+      <c r="K100" s="17" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A101" s="17" t="s">
+        <v>967</v>
+      </c>
+      <c r="B101" s="18" t="s">
+        <v>965</v>
+      </c>
+      <c r="C101" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D101" s="18">
+        <v>600</v>
+      </c>
+      <c r="E101" s="18">
+        <v>400</v>
+      </c>
+      <c r="F101" s="18"/>
+      <c r="G101" s="8">
+        <v>25</v>
+      </c>
+      <c r="H101" s="18" t="s">
+        <v>966</v>
+      </c>
+      <c r="I101" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J101" s="18" t="s">
+        <v>969</v>
+      </c>
+      <c r="K101" s="17" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A102" s="17" t="s">
+        <v>972</v>
+      </c>
+      <c r="B102" s="18" t="s">
+        <v>970</v>
+      </c>
+      <c r="C102" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D102" s="18">
+        <v>1600</v>
+      </c>
+      <c r="E102" s="18">
+        <v>1380</v>
+      </c>
+      <c r="F102" s="18"/>
+      <c r="G102" s="8">
+        <v>26</v>
+      </c>
+      <c r="H102" s="18" t="s">
+        <v>971</v>
+      </c>
+      <c r="I102" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J102" s="18" t="s">
+        <v>974</v>
+      </c>
+      <c r="K102" s="17" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A103" s="17" t="s">
+        <v>977</v>
+      </c>
+      <c r="B103" s="18" t="s">
+        <v>975</v>
+      </c>
+      <c r="C103" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D103" s="18">
+        <v>1100</v>
+      </c>
+      <c r="E103" s="18">
+        <v>840</v>
+      </c>
+      <c r="F103" s="18"/>
+      <c r="G103" s="8">
+        <v>17</v>
+      </c>
+      <c r="H103" s="18" t="s">
+        <v>976</v>
+      </c>
+      <c r="I103" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J103" s="18" t="s">
+        <v>979</v>
+      </c>
+      <c r="K103" s="17" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A104" s="17" t="s">
+        <v>983</v>
+      </c>
+      <c r="B104" s="18" t="s">
+        <v>981</v>
+      </c>
+      <c r="C104" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D104" s="18">
+        <v>1980</v>
+      </c>
+      <c r="E104" s="18">
+        <v>1640</v>
+      </c>
+      <c r="F104" s="18"/>
+      <c r="G104" s="8">
+        <v>19</v>
+      </c>
+      <c r="H104" s="18" t="s">
+        <v>980</v>
+      </c>
+      <c r="I104" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J104" s="18" t="s">
+        <v>984</v>
+      </c>
+      <c r="K104" s="17" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A105" s="17" t="s">
+        <v>987</v>
+      </c>
+      <c r="B105" s="18" t="s">
+        <v>985</v>
+      </c>
+      <c r="C105" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D105" s="18">
+        <v>2100</v>
+      </c>
+      <c r="E105" s="18">
+        <v>1760</v>
+      </c>
+      <c r="F105" s="18"/>
+      <c r="G105" s="8">
+        <v>25</v>
+      </c>
+      <c r="H105" s="18" t="s">
+        <v>928</v>
+      </c>
+      <c r="I105" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J105" s="18" t="s">
+        <v>986</v>
+      </c>
+      <c r="K105" s="17" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A106" s="17" t="s">
+        <v>991</v>
+      </c>
+      <c r="B106" s="18" t="s">
+        <v>989</v>
+      </c>
+      <c r="C106" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D106" s="18">
+        <v>2100</v>
+      </c>
+      <c r="E106" s="18">
+        <v>1760</v>
+      </c>
+      <c r="F106" s="18"/>
+      <c r="G106" s="8">
+        <v>18</v>
+      </c>
+      <c r="H106" s="18" t="s">
+        <v>928</v>
+      </c>
+      <c r="I106" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J106" s="18" t="s">
+        <v>990</v>
+      </c>
+      <c r="K106" s="17" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A107" s="17" t="s">
+        <v>995</v>
+      </c>
+      <c r="B107" s="18" t="s">
+        <v>993</v>
+      </c>
+      <c r="C107" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D107" s="18">
+        <v>2200</v>
+      </c>
+      <c r="E107" s="18">
+        <v>1800</v>
+      </c>
+      <c r="F107" s="18"/>
+      <c r="G107" s="8">
+        <v>9</v>
+      </c>
+      <c r="H107" s="18" t="s">
+        <v>961</v>
+      </c>
+      <c r="I107" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J107" s="18" t="s">
+        <v>996</v>
+      </c>
+      <c r="K107" s="17" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A108" s="17" t="s">
+        <v>999</v>
+      </c>
+      <c r="B108" s="18" t="s">
+        <v>997</v>
+      </c>
+      <c r="C108" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D108" s="18">
+        <v>550</v>
+      </c>
+      <c r="E108" s="18">
+        <v>360</v>
+      </c>
+      <c r="F108" s="18"/>
+      <c r="G108" s="8">
+        <v>26</v>
+      </c>
+      <c r="H108" s="18" t="s">
+        <v>998</v>
+      </c>
+      <c r="I108" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J108" s="18" t="s">
+        <v>1001</v>
+      </c>
+      <c r="K108" s="17" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A109" s="17" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B109" s="18" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C109" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D109" s="18">
+        <v>1500</v>
+      </c>
+      <c r="E109" s="18">
+        <v>1380</v>
+      </c>
+      <c r="F109" s="18"/>
+      <c r="G109" s="8">
+        <v>13</v>
+      </c>
+      <c r="H109" s="18" t="s">
+        <v>971</v>
+      </c>
+      <c r="I109" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J109" s="18" t="s">
+        <v>1003</v>
+      </c>
+      <c r="K109" s="17" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A110" s="17" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B110" s="18" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C110" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D110" s="18">
+        <v>1600</v>
+      </c>
+      <c r="E110" s="18">
+        <v>1300</v>
+      </c>
+      <c r="F110" s="18"/>
+      <c r="G110" s="8">
+        <v>18</v>
+      </c>
+      <c r="H110" s="18" t="s">
+        <v>971</v>
+      </c>
+      <c r="I110" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J110" s="18" t="s">
+        <v>1007</v>
+      </c>
+      <c r="K110" s="17" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A111" s="17" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B111" s="18" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C111" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D111" s="18">
+        <v>2800</v>
+      </c>
+      <c r="E111" s="18">
+        <v>2500</v>
+      </c>
+      <c r="F111" s="18"/>
+      <c r="G111" s="8">
+        <v>16</v>
+      </c>
+      <c r="H111" s="18" t="s">
+        <v>928</v>
+      </c>
+      <c r="I111" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J111" s="18" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K111" s="17" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A112" s="17"/>
+      <c r="B112" s="18"/>
+      <c r="C112" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D112" s="18"/>
+      <c r="E112" s="18"/>
+      <c r="F112" s="18"/>
+      <c r="G112" s="8"/>
+      <c r="H112" s="18"/>
+      <c r="I112" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J112" s="18"/>
+      <c r="K112" s="17"/>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A113" s="17"/>
+      <c r="B113" s="18"/>
+      <c r="C113" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D113" s="18"/>
+      <c r="E113" s="18"/>
+      <c r="F113" s="18"/>
+      <c r="G113" s="8"/>
+      <c r="H113" s="18"/>
+      <c r="I113" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J113" s="18"/>
+      <c r="K113" s="17"/>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A114" s="17"/>
+      <c r="B114" s="18"/>
+      <c r="C114" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D114" s="18"/>
+      <c r="E114" s="18"/>
+      <c r="F114" s="18"/>
+      <c r="G114" s="8"/>
+      <c r="H114" s="18"/>
+      <c r="I114" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J114" s="18"/>
+      <c r="K114" s="17"/>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A115" s="17"/>
+      <c r="B115" s="18"/>
+      <c r="C115" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D115" s="18"/>
+      <c r="E115" s="18"/>
+      <c r="F115" s="18"/>
+      <c r="G115" s="8"/>
+      <c r="H115" s="18"/>
+      <c r="I115" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J115" s="18"/>
+      <c r="K115" s="17"/>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A116" s="17"/>
+      <c r="B116" s="18"/>
+      <c r="C116" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D116" s="18"/>
+      <c r="E116" s="18"/>
+      <c r="F116" s="18"/>
+      <c r="G116" s="8"/>
+      <c r="H116" s="18"/>
+      <c r="I116" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J116" s="18"/>
+      <c r="K116" s="17"/>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A117" s="17"/>
+      <c r="B117" s="18"/>
+      <c r="C117" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D117" s="18"/>
+      <c r="E117" s="18"/>
+      <c r="F117" s="18"/>
+      <c r="G117" s="8"/>
+      <c r="H117" s="18"/>
+      <c r="I117" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J117" s="18"/>
+      <c r="K117" s="17"/>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A118" s="17"/>
+      <c r="B118" s="18"/>
+      <c r="C118" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D118" s="18"/>
+      <c r="E118" s="18"/>
+      <c r="F118" s="18"/>
+      <c r="G118" s="8"/>
+      <c r="H118" s="18"/>
+      <c r="I118" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J118" s="18"/>
+      <c r="K118" s="17"/>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A119" s="17"/>
+      <c r="B119" s="18"/>
+      <c r="C119" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D119" s="18"/>
+      <c r="E119" s="18"/>
+      <c r="F119" s="18"/>
+      <c r="G119" s="8"/>
+      <c r="H119" s="18"/>
+      <c r="I119" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J119" s="18"/>
+      <c r="K119" s="17"/>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A120" s="17"/>
+      <c r="B120" s="18"/>
+      <c r="C120" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D120" s="18"/>
+      <c r="E120" s="18"/>
+      <c r="F120" s="18"/>
+      <c r="G120" s="8"/>
+      <c r="H120" s="18"/>
+      <c r="I120" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J120" s="18"/>
+      <c r="K120" s="17"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A121" s="17"/>
+      <c r="B121" s="18"/>
+      <c r="C121" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D121" s="18"/>
+      <c r="E121" s="18"/>
+      <c r="F121" s="18"/>
+      <c r="G121" s="8"/>
+      <c r="H121" s="18"/>
+      <c r="I121" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J121" s="18"/>
+      <c r="K121" s="17"/>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A122" s="17"/>
+      <c r="B122" s="18"/>
+      <c r="C122" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D122" s="18"/>
+      <c r="E122" s="18"/>
+      <c r="F122" s="18"/>
+      <c r="G122" s="8"/>
+      <c r="H122" s="18"/>
+      <c r="I122" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J122" s="18"/>
+      <c r="K122" s="17"/>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A123" s="17"/>
+      <c r="B123" s="18"/>
+      <c r="C123" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D123" s="18"/>
+      <c r="E123" s="18"/>
+      <c r="F123" s="18"/>
+      <c r="G123" s="8"/>
+      <c r="H123" s="18"/>
+      <c r="I123" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J123" s="18"/>
+      <c r="K123" s="17"/>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A124" s="17"/>
+      <c r="B124" s="18"/>
+      <c r="C124" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D124" s="18"/>
+      <c r="E124" s="18"/>
+      <c r="F124" s="18"/>
+      <c r="G124" s="8"/>
+      <c r="H124" s="18"/>
+      <c r="I124" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J124" s="18"/>
+      <c r="K124" s="17"/>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A125" s="17"/>
+      <c r="B125" s="18"/>
+      <c r="C125" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D125" s="18"/>
+      <c r="E125" s="18"/>
+      <c r="F125" s="18"/>
+      <c r="G125" s="8"/>
+      <c r="H125" s="18"/>
+      <c r="I125" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J125" s="18"/>
+      <c r="K125" s="17"/>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A126" s="17"/>
+      <c r="B126" s="18"/>
+      <c r="C126" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D126" s="18"/>
+      <c r="E126" s="18"/>
+      <c r="F126" s="18"/>
+      <c r="G126" s="8"/>
+      <c r="H126" s="18"/>
+      <c r="I126" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J126" s="18"/>
+      <c r="K126" s="17"/>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A127" s="17"/>
+      <c r="B127" s="18"/>
+      <c r="C127" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D127" s="18"/>
+      <c r="E127" s="18"/>
+      <c r="F127" s="18"/>
+      <c r="G127" s="8"/>
+      <c r="H127" s="18"/>
+      <c r="I127" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J127" s="18"/>
+      <c r="K127" s="17"/>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A128" s="17"/>
+      <c r="B128" s="18"/>
+      <c r="C128" s="18"/>
+      <c r="D128" s="18"/>
+      <c r="E128" s="18"/>
+      <c r="F128" s="18"/>
+      <c r="G128" s="8"/>
+      <c r="H128" s="18"/>
+      <c r="I128" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J128" s="18"/>
+      <c r="K128" s="17"/>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A129" s="17"/>
+      <c r="B129" s="18"/>
+      <c r="C129" s="18"/>
+      <c r="D129" s="18"/>
+      <c r="E129" s="18"/>
+      <c r="F129" s="18"/>
+      <c r="G129" s="8"/>
+      <c r="H129" s="18"/>
+      <c r="I129" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J129" s="18"/>
+      <c r="K129" s="17"/>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A130" s="17"/>
+      <c r="B130" s="18"/>
+      <c r="C130" s="18"/>
+      <c r="D130" s="18"/>
+      <c r="E130" s="18"/>
+      <c r="F130" s="18"/>
+      <c r="G130" s="8"/>
+      <c r="H130" s="18"/>
+      <c r="I130" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J130" s="18"/>
+      <c r="K130" s="17"/>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A131" s="17"/>
+      <c r="B131" s="18"/>
+      <c r="C131" s="18"/>
+      <c r="D131" s="18"/>
+      <c r="E131" s="18"/>
+      <c r="F131" s="18"/>
+      <c r="G131" s="8"/>
+      <c r="H131" s="18"/>
+      <c r="I131" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J131" s="18"/>
+      <c r="K131" s="17"/>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A132" s="17"/>
+      <c r="B132" s="18"/>
+      <c r="C132" s="18"/>
+      <c r="D132" s="18"/>
+      <c r="E132" s="18"/>
+      <c r="F132" s="18"/>
+      <c r="G132" s="8"/>
+      <c r="H132" s="18"/>
+      <c r="I132" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J132" s="18"/>
+      <c r="K132" s="17"/>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A133" s="17"/>
+      <c r="B133" s="18"/>
+      <c r="C133" s="18"/>
+      <c r="D133" s="18"/>
+      <c r="E133" s="18"/>
+      <c r="F133" s="18"/>
+      <c r="G133" s="8"/>
+      <c r="H133" s="18"/>
+      <c r="I133" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J133" s="18"/>
+      <c r="K133" s="17"/>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A134" s="17"/>
+      <c r="B134" s="18"/>
+      <c r="C134" s="18"/>
+      <c r="D134" s="18"/>
+      <c r="E134" s="18"/>
+      <c r="F134" s="18"/>
+      <c r="G134" s="8"/>
+      <c r="H134" s="18"/>
+      <c r="I134" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J134" s="18"/>
+      <c r="K134" s="17"/>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A135" s="17"/>
+      <c r="B135" s="18"/>
+      <c r="C135" s="18"/>
+      <c r="D135" s="18"/>
+      <c r="E135" s="18"/>
+      <c r="F135" s="18"/>
+      <c r="G135" s="8"/>
+      <c r="H135" s="18"/>
+      <c r="I135" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="J135" s="18"/>
+      <c r="K135" s="17"/>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G136" s="8"/>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G137" s="8"/>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G138" s="8"/>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G139" s="8"/>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G140" s="8"/>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G141" s="8"/>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G142" s="8"/>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G143" s="8"/>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G144" s="8"/>
+    </row>
+    <row r="145" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G145" s="8"/>
+    </row>
+    <row r="146" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G146" s="8"/>
+    </row>
+    <row r="147" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G147" s="8"/>
+    </row>
+    <row r="148" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G148" s="8"/>
+    </row>
+    <row r="149" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G149" s="8"/>
+    </row>
+    <row r="150" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G150" s="8"/>
+    </row>
+    <row r="151" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G151" s="8"/>
+    </row>
+    <row r="152" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G152" s="8"/>
+    </row>
+    <row r="153" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G153" s="8"/>
+    </row>
+    <row r="154" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G154" s="8"/>
+    </row>
+    <row r="155" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G155" s="8"/>
+    </row>
+    <row r="156" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G156" s="8"/>
+    </row>
+    <row r="157" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G157" s="8"/>
+    </row>
+    <row r="158" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G158" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K93" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="G2:G93">
+    <cfRule type="cellIs" dxfId="23" priority="22" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="23" operator="lessThan">
+      <formula>20</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="24" operator="greaterThanOrEqual">
+      <formula>20</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G94">
+    <cfRule type="cellIs" dxfId="20" priority="19" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="20" operator="lessThan">
+      <formula>20</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="21" operator="greaterThanOrEqual">
+      <formula>20</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G95">
+    <cfRule type="cellIs" dxfId="17" priority="16" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="17" operator="lessThan">
+      <formula>20</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="18" operator="greaterThanOrEqual">
+      <formula>20</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G96">
+    <cfRule type="cellIs" dxfId="14" priority="13" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="lessThan">
+      <formula>20</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="15" operator="greaterThanOrEqual">
+      <formula>20</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G97">
+    <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="lessThan">
+      <formula>20</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="12" operator="greaterThanOrEqual">
+      <formula>20</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G98">
+    <cfRule type="cellIs" dxfId="8" priority="7" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="lessThan">
+      <formula>20</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="9" operator="greaterThanOrEqual">
+      <formula>20</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G99:G113">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
+      <formula>20</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="greaterThanOrEqual">
+      <formula>20</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G114:G158">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>

--- a/price.xlsx
+++ b/price.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ПРОЕКТ AI\ЛИЧНЫЕ НАРАБОТКИ\AI Skin Lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B16B6B9B-0AC8-4E74-847B-DDFC89E7B5DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE93772-918F-4498-B0F6-AC4F610BE092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-1512" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Зручна таблиця" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2291" uniqueCount="1014">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2296" uniqueCount="1018">
   <si>
     <t>Артикул</t>
   </si>
@@ -6761,6 +6761,49 @@
   </si>
   <si>
     <t>731-1(1)</t>
+  </si>
+  <si>
+    <t>Вдосконалювальний Пептидний крем для періорбітальної зони очей 100 мл</t>
+  </si>
+  <si>
+    <t>✨ Advanced Peptide Eye Cream – технологія “рідких пептидів” для сяючого погляду! ✨
+🌿 Інноваційна формула для делікатної зони навколо очей:
+💎 Ефективно розгладжує тонкі лінії та зморшки
+⚡ Забезпечує миттєвий ліфтинг та моделювання контуру
+🌸 Синхронізує природні процеси відновлення шкіри
+🛡️ Запобігає антиоксидантному стресу
+🚀 Потужні провідникові системи доставляють активні комплекси безпосередньо до клітин
+💚 Результат – свіжий, молодий та сяючий погляд щодня!
+📌 Показання:
+Фото- та хроностаріння
+Зморшки та знижений тонус шкіри
+Гіперпігментація
+Профілактика біостаріння
+Догляд після інвазивних процедур
+📌 Активні компоненти:
+🌱 Декапептиди та олігопептиди – стимуляція синтезу колагену
+💧 Гіалуронат натрію – глибоке зволоження
+🥭 Олія манго та макадамії – живлення та відновлення бар’єру
+🌊 Екстракт фукуса – антиоксидантний захист
+⚡ Аргирелін та нанопептиди – зменшення мімічних зморшок
+🌸 Shadownyl та Agefinity – освітлення та ревіталізація
+🛡️ ПДРН та Inoveol EGCG – регенерація та захист
+📌 Спосіб використання:  
+Нанести невелику кількість крему на чисту шкіру навколо очей. Використовувати щодня вранці та ввечері.
+✔️ Характеристики продукту:
+Тип: Пептидний крем для періорбітальної зони
+Об’єм: 100 мл
+Призначення: Ліфтинг, омолодження, освітлення, зволоження
+Тип шкіри: Чутлива, суха, зріла
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Advanced Peptide Eye Cream – твій must-have для сяючого та молодого погляду! 🌟</t>
+  </si>
+  <si>
+    <t>733</t>
+  </si>
+  <si>
+    <t>733(1)</t>
   </si>
 </sst>
 </file>
@@ -10885,21 +10928,37 @@
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A112" s="17"/>
-      <c r="B112" s="18"/>
+      <c r="A112" s="17" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B112" s="18" t="s">
+        <v>1014</v>
+      </c>
       <c r="C112" s="18" t="s">
         <v>653</v>
       </c>
-      <c r="D112" s="18"/>
-      <c r="E112" s="18"/>
+      <c r="D112" s="18">
+        <v>1600</v>
+      </c>
+      <c r="E112" s="18">
+        <v>1380</v>
+      </c>
       <c r="F112" s="18"/>
-      <c r="G112" s="8"/>
-      <c r="H112" s="18"/>
+      <c r="G112" s="8">
+        <v>18</v>
+      </c>
+      <c r="H112" s="18" t="s">
+        <v>29</v>
+      </c>
       <c r="I112" s="18" t="s">
         <v>657</v>
       </c>
-      <c r="J112" s="18"/>
-      <c r="K112" s="17"/>
+      <c r="J112" s="18" t="s">
+        <v>1015</v>
+      </c>
+      <c r="K112" s="17" t="s">
+        <v>1017</v>
+      </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="17"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ПРОЕКТ AI\ЛИЧНЫЕ НАРАБОТКИ\AI Skin Lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE93772-918F-4498-B0F6-AC4F610BE092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B311886-7D53-48F6-8509-F47A02FF9192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-1512" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,8 +19,17 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Зручна таблиця'!$A$1:$K$93</definedName>
   </definedNames>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -29,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2296" uniqueCount="1018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2421" uniqueCount="1101">
   <si>
     <t>Артикул</t>
   </si>
@@ -6804,6 +6813,790 @@
   </si>
   <si>
     <t>733(1)</t>
+  </si>
+  <si>
+    <t>Омолоджуюча маска "Едельвейс" 300 мл</t>
+  </si>
+  <si>
+    <t>✨ Edelweiss Stem Cell Mask – інтелектуальне омолодження! ✨
+🌿 Концентрована формула зі стовбуровими клітинами едельвейсу:
+💎 Розгладжує тонкі лінії та зморшки
+🌸 Забезпечує виражений ліфтинг-ефект
+💧 Стимулює оновлення клітин та підтримує їх структуру
+🛡️ Зміцнює дерма-епідермальне сполучення
+🌟 Має потужну цитопротекторну дію
+💚 Результат – пружна, сяюча та оновлена шкіра з ефектом перетворення!
+📌 Показання:
+Фото- та хроностаріння
+Зморшки та тьмяний колір обличчя
+Гіперпігментація
+Знижений тонус шкіри
+Профілактика біостаріння
+Догляд після інвазивних процедур
+📌 Активні компоненти:
+🌱 PhytoStem Cells Edelweiss – стовбурові клітини едельвейсу для омолодження
+🌸 Екстракт Ambiaty – регенерація та захист
+💧 Гіалуронат натрію – глибоке зволоження
+🌿 ПДРН – стимуляція відновлення клітин
+🌺 Alpine Rose Active та екстракт рису – антиоксидантний захист та ревіталізація
+📌 Спосіб використання:  
+Нанести маску на чисту шкіру обличчя, залишити на 10–15 хвилин, після чого змити теплою водою. Використовувати 1–2 рази на тиждень.
+✔️ Характеристики продукту:
+Тип: Омолоджуюча концентрована маска
+Об’єм: 300 мл
+Призначення: Ліфтинг, омолодження, освітлення, зволоження, захист
+Тип шкіри: Зріла, суха, комбінована
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Edelweiss Stem Cell Mask – твій must-have для миттєвого омолодження та сяючої шкіри!</t>
+  </si>
+  <si>
+    <t>736</t>
+  </si>
+  <si>
+    <t>736(1)</t>
+  </si>
+  <si>
+    <t>Хронобіологічний енергетичний ліфтінг-крем 230 мл</t>
+  </si>
+  <si>
+    <t>✨ ChronoBio Energy Lifting Cream – нічне перезавантаження для твоєї шкіри! ✨
+🌙 Інноваційна хронобіологічна формула з комплексами Chronodyn та DermCom:
+⚡ Максимально стимулює енергообмін у клітинах
+💎 Забезпечує активне відновлення та видимий ліфтинг обличчя, шиї та підборіддя
+🌸 Усуває обвисання та в’ялість (птоз)
+💧 Підвищує пружність і відновлює тонус
+🛡️ Захищає від фото- та хроностаріння
+💚 Результат – підтягнута, сяюча та енергійна шкіра щоранку!
+📌 Показання до застосування:
+Уповільнення старіння без радикальних методів
+Запобігання динамічним та статичним зморшкам
+Фото- та хроностаріння
+Тьмяний колір обличчя
+Гіперпігментація
+Знижений тонус та вікова шкіра
+Догляд після інвазивних процедур
+📌 Ключові активні компоненти:
+🌱 Chronodyn + DermCom – стимуляція клітинного обміну та регенерації
+🥥 Олії сезаму, пасіфлори, моної де Таїті – живлення та відновлення бар’єру
+💧 Гіалуронат натрію + Hyaluronic Filling Spheres™ – глибоке зволоження та заповнення зморшок
+🌸 Juveleven™ peptide solution, Replexium, Agefinity™ – омолодження та ревіталізація
+🌿 Фукогель, екстракт цикорію, камедь акації – тонізація та захист
+⚡ Кофеїн та сквален – енергія та антиоксидантний захист
+📌 Спосіб використання:  
+Нанести крем на очищену шкіру обличчя, шиї та підборіддя перед сном. Використовувати регулярно для максимального ефекту ліфтингу та відновлення.
+✔️ Характеристики продукту:
+Тип: Нічний хронобіологічний ліфтинг-крем
+Об’єм: 230 мл
+Призначення: Ліфтинг, омолодження, відновлення тонусу, зволоження
+Тип шкіри: Зріла, суха, комбінована
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 ChronoBio Energy Lifting Cream – твій must-have для нічного відновлення та сяючої шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>708-1</t>
+  </si>
+  <si>
+    <t>708-1(1)</t>
+  </si>
+  <si>
+    <t>Передовий денний крем SPF 30 Золоті водорості  230 мл</t>
+  </si>
+  <si>
+    <t>✨ Golden Algae Day Cream SPF 30 – щоденний захист та омолодження! ✨
+🌿 Інноваційна антиоксидантна формула:
+☀️ UVA/UVB-фільтри – надійний захист від сонця та фотостаріння
+🌸 Екстракт золотих водоростей – потужна антиоксидантна дія та відновлення клітин
+💎 Пептидний комплекс – реструктуризація та зміцнення шкіри
+💧 Гіалуронова кислота та олія жожоба – миттєве зволоження та пружність
+💚 Результат – рівний тон, захист від зморшок та сяюча шкіра щодня!
+📌 Основні ефекти:
+Миттєве зволоження та підвищення пружності
+Запобігання динамічним та статичним зморшкам
+Захист від фотостаріння
+Вирівнювання тону обличчя
+Підвищення тонусу вікової шкіри
+📌 Показання:
+Щоденний догляд за віковою шкірою
+Фото- та хроностаріння
+Гіперпігментація та тьмяний колір обличчя
+Догляд після інвазивних процедур та контурної пластики
+📌 Ключові компоненти:
+🌺 ANTILEUKINE™ 6 (екстракт золотих водоростей) – антиоксидантний захист
+🌱 Пептиди (Argireline®, Replexium, Marine Filling Spheres™) – омолодження та ліфтинг
+💧 Hydagen® Aquaporin, гіалуронова кислота – глибоке зволоження
+🥥 Олії жожоба, ши та женьшеня – живлення та відновлення
+🌸 Agefinity™, Sensityl™ – ревіталізація та захист від стресу
+📌 Спосіб використання:  
+Нанести крем на очищену шкіру обличчя щоранку. Рівномірно розподілити по всій поверхні, уникаючи зони навколо очей.
+✔️ Характеристики продукту:
+Тип: Антиоксидантний денний крем з SPF
+Об’єм: 230 мл
+Призначення: Захист SPF 30, омолодження, зволоження, вирівнювання тону
+Тип шкіри: Чутлива, суха, комбінована, вікова
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Golden Algae Day Cream SPF 30 – твій must-have для щоденного захисту та сяйва! 🌟</t>
+  </si>
+  <si>
+    <t>707</t>
+  </si>
+  <si>
+    <t>707(1)</t>
+  </si>
+  <si>
+    <t>Заповнювальна маска-біоміметик з вітаміном С</t>
+  </si>
+  <si>
+    <t>✨ Biomimetic Vitamin C Mask – інноваційне омолодження та сяйво! ✨
+🌿 Ультрасучасна формула з багатоформним вітаміном С та 8 пептидами:
+💎 Помітно омолоджує та коригує всі прояви вікових змін
+🌸 Освітлює пігментні плями та вирівнює тон
+💧 Інтенсивно зволожує завдяки гіалуроновій кислоті
+🛡️ Глибоко ревіталізує та відновлює структуру шкіри
+🌟 Пом’якшує видимість ліній і зморшок
+💚 Результат – гладка, сяюча та оновлена шкіра з ефектом перетворення!
+📌 Показання до застосування:
+Щоденний догляд для уповільнення старіння
+Запобігання динамічним та статичним зморшкам
+Фото- та хроностаріння
+Тьмяний колір обличчя
+Гіперпігментація
+Знижений тонус шкіри
+Догляд після інвазивних процедур
+📌 Ключові активні компоненти:
+☀️ Вітамін С у кількох формах – антиоксидантний захист та освітлення
+🌱 8 пептидів (Replexium, Juveleven™, Collalift® 18 та ін.) – стимуляція синтезу колагену та омолодження
+💧 Гіалуронат натрію + Hyaluronic Filling Spheres™ – глибоке зволоження та заповнення зморшок
+🌸 Ceramosides™ Hp та олія насіння квітки Алтеї – відновлення бар’єру та захист від втрати вологи
+⚡ Agefinity™, Easyliance, Collamung® Onp – ревіталізація та ліфтинг
+🌿 Екстракт цикорію, амінокислоти (лізин, серин, валін), пантенол – живлення та відновлення
+📌 Спосіб використання:  
+Нанести маску на очищену шкіру обличчя, залишити на 10–15 хвилин, після чого змити теплою водою. Використовувати 1–2 рази на тиждень.
+✔️ Характеристики продукту:
+Тип: Заповнювальна маска-біоміметик
+Об’єм: 50 мл
+Призначення: Омолодження, освітлення, ревіталізація, зволоження
+Тип шкіри: Зріла, суха, комбінована
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Biomimetic Vitamin C Mask – твій must-have для сяючої та молодої шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>713</t>
+  </si>
+  <si>
+    <t>713(1)</t>
+  </si>
+  <si>
+    <t>Реструктурирующая маска для зони навколо очей з екстрактом кави арабіка Smart4Derma Arabica eye mask contour relief 100 мл</t>
+  </si>
+  <si>
+    <t>710(1)</t>
+  </si>
+  <si>
+    <t>710</t>
+  </si>
+  <si>
+    <t>Енерго-генеруючий бустер «Золоті водорослі» Smart4Derma Booster-Elixir Golden Seaweed 10 мл</t>
+  </si>
+  <si>
+    <t>✨ Golden Seaweed Booster – трансдермальна енергія молодості! ✨
+🌿 Інноваційна формула з екстрактом золотих водоростей:
+⚡ Активує мітохондріальний енергообмін у клітинах
+💎 Підвищує реструктуризацію шкірного матриксу
+🌸 Зміцнює дермо-епідермальне з’єднання
+💧 Зменшує пігментні плями та гусячі лапки
+🌟 Розгладжує зморшки в Y-зоні шиї
+💚 Результат – підтягнута, сяюча та оновлена шкіра без ознак втоми!
+📌 Показання до застосування:
+Щоденний догляд для уповільнення старіння
+Профілактика зморшок
+Фото- та хроностаріння
+Тьмяний колір обличчя
+Гіперпігментація та знижений тонус
+Вікова шкіра
+Відновлення після інвазивних процедур
+📌 Ключові активні компоненти:
+🌺 Екстракт золотих водоростей (ANTILEUKINE™) – антиоксидантний захист та омолодження
+🌱 Екстракти червоних та японських водоростей, зеленого чаю – ревіталізація та тонізація
+💧 Гіалуронат натрію + Hydagen® Aquaporin – глибоке зволоження
+⚡ Пептиди (Replexium, Agefinity™, Juveleven™, Argireline®) – стимуляція синтезу колагену та ліфтинг
+🌿 ПДРН, біотин трипептид-1, олігопептиди, деекапептид-9 – регенерація та відновлення
+🌸 Амінокислоти (лізин, серин, валін) + пантенол – живлення та захист
+📌 Спосіб використання:  
+Нанести кілька крапель бустера на очищену шкіру обличчя та шиї. Використовувати щодня перед нанесенням крему.
+✔️ Характеристики продукту:
+Тип: Трансдермальний бустер-еліксир
+Об’єм: 30 мл / 50 мл (залежно від упаковки)
+Призначення: Омолодження, освітлення, ліфтинг, зволоження
+Тип шкіри: Зріла, суха, комбінована
+Бренд: Smart Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Golden Seaweed Booster – твій must-have для інтенсивної боротьби зі старінням та сяючої шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>705</t>
+  </si>
+  <si>
+    <t>705(1)</t>
+  </si>
+  <si>
+    <t>Интеллектуальный заполнительный Гидромист 500 мл</t>
+  </si>
+  <si>
+    <t>✨ Інтелектуальний Гідроміст – багатофункціональне зволоження та anti-age догляд! ✨
+🌿 Формула для інтенсивного відновлення:
+💧 Миттєве та тривале зволоження
+🌸 Нормалізація pH та вирівнювання тону шкіри
+💎 Зменшення глибини зморшок та профілактика їх появи
+🛡️ Захист від сухості та еритеми
+🌟 Ефект сяйва зсередини
+💚 Результат – свіжа, гладка та сяюча шкіра щодня!
+📌 Ключові переваги:
+Морський інгредієнт Antarcticine® з криопротекторними властивостями
+💧 Гіалуронат натрію – глибоке зволоження
+🌱 Hydagen® Aquaporin, SPAR'AGE™, морські мінерали, амінокислоти, пантенол – живлення, захист та відновлення
+📌 Показання до застосування:
+Щоденний догляд за віковою шкірою
+Профілактика старіння
+Відновлення після косметологічних процедур
+Борьба з гіперпігментацією та зниженим тонусом
+✔️ Характеристики продукту:
+Тип: Інтелектуальний заповнювальний гідроміст
+Об’єм: 500 мл
+Призначення: Зволоження, омолодження, освітлення, захист
+Тип шкіри: Всі типи, особливо суха та зріла
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Intelligent HydroMist – твій must-have для сяючої та зволоженої шкіри щодня! 🌟</t>
+  </si>
+  <si>
+    <t>702</t>
+  </si>
+  <si>
+    <t>702(1)</t>
+  </si>
+  <si>
+    <t>Гель для вмивання "Активатор Енергії" з кислотами 500 мл</t>
+  </si>
+  <si>
+    <t>701</t>
+  </si>
+  <si>
+    <t>701(1)</t>
+  </si>
+  <si>
+    <t>✨ Energy Activator Cleansing Gel – перезарядка для твоєї шкіри! ✨
+🌿 Інноваційна формула з кислотами та ензимами:
+⚡ Перезаряджає клітини шкіри на 27%
+💧 Відновлює pH-баланс та підтримує оптимальний рівень зволоження
+🌸 Комплекс із трьох кислот у розчині електролітів – м’яке, але ефективне очищення
+🛡️ Компонент OXY 229 PF активує мітохондріальне дихання для енергії клітин
+💎 Дарує свіжість, сяйво та рівний тон
+💚 Результат – чиста, енергійна та сяюча шкіра після кожного вмивання!
+📌 Ключові активні компоненти:
+🌱 Гліколева, піруватна та ферулова кислоти – ексфоліація та вирівнювання тону
+⚡ OXY 229 PF – активація клітинної енергії
+💧 Гіалуронат натрію, сечовина, Д-пантенол – глибоке зволоження та відновлення
+🌸 Екстракт гібіскуса, морські мінерали – антиоксидантний захист та тонізація
+🌟 Hydagen® Aquaporin, Lys'lastine™ V, Perlaura® – підтримка водного балансу та пружності
+🧬 Амінокислоти (аргінін, лізин, серин) – живлення та регенерація
+📌 Показання до застосування:
+Уповільнення старіння без радикальних методів
+Запобігання появі зморшок
+Фото- та хроностаріння
+Тьмяний колір обличчя
+Гіперпігментація
+Знижений тонус шкіри
+Догляд після інвазивних процедур
+📌 Як застосовувати:  
+Нанести невелику кількість гелю на вологу шкіру, розподілити по масажних лініях, легко промасажувати та змити теплою водою. Використовувати щодня для максимального ефекту.
+✔️ Характеристики продукту:
+Тип: Інноваційний гель для вмивання
+Об’єм: 500 мл
+Призначення: Очищення, омолодження, відновлення енергії клітин
+Тип шкіри: Вікова, комбінована, проблемна
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Energy Activator Cleansing Gel – твій must-have для щоденного енергетичного догляду! 🌟</t>
+  </si>
+  <si>
+    <t>Розкішний живильний крем з церамідами 230 мл</t>
+  </si>
+  <si>
+    <t>✨ Luxury Ceramide Cream – глибоке живлення та сяйво! ✨
+🌿 Інноваційна формула для щоденного догляду:
+💧 Технологія подвійного зволоження – миттєвий та тривалий ефект
+🌸 Церамиди – зміцнення захисного бар’єру шкіри
+🥥 Комплекс Multifeel – інтенсивне живлення та відновлення
+🌟 Пантенол – заспокоює та регенерує
+💎 Бореться з проявами старіння, зменшує глибину зморшок
+💚 Результат – гладка, сяюча та здорова шкіра щодня!
+📌 Підходить для:
+Всі типи шкіри
+Суха та зневоднена шкіра
+Зріла та чутлива шкіра
+Відновлення після косметичних процедур
+✔️ Характеристики продукту:
+Тип: Живильний крем з церамідами
+Об’єм: 50 мл / 100 мл / 230 мл (залежно від упаковки)
+Призначення: Зволоження, живлення, відновлення, омолодження
+Тип шкіри: Всі типи, особливо суха та зріла
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Luxury Ceramide Cream – твій must-have для глибокого живлення та сяючої шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>522</t>
+  </si>
+  <si>
+    <t>522(1)</t>
+  </si>
+  <si>
+    <t>Невагомий Крем-гель SPF 50 - 230 мл</t>
+  </si>
+  <si>
+    <t>✨ Weightless SPF 50 Gel-Cream – щоденний захист та комфорт! ✨
+🌿 Інноваційна формула для щоденного догляду:
+☀️ Потужний УФ-захист: комплекс PolyFructol Plus та X50 Skin Barrier запобігає фотостарінню та передчасним зморшкам
+💧 Глибоке зволоження: технологія PatcH2O та Hydagen® Aquaporine працюють на клітинному рівні
+🛡️ Антиоксидантний захист: DN-Age нейтралізує вільні радикали та стрес
+🌸 Легка текстура: миттєво вбирається без липкості, даруючи комфорт
+💚 Результат – пружна, гладка та захищена шкіра з ефектом свіжості після кожного нанесення!
+📌 Показання до застосування:
+Щоденний догляд для всіх типів шкіри
+Захист від фото- та хроностаріння
+Профілактика зморшок та пігментації
+Зволоження та підтримка клітинного балансу
+📌 Як застосовувати:  
+Наносити на чисту, суху шкіру обличчя за 20 хвилин до виходу на сонце. Використовувати щодня для максимального захисту.
+✔️ Характеристики продукту:
+Тип: Крем-гель з SPF
+Об’єм: 50 мл / 230 мл
+Рівень захисту: SPF 50+ PA++++
+Призначення: Захист, зволоження, антиоксидантний догляд
+Тип шкіри: Всі типи
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Weightless SPF 50 Gel-Cream – твій must-have для щоденного захисту та сяючої шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>523</t>
+  </si>
+  <si>
+    <t>523(1)</t>
+  </si>
+  <si>
+    <t>Сонцезахисний ультразволожувальний крем SPF50 з олією канабісу 230 мл</t>
+  </si>
+  <si>
+    <t>✨ Cannabis Ultra-Hydrating Sunscreen SPF 50 – повний спектр захисту та сяйво! ✨
+🌿 Інноваційна формула для щоденного догляду:
+☀️ SPF50 + широкоспектральний UVA/UVB-захист – профілактика фотостаріння та збереження колагену
+💧 Гіалуронова кислота + PolyFructol Plus – глибоке зволоження та підтримка водного балансу
+🌸 Екстракт азіатської центелли – заспокоює та відновлює бар’єрні функції
+🛡️ Токоферол ацетат та аскорбіл глюкозид – антиоксидантний захист від стресу та вільних радикалів
+🌟 Легка текстура з матуючим ефектом – без відчуття тяжкості
+💚 Результат – пружна, сяюча та захищена шкіра щодня!
+📌 Показання до застосування:
+Суха та чутлива шкіра
+Подразнення та зневоднення
+Перші ознаки старіння
+Зниження бар’єрної функції
+📌 Спосіб застосування:  
+Наносити на очищену шкіру обличчя вранці, за 20 хвилин до виходу на сонце. Використовувати щодня для максимального ефекту.
+✔️ Характеристики продукту:
+Тип: Сонцезахисний крем з SPF
+Об’єм: 230 мл
+Рівень захисту: SPF 50+ PA++++
+Призначення: Захист, зволоження, антиоксидантний догляд
+Тип шкіри: Суха, чутлива, зріла
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Cannabis Ultra-Hydrating Sunscreen SPF 50 – твій must-have для щоденного захисту та сяйва шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>516</t>
+  </si>
+  <si>
+    <t>516(1)</t>
+  </si>
+  <si>
+    <t>Крем-маска глибоке зволоження 300 мл</t>
+  </si>
+  <si>
+    <t>✨ Deep Moisture Cream-Mask – миттєве та пролонговане зволоження! ✨
+🌿 Легка пептидна формула з системою доставки X50:
+💧 Створює депо вологи в шкірі для подвійного ефекту гідратації
+🌸 Відновлює бар’єрні функції завдяки комплексу церамідів
+🛡️ Заспокоює подразнення та зменшує сухість
+⚡ Підвищує тонус та еластичність шкіри
+🌟 Дарує свіжість і сяйво вже після першого застосування
+💚 Результат – шкіра стає пружною, гладкою та сяючою!
+📌 Показання до застосування:
+Суха та чутлива шкіра
+Подразнення та зневоднення
+Зниження тонусу
+Перші ознаки старіння
+Відновлення та захист шкіри
+📌 Ключові активні компоненти:
+💧 Hydagen® Aquaporin, гіалуронат натрію, PolyFructol Plus – інтенсивне зволоження
+🌱 Олія авокадо, примули, екстракт центелли – живлення та відновлення
+🌸 Д-пантенол, ніацинамід, бета-глюкан – заспокійливий та регенеруючий ефект
+🛡️ iActive Ceramide, X50 Skin Barrier, токоферол, ферулова кислота, убіхінон – антиоксидантний захист та зміцнення бар’єру
+⚡ Амінокислоти та магнезіум аскорбіл фосфат – стимуляція клітинного оновлення
+✔️ Характеристики продукту:
+Тип: Крем-маска для глибокого зволоження
+Об’єм: 300 мл
+Призначення: Зволоження, живлення, відновлення, антиоксидантний захист
+Тип шкіри: Суха, чутлива, зріла
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Deep Moisture Cream-Mask – твій must-have для миттєвого та тривалого зволоження! 🌟</t>
+  </si>
+  <si>
+    <t>513</t>
+  </si>
+  <si>
+    <t>513(1)</t>
+  </si>
+  <si>
+    <t>Зволожувальний дренажний крем від темних кіл та набряків 100 мл</t>
+  </si>
+  <si>
+    <t>✨ Drainage Moisturizing Eye Cream – сяючий та відпочилий погляд! ✨
+🌿 Активна формула для зони навколо очей:
+💧 Інтенсивне зволоження та відновлення бар’єрної функції
+🌸 Освітлення темних кіл завдяки екстракту водоростей
+🛡️ Зменшення набряків завдяки рутину та ескуліну
+⚡ Комплекс інкапсульованих пептидів – стимуляція синтезу білків для пружності
+🌟 Живлення та захист завдяки олії авокадо та примули
+💚 Результат – світліший тон, менші набряки та пружна шкіра навколо очей!
+📌 Активні компоненти:
+🌱 Екстракт водоростей – покращує кровообіг та освітлює темні кола
+🌸 Рутин + ескулін – протинабрякова дія
+💧 Інулін – підвищує пружність та еластичність
+⚡ Інкапсульовані пептиди – стимулюють синтез кератину, філагрину та лорекину
+🥑 Олія авокадо та примули вечірньої – живлення та захист
+🌟 Токоферол + магнезіум аскорбіл фосфат – антиоксидантний щит
+📌 Показання до застосування:
+Суха та чутлива шкіра навколо очей
+Подразнення та зневоднення
+Зниження тонусу
+Перші ознаки старіння
+Відновлення бар’єрної функції
+✔️ Характеристики продукту:
+Тип: Зволожувальний дренажний крем для очей
+Об’єм: 100 мл
+Призначення: Зволоження, протинабрякова дія, освітлення темних кіл
+Тип шкіри: Суха, чутлива, зріла
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Drainage Moisturizing Eye Cream – твій must-have для сяючого та відпочилого погляду! 🌟</t>
+  </si>
+  <si>
+    <t>507</t>
+  </si>
+  <si>
+    <t>507(1)</t>
+  </si>
+  <si>
+    <t>Дренажна освітлююча маска Глабрідин для очей 100 мл Smart 4 Derma</t>
+  </si>
+  <si>
+    <t>✨ Glabridin Eye Drainage Mask – професійний догляд для сяючого погляду! ✨
+🌿 Інноваційна формула для переорбітальної зони:
+💎 Зміцнює судини та покращує мікроциркуляцію
+⚡ Активізує виведення заліза та білірубіну, зменшуючи тьмяність
+🌸 Освітлює шкіру та зменшує набряки нижніх повік
+💧 Забезпечує глибоке зволоження та підвищує еластичність
+🛡️ Відновлює бар’єрну функцію шкіри
+💚 Результат – свіжий, відпочилий та сяючий погляд!
+📌 Показання до застосування:
+Суха та чутлива шкіра навколо очей
+Подразнення та зневоднення
+Зниження тонусу
+Перші ознаки старіння
+Відновлення та захист
+📌 Активні компоненти:
+🌱 Shadownyl, Рутин, Ескулін – зміцнення судин та протинабрякова дія
+🌸 Inoveol EGCG, екстракти зеленого чаю та каштана – антиоксидантний захист та покращення кровообігу
+💧 PolyFructol Plus, Hydagen® Aquaporin, інулін – глибоке зволоження та підтримка водного балансу
+🛡️ X50® Skin Barrier та комплекс пептидів – стимуляція синтезу кератину та філагрину, відновлення бар’єру
+✔️ Характеристики продукту:
+Тип: Дренажна освітлююча маска для очей
+Об’єм: 100 мл
+Призначення: Зволоження, освітлення, протинабрякова дія, відновлення
+Бренд: Smart4Derma (🇺🇦 Україна + 🇩🇪 Німеччина)
+🌟 Glabridin Eye Mask – твій must-have для сяючого та відпочилого погляду! 🌟</t>
+  </si>
+  <si>
+    <t>511(1)</t>
+  </si>
+  <si>
+    <t>511</t>
+  </si>
+  <si>
+    <t>Зволожуючий гель-тонер для сіяння шкіри 500 мл</t>
+  </si>
+  <si>
+    <t>✨ Polyfructol Toner Bright Skin – професійне сяйво та зволоження! ✨
+🌿 Інноваційна формула для атонічної та зневодненої шкіри:
+💧 Hydagen® Aquaporin + PatcH2O – інтенсивне зволоження та утримання вологи
+🌸 Екстракти ромашки та шавлії – заспокоюють, знімають почервоніння та дискомфорт
+🌟 Ніацинамід – вирівнює тон та додає природне сяйво
+🛡️ Puricare POE LS 9727 + PolyFructol Plus – захист від негативного впливу навколишнього середовища
+⚡ Д-пантенол та натрій гіалуронат – пружність та відчуття свіжості
+💚 Результат – тривале зволоження до 24 годин, свіжий вигляд та сяюча шкіра!
+📌 Результати використання:
+Тривале зволоження на 24 години
+Свіжий та сяючий вигляд шкіри
+Активація процесів оновлення клітин та синтезу колагену
+Захист та покращення бар’єрної функції
+✔️ Характеристики продукту:
+Тип: Зволожуючий гель-тонер
+Об’єм: 500 мл
+Призначення: Зволоження, сяйво, захист
+Тип шкіри: Суха, тьмяна, атонічна
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Polyfructol Toner Bright Skin – твій must-have для сяючої та зволоженої шкіри щодня! 🌟</t>
+  </si>
+  <si>
+    <t>502</t>
+  </si>
+  <si>
+    <t>502(1)</t>
+  </si>
+  <si>
+    <t>Smart4Derma Шовкова ензимна пудра з гранулами жожоба 120 г</t>
+  </si>
+  <si>
+    <t>✨ Silk Enzyme Powder – делікатне очищення та сяйво! ✨
+🌿 Унікальна формула для щоденного догляду:
+💎 Ензими ефективно видаляють забруднення та відмерлі клітини
+🌸 Гранули олії жожоба м’яко відлущують, не травмуючи шкіру
+💧 Центелла азіатська покращує текстуру та еластичність
+🛡️ Трегалоза, алантоїн та екстракт ромашки – зволоження та заспокійливий ефект
+🌟 Створює захисну плівку, підтримуючи гідроліпідний баланс
+💚 Результат – чиста, гладка та сяюча шкіра без подразнень!
+📌 Основні переваги:
+Очищення та вирівнювання тону
+Підтримка природного балансу вологи
+Заспокійливий ефект при запаленнях
+Захист від зовнішніх факторів
+✔️ Характеристики продукту:
+Тип: Ензимна пудра для очищення
+Об’єм: 100–120 г (залежно від упаковки)
+Призначення: Очищення, відлущування, зволоження, захист
+Тип шкіри: Чутлива, комбінована, суха
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Silk Enzyme Powder – твій must-have для делікатного очищення та сяючої шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>521</t>
+  </si>
+  <si>
+    <t>521(1)</t>
+  </si>
+  <si>
+    <t>Пінка для сухої та чутливої шкіри з канабісом Hydro Aloe Mousse 480 мл</t>
+  </si>
+  <si>
+    <t>✨ Luxury Gentle Cleansing Foam – делікатне очищення та комфорт! ✨
+🌿 Спеціальна формула для щоденного догляду:
+💧 Легка текстура ефективно видаляє забруднення та макіяж
+🌸 Вирівнює поверхню шкіри без відчуття стягнутості
+🛡️ Заспокоює подразнення та зменшує запалення
+🌟 Відновлює бар’єрні функції та дарує відчуття свіжості
+💚 Результат – чиста, м’яка та сяюча шкіра після кожного очищення!
+📌 Активні компоненти:
+🌱 Олія коноплі та чіа – насичені омега-кислотами, зменшують подразнення
+🌸 Екстракт ромашки – заспокоює чутливу шкіру
+💧 Інулін та Hydagen® Aquaporin – глибоке зволоження та еластичність
+🛡️ Д-пантенол та бетаїн – відновлення та захист бар’єру
+📌 Показання до застосування:
+Суха та чутлива шкіра
+Подразнення та зневоднення
+Зниження тонусу
+Перші ознаки старіння
+Відновлення бар’єрної функції
+✔️ Характеристики продукту:
+Тип: Очищувальна піна для обличчя
+Об’єм: 150 мл / 200 мл (залежно від упаковки)
+Призначення: Делікатне очищення, зволоження, відновлення
+Тип шкіри: Суха, чутлива
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Luxury Gentle Cleansing Foam – твій must-have для щоденного ніжного очищення та сяйва шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>503</t>
+  </si>
+  <si>
+    <t>503(1)</t>
+  </si>
+  <si>
+    <t>Розкішне молочко для вмивання ОМЕГА  500 мл ніжне очищення</t>
+  </si>
+  <si>
+    <t>✨ Gentle Omega Cleansing – делікатне очищення та регенерація! ✨
+🌿 Багатофункціональна формула для щоденного догляду:
+💧 Ефективно видаляє макіяж та всі типи забруднень (водо- і жиророзчинні)
+🌸 Відновлює та інтенсивно регенерує шкіру
+🛡️ Попереджає подразнення та зневоднення
+⚡ Підтримує водно-ліпідний баланс
+🌟 Активізує кровообіг та покращує тургор
+💚 Результат – чиста, свіжа та сяюча шкіра без відчуття сухості!
+📌 Активні компоненти:
+🌱 Олія коноплі та чіа – насичені омега-кислотами, живлення та протизапальна дія
+🌸 Екстракт ромашки та центелли азіатської – заспокоюють та відновлюють
+💧 Hydagen® Aquaporin, PatcH2O, сечовина – інтенсивне зволоження та утримання вологи
+🛡️ Д-пантенол та натрій аскорбіл фосфат – антиоксидантний захист та регенерація
+📌 Показання до застосування:
+Суха та чутлива шкіра
+Подразнення та зневоднення
+Зниження тонусу
+Перші ознаки старіння
+Відновлення та захист бар’єрної функції
+✔️ Характеристики продукту:
+Тип: Очищуючий засіб для обличчя
+Об’єм: 150 мл / 200 мл (залежно від упаковки)
+Призначення: Очищення, регенерація, зволоження
+Тип шкіри: Суха, чутлива
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Gentle Omega Cleansing – твій must-have для щоденного делікатного очищення та сяйва шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>501</t>
+  </si>
+  <si>
+    <t>501(1)</t>
+  </si>
+  <si>
+    <t>Порозвужувальна себорегулювальна маска «босвелія» 230 мл</t>
+  </si>
+  <si>
+    <t>✨ Boswellia Clay Mask Herbal Pore Control – чиста та збалансована шкіра! ✨
+🌿 Активна формула для проблемної шкіри:
+💧 Зменшує пори та контролює себум
+🌸 Знижує запалення, подразнення та почервоніння
+🛡️ Нормалізує мікробіом шкіри та створює антисептичний бар’єр
+⚡ Має тонізуючу та регенеруючу дію
+🌟 Покращує стан проблемної шкіри та дарує відчуття свіжості
+💚 Результат – матова, рівна та здорова шкіра без надлишку себуму!
+📌 Показання до застосування:
+Акне 1–3 ступеня, постакне
+Розширені пори, нерівний тон
+Атопічний дерматит, екзема, псоріаз
+Подразнення та свербіж
+📌 Активні компоненти:
+🌱 Олії виноградних та персикових кісточок – живлення та відновлення
+🌸 Каолін – глибоке очищення та себорегуляція
+💧 Д-пантенол, гліцерин, ніацинамід – зволоження та регенерація
+🛡️ Екстракти епілобіуму, прополісу, каштану та календули – протизапальна дія
+⚡ Кофеїн, Bosexil, Bix'Activ – контроль себуму та тонізуючий ефект
+🌟 Бісаболол, алантоїн, ацетил тетрапептид-15 – заспокоюють та відновлюють
+✔️ Характеристики продукту:
+Тип: Себорегулююча порозвужуюча маска
+Об’єм: 50 мл
+Призначення: Очищення, себорегуляція, протизапальна дія
+Тип шкіри: Проблемна, жирна, комбінована
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Boswellia Clay Mask – твій must-have для чистої та збалансованої шкіри без недоліків! 🌟</t>
+  </si>
+  <si>
+    <t>408</t>
+  </si>
+  <si>
+    <t>408(1)</t>
+  </si>
+  <si>
+    <t>Нічний себорегулювальний флюїд «Азеламід» 230 мл</t>
+  </si>
+  <si>
+    <t>✨ Azelamid Night Fluid – нічна терапія проти акне! ✨
+🌿 Лікувальна формула для проблемної шкіри:
+💧 Глибоко очищає пори та зменшує виділення себуму
+🌸 Усуває запалення та почервоніння
+🛡️ Відновлює баланс мікробіому та бар’єрні функції
+⚡ Заспокоює подразнення та прискорює регенерацію
+🌟 Дарує рівний тон та здоровий вигляд шкіри
+💚 Результат – чиста, матова та спокійна шкіра вже після кількох застосувань!
+📌 Активні компоненти:
+🌱 Bix'Activ та прополіс – пригнічують P.Acne, забезпечують антибактеріальний ефект
+🌸 Екстракт епілобіуму – регулює активність сальних залоз та мікробіом
+💧 Азелаїнова та саліцилова кислоти – відлущують та очищають пори
+🛡️ Босвелія – покращує мікроциркуляцію та зменшує почервоніння
+🌟 Ніацинамід та D-пантенол – заспокоюють та стимулюють відновлення
+🌸 Екстракти ромашки, шавлії та каштана – протизапальна та тонізуюча дія
+📌 Показання до застосування:
+Акне 1–3 ступеня
+Постакне та розширені пори
+Нерівний тон шкіри
+Атопічний дерматит, псоріаз, екзема
+Подразнення та свербіж
+✔️ Характеристики продукту:
+Тип: Нічний себорегулюючий флюїд
+Об’єм: 50 мл
+Призначення: Лікування акне, себорегуляція, протизапальна дія
+Тип шкіри: Проблемна, жирна, комбінована
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Azelamid Night Fluid – твій must-have для нічного догляду та боротьби з акне! 🌟</t>
+  </si>
+  <si>
+    <t>409-1</t>
+  </si>
+  <si>
+    <t>409-1(1)</t>
+  </si>
+  <si>
+    <t>Трансдермальний санблок SPF 30 - 230 мл</t>
+  </si>
+  <si>
+    <t>✨ Therapeutic Sunscreen SPF 30 – захист та лікування! ✨
+🌿 Формула спеціально для проблемної шкіри:
+☀️ SPF 30 широкого спектра – надійний захист від UVA/UVB
+💧 Зменшує пори та контролює себум
+🌸 Лікує акне 1–3 ступеня та постакне
+🛡️ Бореться з дерматитом, псоріазом та екземою
+⚡ Вирівнює тон та зменшує почервоніння
+💚 Результат – здорова, матова та захищена шкіра без недоліків!
+📌 Активні компоненти:
+🌱 Ніацинамід – відновлює мікробіом та регулює себум
+🌸 Екстракт епілобіуму флешері – протизапальна дія
+💧 Бета-глюкан – відновлює та заспокоює
+🛡️ Екстракт бікс орлеана – зменшує пори та жирність
+🌟 Бісаболол, Д-пантенол, пантеніл триацетат – знімають подразнення та почервоніння
+⚡ Екстракт босвелії – ефективний при дерматиті та екземі
+🌸 Додатково: екстракти шавлії, алое, ромашки, прополіс, олії льону та винограду, токоферол ацетат
+📌 Показання до застосування:
+Акне 1–3 ступеня, постакне
+Себорея та розширені пори
+Атопічний дерматит, псоріаз, екзема
+Подразнення та свербіж
+Нерівний тон шкіри
+✔️ Характеристики продукту:
+Тип: Лікувальний сонцезахисний крем
+Об’єм: 50 мл / 100 мл / 230 мл
+Рівень захисту: SPF 30
+Призначення: Захист, лікування акне, себорегуляція, відновлення
+Тип шкіри: Проблемна, жирна, комбінована
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Therapeutic Sunscreen SPF 30 – твій must-have для комплексного догляду та захисту проблемної шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>406</t>
+  </si>
+  <si>
+    <t>406(1)</t>
   </si>
 </sst>
 </file>
@@ -6958,10 +7751,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -10961,354 +11754,704 @@
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A113" s="17"/>
-      <c r="B113" s="18"/>
+      <c r="A113" s="17" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B113" s="18" t="s">
+        <v>1018</v>
+      </c>
       <c r="C113" s="18" t="s">
         <v>653</v>
       </c>
-      <c r="D113" s="18"/>
-      <c r="E113" s="18"/>
+      <c r="D113" s="18">
+        <v>3200</v>
+      </c>
+      <c r="E113" s="18">
+        <v>2800</v>
+      </c>
       <c r="F113" s="18"/>
-      <c r="G113" s="8"/>
-      <c r="H113" s="18"/>
+      <c r="G113" s="8">
+        <v>21</v>
+      </c>
+      <c r="H113" s="18" t="s">
+        <v>961</v>
+      </c>
       <c r="I113" s="18" t="s">
         <v>657</v>
       </c>
-      <c r="J113" s="18"/>
-      <c r="K113" s="17"/>
+      <c r="J113" s="18" t="s">
+        <v>1019</v>
+      </c>
+      <c r="K113" s="17" t="s">
+        <v>1021</v>
+      </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A114" s="17"/>
-      <c r="B114" s="18"/>
+      <c r="A114" s="17" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B114" s="18" t="s">
+        <v>1022</v>
+      </c>
       <c r="C114" s="18" t="s">
         <v>653</v>
       </c>
-      <c r="D114" s="18"/>
-      <c r="E114" s="18"/>
+      <c r="D114" s="18">
+        <v>3200</v>
+      </c>
+      <c r="E114" s="18">
+        <v>2740</v>
+      </c>
       <c r="F114" s="18"/>
-      <c r="G114" s="8"/>
-      <c r="H114" s="18"/>
+      <c r="G114" s="8">
+        <v>18</v>
+      </c>
+      <c r="H114" s="18" t="s">
+        <v>928</v>
+      </c>
       <c r="I114" s="18" t="s">
         <v>657</v>
       </c>
-      <c r="J114" s="18"/>
-      <c r="K114" s="17"/>
+      <c r="J114" s="18" t="s">
+        <v>1023</v>
+      </c>
+      <c r="K114" s="17" t="s">
+        <v>1025</v>
+      </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A115" s="17"/>
-      <c r="B115" s="18"/>
+      <c r="A115" s="17" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B115" s="18" t="s">
+        <v>1026</v>
+      </c>
       <c r="C115" s="18" t="s">
         <v>653</v>
       </c>
-      <c r="D115" s="18"/>
-      <c r="E115" s="18"/>
+      <c r="D115" s="18">
+        <v>3000</v>
+      </c>
+      <c r="E115" s="18">
+        <v>2500</v>
+      </c>
       <c r="F115" s="18"/>
-      <c r="G115" s="8"/>
-      <c r="H115" s="18"/>
+      <c r="G115" s="8">
+        <v>21</v>
+      </c>
+      <c r="H115" s="18" t="s">
+        <v>928</v>
+      </c>
       <c r="I115" s="18" t="s">
         <v>657</v>
       </c>
-      <c r="J115" s="18"/>
-      <c r="K115" s="17"/>
+      <c r="J115" s="18" t="s">
+        <v>1027</v>
+      </c>
+      <c r="K115" s="17" t="s">
+        <v>1029</v>
+      </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A116" s="17"/>
-      <c r="B116" s="18"/>
+      <c r="A116" s="17" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B116" s="18" t="s">
+        <v>1030</v>
+      </c>
       <c r="C116" s="18" t="s">
         <v>653</v>
       </c>
-      <c r="D116" s="18"/>
-      <c r="E116" s="18"/>
+      <c r="D116" s="18">
+        <v>2400</v>
+      </c>
+      <c r="E116" s="18">
+        <v>2000</v>
+      </c>
       <c r="F116" s="18"/>
-      <c r="G116" s="8"/>
-      <c r="H116" s="18"/>
+      <c r="G116" s="8">
+        <v>21</v>
+      </c>
+      <c r="H116" s="18" t="s">
+        <v>961</v>
+      </c>
       <c r="I116" s="18" t="s">
         <v>657</v>
       </c>
-      <c r="J116" s="18"/>
-      <c r="K116" s="17"/>
+      <c r="J116" s="18" t="s">
+        <v>1031</v>
+      </c>
+      <c r="K116" s="17" t="s">
+        <v>1033</v>
+      </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A117" s="17"/>
-      <c r="B117" s="18"/>
+      <c r="A117" s="17" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B117" s="18" t="s">
+        <v>1034</v>
+      </c>
       <c r="C117" s="18" t="s">
         <v>653</v>
       </c>
-      <c r="D117" s="18"/>
-      <c r="E117" s="18"/>
+      <c r="D117" s="18">
+        <v>2100</v>
+      </c>
+      <c r="E117" s="18">
+        <v>1800</v>
+      </c>
       <c r="F117" s="18"/>
-      <c r="G117" s="8"/>
-      <c r="H117" s="18"/>
+      <c r="G117" s="8">
+        <v>14</v>
+      </c>
+      <c r="H117" s="18" t="s">
+        <v>29</v>
+      </c>
       <c r="I117" s="18" t="s">
         <v>657</v>
       </c>
-      <c r="J117" s="18"/>
-      <c r="K117" s="17"/>
+      <c r="J117" s="18" t="s">
+        <v>840</v>
+      </c>
+      <c r="K117" s="17" t="s">
+        <v>1035</v>
+      </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A118" s="17"/>
-      <c r="B118" s="18"/>
+      <c r="A118" s="17" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B118" s="18" t="s">
+        <v>1037</v>
+      </c>
       <c r="C118" s="18" t="s">
         <v>653</v>
       </c>
-      <c r="D118" s="18"/>
-      <c r="E118" s="18"/>
+      <c r="D118" s="18">
+        <v>550</v>
+      </c>
+      <c r="E118" s="18">
+        <v>480</v>
+      </c>
       <c r="F118" s="18"/>
-      <c r="G118" s="8"/>
-      <c r="H118" s="18"/>
+      <c r="G118" s="8">
+        <v>16</v>
+      </c>
+      <c r="H118" s="18" t="s">
+        <v>998</v>
+      </c>
       <c r="I118" s="18" t="s">
         <v>657</v>
       </c>
-      <c r="J118" s="18"/>
-      <c r="K118" s="17"/>
+      <c r="J118" s="18" t="s">
+        <v>1038</v>
+      </c>
+      <c r="K118" s="17" t="s">
+        <v>1040</v>
+      </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A119" s="17"/>
-      <c r="B119" s="18"/>
+      <c r="A119" s="17" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B119" s="18" t="s">
+        <v>1041</v>
+      </c>
       <c r="C119" s="18" t="s">
         <v>653</v>
       </c>
-      <c r="D119" s="18"/>
-      <c r="E119" s="18"/>
+      <c r="D119" s="18">
+        <v>1900</v>
+      </c>
+      <c r="E119" s="18">
+        <v>1600</v>
+      </c>
       <c r="F119" s="18"/>
-      <c r="G119" s="8"/>
-      <c r="H119" s="18"/>
+      <c r="G119" s="8">
+        <v>18</v>
+      </c>
+      <c r="H119" s="18" t="s">
+        <v>971</v>
+      </c>
       <c r="I119" s="18" t="s">
         <v>657</v>
       </c>
-      <c r="J119" s="18"/>
-      <c r="K119" s="17"/>
+      <c r="J119" s="18" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K119" s="17" t="s">
+        <v>1044</v>
+      </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A120" s="17"/>
-      <c r="B120" s="18"/>
+      <c r="A120" s="17" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B120" s="18" t="s">
+        <v>1045</v>
+      </c>
       <c r="C120" s="18" t="s">
         <v>653</v>
       </c>
-      <c r="D120" s="18"/>
-      <c r="E120" s="18"/>
+      <c r="D120" s="18">
+        <v>1500</v>
+      </c>
+      <c r="E120" s="18">
+        <v>1240</v>
+      </c>
       <c r="F120" s="18"/>
-      <c r="G120" s="8"/>
-      <c r="H120" s="18"/>
+      <c r="G120" s="8">
+        <v>17</v>
+      </c>
+      <c r="H120" s="18" t="s">
+        <v>971</v>
+      </c>
       <c r="I120" s="18" t="s">
         <v>657</v>
       </c>
-      <c r="J120" s="18"/>
-      <c r="K120" s="17"/>
+      <c r="J120" s="18" t="s">
+        <v>1048</v>
+      </c>
+      <c r="K120" s="17" t="s">
+        <v>1047</v>
+      </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A121" s="17"/>
-      <c r="B121" s="18"/>
+      <c r="A121" s="17" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B121" s="18" t="s">
+        <v>1049</v>
+      </c>
       <c r="C121" s="18" t="s">
         <v>653</v>
       </c>
-      <c r="D121" s="18"/>
-      <c r="E121" s="18"/>
+      <c r="D121" s="18">
+        <v>1700</v>
+      </c>
+      <c r="E121" s="18">
+        <v>1540</v>
+      </c>
       <c r="F121" s="18"/>
-      <c r="G121" s="8"/>
-      <c r="H121" s="18"/>
+      <c r="G121" s="8">
+        <v>15</v>
+      </c>
+      <c r="H121" s="18" t="s">
+        <v>928</v>
+      </c>
       <c r="I121" s="18" t="s">
         <v>657</v>
       </c>
-      <c r="J121" s="18"/>
-      <c r="K121" s="17"/>
+      <c r="J121" s="18" t="s">
+        <v>1050</v>
+      </c>
+      <c r="K121" s="17" t="s">
+        <v>1052</v>
+      </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A122" s="17"/>
-      <c r="B122" s="18"/>
+      <c r="A122" s="17" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B122" s="18" t="s">
+        <v>1053</v>
+      </c>
       <c r="C122" s="18" t="s">
         <v>653</v>
       </c>
-      <c r="D122" s="18"/>
-      <c r="E122" s="18"/>
+      <c r="D122" s="18">
+        <v>2400</v>
+      </c>
+      <c r="E122" s="18">
+        <v>2000</v>
+      </c>
       <c r="F122" s="18"/>
-      <c r="G122" s="8"/>
-      <c r="H122" s="18"/>
+      <c r="G122" s="8">
+        <v>24</v>
+      </c>
+      <c r="H122" s="18" t="s">
+        <v>928</v>
+      </c>
       <c r="I122" s="18" t="s">
         <v>657</v>
       </c>
-      <c r="J122" s="18"/>
-      <c r="K122" s="17"/>
+      <c r="J122" s="18" t="s">
+        <v>1054</v>
+      </c>
+      <c r="K122" s="17" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A123" s="17"/>
-      <c r="B123" s="18"/>
+      <c r="A123" s="17" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B123" s="18" t="s">
+        <v>1057</v>
+      </c>
       <c r="C123" s="18" t="s">
         <v>653</v>
       </c>
-      <c r="D123" s="18"/>
-      <c r="E123" s="18"/>
+      <c r="D123" s="18">
+        <v>2400</v>
+      </c>
+      <c r="E123" s="18">
+        <v>2000</v>
+      </c>
       <c r="F123" s="18"/>
-      <c r="G123" s="8"/>
-      <c r="H123" s="18"/>
+      <c r="G123" s="8">
+        <v>25</v>
+      </c>
+      <c r="H123" s="18" t="s">
+        <v>928</v>
+      </c>
       <c r="I123" s="18" t="s">
         <v>657</v>
       </c>
-      <c r="J123" s="18"/>
-      <c r="K123" s="17"/>
+      <c r="J123" s="18" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K123" s="17" t="s">
+        <v>1060</v>
+      </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A124" s="17"/>
-      <c r="B124" s="18"/>
+      <c r="A124" s="17" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B124" s="18" t="s">
+        <v>1061</v>
+      </c>
       <c r="C124" s="18" t="s">
         <v>653</v>
       </c>
-      <c r="D124" s="18"/>
-      <c r="E124" s="18"/>
+      <c r="D124" s="18">
+        <v>1500</v>
+      </c>
+      <c r="E124" s="18">
+        <v>1260</v>
+      </c>
       <c r="F124" s="18"/>
-      <c r="G124" s="8"/>
-      <c r="H124" s="18"/>
+      <c r="G124" s="8">
+        <v>21</v>
+      </c>
+      <c r="H124" s="18" t="s">
+        <v>961</v>
+      </c>
       <c r="I124" s="18" t="s">
         <v>657</v>
       </c>
-      <c r="J124" s="18"/>
-      <c r="K124" s="17"/>
+      <c r="J124" s="18" t="s">
+        <v>1062</v>
+      </c>
+      <c r="K124" s="17" t="s">
+        <v>1064</v>
+      </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A125" s="17"/>
-      <c r="B125" s="18"/>
+      <c r="A125" s="17" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B125" s="18" t="s">
+        <v>1065</v>
+      </c>
       <c r="C125" s="18" t="s">
         <v>653</v>
       </c>
-      <c r="D125" s="18"/>
-      <c r="E125" s="18"/>
+      <c r="D125" s="18">
+        <v>1400</v>
+      </c>
+      <c r="E125" s="18">
+        <v>1220</v>
+      </c>
       <c r="F125" s="18"/>
-      <c r="G125" s="8"/>
-      <c r="H125" s="18"/>
+      <c r="G125" s="8">
+        <v>25</v>
+      </c>
+      <c r="H125" s="18" t="s">
+        <v>29</v>
+      </c>
       <c r="I125" s="18" t="s">
         <v>657</v>
       </c>
-      <c r="J125" s="18"/>
-      <c r="K125" s="17"/>
+      <c r="J125" s="18" t="s">
+        <v>1066</v>
+      </c>
+      <c r="K125" s="17" t="s">
+        <v>1068</v>
+      </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A126" s="17"/>
-      <c r="B126" s="18"/>
+      <c r="A126" s="17" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B126" s="18" t="s">
+        <v>1069</v>
+      </c>
       <c r="C126" s="18" t="s">
         <v>653</v>
       </c>
-      <c r="D126" s="18"/>
-      <c r="E126" s="18"/>
+      <c r="D126" s="18">
+        <v>1500</v>
+      </c>
+      <c r="E126" s="18">
+        <v>1300</v>
+      </c>
       <c r="F126" s="18"/>
-      <c r="G126" s="8"/>
-      <c r="H126" s="18"/>
+      <c r="G126" s="8">
+        <v>21</v>
+      </c>
+      <c r="H126" s="18" t="s">
+        <v>29</v>
+      </c>
       <c r="I126" s="18" t="s">
         <v>657</v>
       </c>
-      <c r="J126" s="18"/>
-      <c r="K126" s="17"/>
+      <c r="J126" s="18" t="s">
+        <v>1070</v>
+      </c>
+      <c r="K126" s="17" t="s">
+        <v>1071</v>
+      </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A127" s="17"/>
-      <c r="B127" s="18"/>
+      <c r="A127" s="17" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B127" s="18" t="s">
+        <v>1073</v>
+      </c>
       <c r="C127" s="18" t="s">
         <v>653</v>
       </c>
-      <c r="D127" s="18"/>
-      <c r="E127" s="18"/>
+      <c r="D127" s="18">
+        <v>1600</v>
+      </c>
+      <c r="E127" s="18">
+        <v>1440</v>
+      </c>
       <c r="F127" s="18"/>
-      <c r="G127" s="8"/>
-      <c r="H127" s="18"/>
+      <c r="G127" s="8">
+        <v>15</v>
+      </c>
+      <c r="H127" s="18" t="s">
+        <v>971</v>
+      </c>
       <c r="I127" s="18" t="s">
         <v>657</v>
       </c>
-      <c r="J127" s="18"/>
-      <c r="K127" s="17"/>
+      <c r="J127" s="18" t="s">
+        <v>1074</v>
+      </c>
+      <c r="K127" s="17" t="s">
+        <v>1076</v>
+      </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A128" s="17"/>
-      <c r="B128" s="18"/>
-      <c r="C128" s="18"/>
-      <c r="D128" s="18"/>
-      <c r="E128" s="18"/>
+      <c r="A128" s="17" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B128" s="18" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C128" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D128" s="18">
+        <v>1100</v>
+      </c>
+      <c r="E128" s="18">
+        <v>750</v>
+      </c>
       <c r="F128" s="18"/>
-      <c r="G128" s="8"/>
-      <c r="H128" s="18"/>
+      <c r="G128" s="8">
+        <v>18</v>
+      </c>
+      <c r="H128" s="18" t="s">
+        <v>932</v>
+      </c>
       <c r="I128" s="18" t="s">
         <v>657</v>
       </c>
-      <c r="J128" s="18"/>
-      <c r="K128" s="17"/>
+      <c r="J128" s="18" t="s">
+        <v>1078</v>
+      </c>
+      <c r="K128" s="17" t="s">
+        <v>1080</v>
+      </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A129" s="17"/>
-      <c r="B129" s="18"/>
-      <c r="C129" s="18"/>
-      <c r="D129" s="18"/>
-      <c r="E129" s="18"/>
+      <c r="A129" s="17" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B129" s="18" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C129" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D129" s="18">
+        <v>1600</v>
+      </c>
+      <c r="E129" s="18">
+        <v>1300</v>
+      </c>
       <c r="F129" s="18"/>
-      <c r="G129" s="8"/>
-      <c r="H129" s="18"/>
+      <c r="G129" s="8">
+        <v>12</v>
+      </c>
+      <c r="H129" s="18" t="s">
+        <v>980</v>
+      </c>
       <c r="I129" s="18" t="s">
         <v>657</v>
       </c>
-      <c r="J129" s="18"/>
-      <c r="K129" s="17"/>
+      <c r="J129" s="18" t="s">
+        <v>1082</v>
+      </c>
+      <c r="K129" s="17" t="s">
+        <v>1084</v>
+      </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A130" s="17"/>
-      <c r="B130" s="18"/>
-      <c r="C130" s="18"/>
-      <c r="D130" s="18"/>
-      <c r="E130" s="18"/>
+      <c r="A130" s="17" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B130" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C130" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D130" s="18">
+        <v>1300</v>
+      </c>
+      <c r="E130" s="18">
+        <v>1140</v>
+      </c>
       <c r="F130" s="18"/>
-      <c r="G130" s="8"/>
-      <c r="H130" s="18"/>
+      <c r="G130" s="8">
+        <v>15</v>
+      </c>
+      <c r="H130" s="18" t="s">
+        <v>971</v>
+      </c>
       <c r="I130" s="18" t="s">
         <v>657</v>
       </c>
-      <c r="J130" s="18"/>
-      <c r="K130" s="17"/>
+      <c r="J130" s="18" t="s">
+        <v>1086</v>
+      </c>
+      <c r="K130" s="17" t="s">
+        <v>1088</v>
+      </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A131" s="17"/>
-      <c r="B131" s="18"/>
-      <c r="C131" s="18"/>
-      <c r="D131" s="18"/>
-      <c r="E131" s="18"/>
+      <c r="A131" s="17" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B131" s="18" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C131" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D131" s="18">
+        <v>1400</v>
+      </c>
+      <c r="E131" s="18">
+        <v>1240</v>
+      </c>
       <c r="F131" s="18"/>
-      <c r="G131" s="8"/>
-      <c r="H131" s="18"/>
+      <c r="G131" s="8">
+        <v>19</v>
+      </c>
+      <c r="H131" s="18" t="s">
+        <v>928</v>
+      </c>
       <c r="I131" s="18" t="s">
         <v>657</v>
       </c>
-      <c r="J131" s="18"/>
-      <c r="K131" s="17"/>
+      <c r="J131" s="18" t="s">
+        <v>1090</v>
+      </c>
+      <c r="K131" s="17" t="s">
+        <v>1092</v>
+      </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A132" s="17"/>
-      <c r="B132" s="18"/>
-      <c r="C132" s="18"/>
-      <c r="D132" s="18"/>
-      <c r="E132" s="18"/>
+      <c r="A132" s="17" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B132" s="18" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C132" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D132" s="18">
+        <v>2500</v>
+      </c>
+      <c r="E132" s="18">
+        <v>2200</v>
+      </c>
       <c r="F132" s="18"/>
-      <c r="G132" s="8"/>
-      <c r="H132" s="18"/>
+      <c r="G132" s="8">
+        <v>25</v>
+      </c>
+      <c r="H132" s="18" t="s">
+        <v>928</v>
+      </c>
       <c r="I132" s="18" t="s">
         <v>657</v>
       </c>
-      <c r="J132" s="18"/>
-      <c r="K132" s="17"/>
+      <c r="J132" s="18" t="s">
+        <v>1094</v>
+      </c>
+      <c r="K132" s="17" t="s">
+        <v>1096</v>
+      </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A133" s="17"/>
-      <c r="B133" s="18"/>
-      <c r="C133" s="18"/>
-      <c r="D133" s="18"/>
-      <c r="E133" s="18"/>
+      <c r="A133" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B133" s="18" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C133" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D133" s="18">
+        <v>1800</v>
+      </c>
+      <c r="E133" s="18">
+        <v>1440</v>
+      </c>
       <c r="F133" s="18"/>
-      <c r="G133" s="8"/>
-      <c r="H133" s="18"/>
+      <c r="G133" s="8">
+        <v>16</v>
+      </c>
+      <c r="H133" s="18" t="s">
+        <v>928</v>
+      </c>
       <c r="I133" s="18" t="s">
         <v>657</v>
       </c>
-      <c r="J133" s="18"/>
-      <c r="K133" s="17"/>
+      <c r="J133" s="18" t="s">
+        <v>1098</v>
+      </c>
+      <c r="K133" s="17" t="s">
+        <v>1100</v>
+      </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" s="17"/>
       <c r="B134" s="18"/>
-      <c r="C134" s="18"/>
+      <c r="C134" s="18" t="s">
+        <v>653</v>
+      </c>
       <c r="D134" s="18"/>
       <c r="E134" s="18"/>
       <c r="F134" s="18"/>
@@ -11323,7 +12466,9 @@
     <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="17"/>
       <c r="B135" s="18"/>
-      <c r="C135" s="18"/>
+      <c r="C135" s="18" t="s">
+        <v>653</v>
+      </c>
       <c r="D135" s="18"/>
       <c r="E135" s="18"/>
       <c r="F135" s="18"/>
@@ -11336,72 +12481,216 @@
       <c r="K135" s="17"/>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A136" s="17"/>
+      <c r="B136" s="18"/>
+      <c r="C136" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D136" s="18"/>
+      <c r="E136" s="18"/>
+      <c r="F136" s="18"/>
       <c r="G136" s="8"/>
+      <c r="H136" s="18"/>
+      <c r="I136" s="18"/>
+      <c r="J136" s="18"/>
+      <c r="K136" s="17"/>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A137" s="17"/>
+      <c r="B137" s="18"/>
+      <c r="C137" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D137" s="18"/>
+      <c r="E137" s="18"/>
+      <c r="F137" s="18"/>
       <c r="G137" s="8"/>
+      <c r="H137" s="18"/>
+      <c r="I137" s="18"/>
+      <c r="J137" s="18"/>
+      <c r="K137" s="17"/>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A138" s="17"/>
+      <c r="B138" s="18"/>
+      <c r="C138" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D138" s="18"/>
+      <c r="E138" s="18"/>
+      <c r="F138" s="18"/>
       <c r="G138" s="8"/>
+      <c r="H138" s="18"/>
+      <c r="I138" s="18"/>
+      <c r="J138" s="18"/>
+      <c r="K138" s="17"/>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A139" s="17"/>
+      <c r="B139" s="18"/>
+      <c r="C139" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D139" s="18"/>
+      <c r="E139" s="18"/>
+      <c r="F139" s="18"/>
       <c r="G139" s="8"/>
+      <c r="H139" s="18"/>
+      <c r="I139" s="18"/>
+      <c r="J139" s="18"/>
+      <c r="K139" s="17"/>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A140" s="17"/>
+      <c r="B140" s="18"/>
+      <c r="C140" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D140" s="18"/>
+      <c r="E140" s="18"/>
+      <c r="F140" s="18"/>
       <c r="G140" s="8"/>
+      <c r="H140" s="18"/>
+      <c r="I140" s="18"/>
+      <c r="J140" s="18"/>
+      <c r="K140" s="17"/>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A141" s="17"/>
+      <c r="B141" s="18"/>
+      <c r="C141" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D141" s="18"/>
+      <c r="E141" s="18"/>
+      <c r="F141" s="18"/>
       <c r="G141" s="8"/>
+      <c r="H141" s="18"/>
+      <c r="I141" s="18"/>
+      <c r="J141" s="18"/>
+      <c r="K141" s="17"/>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A142" s="17"/>
+      <c r="B142" s="18"/>
+      <c r="C142" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D142" s="18"/>
+      <c r="E142" s="18"/>
+      <c r="F142" s="18"/>
       <c r="G142" s="8"/>
+      <c r="H142" s="18"/>
+      <c r="I142" s="18"/>
+      <c r="J142" s="18"/>
+      <c r="K142" s="17"/>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A143" s="17"/>
+      <c r="B143" s="18"/>
+      <c r="C143" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D143" s="18"/>
+      <c r="E143" s="18"/>
+      <c r="F143" s="18"/>
       <c r="G143" s="8"/>
+      <c r="H143" s="18"/>
+      <c r="I143" s="18"/>
+      <c r="J143" s="18"/>
+      <c r="K143" s="17"/>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A144" s="17"/>
+      <c r="B144" s="18"/>
+      <c r="C144" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D144" s="18"/>
+      <c r="E144" s="18"/>
+      <c r="F144" s="18"/>
       <c r="G144" s="8"/>
-    </row>
-    <row r="145" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="H144" s="18"/>
+      <c r="I144" s="18"/>
+      <c r="J144" s="18"/>
+      <c r="K144" s="17"/>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A145" s="17"/>
+      <c r="B145" s="18"/>
+      <c r="C145" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D145" s="18"/>
+      <c r="E145" s="18"/>
+      <c r="F145" s="18"/>
       <c r="G145" s="8"/>
-    </row>
-    <row r="146" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="H145" s="18"/>
+      <c r="I145" s="18"/>
+      <c r="J145" s="18"/>
+      <c r="K145" s="17"/>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A146" s="17"/>
+      <c r="B146" s="18"/>
+      <c r="C146" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D146" s="18"/>
+      <c r="E146" s="18"/>
+      <c r="F146" s="18"/>
       <c r="G146" s="8"/>
-    </row>
-    <row r="147" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="H146" s="18"/>
+      <c r="I146" s="18"/>
+      <c r="J146" s="18"/>
+      <c r="K146" s="17"/>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A147" s="17"/>
+      <c r="B147" s="18"/>
+      <c r="C147" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="D147" s="18"/>
+      <c r="E147" s="18"/>
+      <c r="F147" s="18"/>
       <c r="G147" s="8"/>
-    </row>
-    <row r="148" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="H147" s="18"/>
+      <c r="I147" s="18"/>
+      <c r="J147" s="18"/>
+      <c r="K147" s="17"/>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G148" s="8"/>
     </row>
-    <row r="149" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G149" s="8"/>
     </row>
-    <row r="150" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G150" s="8"/>
     </row>
-    <row r="151" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G151" s="8"/>
     </row>
-    <row r="152" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G152" s="8"/>
     </row>
-    <row r="153" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G153" s="8"/>
     </row>
-    <row r="154" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G154" s="8"/>
     </row>
-    <row r="155" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G155" s="8"/>
     </row>
-    <row r="156" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G156" s="8"/>
     </row>
-    <row r="157" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G157" s="8"/>
     </row>
-    <row r="158" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G158" s="8"/>
     </row>
   </sheetData>

--- a/price.xlsx
+++ b/price.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ПРОЕКТ AI\ЛИЧНЫЕ НАРАБОТКИ\AI Skin Lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B311886-7D53-48F6-8509-F47A02FF9192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{523C46E5-A093-4C55-9D73-EDC66DA07E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-1512" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2421" uniqueCount="1101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2524" uniqueCount="1155">
   <si>
     <t>Артикул</t>
   </si>
@@ -7597,6 +7597,539 @@
   </si>
   <si>
     <t>406(1)</t>
+  </si>
+  <si>
+    <t>Мінеральний себорегулювальний тонер 500 мл</t>
+  </si>
+  <si>
+    <t>✨ Mineral BHA-Toner – чистота та баланс шкіри! ✨
+🌿 Активний тонік-ексфоліант із мультимінеральним комплексом:
+🔄 Стимулює оновлення клітин та контролює себум
+⚖️ Балансує мікрофлору шкіри
+💎 Прискорює регенерацію тканин
+💧 Зволожує та підвищує еластичність
+💚 Результат – свіжа, матова та здорова шкіра без недоліків!
+📌 Показання до застосування:
+Акне 1–3 ступеня
+Постакне та розширені пори
+Нерівний тон шкіри
+Атопічний дерматит, псоріаз, екзема
+Подразнення та свербіж
+📌 Активні компоненти:
+🔥 Азелаїнова та саліцилова кислоти – протизапальна дія та очищення пор
+✨ Ніацинамід та глюконолактон – регенерація та вирівнювання тону
+🌼 Екстракти ромашки, шавлії, епілобіуму – заспокійливий ефект
+🍯 Прополіс та Bosexil – антисептична та відновлююча дія
+🪨 Мінерали (магній, калій, цинк, натрій, кальцій) – живлення та баланс
+✔️ Характеристики продукту:
+Тип: Себорегулюючий тонік-ексфоліант
+Об’єм: 200 мл / 500 мл
+Призначення: Очищення, себорегуляція, відновлення
+Тип шкіри: Проблемна, жирна, комбінована
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Mineral BHA-Toner – твій must-have для догляду за проблемною шкірою! 🌟</t>
+  </si>
+  <si>
+    <t>402</t>
+  </si>
+  <si>
+    <t>402(1)</t>
+  </si>
+  <si>
+    <t>Інтенсивний очищувальний гель з босвелією 500 мл</t>
+  </si>
+  <si>
+    <t>✨ Boswellia Pro-Gel Deep Cleanse – інтенсивне очищення та баланс! ✨
+🌿 Універсальна формула для проблемної шкіри:
+💧 Усуває жирний блиск та гіперкератоз
+🌸 Регулює вироблення себуму та зменшує запалення
+🛡️ Відновлює бар’єрні функції епідермісу
+⚡ Корегує прояви себореї та екземи
+🌟 Дарує відчуття свіжості та чистоти після кожного застосування
+💚 Результат – чиста, матова та здорова шкіра без подразнень!
+📌 Показання до застосування:
+Акне 1–3 ступеня та постакне
+Розширені пори
+Нерівний тон обличчя
+Атопічний дерматит, псоріаз, екзема
+Подразнення та свербіж
+📌 Активні компоненти:
+🌱 Екстракти ромашки та шавлії – заспокоюють та знімають подразнення
+🌸 Азелаїнова та саліцилова кислоти – очищають пори та відлущують
+💧 Сечовина та Д-пантенол – зволоження та відновлення
+🛡️ Прополіс та Bosexil – антибактеріальна та протизапальна дія
+🌟 Ніацинамід та екстракт кінського каштана – регуляція себуму та тонізуючий ефект
+✔️ Характеристики продукту:
+Тип: Очищаючий гель для проблемної шкіри
+Об’єм: 200 мл / 500 мл
+Призначення: Очищення, себорегуляція, протизапальна дія
+Тип шкіри: Проблемна, жирна, комбінована
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Boswellia Pro-Gel Deep Cleanse – твій must-have для щоденного інтенсивного очищення та здорової шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>401</t>
+  </si>
+  <si>
+    <t>401(1)</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>311(1)</t>
+  </si>
+  <si>
+    <t>Протизапальний бустер Кутибіом для корекції акне 10 мл</t>
+  </si>
+  <si>
+    <t>✨ Cutibiome Booster – інтенсивна корекція акне! ✨
+🌿 Ампульний концентрат для професійного та домашнього догляду:
+💧 Ефективно відлущує пори зсередини
+🌸 Розщеплює пробки себуму та очищає шкіру
+🛡️ Пригнічує ріст бактерій Cutibacterium acnes та Propionibacterium acnes
+⚡ Нормалізує мікробіом та забезпечує себорегуляцію
+🌟 Має антибактеріальну та протизапальну дію
+💚 Результат – чиста, матова та здорова шкіра без запальних елементів!
+📌 Показання до застосування:
+Жирна та комбінована шкіра
+Акне 1–2 ступеня
+Постакне та розширені пори
+Нерівний тон обличчя
+Запальні процеси
+📌 Переваги:
+Антибактеріальна та протизапальна дія
+Зменшення слідів постакне
+Зволоження та матуючий ефект
+Ідеальний для апаратних методик: фонофорез, мікротоки, RF
+📌 Активні компоненти:
+🌱 Ніацинамід, Sebaryl, Саліцилова кислота – себорегуляція та очищення пор
+🌸 Екстракт ромашки та гідролат лайма – заспокоюють та освіжають
+💧 Лактобіонова кислота – м’яке відлущення та зволоження
+🛡️ Skinasensyl та CutiBiome CLR – нормалізація мікробіому та протизапальний ефект
+✔️ Характеристики продукту:
+Тип: Ампульний концентрат-бустер
+Об’єм: 10 мл
+Призначення: Корекція акне, себорегуляція, протизапальна дія
+Тип шкіри: Жирна, комбінована, проблемна
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Cutibiome Booster – твій must-have для інтенсивної корекції акне та здорової шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>307(1)</t>
+  </si>
+  <si>
+    <t>Лаймовий гідруючий гель для атравматичної чистки 250 мл</t>
+  </si>
+  <si>
+    <t>✨ Lime Hydrating Gel – професійна атравматична чистка! ✨
+🌿 Формула для апаратної та мануальної чистки:
+💧 Розпушує верхній роговий шар епідермісу
+🌸 Розріджує ліпідний шар та відлущує ороговілі клітини
+🛡️ Нормалізує мікробіом та забезпечує себорегуляцію
+⚡ Має матуючий ефект та зволожує шкіру
+🌟 Заспокоює подразнення та дарує свіжість
+💚 Результат – чиста, рівна та здорова шкіра без травмування!
+📌 Показання до застосування:
+Жирна та комбінована шкіра
+Акне 1–2 ступеня та постакне
+Нерівний тон обличчя
+Розширені пори
+Запальні процеси
+📌 Активні компоненти:
+🌱 Мочевина – розпушує роговий шар та зволожує
+🌸 Екстракти алоє, ромашки та чайного дерева – заспокоюють та знімають запалення
+💧 Ніацинамід та гліцерин – підтримують водний баланс та еластичність
+🛡️ Камфора та саліцилат натрію – антисептична та себорегулююча дія
+🌟 Ефірна олія лайма – освіжає та тонізує
+✔️ Характеристики продукту:
+Тип: Гідруючий гель для атравматичної чистки
+Об’єм: 250 мл
+Призначення: Очищення, себорегуляція, зволоження, заспокійливий ефект
+Тип шкіри: Жирна, комбінована, проблемна
+Бренд: Smart Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Lime Hydrating Gel – твій must-have для професійної атравматичної чистки та сяйва шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>305(1)</t>
+  </si>
+  <si>
+    <t>✨ CUTIBIOME TONER – контроль себуму та рівний тон! ✨
+🌿 Інтенсивна терапія для проблемної шкіри:
+💧 Зволожує та нормалізує рН
+🌸 Вирівнює тон та зменшує сліди постакне
+🛡️ Має виражену антибактеріальну та протизапальну дію
+⚡ Нормалізує мікробіом та регулює роботу сальних залоз
+🌟 Дарує матуючий ефект без пересушування
+💚 Результат – чиста, матова та здорова шкіра з рівним тоном!
+📌 Показання до застосування:
+Жирна та комбінована шкіра
+Акне 1–2 ступеня
+Постакне та розширені пори
+Нерівний тон обличчя
+Запальні процеси
+📌 Активні компоненти:
+🌱 Кислотний комплекс BHA + PHA (саліцилова та лактобіонова кислоти) – очищення та делікатне відлущування
+🌸 Азелаїнова кислота – протизапальна та антибактеріальна дія
+💧 Ніацинамід та цинк глюканат – себорегуляція та зволоження
+🛡️ Екстракти алоє та ромашки – заспокоюють та знімають подразнення
+⚡ Кофеїн – тонізує та активізує мікроциркуляцію
+🌟 Ефірні олії чайного дерева та лайма, CutiBiome CLR – нормалізація мікробіому та антисептичний ефект
+✔️ Характеристики продукту:
+Тип: Себорегулюючий мультикислотний тонер
+Об’єм: 100 мл
+Призначення: Зволоження, себорегуляція, антибактеріальна дія
+Тип шкіри: Жирна, комбінована, проблемна
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 CUTIBIOME TONER – твій must-have для догляду за проблемною шкірою та контролю акне! 🌟</t>
+  </si>
+  <si>
+    <t>303(1)</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>Очищувальна мультикислотна пінка для жирної, комбінованої та шкіри з акне 480 мл</t>
+  </si>
+  <si>
+    <t>✨ Smart4Derma AHA-BHA-PHA Foam – глибоке очищення та контроль акне! ✨
+🌿 Спеціальна формула для жирної та проблемної шкіри:
+💧 Делікатно, але ефективно видаляє забруднення, себум та залишки макіяжу
+🌸 Регулює вироблення себуму та зменшує пори (ніацинамід, азелаїнова та гліколева кислоти)
+🛡️ Має антибактеріальну та заспокійливу дію (олії чайного дерева та лайма)
+⚡ Підтримує мікробіом шкіри завдяки PHA-кислотам
+🌟 Робить шкіру гладкою, матовою та свіжою
+💚 Результат – чиста, матова та здорова шкіра без недоліків!
+📌 Активні компоненти:
+🌱 AHA, BHA, PHA кислоти (гліколева, молочна, винна, яблучна, лактобіонова, саліцилова)
+🌸 Азелаїнова кислота – протизапальна дія
+💧 Ніацинамід – себорегуляція та зволоження
+🛡️ Олії лайма та чайного дерева – антисептичний ефект
+⚡ Кофеїн та цинк – тонізуюча та протизапальна дія
+📌 Застосування:  
+Нанести на вологу шкіру, помасажувати 1–2 хвилини та змити. Використовувати двічі на день.
+✔️ Характеристики продукту:
+Тип: Очищувальна пінка для обличчя
+Об’єм: 480 мл
+Призначення: Очищення, себорегуляція, антибактеріальна дія
+Тип шкіри: Жирна, комбінована, проблемна
+Лінійка: Acne Balance
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Smart4Derma AHA-BHA-PHA Foam – твій must-have для щоденного контролю акне та сяючої шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>302(1)</t>
+  </si>
+  <si>
+    <t>Освітлювальна тонізувальна альгінатна маска 200г</t>
+  </si>
+  <si>
+    <t>200 г</t>
+  </si>
+  <si>
+    <t>✨ Smart4Derma Alginate Mask – сяйво та рівний тон! ✨
+🌿 Професійна формула для освітлення та тонізації:
+💧 Глибоко зволожує та вирівнює тон
+🌸 Зменшує пігментні плями та сліди постакне
+🛡️ Заспокоює почервоніння та дарує свіжість
+⚡ Має антиоксидантну та омолоджувальну дію
+🌟 Тонізує та підсилює ефект ліфтингу
+💚 Результат – сяюча, рівна та доглянута шкіра вже після першого застосування!
+📌 Активні компоненти:
+🌱 Альгінат – основа для глибокого проникнення активних речовин
+🌸 Екстракти маргаритки, кресу, алое, софори – природне освітлення та вирівнювання тону
+💧 Аскорбіл глюкозид (вітамін С) – антиоксидант та освітлення
+🛡️ Убіхінон – потужний антиоксидантний захист
+🌟 Гіалуронат натрію – інтенсивне зволоження
+⚡ Кофеїн – тонізування та ліфтинг
+🌸 Нонапептид та ізофлавони сої – омолодження та вирівнювання тону
+📌 Показання до застосування:
+Тьмяність та неоднорідний тон
+Пігментні плями різного походження
+Сліди постакне
+Зневоднення та зморшки
+📌 Спосіб застосування:  
+Змішати 30 г порошку з 40 мл води до однорідної консистенції.
+Нанести товстим шаром на обличчя, шию, декольте, зону очей і губ.
+Маска застигає за 5 хвилин. Тримати 15–30 хвилин, зняти єдиним шаром.
+Для підсилення ефекту під маску можна наносити освітлювальні сироватки.
+✔️ Характеристики продукту:
+Тип: Альгінатна маска освітлювально-тонізувальна
+Об’єм: 200 г
+Призначення: Освітлення, тонізація, зволоження, омолодження
+Тип шкіри: Тьмяна, з пігментними плямами, постакне
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Smart4Derma Alginate Mask – твій must-have для сяючої та рівної шкіри!</t>
+  </si>
+  <si>
+    <t>848</t>
+  </si>
+  <si>
+    <t>848(1)</t>
+  </si>
+  <si>
+    <t>Альгінатна маска ліфтингова «золоті водорості» 200г</t>
+  </si>
+  <si>
+    <t>✨ Smart4Derma Alginate Mask Golden Algae – ліфтинг та омолодження! ✨
+🌿 Професійна формула для обличчя, шиї та декольте:
+💧 Глибоке зволоження та підтягування шкіри
+🌸 Покращення тургору та природне сяйво
+🛡️ Стимуляція синтезу колагену та еластину
+⚡ Виражений антивіковий ефект
+💚 Результат – пружна, сяюча та омолоджена шкіра вже після першого застосування!
+📌 Активні компоненти:
+🌱 sh-олігопептид-1 – фактор росту для регенерації
+🌸 Екстракти золотих та червоних водоростей – потужний ліфтинг та антиоксидантний захист
+💧 Гіалуронат натрію – інтенсивне зволоження
+🛡️ Зелений чай, алое, кофеїн – тонізація та антиоксидантна дія
+⚡ ПДРН, лецитин, убіхінон – омолодження та відновлення клітин
+📌 Показання до застосування:
+Вікова та зневоднена шкіра
+Зморшки та пігментація
+Знижений тонус
+Набряклість
+📌 Спосіб застосування:  
+Змішати 30 г порошку з 40 мл води до однорідної консистенції.
+Нанести товстим шаром на обличчя, шию, декольте, включаючи зону очей та губ.
+Маска застигає за 5 хвилин. Тримати 15–30 хвилин, зняти єдиним шаром.
+Для підсилення ефекту рекомендується наносити антивікові сироватки під маску.
+✔️ Характеристики продукту:
+Тип: Антивікова альгінатна маска
+Об’єм: 200 г
+Призначення: Ліфтинг, омолодження, зволоження
+Тип шкіри: Вікова, зневоднена, з пігментацією
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Smart4Derma Golden Algae Mask – твій must-have для ліфтингу та сяйва шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>715</t>
+  </si>
+  <si>
+    <t>715(1)</t>
+  </si>
+  <si>
+    <t>✨ Smart4Derma Alginate Moisture Mask – глибоке зволоження та відновлення! ✨
+🌿 Професійна формула для обличчя, шиї та декольте:
+💧 Формує 3D-сітку для проникнення активних компонентів
+🌸 Забезпечує пролонговане зволоження та регенерацію
+🛡️ Зменшує зморшки та пігментацію
+⚡ Освітлює, тонізує та знімає набряки
+🌟 Дарує гладкість та ліфтинг-ефект
+💚 Результат – пружна, сяюча та доглянута шкіра після кожного застосування!
+📌 Активні компоненти:
+🌱 Альгінат – основа для глибокого проникнення
+🌸 Центелла азійська – заспокоює та відновлює
+💧 Гіалуронат натрію та сечовина – інтенсивне зволоження
+🛡️ Комплекс амінокислот, есцин, гліциризат амонію – регенерація та захист
+⚡ Гідролізований білок дріжджів, аскорбіл фосфат магнію, бета-глюкан – антиоксидантна дія
+🌟 sh-олігопептид-1 – стимуляція росту клітин та омолодження
+📌 Ефект від застосування:
+Глибоке зволоження
+Відновлення та регенерація
+Зменшення зморшок
+Освітлення та тонізація
+Ліфтинг та гладкість
+Зняття набряклості
+📌 Спосіб застосування:  
+Змішати 30 г порошку з 40 мл води до консистенції густої сметани.
+Нанести товстим шаром на очищену шкіру обличчя, шиї та декольте, включаючи ділянки очей і губ.
+Знімати через 25–30 хвилин єдиним пластом.
+Для посилення ефекту рекомендується використовувати сироватки під маску.
+✔️ Характеристики продукту:
+Тип: Альгінатна зволожувальна маска
+Об’єм: 200 г
+Призначення: Зволоження, відновлення, омолодження
+Тип шкіри: Суха, зневоднена, вікова
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Smart4Derma Alginate Moisture Mask – твій must-have для глибокого зволоження та сяйва шкіри!</t>
+  </si>
+  <si>
+    <t>515</t>
+  </si>
+  <si>
+    <t>515(1)</t>
+  </si>
+  <si>
+    <t>Альгінатна маска для проблемної шкіри з вулканічним пилом 200 г</t>
+  </si>
+  <si>
+    <t>Альгінатна маска зволожувальна 200 г</t>
+  </si>
+  <si>
+    <t>✨ Smart4Derma Alginate Mask Volcanic Dust – очищення та баланс! ✨
+🌿 Професійна формула для жирної та проблемної шкіри:
+💧 Себорегуляція та нормалізація вироблення себума
+🌸 Глибоке зволоження та заспокійливий ефект
+🛡️ Зняття запалень та подразнень
+⚡ Антибактеріальна дія та зменшення акне
+🌟 Освітлення та дренажний ефект
+💚 Результат – чиста, матова та здорова шкіра без недоліків!
+📌 Активні компоненти:
+🌱 Вулканічний пил та діатоміт – себорегуляція та очищення
+🌸 Екстракти лайма, ромашки, чайного дерева – антисептична та заспокійлива дія
+💧 Центелла азіатська – відновлення та регенерація
+🛡️ Ніацинамід – контроль себуму та вирівнювання тону
+🌟 CutiBiome – нормалізація мікробіому
+📌 Застосування:
+Підходить для обличчя, шиї, декольте, зони очей і губ
+30 г порошку змішати з 40 мл води до однорідної консистенції
+Нанести товстим шаром, витримати 15–30 хвилин
+Зняти одним рухом цілісним пластом
+Для посилення ефекту рекомендується наносити сироватки під маску
+✔️ Характеристики продукту:
+Тип: Альгінатна маска з вулканічним пилом
+Об’єм: 200 г
+Призначення: Очищення, себорегуляція, антибактеріальна дія, освітлення
+Тип шкіри: Жирна, комбінована, проблемна
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Smart4Derma Volcanic Alginate Mask – твій must-have для догляду за проблемною шкірою та контролю акне! 🌟</t>
+  </si>
+  <si>
+    <t>314</t>
+  </si>
+  <si>
+    <t>314(1)</t>
+  </si>
+  <si>
+    <t>Ліполітичний контурний гель із зеленою кавою та водоростями 500 мл</t>
+  </si>
+  <si>
+    <t>✨ Smart4Derma Lipolytic Gel Green Coffee – скульптурування та антицелюлітний ефект! ✨
+🌿 Професійна формула для моделювання обличчя та тіла:
+💧 Інтенсивно стимулює ліполіз та активізує кровообіг
+🌸 Має виражену дефіброзуючу дію – пом’якшує рубцеві зміни
+🛡️ Зменшує фіброз жирової тканини при целюліті
+⚡ Мінімізує нерівності, розтяжки та прояви целюліту
+🌟 Усуває набряки та підтримує тонус шкіри
+💚 Результат – підтягнута, гладка та пружна шкіра з ефектом скульптурування!
+📌 Активні компоненти:
+🌱 Екстракт зеленої кави – стимуляція ліполізу та антицелюлітна дія
+🌊 Екстракти водоростей (фукус, ламінарія, саргасові, спіруліна) – дренаж та детокс
+💧 Гіалуронова кислота та сік алое – інтенсивне зволоження та відновлення
+🛡️ Екстракт артишока, центелли азійської – антиоксидантна та тонізуюча дія
+⚡ L-карнітин, кофеїн, метилсіланол мануроат, манітол – стимуляція метаболізму та розщеплення жирів
+🌟 Hydagen® Aquaporin, бензил нікотинат, епігалокатехінгалат глюкозид – активація мікроциркуляції та регенерація
+📌 Особливості:
+Зручний дозатор для економного використання
+Підходить для професійного та домашнього догляду
+Ідеальний для антицелюлітних програм та моделювання контурів
+✔️ Характеристики продукту:
+Тип: Ліполітичний гель для обличчя та тіла
+Об’єм: 500 мл
+Призначення: Антицелюлітна дія, ліполіз, підтягування
+Тип шкіри: Будь-яка, особливо з проявами целюліту та набряками
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+🌟 Smart4Derma Lipolytic Gel – твій must-have для гладкої та підтягнутої шкіри без целюліту! 🌟</t>
+  </si>
+  <si>
+    <t>266</t>
+  </si>
+  <si>
+    <t>266(1)</t>
+  </si>
+  <si>
+    <t>Протизапальний гель з ніацинамідом 500 мл</t>
+  </si>
+  <si>
+    <t>✨ Smart4Derma Anti-Inflammatory Gel – чиста та спокійна шкіра! ✨
+🌿 Професійна формула для проблемної шкіри:
+💧 Нормалізує гідроліпідний баланс та контролює себум
+🌸 Інгібує 5-альфа-редуктазу, попереджаючи закупорку пір
+🛡️ Має протизапальну та антибактеріальну дію
+⚡ Освітлює плями постакне та оновлює епідерміс
+🌟 Дарує матуючий ефект та здоровий вигляд шкіри
+💚 Результат – рівна, матова та доглянута шкіра без запальних елементів!
+📌 Активні компоненти:
+🌱 Ніацинамід – протизапальна та депігментуюча дія
+🌸 Алое барбаденсіс – заспокоює та зволожує
+💧 Екстракт лайма – антиоксидантний ефект
+🛡️ Ромашка – протизапальні властивості
+⚡ Чайне дерево – антибактеріальна дія
+🌟 Мінерали Мертвого моря – живлення та відновлення
+📌 Основні властивості:
+Інгібує 5-альфа-редуктазу
+Дезінфікує та матує шкіру
+Знімає запалення та подразнення
+Освітлює плями постакне
+Допомагає боротися із закупореними порами
+✔️ Характеристики продукту:
+Тип: Протизапальний гель для проблемної шкіри
+Об’єм: 500 мл
+Призначення: Протизапальна, антибактеріальна та депігментуюча дія
+Тип шкіри: Жирна, комбінована, проблемна
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+Особливість: Зручний дозатор для економного використання
+🌟 Smart4Derma Niacinamide Gel – твій must-have для контролю акне та здорової шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>265</t>
+  </si>
+  <si>
+    <t>265(1)</t>
+  </si>
+  <si>
+    <t>Інтенсивний освітлювальний гель «ꜱʏᴍ ᴡʜɪᴛᴇ» 500 мл</t>
+  </si>
+  <si>
+    <t>✨ Smart4Derma SYM WHITE Gel – освітлення та захист! ✨
+🌿 Інтенсивна формула для боротьби з пігментацією та фотостарінням:
+💧 Блокує вироблення та передачу меланіну
+🌸 Освітлює існуючі пігментні плями
+🛡️ Запобігає появі нових плям
+⚡ Відновлює гідроліпідний баланс та зміцнює бар’єрні функції
+🌟 Має антиоксидантну дію та не подразнює шкіру
+💚 Результат – рівний тон, сяйво та здоровий вигляд шкіри!
+📌 Активні компоненти:
+🌱 SYMWHITE та арбутин – блокують тирозиназу та освітлюють пігментацію
+🌸 Екстракти толокнянки, кресса, лакриці, софори японської – природне освітлення та антиоксидантний ефект
+💧 Гіалуронова кислота та лецитин – інтенсивне зволоження та відновлення
+🛡️ Ізофлавони сої, нанопептид-1, аскорбіл пальмітат – омолодження та регенерація
+⚡ Глутатіон, диглюкозил галова кислота, AMITOSE DGA – антиоксидантний захист та вирівнювання тону
+🌊 Екстракт бурої водорості – живлення та тонізація
+📌 Основні переваги:
+Інгібує фермент тирозиназу
+Блокує передачу меланіну
+Освітлює та запобігає пігментації
+Зволожує та відновлює баланс шкіри
+Має м’яку дію без подразнень
+✔️ Характеристики продукту:
+Тип: Освітлюючий гель проти пігментації
+Об’єм: 500 мл
+Призначення: Освітлення, антиоксидантний захист, профілактика фотостаріння
+Тип шкіри: З пігментацією, нерівним тоном, вікова
+Бренд: Smart4Derma
+Країна виробництва: 🇺🇦 Україна
+Особливість: Зручний дозатор для економного використання
+🌟 Smart4Derma SYM WHITE Gel – твій must-have у боротьбі з пігментацією та фотостарінням! 🌟</t>
+  </si>
+  <si>
+    <t>264</t>
+  </si>
+  <si>
+    <t>264(1)</t>
   </si>
 </sst>
 </file>
@@ -7726,18 +8259,15 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7751,10 +8281,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -8214,25 +8753,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K158"/>
+  <dimension ref="A1:K160"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" style="12" customWidth="1"/>
-    <col min="2" max="2" width="37.44140625" style="9" customWidth="1"/>
-    <col min="3" max="3" width="16" style="9" customWidth="1"/>
-    <col min="4" max="4" width="14.88671875" style="9" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" style="9" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" style="9" customWidth="1"/>
-    <col min="7" max="7" width="12" style="9" customWidth="1"/>
-    <col min="8" max="8" width="18.88671875" style="9" customWidth="1"/>
-    <col min="9" max="9" width="21.109375" style="9" customWidth="1"/>
-    <col min="10" max="10" width="56" style="9" customWidth="1"/>
-    <col min="11" max="11" width="18" style="12" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="9"/>
+    <col min="1" max="1" width="12" style="14" customWidth="1"/>
+    <col min="2" max="2" width="37.44140625" style="15" customWidth="1"/>
+    <col min="3" max="3" width="16" style="15" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" style="15" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" style="15" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" style="15" customWidth="1"/>
+    <col min="7" max="7" width="12" style="15" customWidth="1"/>
+    <col min="8" max="8" width="18.88671875" style="15" customWidth="1"/>
+    <col min="9" max="9" width="21.109375" style="15" customWidth="1"/>
+    <col min="10" max="10" width="56" style="15" customWidth="1"/>
+    <col min="11" max="11" width="18" style="14" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="7" customFormat="1" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:11" s="18" customFormat="1" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
@@ -8262,4436 +8801,4751 @@
       <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="10" t="s">
         <v>649</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="11" t="s">
         <v>650</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="11" t="s">
         <v>653</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="7">
         <v>3500</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="7">
         <v>3100</v>
       </c>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8">
+      <c r="F2" s="7"/>
+      <c r="G2" s="7">
         <v>10</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="11" t="s">
         <v>652</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="11" t="s">
         <v>657</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="11" t="s">
         <v>651</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="12" t="s">
         <v>649</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="10" t="s">
         <v>655</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="11" t="s">
         <v>654</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="11" t="s">
         <v>658</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="7">
         <v>1400</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="7">
         <v>1000</v>
       </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8">
+      <c r="F3" s="7"/>
+      <c r="G3" s="7">
         <v>25</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="11" t="s">
         <v>657</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="11" t="s">
         <v>656</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="12" t="s">
         <v>655</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="10" t="s">
         <v>660</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="11" t="s">
         <v>659</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="11" t="s">
         <v>658</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="7">
         <v>1350</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="7">
         <v>1100</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8">
+      <c r="F4" s="7"/>
+      <c r="G4" s="7">
         <v>35</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="11" t="s">
         <v>657</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="11" t="s">
         <v>661</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="K4" s="12" t="s">
         <v>660</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="10" t="s">
         <v>663</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="11" t="s">
         <v>662</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="11" t="s">
         <v>658</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="7">
         <v>1300</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="7">
         <v>1100</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8">
+      <c r="F5" s="7"/>
+      <c r="G5" s="7">
         <v>31</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="11" t="s">
         <v>664</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="11" t="s">
         <v>657</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="J5" s="11" t="s">
         <v>665</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="12" t="s">
         <v>663</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="9" t="s">
         <v>668</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>666</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="7">
         <v>1200</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="7">
         <v>1100</v>
       </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8">
+      <c r="F6" s="7"/>
+      <c r="G6" s="7">
         <v>15</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="7" t="s">
         <v>667</v>
       </c>
-      <c r="K6" s="16" t="s">
+      <c r="K6" s="13" t="s">
         <v>668</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="9" t="s">
         <v>670</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>669</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="7">
         <v>1000</v>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8">
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7">
         <v>22</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="7" t="s">
         <v>672</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="7" t="s">
         <v>671</v>
       </c>
-      <c r="K7" s="16" t="s">
+      <c r="K7" s="13" t="s">
         <v>670</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="9" t="s">
         <v>674</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>673</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="7">
         <v>1000</v>
       </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8">
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7">
         <v>28</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="7" t="s">
         <v>672</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="7" t="s">
         <v>675</v>
       </c>
-      <c r="K8" s="16" t="s">
+      <c r="K8" s="13" t="s">
         <v>674</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="9" t="s">
         <v>677</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>676</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="7">
         <v>1000</v>
       </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8">
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7">
         <v>26</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" s="7" t="s">
         <v>678</v>
       </c>
-      <c r="K9" s="16" t="s">
+      <c r="K9" s="13" t="s">
         <v>677</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="9" t="s">
         <v>680</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>679</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="7">
         <v>1100</v>
       </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8">
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7">
         <v>22</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="J10" s="7" t="s">
         <v>681</v>
       </c>
-      <c r="K10" s="16" t="s">
+      <c r="K10" s="13" t="s">
         <v>680</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="9" t="s">
         <v>683</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>682</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="7">
         <v>800</v>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8">
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7">
         <v>22</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="7" t="s">
         <v>672</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="J11" s="7" t="s">
         <v>684</v>
       </c>
-      <c r="K11" s="16" t="s">
+      <c r="K11" s="13" t="s">
         <v>683</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="9" t="s">
         <v>687</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>685</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="7">
         <v>1100</v>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8">
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7">
         <v>8</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="J12" s="7" t="s">
         <v>686</v>
       </c>
-      <c r="K12" s="16" t="s">
+      <c r="K12" s="13" t="s">
         <v>687</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="9" t="s">
         <v>689</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>688</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="7">
         <v>1100</v>
       </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8">
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7">
         <v>22</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="I13" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="J13" s="7" t="s">
         <v>690</v>
       </c>
-      <c r="K13" s="16" t="s">
+      <c r="K13" s="13" t="s">
         <v>689</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="9" t="s">
         <v>693</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>691</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="7">
         <v>1200</v>
       </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8">
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7">
         <v>22</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J14" s="7" t="s">
         <v>692</v>
       </c>
-      <c r="K14" s="16" t="s">
+      <c r="K14" s="13" t="s">
         <v>693</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="9" t="s">
         <v>696</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>694</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="7">
         <v>700</v>
       </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8">
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7">
         <v>15</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="H15" s="7" t="s">
         <v>695</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="J15" s="7" t="s">
         <v>697</v>
       </c>
-      <c r="K15" s="16" t="s">
+      <c r="K15" s="13" t="s">
         <v>696</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="9" t="s">
         <v>699</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>698</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="7">
         <v>1400</v>
       </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8">
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7">
         <v>22</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="I16" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="J16" s="7" t="s">
         <v>700</v>
       </c>
-      <c r="K16" s="16" t="s">
+      <c r="K16" s="13" t="s">
         <v>699</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="9" t="s">
         <v>702</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>701</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="7">
         <v>1400</v>
       </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8">
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7">
         <v>18</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="I17" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="J17" s="7" t="s">
         <v>703</v>
       </c>
-      <c r="K17" s="16" t="s">
+      <c r="K17" s="13" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="9" t="s">
         <v>705</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>704</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="7">
         <v>1100</v>
       </c>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8">
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7">
         <v>32</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I18" s="8" t="s">
+      <c r="I18" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="J18" s="7" t="s">
         <v>706</v>
       </c>
-      <c r="K18" s="16" t="s">
+      <c r="K18" s="13" t="s">
         <v>705</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="9" t="s">
         <v>708</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="7" t="s">
         <v>707</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="7">
         <v>1700</v>
       </c>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8">
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7">
         <v>24</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H19" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="I19" s="8" t="s">
+      <c r="I19" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="J19" s="7" t="s">
         <v>709</v>
       </c>
-      <c r="K19" s="16" t="s">
+      <c r="K19" s="13" t="s">
         <v>708</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="9" t="s">
         <v>710</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="7" t="s">
         <v>807</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="7">
         <v>1300</v>
       </c>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8">
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7">
         <v>22</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H20" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="I20" s="8" t="s">
+      <c r="I20" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="J20" s="7" t="s">
         <v>711</v>
       </c>
-      <c r="K20" s="16" t="s">
+      <c r="K20" s="13" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="9" t="s">
         <v>713</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="7" t="s">
         <v>712</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="7">
         <v>900</v>
       </c>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8">
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7">
         <v>20</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="7" t="s">
         <v>672</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="I21" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="J21" s="7" t="s">
         <v>714</v>
       </c>
-      <c r="K21" s="16" t="s">
+      <c r="K21" s="13" t="s">
         <v>713</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="9" t="s">
         <v>717</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="7" t="s">
         <v>715</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="7">
         <v>1500</v>
       </c>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8">
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7">
         <v>23</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="H22" s="7" t="s">
         <v>672</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="I22" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="J22" s="7" t="s">
         <v>716</v>
       </c>
-      <c r="K22" s="16" t="s">
+      <c r="K22" s="13" t="s">
         <v>717</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="9" t="s">
         <v>720</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="7" t="s">
         <v>718</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="7">
         <v>1200</v>
       </c>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8">
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7">
         <v>36</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="I23" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J23" s="8" t="s">
+      <c r="J23" s="7" t="s">
         <v>719</v>
       </c>
-      <c r="K23" s="16" t="s">
+      <c r="K23" s="13" t="s">
         <v>720</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="9" t="s">
         <v>722</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="7" t="s">
         <v>721</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="7">
         <v>1200</v>
       </c>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8">
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7">
         <v>22</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="I24" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="J24" s="7" t="s">
         <v>723</v>
       </c>
-      <c r="K24" s="16" t="s">
+      <c r="K24" s="13" t="s">
         <v>722</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="9" t="s">
         <v>726</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="7" t="s">
         <v>724</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="7">
         <v>1200</v>
       </c>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8">
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7">
         <v>17</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="H25" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I25" s="8" t="s">
+      <c r="I25" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J25" s="8" t="s">
+      <c r="J25" s="7" t="s">
         <v>725</v>
       </c>
-      <c r="K25" s="16" t="s">
+      <c r="K25" s="13" t="s">
         <v>726</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="9" t="s">
         <v>728</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="7" t="s">
         <v>727</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="7">
         <v>1200</v>
       </c>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8">
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7">
         <v>16</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="H26" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I26" s="8" t="s">
+      <c r="I26" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J26" s="8" t="s">
+      <c r="J26" s="7" t="s">
         <v>729</v>
       </c>
-      <c r="K26" s="16" t="s">
+      <c r="K26" s="13" t="s">
         <v>728</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="9" t="s">
         <v>731</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="7" t="s">
         <v>730</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="7">
         <v>1200</v>
       </c>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8">
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7">
         <v>16</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="H27" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="I27" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J27" s="8" t="s">
+      <c r="J27" s="7" t="s">
         <v>732</v>
       </c>
-      <c r="K27" s="16" t="s">
+      <c r="K27" s="13" t="s">
         <v>731</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="9" t="s">
         <v>734</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="7" t="s">
         <v>733</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="7">
         <v>900</v>
       </c>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8">
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7">
         <v>25</v>
       </c>
-      <c r="H28" s="8" t="s">
+      <c r="H28" s="7" t="s">
         <v>672</v>
       </c>
-      <c r="I28" s="8" t="s">
+      <c r="I28" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J28" s="8" t="s">
+      <c r="J28" s="7" t="s">
         <v>735</v>
       </c>
-      <c r="K28" s="16" t="s">
+      <c r="K28" s="13" t="s">
         <v>734</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="9" t="s">
         <v>737</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="7" t="s">
         <v>736</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="7">
         <v>800</v>
       </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8">
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7">
         <v>25</v>
       </c>
-      <c r="H29" s="8" t="s">
+      <c r="H29" s="7" t="s">
         <v>695</v>
       </c>
-      <c r="I29" s="8" t="s">
+      <c r="I29" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J29" s="8" t="s">
+      <c r="J29" s="7" t="s">
         <v>738</v>
       </c>
-      <c r="K29" s="16" t="s">
+      <c r="K29" s="13" t="s">
         <v>737</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="9" t="s">
         <v>741</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="7" t="s">
         <v>739</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="7">
         <v>2420</v>
       </c>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8">
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7">
         <v>16</v>
       </c>
-      <c r="H30" s="8" t="s">
+      <c r="H30" s="7" t="s">
         <v>652</v>
       </c>
-      <c r="I30" s="8" t="s">
+      <c r="I30" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J30" s="8" t="s">
+      <c r="J30" s="7" t="s">
         <v>740</v>
       </c>
-      <c r="K30" s="16" t="s">
+      <c r="K30" s="13" t="s">
         <v>741</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="9" t="s">
         <v>743</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="7" t="s">
         <v>742</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="7">
         <v>2800</v>
       </c>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8">
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7">
         <v>14</v>
       </c>
-      <c r="H31" s="8" t="s">
+      <c r="H31" s="7" t="s">
         <v>652</v>
       </c>
-      <c r="I31" s="8" t="s">
+      <c r="I31" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J31" s="8" t="s">
+      <c r="J31" s="7" t="s">
         <v>744</v>
       </c>
-      <c r="K31" s="16" t="s">
+      <c r="K31" s="13" t="s">
         <v>743</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="9" t="s">
         <v>746</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="7" t="s">
         <v>745</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="7">
         <v>900</v>
       </c>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8">
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7">
         <v>17</v>
       </c>
-      <c r="H32" s="8" t="s">
+      <c r="H32" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I32" s="8" t="s">
+      <c r="I32" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J32" s="8" t="s">
+      <c r="J32" s="7" t="s">
         <v>747</v>
       </c>
-      <c r="K32" s="16" t="s">
+      <c r="K32" s="13" t="s">
         <v>746</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="9" t="s">
         <v>749</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="7" t="s">
         <v>748</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D33" s="8">
+      <c r="D33" s="7">
         <v>1100</v>
       </c>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8">
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7">
         <v>9</v>
       </c>
-      <c r="H33" s="8" t="s">
+      <c r="H33" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="I33" s="8" t="s">
+      <c r="I33" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J33" s="8" t="s">
+      <c r="J33" s="7" t="s">
         <v>750</v>
       </c>
-      <c r="K33" s="16" t="s">
+      <c r="K33" s="13" t="s">
         <v>749</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="9" t="s">
         <v>753</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="7" t="s">
         <v>751</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D34" s="8">
+      <c r="D34" s="7">
         <v>4100</v>
       </c>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8">
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7">
         <v>17</v>
       </c>
-      <c r="H34" s="8" t="s">
+      <c r="H34" s="7" t="s">
         <v>652</v>
       </c>
-      <c r="I34" s="8" t="s">
+      <c r="I34" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J34" s="8" t="s">
+      <c r="J34" s="7" t="s">
         <v>752</v>
       </c>
-      <c r="K34" s="16" t="s">
+      <c r="K34" s="13" t="s">
         <v>754</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="9" t="s">
         <v>756</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="7" t="s">
         <v>755</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D35" s="8">
+      <c r="D35" s="7">
         <v>680</v>
       </c>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8">
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7">
         <v>15</v>
       </c>
-      <c r="H35" s="8" t="s">
+      <c r="H35" s="7" t="s">
         <v>695</v>
       </c>
-      <c r="I35" s="8" t="s">
+      <c r="I35" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J35" s="8" t="s">
+      <c r="J35" s="7" t="s">
         <v>757</v>
       </c>
-      <c r="K35" s="16" t="s">
+      <c r="K35" s="13" t="s">
         <v>756</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="9" t="s">
         <v>760</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="7" t="s">
         <v>758</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D36" s="8">
+      <c r="D36" s="7">
         <v>1180</v>
       </c>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8">
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7">
         <v>19</v>
       </c>
-      <c r="H36" s="8" t="s">
+      <c r="H36" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I36" s="8" t="s">
+      <c r="I36" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J36" s="8" t="s">
+      <c r="J36" s="7" t="s">
         <v>759</v>
       </c>
-      <c r="K36" s="16" t="s">
+      <c r="K36" s="13" t="s">
         <v>760</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="9" t="s">
         <v>763</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="7" t="s">
         <v>761</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D37" s="8">
+      <c r="D37" s="7">
         <v>1100</v>
       </c>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8">
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7">
         <v>15</v>
       </c>
-      <c r="H37" s="8" t="s">
+      <c r="H37" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I37" s="8" t="s">
+      <c r="I37" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J37" s="8" t="s">
+      <c r="J37" s="7" t="s">
         <v>762</v>
       </c>
-      <c r="K37" s="16" t="s">
+      <c r="K37" s="13" t="s">
         <v>763</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A38" s="11" t="s">
+      <c r="A38" s="9" t="s">
         <v>766</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="7" t="s">
         <v>764</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D38" s="8">
+      <c r="D38" s="7">
         <v>920</v>
       </c>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8">
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7">
         <v>19</v>
       </c>
-      <c r="H38" s="8" t="s">
+      <c r="H38" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I38" s="8" t="s">
+      <c r="I38" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J38" s="8" t="s">
+      <c r="J38" s="7" t="s">
         <v>765</v>
       </c>
-      <c r="K38" s="16" t="s">
+      <c r="K38" s="13" t="s">
         <v>766</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A39" s="11" t="s">
+      <c r="A39" s="9" t="s">
         <v>768</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="7" t="s">
         <v>767</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D39" s="8">
+      <c r="D39" s="7">
         <v>760</v>
       </c>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8">
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7">
         <v>24</v>
       </c>
-      <c r="H39" s="8" t="s">
+      <c r="H39" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="I39" s="8" t="s">
+      <c r="I39" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J39" s="8" t="s">
+      <c r="J39" s="7" t="s">
         <v>769</v>
       </c>
-      <c r="K39" s="16" t="s">
+      <c r="K39" s="13" t="s">
         <v>768</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A40" s="11" t="s">
+      <c r="A40" s="9" t="s">
         <v>771</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="7" t="s">
         <v>770</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D40" s="8">
+      <c r="D40" s="7">
         <v>880</v>
       </c>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8">
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7">
         <v>27</v>
       </c>
-      <c r="H40" s="8" t="s">
+      <c r="H40" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I40" s="8" t="s">
+      <c r="I40" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J40" s="8" t="s">
+      <c r="J40" s="7" t="s">
         <v>772</v>
       </c>
-      <c r="K40" s="16" t="s">
+      <c r="K40" s="13" t="s">
         <v>771</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A41" s="11" t="s">
+      <c r="A41" s="9" t="s">
         <v>774</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="7" t="s">
         <v>773</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D41" s="8">
+      <c r="D41" s="7">
         <v>1720</v>
       </c>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8">
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7">
         <v>28</v>
       </c>
-      <c r="H41" s="8" t="s">
+      <c r="H41" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I41" s="8" t="s">
+      <c r="I41" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J41" s="8" t="s">
+      <c r="J41" s="7" t="s">
         <v>775</v>
       </c>
-      <c r="K41" s="16" t="s">
+      <c r="K41" s="13" t="s">
         <v>774</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A42" s="11" t="s">
+      <c r="A42" s="9" t="s">
         <v>777</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="7" t="s">
         <v>776</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D42" s="8">
+      <c r="D42" s="7">
         <v>860</v>
       </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8">
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7">
         <v>16</v>
       </c>
-      <c r="H42" s="8" t="s">
+      <c r="H42" s="7" t="s">
         <v>672</v>
       </c>
-      <c r="I42" s="8" t="s">
+      <c r="I42" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J42" s="8" t="s">
+      <c r="J42" s="7" t="s">
         <v>778</v>
       </c>
-      <c r="K42" s="16" t="s">
+      <c r="K42" s="13" t="s">
         <v>777</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A43" s="11" t="s">
+      <c r="A43" s="9" t="s">
         <v>781</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="7" t="s">
         <v>779</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D43" s="8">
+      <c r="D43" s="7">
         <v>740</v>
       </c>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8">
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7">
         <v>26</v>
       </c>
-      <c r="H43" s="8" t="s">
+      <c r="H43" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I43" s="8" t="s">
+      <c r="I43" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J43" s="8" t="s">
+      <c r="J43" s="7" t="s">
         <v>780</v>
       </c>
-      <c r="K43" s="16" t="s">
+      <c r="K43" s="13" t="s">
         <v>781</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A44" s="11" t="s">
+      <c r="A44" s="9" t="s">
         <v>784</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="7" t="s">
         <v>782</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="C44" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D44" s="8">
+      <c r="D44" s="7">
         <v>540</v>
       </c>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8">
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7">
         <v>17</v>
       </c>
-      <c r="H44" s="8" t="s">
+      <c r="H44" s="7" t="s">
         <v>783</v>
       </c>
-      <c r="I44" s="8" t="s">
+      <c r="I44" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J44" s="8" t="s">
+      <c r="J44" s="7" t="s">
         <v>785</v>
       </c>
-      <c r="K44" s="16" t="s">
+      <c r="K44" s="13" t="s">
         <v>784</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="9" t="s">
         <v>787</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="7" t="s">
         <v>786</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D45" s="8">
+      <c r="D45" s="7">
         <v>740</v>
       </c>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8">
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7">
         <v>19</v>
       </c>
-      <c r="H45" s="8" t="s">
+      <c r="H45" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I45" s="8" t="s">
+      <c r="I45" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J45" s="8" t="s">
+      <c r="J45" s="7" t="s">
         <v>788</v>
       </c>
-      <c r="K45" s="16" t="s">
+      <c r="K45" s="13" t="s">
         <v>787</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A46" s="11" t="s">
+      <c r="A46" s="9" t="s">
         <v>790</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="7" t="s">
         <v>795</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C46" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D46" s="8">
+      <c r="D46" s="7">
         <v>640</v>
       </c>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8">
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7">
         <v>29</v>
       </c>
-      <c r="H46" s="8" t="s">
+      <c r="H46" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I46" s="8" t="s">
+      <c r="I46" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J46" s="8" t="s">
+      <c r="J46" s="7" t="s">
         <v>789</v>
       </c>
-      <c r="K46" s="16" t="s">
+      <c r="K46" s="13" t="s">
         <v>790</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A47" s="11" t="s">
+      <c r="A47" s="9" t="s">
         <v>791</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="7" t="s">
         <v>794</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C47" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D47" s="8">
+      <c r="D47" s="7">
         <v>1460</v>
       </c>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8">
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7">
         <v>17</v>
       </c>
-      <c r="H47" s="8" t="s">
+      <c r="H47" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I47" s="8" t="s">
+      <c r="I47" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J47" s="8" t="s">
+      <c r="J47" s="7" t="s">
         <v>792</v>
       </c>
-      <c r="K47" s="16" t="s">
+      <c r="K47" s="13" t="s">
         <v>791</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A48" s="11" t="s">
+      <c r="A48" s="9" t="s">
         <v>796</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="7" t="s">
         <v>793</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="C48" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D48" s="8">
+      <c r="D48" s="7">
         <v>800</v>
       </c>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8">
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7">
         <v>19</v>
       </c>
-      <c r="H48" s="8" t="s">
+      <c r="H48" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I48" s="8" t="s">
+      <c r="I48" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J48" s="8" t="s">
+      <c r="J48" s="7" t="s">
         <v>797</v>
       </c>
-      <c r="K48" s="16" t="s">
+      <c r="K48" s="13" t="s">
         <v>796</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A49" s="11" t="s">
+      <c r="A49" s="9" t="s">
         <v>799</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="7" t="s">
         <v>798</v>
       </c>
-      <c r="C49" s="8" t="s">
+      <c r="C49" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D49" s="8">
+      <c r="D49" s="7">
         <v>860</v>
       </c>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8">
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7">
         <v>22</v>
       </c>
-      <c r="H49" s="8" t="s">
+      <c r="H49" s="7" t="s">
         <v>672</v>
       </c>
-      <c r="I49" s="8" t="s">
+      <c r="I49" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J49" s="8" t="s">
+      <c r="J49" s="7" t="s">
         <v>800</v>
       </c>
-      <c r="K49" s="16" t="s">
+      <c r="K49" s="13" t="s">
         <v>799</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="9" t="s">
         <v>802</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="7" t="s">
         <v>801</v>
       </c>
-      <c r="C50" s="8" t="s">
+      <c r="C50" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D50" s="8">
+      <c r="D50" s="7">
         <v>800</v>
       </c>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="8">
+      <c r="E50" s="7"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7">
         <v>25</v>
       </c>
-      <c r="H50" s="8" t="s">
+      <c r="H50" s="7" t="s">
         <v>672</v>
       </c>
-      <c r="I50" s="8" t="s">
+      <c r="I50" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J50" s="8" t="s">
+      <c r="J50" s="7" t="s">
         <v>803</v>
       </c>
-      <c r="K50" s="16" t="s">
+      <c r="K50" s="13" t="s">
         <v>802</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="9" t="s">
         <v>805</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B51" s="7" t="s">
         <v>804</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="C51" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D51" s="8">
+      <c r="D51" s="7">
         <v>1400</v>
       </c>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8">
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7">
         <v>18</v>
       </c>
-      <c r="H51" s="8" t="s">
+      <c r="H51" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I51" s="8" t="s">
+      <c r="I51" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J51" s="8" t="s">
+      <c r="J51" s="7" t="s">
         <v>806</v>
       </c>
-      <c r="K51" s="16" t="s">
+      <c r="K51" s="13" t="s">
         <v>805</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A52" s="11" t="s">
+      <c r="A52" s="9" t="s">
         <v>810</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="7" t="s">
         <v>808</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="C52" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D52" s="8">
+      <c r="D52" s="7">
         <v>1260</v>
       </c>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8">
+      <c r="E52" s="7"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="7">
         <v>26</v>
       </c>
-      <c r="H52" s="8" t="s">
+      <c r="H52" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I52" s="8" t="s">
+      <c r="I52" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J52" s="8" t="s">
+      <c r="J52" s="7" t="s">
         <v>809</v>
       </c>
-      <c r="K52" s="16" t="s">
+      <c r="K52" s="13" t="s">
         <v>810</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A53" s="11" t="s">
+      <c r="A53" s="9" t="s">
         <v>812</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B53" s="7" t="s">
         <v>811</v>
       </c>
-      <c r="C53" s="8" t="s">
+      <c r="C53" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D53" s="8">
+      <c r="D53" s="7">
         <v>800</v>
       </c>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
-      <c r="G53" s="8">
+      <c r="E53" s="7"/>
+      <c r="F53" s="7"/>
+      <c r="G53" s="7">
         <v>24</v>
       </c>
-      <c r="H53" s="8" t="s">
+      <c r="H53" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="I53" s="8" t="s">
+      <c r="I53" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J53" s="8" t="s">
+      <c r="J53" s="7" t="s">
         <v>813</v>
       </c>
-      <c r="K53" s="16" t="s">
+      <c r="K53" s="13" t="s">
         <v>812</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A54" s="11" t="s">
+      <c r="A54" s="9" t="s">
         <v>816</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="7" t="s">
         <v>814</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="C54" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D54" s="8">
+      <c r="D54" s="7">
         <v>1380</v>
       </c>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8">
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7">
         <v>17</v>
       </c>
-      <c r="H54" s="8" t="s">
+      <c r="H54" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="I54" s="8" t="s">
+      <c r="I54" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J54" s="8" t="s">
+      <c r="J54" s="7" t="s">
         <v>815</v>
       </c>
-      <c r="K54" s="16" t="s">
+      <c r="K54" s="13" t="s">
         <v>816</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A55" s="11" t="s">
+      <c r="A55" s="9" t="s">
         <v>818</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="7" t="s">
         <v>817</v>
       </c>
-      <c r="C55" s="8" t="s">
+      <c r="C55" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D55" s="8">
+      <c r="D55" s="7">
         <v>840</v>
       </c>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
-      <c r="G55" s="8">
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7">
         <v>18</v>
       </c>
-      <c r="H55" s="8" t="s">
+      <c r="H55" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I55" s="8" t="s">
+      <c r="I55" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J55" s="8" t="s">
+      <c r="J55" s="7" t="s">
         <v>819</v>
       </c>
-      <c r="K55" s="16" t="s">
+      <c r="K55" s="13" t="s">
         <v>818</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A56" s="11" t="s">
+      <c r="A56" s="9" t="s">
         <v>822</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B56" s="7" t="s">
         <v>820</v>
       </c>
-      <c r="C56" s="8" t="s">
+      <c r="C56" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D56" s="8">
+      <c r="D56" s="7">
         <v>1680</v>
       </c>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8">
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="7">
         <v>25</v>
       </c>
-      <c r="H56" s="8" t="s">
+      <c r="H56" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I56" s="8" t="s">
+      <c r="I56" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J56" s="8" t="s">
+      <c r="J56" s="7" t="s">
         <v>821</v>
       </c>
-      <c r="K56" s="16" t="s">
+      <c r="K56" s="13" t="s">
         <v>822</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A57" s="11" t="s">
+      <c r="A57" s="9" t="s">
         <v>825</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" s="7" t="s">
         <v>823</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D57" s="8">
+      <c r="D57" s="7">
         <v>1200</v>
       </c>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
-      <c r="G57" s="8">
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="7">
         <v>21</v>
       </c>
-      <c r="H57" s="8" t="s">
+      <c r="H57" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I57" s="8" t="s">
+      <c r="I57" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J57" s="8" t="s">
+      <c r="J57" s="7" t="s">
         <v>824</v>
       </c>
-      <c r="K57" s="16" t="s">
+      <c r="K57" s="13" t="s">
         <v>825</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A58" s="11" t="s">
+      <c r="A58" s="9" t="s">
         <v>828</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" s="7" t="s">
         <v>826</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="C58" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D58" s="8">
+      <c r="D58" s="7">
         <v>1100</v>
       </c>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8">
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="7">
         <v>14</v>
       </c>
-      <c r="H58" s="8" t="s">
+      <c r="H58" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I58" s="8" t="s">
+      <c r="I58" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J58" s="8" t="s">
+      <c r="J58" s="7" t="s">
         <v>827</v>
       </c>
-      <c r="K58" s="16" t="s">
+      <c r="K58" s="13" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A59" s="11" t="s">
+      <c r="A59" s="9" t="s">
         <v>831</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="B59" s="7" t="s">
         <v>829</v>
       </c>
-      <c r="C59" s="8" t="s">
+      <c r="C59" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D59" s="8">
+      <c r="D59" s="7">
         <v>1700</v>
       </c>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
-      <c r="G59" s="8">
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="7">
         <v>21</v>
       </c>
-      <c r="H59" s="8" t="s">
+      <c r="H59" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I59" s="8" t="s">
+      <c r="I59" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J59" s="8" t="s">
+      <c r="J59" s="7" t="s">
         <v>830</v>
       </c>
-      <c r="K59" s="16" t="s">
+      <c r="K59" s="13" t="s">
         <v>831</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A60" s="11" t="s">
+      <c r="A60" s="9" t="s">
         <v>834</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="7" t="s">
         <v>832</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="C60" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D60" s="8">
+      <c r="D60" s="7">
         <v>1060</v>
       </c>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8"/>
-      <c r="G60" s="8">
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="7">
         <v>14</v>
       </c>
-      <c r="H60" s="8" t="s">
+      <c r="H60" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="I60" s="8" t="s">
+      <c r="I60" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J60" s="8" t="s">
+      <c r="J60" s="7" t="s">
         <v>833</v>
       </c>
-      <c r="K60" s="16" t="s">
+      <c r="K60" s="13" t="s">
         <v>834</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A61" s="11" t="s">
+      <c r="A61" s="9" t="s">
         <v>837</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="B61" s="7" t="s">
         <v>835</v>
       </c>
-      <c r="C61" s="8" t="s">
+      <c r="C61" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D61" s="8">
+      <c r="D61" s="7">
         <v>1200</v>
       </c>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
-      <c r="G61" s="8">
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="7">
         <v>18</v>
       </c>
-      <c r="H61" s="8" t="s">
+      <c r="H61" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="I61" s="8" t="s">
+      <c r="I61" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J61" s="8" t="s">
+      <c r="J61" s="7" t="s">
         <v>836</v>
       </c>
-      <c r="K61" s="16" t="s">
+      <c r="K61" s="13" t="s">
         <v>837</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A62" s="11" t="s">
+      <c r="A62" s="9" t="s">
         <v>839</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="7" t="s">
         <v>838</v>
       </c>
-      <c r="C62" s="8" t="s">
+      <c r="C62" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D62" s="8">
+      <c r="D62" s="7">
         <v>1440</v>
       </c>
-      <c r="E62" s="8"/>
-      <c r="F62" s="8"/>
-      <c r="G62" s="8">
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
+      <c r="G62" s="7">
         <v>17</v>
       </c>
-      <c r="H62" s="8" t="s">
+      <c r="H62" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I62" s="8" t="s">
+      <c r="I62" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J62" s="8" t="s">
+      <c r="J62" s="7" t="s">
         <v>840</v>
       </c>
-      <c r="K62" s="16" t="s">
+      <c r="K62" s="13" t="s">
         <v>839</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A63" s="11" t="s">
+      <c r="A63" s="9" t="s">
         <v>843</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="B63" s="7" t="s">
         <v>841</v>
       </c>
-      <c r="C63" s="8" t="s">
+      <c r="C63" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D63" s="8">
+      <c r="D63" s="7">
         <v>1140</v>
       </c>
-      <c r="E63" s="8"/>
-      <c r="F63" s="8"/>
-      <c r="G63" s="8">
+      <c r="E63" s="7"/>
+      <c r="F63" s="7"/>
+      <c r="G63" s="7">
         <v>16</v>
       </c>
-      <c r="H63" s="8" t="s">
+      <c r="H63" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I63" s="8" t="s">
+      <c r="I63" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J63" s="8" t="s">
+      <c r="J63" s="7" t="s">
         <v>842</v>
       </c>
-      <c r="K63" s="16" t="s">
+      <c r="K63" s="13" t="s">
         <v>843</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A64" s="11" t="s">
+      <c r="A64" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B64" s="7" t="s">
         <v>844</v>
       </c>
-      <c r="C64" s="8" t="s">
+      <c r="C64" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D64" s="8">
+      <c r="D64" s="7">
         <v>1000</v>
       </c>
-      <c r="E64" s="8"/>
-      <c r="F64" s="8"/>
-      <c r="G64" s="8">
+      <c r="E64" s="7"/>
+      <c r="F64" s="7"/>
+      <c r="G64" s="7">
         <v>19</v>
       </c>
-      <c r="H64" s="8" t="s">
+      <c r="H64" s="7" t="s">
         <v>672</v>
       </c>
-      <c r="I64" s="8" t="s">
+      <c r="I64" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J64" s="8" t="s">
+      <c r="J64" s="7" t="s">
         <v>845</v>
       </c>
-      <c r="K64" s="16" t="s">
+      <c r="K64" s="13" t="s">
         <v>846</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A65" s="11" t="s">
+      <c r="A65" s="9" t="s">
         <v>849</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="B65" s="7" t="s">
         <v>847</v>
       </c>
-      <c r="C65" s="8" t="s">
+      <c r="C65" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D65" s="8">
+      <c r="D65" s="7">
         <v>780</v>
       </c>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8"/>
-      <c r="G65" s="8">
+      <c r="E65" s="7"/>
+      <c r="F65" s="7"/>
+      <c r="G65" s="7">
         <v>16</v>
       </c>
-      <c r="H65" s="8" t="s">
+      <c r="H65" s="7" t="s">
         <v>672</v>
       </c>
-      <c r="I65" s="8" t="s">
+      <c r="I65" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J65" s="8" t="s">
+      <c r="J65" s="7" t="s">
         <v>848</v>
       </c>
-      <c r="K65" s="16" t="s">
+      <c r="K65" s="13" t="s">
         <v>849</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A66" s="11" t="s">
+      <c r="A66" s="9" t="s">
         <v>853</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" s="7" t="s">
         <v>850</v>
       </c>
-      <c r="C66" s="8" t="s">
+      <c r="C66" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D66" s="8">
+      <c r="D66" s="7">
         <v>1320</v>
       </c>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
-      <c r="G66" s="8">
+      <c r="E66" s="7"/>
+      <c r="F66" s="7"/>
+      <c r="G66" s="7">
         <v>19</v>
       </c>
-      <c r="H66" s="8" t="s">
+      <c r="H66" s="7" t="s">
         <v>851</v>
       </c>
-      <c r="I66" s="8" t="s">
+      <c r="I66" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J66" s="8" t="s">
+      <c r="J66" s="7" t="s">
         <v>852</v>
       </c>
-      <c r="K66" s="16" t="s">
+      <c r="K66" s="13" t="s">
         <v>853</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A67" s="11" t="s">
+      <c r="A67" s="9" t="s">
         <v>856</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B67" s="7" t="s">
         <v>854</v>
       </c>
-      <c r="C67" s="8" t="s">
+      <c r="C67" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D67" s="8">
+      <c r="D67" s="7">
         <v>680</v>
       </c>
-      <c r="E67" s="8"/>
-      <c r="F67" s="8"/>
-      <c r="G67" s="8">
+      <c r="E67" s="7"/>
+      <c r="F67" s="7"/>
+      <c r="G67" s="7">
         <v>25</v>
       </c>
-      <c r="H67" s="8" t="s">
+      <c r="H67" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I67" s="8" t="s">
+      <c r="I67" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J67" s="8" t="s">
+      <c r="J67" s="7" t="s">
         <v>855</v>
       </c>
-      <c r="K67" s="16" t="s">
+      <c r="K67" s="13" t="s">
         <v>856</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A68" s="11" t="s">
+      <c r="A68" s="9" t="s">
         <v>859</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" s="7" t="s">
         <v>857</v>
       </c>
-      <c r="C68" s="8" t="s">
+      <c r="C68" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D68" s="8">
+      <c r="D68" s="7">
         <v>980</v>
       </c>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="8">
+      <c r="E68" s="7"/>
+      <c r="F68" s="7"/>
+      <c r="G68" s="7">
         <v>17</v>
       </c>
-      <c r="H68" s="8" t="s">
+      <c r="H68" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I68" s="8" t="s">
+      <c r="I68" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J68" s="8" t="s">
+      <c r="J68" s="7" t="s">
         <v>858</v>
       </c>
-      <c r="K68" s="16" t="s">
+      <c r="K68" s="13" t="s">
         <v>859</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A69" s="11" t="s">
+      <c r="A69" s="9" t="s">
         <v>861</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="B69" s="7" t="s">
         <v>860</v>
       </c>
-      <c r="C69" s="8" t="s">
+      <c r="C69" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D69" s="8">
+      <c r="D69" s="7">
         <v>1260</v>
       </c>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
-      <c r="G69" s="8">
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
+      <c r="G69" s="7">
         <v>21</v>
       </c>
-      <c r="H69" s="8" t="s">
+      <c r="H69" s="7" t="s">
         <v>695</v>
       </c>
-      <c r="I69" s="8" t="s">
+      <c r="I69" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J69" s="8" t="s">
+      <c r="J69" s="7" t="s">
         <v>862</v>
       </c>
-      <c r="K69" s="16" t="s">
+      <c r="K69" s="13" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A70" s="11" t="s">
+      <c r="A70" s="9" t="s">
         <v>865</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" s="7" t="s">
         <v>863</v>
       </c>
-      <c r="C70" s="8" t="s">
+      <c r="C70" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D70" s="8">
+      <c r="D70" s="7">
         <v>1020</v>
       </c>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8"/>
-      <c r="G70" s="8">
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
+      <c r="G70" s="7">
         <v>26</v>
       </c>
-      <c r="H70" s="8" t="s">
+      <c r="H70" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I70" s="8" t="s">
+      <c r="I70" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J70" s="8" t="s">
+      <c r="J70" s="7" t="s">
         <v>864</v>
       </c>
-      <c r="K70" s="16" t="s">
+      <c r="K70" s="13" t="s">
         <v>865</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A71" s="11" t="s">
+      <c r="A71" s="9" t="s">
         <v>867</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="B71" s="7" t="s">
         <v>866</v>
       </c>
-      <c r="C71" s="8" t="s">
+      <c r="C71" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D71" s="8">
+      <c r="D71" s="7">
         <v>980</v>
       </c>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="8">
+      <c r="E71" s="7"/>
+      <c r="F71" s="7"/>
+      <c r="G71" s="7">
         <v>16</v>
       </c>
-      <c r="H71" s="8" t="s">
+      <c r="H71" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="I71" s="8" t="s">
+      <c r="I71" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J71" s="8" t="s">
+      <c r="J71" s="7" t="s">
         <v>868</v>
       </c>
-      <c r="K71" s="16" t="s">
+      <c r="K71" s="13" t="s">
         <v>867</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A72" s="11" t="s">
+      <c r="A72" s="9" t="s">
         <v>871</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" s="7" t="s">
         <v>869</v>
       </c>
-      <c r="C72" s="8" t="s">
+      <c r="C72" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D72" s="8">
+      <c r="D72" s="7">
         <v>1220</v>
       </c>
-      <c r="E72" s="8"/>
-      <c r="F72" s="8"/>
-      <c r="G72" s="8">
+      <c r="E72" s="7"/>
+      <c r="F72" s="7"/>
+      <c r="G72" s="7">
         <v>17</v>
       </c>
-      <c r="H72" s="8" t="s">
+      <c r="H72" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I72" s="8" t="s">
+      <c r="I72" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J72" s="8" t="s">
+      <c r="J72" s="7" t="s">
         <v>870</v>
       </c>
-      <c r="K72" s="16" t="s">
+      <c r="K72" s="13" t="s">
         <v>871</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A73" s="11" t="s">
+      <c r="A73" s="9" t="s">
         <v>874</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="B73" s="7" t="s">
         <v>872</v>
       </c>
-      <c r="C73" s="8" t="s">
+      <c r="C73" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D73" s="8">
+      <c r="D73" s="7">
         <v>1140</v>
       </c>
-      <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
-      <c r="G73" s="8">
+      <c r="E73" s="7"/>
+      <c r="F73" s="7"/>
+      <c r="G73" s="7">
         <v>21</v>
       </c>
-      <c r="H73" s="8" t="s">
+      <c r="H73" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I73" s="8" t="s">
+      <c r="I73" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J73" s="8" t="s">
+      <c r="J73" s="7" t="s">
         <v>873</v>
       </c>
-      <c r="K73" s="16" t="s">
+      <c r="K73" s="13" t="s">
         <v>874</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A74" s="11" t="s">
+      <c r="A74" s="9" t="s">
         <v>877</v>
       </c>
-      <c r="B74" s="8" t="s">
+      <c r="B74" s="7" t="s">
         <v>875</v>
       </c>
-      <c r="C74" s="8" t="s">
+      <c r="C74" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D74" s="8">
+      <c r="D74" s="7">
         <v>780</v>
       </c>
-      <c r="E74" s="8"/>
-      <c r="F74" s="8"/>
-      <c r="G74" s="8">
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="7">
         <v>24</v>
       </c>
-      <c r="H74" s="8" t="s">
+      <c r="H74" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I74" s="8" t="s">
+      <c r="I74" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J74" s="8" t="s">
+      <c r="J74" s="7" t="s">
         <v>876</v>
       </c>
-      <c r="K74" s="16" t="s">
+      <c r="K74" s="13" t="s">
         <v>877</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A75" s="11" t="s">
+      <c r="A75" s="9" t="s">
         <v>880</v>
       </c>
-      <c r="B75" s="8" t="s">
+      <c r="B75" s="7" t="s">
         <v>878</v>
       </c>
-      <c r="C75" s="8" t="s">
+      <c r="C75" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D75" s="8">
+      <c r="D75" s="7">
         <v>660</v>
       </c>
-      <c r="E75" s="8"/>
-      <c r="F75" s="8"/>
-      <c r="G75" s="8">
+      <c r="E75" s="7"/>
+      <c r="F75" s="7"/>
+      <c r="G75" s="7">
         <v>13</v>
       </c>
-      <c r="H75" s="8" t="s">
+      <c r="H75" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="I75" s="8" t="s">
+      <c r="I75" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J75" s="8" t="s">
+      <c r="J75" s="7" t="s">
         <v>879</v>
       </c>
-      <c r="K75" s="16" t="s">
+      <c r="K75" s="13" t="s">
         <v>880</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A76" s="11" t="s">
+      <c r="A76" s="9" t="s">
         <v>883</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="B76" s="7" t="s">
         <v>881</v>
       </c>
-      <c r="C76" s="8" t="s">
+      <c r="C76" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D76" s="8">
+      <c r="D76" s="7">
         <v>1000</v>
       </c>
-      <c r="E76" s="8"/>
-      <c r="F76" s="8"/>
-      <c r="G76" s="8">
+      <c r="E76" s="7"/>
+      <c r="F76" s="7"/>
+      <c r="G76" s="7">
         <v>14</v>
       </c>
-      <c r="H76" s="8" t="s">
+      <c r="H76" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I76" s="8" t="s">
+      <c r="I76" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J76" s="8" t="s">
+      <c r="J76" s="7" t="s">
         <v>882</v>
       </c>
-      <c r="K76" s="16" t="s">
+      <c r="K76" s="13" t="s">
         <v>883</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A77" s="11" t="s">
+      <c r="A77" s="9" t="s">
         <v>887</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="B77" s="7" t="s">
         <v>885</v>
       </c>
-      <c r="C77" s="8" t="s">
+      <c r="C77" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D77" s="8">
+      <c r="D77" s="7">
         <v>1280</v>
       </c>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
-      <c r="G77" s="8">
+      <c r="E77" s="7"/>
+      <c r="F77" s="7"/>
+      <c r="G77" s="7">
         <v>19</v>
       </c>
-      <c r="H77" s="8" t="s">
+      <c r="H77" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I77" s="8" t="s">
+      <c r="I77" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J77" s="8" t="s">
+      <c r="J77" s="7" t="s">
         <v>886</v>
       </c>
-      <c r="K77" s="16" t="s">
+      <c r="K77" s="13" t="s">
         <v>887</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A78" s="11" t="s">
+      <c r="A78" s="9" t="s">
         <v>890</v>
       </c>
-      <c r="B78" s="8" t="s">
+      <c r="B78" s="7" t="s">
         <v>888</v>
       </c>
-      <c r="C78" s="8" t="s">
+      <c r="C78" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D78" s="8">
+      <c r="D78" s="7">
         <v>940</v>
       </c>
-      <c r="E78" s="8"/>
-      <c r="F78" s="8"/>
-      <c r="G78" s="8">
+      <c r="E78" s="7"/>
+      <c r="F78" s="7"/>
+      <c r="G78" s="7">
         <v>26</v>
       </c>
-      <c r="H78" s="8" t="s">
+      <c r="H78" s="7" t="s">
         <v>672</v>
       </c>
-      <c r="I78" s="8" t="s">
+      <c r="I78" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J78" s="8" t="s">
+      <c r="J78" s="7" t="s">
         <v>889</v>
       </c>
-      <c r="K78" s="16" t="s">
+      <c r="K78" s="13" t="s">
         <v>890</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A79" s="11" t="s">
+      <c r="A79" s="9" t="s">
         <v>893</v>
       </c>
-      <c r="B79" s="8" t="s">
+      <c r="B79" s="7" t="s">
         <v>891</v>
       </c>
-      <c r="C79" s="8" t="s">
+      <c r="C79" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D79" s="8">
+      <c r="D79" s="7">
         <v>480</v>
       </c>
-      <c r="E79" s="8"/>
-      <c r="F79" s="8"/>
-      <c r="G79" s="8">
+      <c r="E79" s="7"/>
+      <c r="F79" s="7"/>
+      <c r="G79" s="7">
         <v>15</v>
       </c>
-      <c r="H79" s="8" t="s">
+      <c r="H79" s="7" t="s">
         <v>783</v>
       </c>
-      <c r="I79" s="8" t="s">
+      <c r="I79" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J79" s="8" t="s">
+      <c r="J79" s="7" t="s">
         <v>892</v>
       </c>
-      <c r="K79" s="16" t="s">
+      <c r="K79" s="13" t="s">
         <v>893</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A80" s="11" t="s">
+      <c r="A80" s="9" t="s">
         <v>896</v>
       </c>
-      <c r="B80" s="8" t="s">
+      <c r="B80" s="7" t="s">
         <v>894</v>
       </c>
-      <c r="C80" s="8" t="s">
+      <c r="C80" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D80" s="8">
+      <c r="D80" s="7">
         <v>700</v>
       </c>
-      <c r="E80" s="8"/>
-      <c r="F80" s="8"/>
-      <c r="G80" s="8">
+      <c r="E80" s="7"/>
+      <c r="F80" s="7"/>
+      <c r="G80" s="7">
         <v>12</v>
       </c>
-      <c r="H80" s="8" t="s">
+      <c r="H80" s="7" t="s">
         <v>672</v>
       </c>
-      <c r="I80" s="8" t="s">
+      <c r="I80" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J80" s="8" t="s">
+      <c r="J80" s="7" t="s">
         <v>895</v>
       </c>
-      <c r="K80" s="16" t="s">
+      <c r="K80" s="13" t="s">
         <v>896</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A81" s="11" t="s">
+      <c r="A81" s="9" t="s">
         <v>899</v>
       </c>
-      <c r="B81" s="8" t="s">
+      <c r="B81" s="7" t="s">
         <v>897</v>
       </c>
-      <c r="C81" s="8" t="s">
+      <c r="C81" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D81" s="8">
+      <c r="D81" s="7">
         <v>620</v>
       </c>
-      <c r="E81" s="8"/>
-      <c r="F81" s="8"/>
-      <c r="G81" s="8">
+      <c r="E81" s="7"/>
+      <c r="F81" s="7"/>
+      <c r="G81" s="7">
         <v>24</v>
       </c>
-      <c r="H81" s="8" t="s">
+      <c r="H81" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I81" s="8" t="s">
+      <c r="I81" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J81" s="8" t="s">
+      <c r="J81" s="7" t="s">
         <v>898</v>
       </c>
-      <c r="K81" s="16" t="s">
+      <c r="K81" s="13" t="s">
         <v>899</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A82" s="11" t="s">
+      <c r="A82" s="9" t="s">
         <v>902</v>
       </c>
-      <c r="B82" s="8" t="s">
+      <c r="B82" s="7" t="s">
         <v>900</v>
       </c>
-      <c r="C82" s="8" t="s">
+      <c r="C82" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D82" s="8">
+      <c r="D82" s="7">
         <v>680</v>
       </c>
-      <c r="E82" s="8"/>
-      <c r="F82" s="8"/>
-      <c r="G82" s="8">
+      <c r="E82" s="7"/>
+      <c r="F82" s="7"/>
+      <c r="G82" s="7">
         <v>12</v>
       </c>
-      <c r="H82" s="8" t="s">
+      <c r="H82" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I82" s="8" t="s">
+      <c r="I82" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J82" s="8" t="s">
+      <c r="J82" s="7" t="s">
         <v>901</v>
       </c>
-      <c r="K82" s="16" t="s">
+      <c r="K82" s="13" t="s">
         <v>902</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A83" s="11" t="s">
+      <c r="A83" s="9" t="s">
         <v>905</v>
       </c>
-      <c r="B83" s="8" t="s">
+      <c r="B83" s="7" t="s">
         <v>903</v>
       </c>
-      <c r="C83" s="8" t="s">
+      <c r="C83" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D83" s="8">
+      <c r="D83" s="7">
         <v>700</v>
       </c>
-      <c r="E83" s="8"/>
-      <c r="F83" s="8"/>
-      <c r="G83" s="8">
+      <c r="E83" s="7"/>
+      <c r="F83" s="7"/>
+      <c r="G83" s="7">
         <v>16</v>
       </c>
-      <c r="H83" s="8" t="s">
+      <c r="H83" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I83" s="8" t="s">
+      <c r="I83" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J83" s="8" t="s">
+      <c r="J83" s="7" t="s">
         <v>904</v>
       </c>
-      <c r="K83" s="16" t="s">
+      <c r="K83" s="13" t="s">
         <v>905</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A84" s="11" t="s">
+      <c r="A84" s="9" t="s">
         <v>907</v>
       </c>
-      <c r="B84" s="8" t="s">
+      <c r="B84" s="7" t="s">
         <v>906</v>
       </c>
-      <c r="C84" s="8" t="s">
+      <c r="C84" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D84" s="8">
+      <c r="D84" s="7">
         <v>700</v>
       </c>
-      <c r="E84" s="8"/>
-      <c r="F84" s="8"/>
-      <c r="G84" s="8">
+      <c r="E84" s="7"/>
+      <c r="F84" s="7"/>
+      <c r="G84" s="7">
         <v>21</v>
       </c>
-      <c r="H84" s="8" t="s">
+      <c r="H84" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I84" s="8" t="s">
+      <c r="I84" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J84" s="8" t="s">
+      <c r="J84" s="7" t="s">
         <v>908</v>
       </c>
-      <c r="K84" s="16" t="s">
+      <c r="K84" s="13" t="s">
         <v>907</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A85" s="11" t="s">
+      <c r="A85" s="9" t="s">
         <v>910</v>
       </c>
-      <c r="B85" s="8" t="s">
+      <c r="B85" s="7" t="s">
         <v>909</v>
       </c>
-      <c r="C85" s="8" t="s">
+      <c r="C85" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D85" s="8">
+      <c r="D85" s="7">
         <v>860</v>
       </c>
-      <c r="E85" s="8"/>
-      <c r="F85" s="8"/>
-      <c r="G85" s="8">
+      <c r="E85" s="7"/>
+      <c r="F85" s="7"/>
+      <c r="G85" s="7">
         <v>23</v>
       </c>
-      <c r="H85" s="8" t="s">
+      <c r="H85" s="7" t="s">
         <v>672</v>
       </c>
-      <c r="I85" s="8" t="s">
+      <c r="I85" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J85" s="8" t="s">
+      <c r="J85" s="7" t="s">
         <v>911</v>
       </c>
-      <c r="K85" s="16" t="s">
+      <c r="K85" s="13" t="s">
         <v>910</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A86" s="11" t="s">
+      <c r="A86" s="9" t="s">
         <v>914</v>
       </c>
-      <c r="B86" s="8" t="s">
+      <c r="B86" s="7" t="s">
         <v>912</v>
       </c>
-      <c r="C86" s="8" t="s">
+      <c r="C86" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D86" s="8">
+      <c r="D86" s="7">
         <v>720</v>
       </c>
-      <c r="E86" s="8"/>
-      <c r="F86" s="8"/>
-      <c r="G86" s="8">
+      <c r="E86" s="7"/>
+      <c r="F86" s="7"/>
+      <c r="G86" s="7">
         <v>24</v>
       </c>
-      <c r="H86" s="8" t="s">
+      <c r="H86" s="7" t="s">
         <v>672</v>
       </c>
-      <c r="I86" s="8" t="s">
+      <c r="I86" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J86" s="8" t="s">
+      <c r="J86" s="7" t="s">
         <v>913</v>
       </c>
-      <c r="K86" s="16" t="s">
+      <c r="K86" s="13" t="s">
         <v>914</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A87" s="11" t="s">
+      <c r="A87" s="9" t="s">
         <v>917</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="B87" s="7" t="s">
         <v>916</v>
       </c>
-      <c r="C87" s="8" t="s">
+      <c r="C87" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D87" s="8">
+      <c r="D87" s="7">
         <v>1160</v>
       </c>
-      <c r="E87" s="8"/>
-      <c r="F87" s="8"/>
-      <c r="G87" s="8">
+      <c r="E87" s="7"/>
+      <c r="F87" s="7"/>
+      <c r="G87" s="7">
         <v>17</v>
       </c>
-      <c r="H87" s="8" t="s">
+      <c r="H87" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I87" s="8" t="s">
+      <c r="I87" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J87" s="8" t="s">
+      <c r="J87" s="7" t="s">
         <v>915</v>
       </c>
-      <c r="K87" s="16" t="s">
+      <c r="K87" s="13" t="s">
         <v>917</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A88" s="11" t="s">
+      <c r="A88" s="9" t="s">
         <v>920</v>
       </c>
-      <c r="B88" s="8" t="s">
+      <c r="B88" s="7" t="s">
         <v>919</v>
       </c>
-      <c r="C88" s="8" t="s">
+      <c r="C88" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D88" s="8">
+      <c r="D88" s="7">
         <v>680</v>
       </c>
-      <c r="E88" s="8"/>
-      <c r="F88" s="8"/>
-      <c r="G88" s="8">
+      <c r="E88" s="7"/>
+      <c r="F88" s="7"/>
+      <c r="G88" s="7">
         <v>15</v>
       </c>
-      <c r="H88" s="8" t="s">
+      <c r="H88" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I88" s="8" t="s">
+      <c r="I88" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J88" s="8" t="s">
+      <c r="J88" s="7" t="s">
         <v>918</v>
       </c>
-      <c r="K88" s="16" t="s">
+      <c r="K88" s="13" t="s">
         <v>920</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A89" s="11" t="s">
+      <c r="A89" s="9" t="s">
         <v>923</v>
       </c>
-      <c r="B89" s="8" t="s">
+      <c r="B89" s="7" t="s">
         <v>922</v>
       </c>
-      <c r="C89" s="8" t="s">
+      <c r="C89" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D89" s="8">
+      <c r="D89" s="7">
         <v>780</v>
       </c>
-      <c r="E89" s="8"/>
-      <c r="F89" s="8"/>
-      <c r="G89" s="8">
+      <c r="E89" s="7"/>
+      <c r="F89" s="7"/>
+      <c r="G89" s="7">
         <v>25</v>
       </c>
-      <c r="H89" s="8" t="s">
+      <c r="H89" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I89" s="8" t="s">
+      <c r="I89" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J89" s="8" t="s">
+      <c r="J89" s="7" t="s">
         <v>921</v>
       </c>
-      <c r="K89" s="16" t="s">
+      <c r="K89" s="13" t="s">
         <v>923</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A90" s="11" t="s">
+      <c r="A90" s="9" t="s">
         <v>926</v>
       </c>
-      <c r="B90" s="8" t="s">
+      <c r="B90" s="7" t="s">
         <v>924</v>
       </c>
-      <c r="C90" s="8" t="s">
+      <c r="C90" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D90" s="8">
+      <c r="D90" s="7">
         <v>1100</v>
       </c>
-      <c r="E90" s="8"/>
-      <c r="F90" s="8"/>
-      <c r="G90" s="8">
+      <c r="E90" s="7"/>
+      <c r="F90" s="7"/>
+      <c r="G90" s="7">
         <v>21</v>
       </c>
-      <c r="H90" s="8" t="s">
+      <c r="H90" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I90" s="8" t="s">
+      <c r="I90" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J90" s="8" t="s">
+      <c r="J90" s="7" t="s">
         <v>925</v>
       </c>
-      <c r="K90" s="16" t="s">
+      <c r="K90" s="13" t="s">
         <v>926</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A91" s="11" t="s">
+      <c r="A91" s="9" t="s">
         <v>930</v>
       </c>
-      <c r="B91" s="8" t="s">
+      <c r="B91" s="7" t="s">
         <v>927</v>
       </c>
-      <c r="C91" s="8" t="s">
+      <c r="C91" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D91" s="8">
+      <c r="D91" s="7">
         <v>1440</v>
       </c>
-      <c r="E91" s="8"/>
-      <c r="F91" s="8"/>
-      <c r="G91" s="8">
+      <c r="E91" s="7"/>
+      <c r="F91" s="7"/>
+      <c r="G91" s="7">
         <v>16</v>
       </c>
-      <c r="H91" s="8" t="s">
+      <c r="H91" s="7" t="s">
         <v>928</v>
       </c>
-      <c r="I91" s="8" t="s">
+      <c r="I91" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J91" s="8" t="s">
+      <c r="J91" s="7" t="s">
         <v>929</v>
       </c>
-      <c r="K91" s="16" t="s">
+      <c r="K91" s="13" t="s">
         <v>930</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A92" s="11" t="s">
+      <c r="A92" s="9" t="s">
         <v>934</v>
       </c>
-      <c r="B92" s="8" t="s">
+      <c r="B92" s="7" t="s">
         <v>931</v>
       </c>
-      <c r="C92" s="8" t="s">
+      <c r="C92" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D92" s="8">
+      <c r="D92" s="7">
         <v>680</v>
       </c>
-      <c r="E92" s="8"/>
-      <c r="F92" s="8"/>
-      <c r="G92" s="8">
+      <c r="E92" s="7"/>
+      <c r="F92" s="7"/>
+      <c r="G92" s="7">
         <v>17</v>
       </c>
-      <c r="H92" s="8" t="s">
+      <c r="H92" s="7" t="s">
         <v>932</v>
       </c>
-      <c r="I92" s="8" t="s">
+      <c r="I92" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J92" s="8" t="s">
+      <c r="J92" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="K92" s="16" t="s">
+      <c r="K92" s="13" t="s">
         <v>934</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A93" s="11" t="s">
+      <c r="A93" s="9" t="s">
         <v>937</v>
       </c>
-      <c r="B93" s="8" t="s">
+      <c r="B93" s="7" t="s">
         <v>935</v>
       </c>
-      <c r="C93" s="8" t="s">
+      <c r="C93" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D93" s="8">
+      <c r="D93" s="7">
         <v>900</v>
       </c>
-      <c r="E93" s="8"/>
-      <c r="F93" s="8" t="s">
+      <c r="E93" s="7"/>
+      <c r="F93" s="7" t="s">
         <v>884</v>
       </c>
-      <c r="G93" s="8">
+      <c r="G93" s="7">
         <v>19</v>
       </c>
-      <c r="H93" s="8" t="s">
+      <c r="H93" s="7" t="s">
         <v>672</v>
       </c>
-      <c r="I93" s="8" t="s">
+      <c r="I93" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J93" s="8" t="s">
+      <c r="J93" s="7" t="s">
         <v>936</v>
       </c>
-      <c r="K93" s="16" t="s">
+      <c r="K93" s="13" t="s">
         <v>937</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A94" s="17" t="s">
+      <c r="A94" s="16" t="s">
         <v>939</v>
       </c>
-      <c r="B94" s="18" t="s">
+      <c r="B94" s="17" t="s">
         <v>938</v>
       </c>
-      <c r="C94" s="18" t="s">
+      <c r="C94" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D94" s="18">
+      <c r="D94" s="17">
         <v>480</v>
       </c>
-      <c r="E94" s="18"/>
-      <c r="F94" s="18"/>
-      <c r="G94" s="8">
+      <c r="E94" s="17"/>
+      <c r="F94" s="17"/>
+      <c r="G94" s="7">
         <v>16</v>
       </c>
-      <c r="H94" s="18" t="s">
+      <c r="H94" s="17" t="s">
         <v>783</v>
       </c>
-      <c r="I94" s="8" t="s">
+      <c r="I94" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="J94" s="18" t="s">
+      <c r="J94" s="17" t="s">
         <v>940</v>
       </c>
-      <c r="K94" s="17" t="s">
+      <c r="K94" s="16" t="s">
         <v>939</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A95" s="17" t="s">
+      <c r="A95" s="16" t="s">
         <v>942</v>
       </c>
-      <c r="B95" s="18" t="s">
+      <c r="B95" s="17" t="s">
         <v>941</v>
       </c>
-      <c r="C95" s="18" t="s">
+      <c r="C95" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D95" s="18">
+      <c r="D95" s="17">
         <v>1060</v>
       </c>
-      <c r="E95" s="18"/>
-      <c r="F95" s="18"/>
-      <c r="G95" s="8">
+      <c r="E95" s="17"/>
+      <c r="F95" s="17"/>
+      <c r="G95" s="7">
         <v>15</v>
       </c>
-      <c r="H95" s="18" t="s">
+      <c r="H95" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="I95" s="18" t="s">
+      <c r="I95" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J95" s="18" t="s">
+      <c r="J95" s="17" t="s">
         <v>943</v>
       </c>
-      <c r="K95" s="17" t="s">
+      <c r="K95" s="16" t="s">
         <v>942</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A96" s="17" t="s">
+      <c r="A96" s="16" t="s">
         <v>946</v>
       </c>
-      <c r="B96" s="18" t="s">
+      <c r="B96" s="17" t="s">
         <v>944</v>
       </c>
-      <c r="C96" s="18" t="s">
+      <c r="C96" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D96" s="18">
+      <c r="D96" s="17">
         <v>1400</v>
       </c>
-      <c r="E96" s="18">
+      <c r="E96" s="17">
         <v>1100</v>
       </c>
-      <c r="F96" s="18"/>
-      <c r="G96" s="8">
+      <c r="F96" s="17"/>
+      <c r="G96" s="7">
         <v>25</v>
       </c>
-      <c r="H96" s="18" t="s">
+      <c r="H96" s="17" t="s">
         <v>664</v>
       </c>
-      <c r="I96" s="18" t="s">
+      <c r="I96" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J96" s="18" t="s">
+      <c r="J96" s="17" t="s">
         <v>945</v>
       </c>
-      <c r="K96" s="17" t="s">
+      <c r="K96" s="16" t="s">
         <v>947</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A97" s="17" t="s">
+      <c r="A97" s="16" t="s">
         <v>951</v>
       </c>
-      <c r="B97" s="18" t="s">
+      <c r="B97" s="17" t="s">
         <v>948</v>
       </c>
-      <c r="C97" s="18" t="s">
+      <c r="C97" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D97" s="18">
+      <c r="D97" s="17">
         <v>2500</v>
       </c>
-      <c r="E97" s="18">
+      <c r="E97" s="17">
         <v>2200</v>
       </c>
-      <c r="F97" s="18"/>
-      <c r="G97" s="8">
+      <c r="F97" s="17"/>
+      <c r="G97" s="7">
         <v>15</v>
       </c>
-      <c r="H97" s="18" t="s">
+      <c r="H97" s="17" t="s">
         <v>928</v>
       </c>
-      <c r="I97" s="18" t="s">
+      <c r="I97" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J97" s="18" t="s">
+      <c r="J97" s="17" t="s">
         <v>949</v>
       </c>
-      <c r="K97" s="17" t="s">
+      <c r="K97" s="16" t="s">
         <v>950</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A98" s="17" t="s">
+      <c r="A98" s="16" t="s">
         <v>953</v>
       </c>
-      <c r="B98" s="18" t="s">
+      <c r="B98" s="17" t="s">
         <v>952</v>
       </c>
-      <c r="C98" s="18" t="s">
+      <c r="C98" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D98" s="18">
+      <c r="D98" s="17">
         <v>1600</v>
       </c>
-      <c r="E98" s="18">
+      <c r="E98" s="17">
         <v>1460</v>
       </c>
-      <c r="F98" s="18"/>
-      <c r="G98" s="8">
+      <c r="F98" s="17"/>
+      <c r="G98" s="7">
         <v>21</v>
       </c>
-      <c r="H98" s="18" t="s">
+      <c r="H98" s="17" t="s">
         <v>928</v>
       </c>
-      <c r="I98" s="18" t="s">
+      <c r="I98" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J98" s="18" t="s">
+      <c r="J98" s="17" t="s">
         <v>955</v>
       </c>
-      <c r="K98" s="17" t="s">
+      <c r="K98" s="16" t="s">
         <v>954</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A99" s="17" t="s">
+      <c r="A99" s="16" t="s">
         <v>957</v>
       </c>
-      <c r="B99" s="18" t="s">
+      <c r="B99" s="17" t="s">
         <v>956</v>
       </c>
-      <c r="C99" s="18" t="s">
+      <c r="C99" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D99" s="18">
+      <c r="D99" s="17">
         <v>1650</v>
       </c>
-      <c r="E99" s="18">
+      <c r="E99" s="17">
         <v>1430</v>
       </c>
-      <c r="F99" s="18"/>
-      <c r="G99" s="8">
+      <c r="F99" s="17"/>
+      <c r="G99" s="7">
         <v>26</v>
       </c>
-      <c r="H99" s="18" t="s">
+      <c r="H99" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="I99" s="18" t="s">
+      <c r="I99" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J99" s="18" t="s">
+      <c r="J99" s="17" t="s">
         <v>959</v>
       </c>
-      <c r="K99" s="17" t="s">
+      <c r="K99" s="16" t="s">
         <v>958</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A100" s="17" t="s">
+      <c r="A100" s="16" t="s">
         <v>962</v>
       </c>
-      <c r="B100" s="18" t="s">
+      <c r="B100" s="17" t="s">
         <v>960</v>
       </c>
-      <c r="C100" s="18" t="s">
+      <c r="C100" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D100" s="18">
+      <c r="D100" s="17">
         <v>2300</v>
       </c>
-      <c r="E100" s="18">
+      <c r="E100" s="17">
         <v>1900</v>
       </c>
-      <c r="F100" s="18"/>
-      <c r="G100" s="8">
+      <c r="F100" s="17"/>
+      <c r="G100" s="7">
         <v>17</v>
       </c>
-      <c r="H100" s="18" t="s">
+      <c r="H100" s="17" t="s">
         <v>961</v>
       </c>
-      <c r="I100" s="18" t="s">
+      <c r="I100" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J100" s="18" t="s">
+      <c r="J100" s="17" t="s">
         <v>964</v>
       </c>
-      <c r="K100" s="17" t="s">
+      <c r="K100" s="16" t="s">
         <v>963</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A101" s="17" t="s">
+      <c r="A101" s="16" t="s">
         <v>967</v>
       </c>
-      <c r="B101" s="18" t="s">
+      <c r="B101" s="17" t="s">
         <v>965</v>
       </c>
-      <c r="C101" s="18" t="s">
+      <c r="C101" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D101" s="18">
+      <c r="D101" s="17">
         <v>600</v>
       </c>
-      <c r="E101" s="18">
+      <c r="E101" s="17">
         <v>400</v>
       </c>
-      <c r="F101" s="18"/>
-      <c r="G101" s="8">
+      <c r="F101" s="17"/>
+      <c r="G101" s="7">
         <v>25</v>
       </c>
-      <c r="H101" s="18" t="s">
+      <c r="H101" s="17" t="s">
         <v>966</v>
       </c>
-      <c r="I101" s="18" t="s">
+      <c r="I101" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J101" s="18" t="s">
+      <c r="J101" s="17" t="s">
         <v>969</v>
       </c>
-      <c r="K101" s="17" t="s">
+      <c r="K101" s="16" t="s">
         <v>968</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A102" s="17" t="s">
+      <c r="A102" s="16" t="s">
         <v>972</v>
       </c>
-      <c r="B102" s="18" t="s">
+      <c r="B102" s="17" t="s">
         <v>970</v>
       </c>
-      <c r="C102" s="18" t="s">
+      <c r="C102" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D102" s="18">
+      <c r="D102" s="17">
         <v>1600</v>
       </c>
-      <c r="E102" s="18">
+      <c r="E102" s="17">
         <v>1380</v>
       </c>
-      <c r="F102" s="18"/>
-      <c r="G102" s="8">
+      <c r="F102" s="17"/>
+      <c r="G102" s="7">
         <v>26</v>
       </c>
-      <c r="H102" s="18" t="s">
+      <c r="H102" s="17" t="s">
         <v>971</v>
       </c>
-      <c r="I102" s="18" t="s">
+      <c r="I102" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J102" s="18" t="s">
+      <c r="J102" s="17" t="s">
         <v>974</v>
       </c>
-      <c r="K102" s="17" t="s">
+      <c r="K102" s="16" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A103" s="17" t="s">
+      <c r="A103" s="16" t="s">
         <v>977</v>
       </c>
-      <c r="B103" s="18" t="s">
+      <c r="B103" s="17" t="s">
         <v>975</v>
       </c>
-      <c r="C103" s="18" t="s">
+      <c r="C103" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D103" s="18">
+      <c r="D103" s="17">
         <v>1100</v>
       </c>
-      <c r="E103" s="18">
+      <c r="E103" s="17">
         <v>840</v>
       </c>
-      <c r="F103" s="18"/>
-      <c r="G103" s="8">
+      <c r="F103" s="17"/>
+      <c r="G103" s="7">
         <v>17</v>
       </c>
-      <c r="H103" s="18" t="s">
+      <c r="H103" s="17" t="s">
         <v>976</v>
       </c>
-      <c r="I103" s="18" t="s">
+      <c r="I103" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J103" s="18" t="s">
+      <c r="J103" s="17" t="s">
         <v>979</v>
       </c>
-      <c r="K103" s="17" t="s">
+      <c r="K103" s="16" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A104" s="17" t="s">
+      <c r="A104" s="16" t="s">
         <v>983</v>
       </c>
-      <c r="B104" s="18" t="s">
+      <c r="B104" s="17" t="s">
         <v>981</v>
       </c>
-      <c r="C104" s="18" t="s">
+      <c r="C104" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D104" s="18">
+      <c r="D104" s="17">
         <v>1980</v>
       </c>
-      <c r="E104" s="18">
+      <c r="E104" s="17">
         <v>1640</v>
       </c>
-      <c r="F104" s="18"/>
-      <c r="G104" s="8">
+      <c r="F104" s="17"/>
+      <c r="G104" s="7">
         <v>19</v>
       </c>
-      <c r="H104" s="18" t="s">
+      <c r="H104" s="17" t="s">
         <v>980</v>
       </c>
-      <c r="I104" s="18" t="s">
+      <c r="I104" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J104" s="18" t="s">
+      <c r="J104" s="17" t="s">
         <v>984</v>
       </c>
-      <c r="K104" s="17" t="s">
+      <c r="K104" s="16" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A105" s="17" t="s">
+      <c r="A105" s="16" t="s">
         <v>987</v>
       </c>
-      <c r="B105" s="18" t="s">
+      <c r="B105" s="17" t="s">
         <v>985</v>
       </c>
-      <c r="C105" s="18" t="s">
+      <c r="C105" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D105" s="18">
+      <c r="D105" s="17">
         <v>2100</v>
       </c>
-      <c r="E105" s="18">
+      <c r="E105" s="17">
         <v>1760</v>
       </c>
-      <c r="F105" s="18"/>
-      <c r="G105" s="8">
+      <c r="F105" s="17"/>
+      <c r="G105" s="7">
         <v>25</v>
       </c>
-      <c r="H105" s="18" t="s">
+      <c r="H105" s="17" t="s">
         <v>928</v>
       </c>
-      <c r="I105" s="18" t="s">
+      <c r="I105" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J105" s="18" t="s">
+      <c r="J105" s="17" t="s">
         <v>986</v>
       </c>
-      <c r="K105" s="17" t="s">
+      <c r="K105" s="16" t="s">
         <v>988</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A106" s="17" t="s">
+      <c r="A106" s="16" t="s">
         <v>991</v>
       </c>
-      <c r="B106" s="18" t="s">
+      <c r="B106" s="17" t="s">
         <v>989</v>
       </c>
-      <c r="C106" s="18" t="s">
+      <c r="C106" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D106" s="18">
+      <c r="D106" s="17">
         <v>2100</v>
       </c>
-      <c r="E106" s="18">
+      <c r="E106" s="17">
         <v>1760</v>
       </c>
-      <c r="F106" s="18"/>
-      <c r="G106" s="8">
+      <c r="F106" s="17"/>
+      <c r="G106" s="7">
         <v>18</v>
       </c>
-      <c r="H106" s="18" t="s">
+      <c r="H106" s="17" t="s">
         <v>928</v>
       </c>
-      <c r="I106" s="18" t="s">
+      <c r="I106" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J106" s="18" t="s">
+      <c r="J106" s="17" t="s">
         <v>990</v>
       </c>
-      <c r="K106" s="17" t="s">
+      <c r="K106" s="16" t="s">
         <v>992</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A107" s="17" t="s">
+      <c r="A107" s="16" t="s">
         <v>995</v>
       </c>
-      <c r="B107" s="18" t="s">
+      <c r="B107" s="17" t="s">
         <v>993</v>
       </c>
-      <c r="C107" s="18" t="s">
+      <c r="C107" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D107" s="18">
+      <c r="D107" s="17">
         <v>2200</v>
       </c>
-      <c r="E107" s="18">
+      <c r="E107" s="17">
         <v>1800</v>
       </c>
-      <c r="F107" s="18"/>
-      <c r="G107" s="8">
+      <c r="F107" s="17"/>
+      <c r="G107" s="7">
         <v>9</v>
       </c>
-      <c r="H107" s="18" t="s">
+      <c r="H107" s="17" t="s">
         <v>961</v>
       </c>
-      <c r="I107" s="18" t="s">
+      <c r="I107" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J107" s="18" t="s">
+      <c r="J107" s="17" t="s">
         <v>996</v>
       </c>
-      <c r="K107" s="17" t="s">
+      <c r="K107" s="16" t="s">
         <v>994</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A108" s="17" t="s">
+      <c r="A108" s="16" t="s">
         <v>999</v>
       </c>
-      <c r="B108" s="18" t="s">
+      <c r="B108" s="17" t="s">
         <v>997</v>
       </c>
-      <c r="C108" s="18" t="s">
+      <c r="C108" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D108" s="18">
+      <c r="D108" s="17">
         <v>550</v>
       </c>
-      <c r="E108" s="18">
+      <c r="E108" s="17">
         <v>360</v>
       </c>
-      <c r="F108" s="18"/>
-      <c r="G108" s="8">
+      <c r="F108" s="17"/>
+      <c r="G108" s="7">
         <v>26</v>
       </c>
-      <c r="H108" s="18" t="s">
+      <c r="H108" s="17" t="s">
         <v>998</v>
       </c>
-      <c r="I108" s="18" t="s">
+      <c r="I108" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J108" s="18" t="s">
+      <c r="J108" s="17" t="s">
         <v>1001</v>
       </c>
-      <c r="K108" s="17" t="s">
+      <c r="K108" s="16" t="s">
         <v>1000</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A109" s="17" t="s">
+      <c r="A109" s="16" t="s">
         <v>1004</v>
       </c>
-      <c r="B109" s="18" t="s">
+      <c r="B109" s="17" t="s">
         <v>1002</v>
       </c>
-      <c r="C109" s="18" t="s">
+      <c r="C109" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D109" s="18">
+      <c r="D109" s="17">
         <v>1500</v>
       </c>
-      <c r="E109" s="18">
+      <c r="E109" s="17">
         <v>1380</v>
       </c>
-      <c r="F109" s="18"/>
-      <c r="G109" s="8">
+      <c r="F109" s="17"/>
+      <c r="G109" s="7">
         <v>13</v>
       </c>
-      <c r="H109" s="18" t="s">
+      <c r="H109" s="17" t="s">
         <v>971</v>
       </c>
-      <c r="I109" s="18" t="s">
+      <c r="I109" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J109" s="18" t="s">
+      <c r="J109" s="17" t="s">
         <v>1003</v>
       </c>
-      <c r="K109" s="17" t="s">
+      <c r="K109" s="16" t="s">
         <v>1005</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A110" s="17" t="s">
+      <c r="A110" s="16" t="s">
         <v>1008</v>
       </c>
-      <c r="B110" s="18" t="s">
+      <c r="B110" s="17" t="s">
         <v>1006</v>
       </c>
-      <c r="C110" s="18" t="s">
+      <c r="C110" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D110" s="18">
+      <c r="D110" s="17">
         <v>1600</v>
       </c>
-      <c r="E110" s="18">
+      <c r="E110" s="17">
         <v>1300</v>
       </c>
-      <c r="F110" s="18"/>
-      <c r="G110" s="8">
+      <c r="F110" s="17"/>
+      <c r="G110" s="7">
         <v>18</v>
       </c>
-      <c r="H110" s="18" t="s">
+      <c r="H110" s="17" t="s">
         <v>971</v>
       </c>
-      <c r="I110" s="18" t="s">
+      <c r="I110" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J110" s="18" t="s">
+      <c r="J110" s="17" t="s">
         <v>1007</v>
       </c>
-      <c r="K110" s="17" t="s">
+      <c r="K110" s="16" t="s">
         <v>1009</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A111" s="17" t="s">
+      <c r="A111" s="16" t="s">
         <v>1012</v>
       </c>
-      <c r="B111" s="18" t="s">
+      <c r="B111" s="17" t="s">
         <v>1010</v>
       </c>
-      <c r="C111" s="18" t="s">
+      <c r="C111" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D111" s="18">
+      <c r="D111" s="17">
         <v>2800</v>
       </c>
-      <c r="E111" s="18">
+      <c r="E111" s="17">
         <v>2500</v>
       </c>
-      <c r="F111" s="18"/>
-      <c r="G111" s="8">
+      <c r="F111" s="17"/>
+      <c r="G111" s="7">
         <v>16</v>
       </c>
-      <c r="H111" s="18" t="s">
+      <c r="H111" s="17" t="s">
         <v>928</v>
       </c>
-      <c r="I111" s="18" t="s">
+      <c r="I111" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J111" s="18" t="s">
+      <c r="J111" s="17" t="s">
         <v>1011</v>
       </c>
-      <c r="K111" s="17" t="s">
+      <c r="K111" s="16" t="s">
         <v>1013</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A112" s="17" t="s">
+      <c r="A112" s="16" t="s">
         <v>1016</v>
       </c>
-      <c r="B112" s="18" t="s">
+      <c r="B112" s="17" t="s">
         <v>1014</v>
       </c>
-      <c r="C112" s="18" t="s">
+      <c r="C112" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D112" s="18">
+      <c r="D112" s="17">
         <v>1600</v>
       </c>
-      <c r="E112" s="18">
+      <c r="E112" s="17">
         <v>1380</v>
       </c>
-      <c r="F112" s="18"/>
-      <c r="G112" s="8">
+      <c r="F112" s="17"/>
+      <c r="G112" s="7">
         <v>18</v>
       </c>
-      <c r="H112" s="18" t="s">
+      <c r="H112" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="I112" s="18" t="s">
+      <c r="I112" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J112" s="18" t="s">
+      <c r="J112" s="17" t="s">
         <v>1015</v>
       </c>
-      <c r="K112" s="17" t="s">
+      <c r="K112" s="16" t="s">
         <v>1017</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A113" s="17" t="s">
+      <c r="A113" s="16" t="s">
         <v>1020</v>
       </c>
-      <c r="B113" s="18" t="s">
+      <c r="B113" s="17" t="s">
         <v>1018</v>
       </c>
-      <c r="C113" s="18" t="s">
+      <c r="C113" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D113" s="18">
+      <c r="D113" s="17">
         <v>3200</v>
       </c>
-      <c r="E113" s="18">
+      <c r="E113" s="17">
         <v>2800</v>
       </c>
-      <c r="F113" s="18"/>
-      <c r="G113" s="8">
+      <c r="F113" s="17"/>
+      <c r="G113" s="7">
         <v>21</v>
       </c>
-      <c r="H113" s="18" t="s">
+      <c r="H113" s="17" t="s">
         <v>961</v>
       </c>
-      <c r="I113" s="18" t="s">
+      <c r="I113" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J113" s="18" t="s">
+      <c r="J113" s="17" t="s">
         <v>1019</v>
       </c>
-      <c r="K113" s="17" t="s">
+      <c r="K113" s="16" t="s">
         <v>1021</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A114" s="17" t="s">
+      <c r="A114" s="16" t="s">
         <v>1024</v>
       </c>
-      <c r="B114" s="18" t="s">
+      <c r="B114" s="17" t="s">
         <v>1022</v>
       </c>
-      <c r="C114" s="18" t="s">
+      <c r="C114" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D114" s="18">
+      <c r="D114" s="17">
         <v>3200</v>
       </c>
-      <c r="E114" s="18">
+      <c r="E114" s="17">
         <v>2740</v>
       </c>
-      <c r="F114" s="18"/>
-      <c r="G114" s="8">
+      <c r="F114" s="17"/>
+      <c r="G114" s="7">
         <v>18</v>
       </c>
-      <c r="H114" s="18" t="s">
+      <c r="H114" s="17" t="s">
         <v>928</v>
       </c>
-      <c r="I114" s="18" t="s">
+      <c r="I114" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J114" s="18" t="s">
+      <c r="J114" s="17" t="s">
         <v>1023</v>
       </c>
-      <c r="K114" s="17" t="s">
+      <c r="K114" s="16" t="s">
         <v>1025</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A115" s="17" t="s">
+      <c r="A115" s="16" t="s">
         <v>1028</v>
       </c>
-      <c r="B115" s="18" t="s">
+      <c r="B115" s="17" t="s">
         <v>1026</v>
       </c>
-      <c r="C115" s="18" t="s">
+      <c r="C115" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D115" s="18">
+      <c r="D115" s="17">
         <v>3000</v>
       </c>
-      <c r="E115" s="18">
+      <c r="E115" s="17">
         <v>2500</v>
       </c>
-      <c r="F115" s="18"/>
-      <c r="G115" s="8">
+      <c r="F115" s="17"/>
+      <c r="G115" s="7">
         <v>21</v>
       </c>
-      <c r="H115" s="18" t="s">
+      <c r="H115" s="17" t="s">
         <v>928</v>
       </c>
-      <c r="I115" s="18" t="s">
+      <c r="I115" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J115" s="18" t="s">
+      <c r="J115" s="17" t="s">
         <v>1027</v>
       </c>
-      <c r="K115" s="17" t="s">
+      <c r="K115" s="16" t="s">
         <v>1029</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A116" s="17" t="s">
+      <c r="A116" s="16" t="s">
         <v>1032</v>
       </c>
-      <c r="B116" s="18" t="s">
+      <c r="B116" s="17" t="s">
         <v>1030</v>
       </c>
-      <c r="C116" s="18" t="s">
+      <c r="C116" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D116" s="18">
+      <c r="D116" s="17">
         <v>2400</v>
       </c>
-      <c r="E116" s="18">
+      <c r="E116" s="17">
         <v>2000</v>
       </c>
-      <c r="F116" s="18"/>
-      <c r="G116" s="8">
+      <c r="F116" s="17"/>
+      <c r="G116" s="7">
         <v>21</v>
       </c>
-      <c r="H116" s="18" t="s">
+      <c r="H116" s="17" t="s">
         <v>961</v>
       </c>
-      <c r="I116" s="18" t="s">
+      <c r="I116" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J116" s="18" t="s">
+      <c r="J116" s="17" t="s">
         <v>1031</v>
       </c>
-      <c r="K116" s="17" t="s">
+      <c r="K116" s="16" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A117" s="17" t="s">
+      <c r="A117" s="16" t="s">
         <v>1036</v>
       </c>
-      <c r="B117" s="18" t="s">
+      <c r="B117" s="17" t="s">
         <v>1034</v>
       </c>
-      <c r="C117" s="18" t="s">
+      <c r="C117" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D117" s="18">
+      <c r="D117" s="17">
         <v>2100</v>
       </c>
-      <c r="E117" s="18">
+      <c r="E117" s="17">
         <v>1800</v>
       </c>
-      <c r="F117" s="18"/>
-      <c r="G117" s="8">
+      <c r="F117" s="17"/>
+      <c r="G117" s="7">
         <v>14</v>
       </c>
-      <c r="H117" s="18" t="s">
+      <c r="H117" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="I117" s="18" t="s">
+      <c r="I117" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J117" s="18" t="s">
+      <c r="J117" s="17" t="s">
         <v>840</v>
       </c>
-      <c r="K117" s="17" t="s">
+      <c r="K117" s="16" t="s">
         <v>1035</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A118" s="17" t="s">
+      <c r="A118" s="16" t="s">
         <v>1039</v>
       </c>
-      <c r="B118" s="18" t="s">
+      <c r="B118" s="17" t="s">
         <v>1037</v>
       </c>
-      <c r="C118" s="18" t="s">
+      <c r="C118" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D118" s="18">
+      <c r="D118" s="17">
         <v>550</v>
       </c>
-      <c r="E118" s="18">
+      <c r="E118" s="17">
         <v>480</v>
       </c>
-      <c r="F118" s="18"/>
-      <c r="G118" s="8">
+      <c r="F118" s="17"/>
+      <c r="G118" s="7">
         <v>16</v>
       </c>
-      <c r="H118" s="18" t="s">
+      <c r="H118" s="17" t="s">
         <v>998</v>
       </c>
-      <c r="I118" s="18" t="s">
+      <c r="I118" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J118" s="18" t="s">
+      <c r="J118" s="17" t="s">
         <v>1038</v>
       </c>
-      <c r="K118" s="17" t="s">
+      <c r="K118" s="16" t="s">
         <v>1040</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A119" s="17" t="s">
+      <c r="A119" s="16" t="s">
         <v>1043</v>
       </c>
-      <c r="B119" s="18" t="s">
+      <c r="B119" s="17" t="s">
         <v>1041</v>
       </c>
-      <c r="C119" s="18" t="s">
+      <c r="C119" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D119" s="18">
+      <c r="D119" s="17">
         <v>1900</v>
       </c>
-      <c r="E119" s="18">
+      <c r="E119" s="17">
         <v>1600</v>
       </c>
-      <c r="F119" s="18"/>
-      <c r="G119" s="8">
+      <c r="F119" s="17"/>
+      <c r="G119" s="7">
         <v>18</v>
       </c>
-      <c r="H119" s="18" t="s">
+      <c r="H119" s="17" t="s">
         <v>971</v>
       </c>
-      <c r="I119" s="18" t="s">
+      <c r="I119" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J119" s="18" t="s">
+      <c r="J119" s="17" t="s">
         <v>1042</v>
       </c>
-      <c r="K119" s="17" t="s">
+      <c r="K119" s="16" t="s">
         <v>1044</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A120" s="17" t="s">
+      <c r="A120" s="16" t="s">
         <v>1046</v>
       </c>
-      <c r="B120" s="18" t="s">
+      <c r="B120" s="17" t="s">
         <v>1045</v>
       </c>
-      <c r="C120" s="18" t="s">
+      <c r="C120" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D120" s="18">
+      <c r="D120" s="17">
         <v>1500</v>
       </c>
-      <c r="E120" s="18">
+      <c r="E120" s="17">
         <v>1240</v>
       </c>
-      <c r="F120" s="18"/>
-      <c r="G120" s="8">
+      <c r="F120" s="17"/>
+      <c r="G120" s="7">
         <v>17</v>
       </c>
-      <c r="H120" s="18" t="s">
+      <c r="H120" s="17" t="s">
         <v>971</v>
       </c>
-      <c r="I120" s="18" t="s">
+      <c r="I120" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J120" s="18" t="s">
+      <c r="J120" s="17" t="s">
         <v>1048</v>
       </c>
-      <c r="K120" s="17" t="s">
+      <c r="K120" s="16" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A121" s="17" t="s">
+      <c r="A121" s="16" t="s">
         <v>1051</v>
       </c>
-      <c r="B121" s="18" t="s">
+      <c r="B121" s="17" t="s">
         <v>1049</v>
       </c>
-      <c r="C121" s="18" t="s">
+      <c r="C121" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D121" s="18">
+      <c r="D121" s="17">
         <v>1700</v>
       </c>
-      <c r="E121" s="18">
+      <c r="E121" s="17">
         <v>1540</v>
       </c>
-      <c r="F121" s="18"/>
-      <c r="G121" s="8">
+      <c r="F121" s="17"/>
+      <c r="G121" s="7">
         <v>15</v>
       </c>
-      <c r="H121" s="18" t="s">
+      <c r="H121" s="17" t="s">
         <v>928</v>
       </c>
-      <c r="I121" s="18" t="s">
+      <c r="I121" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J121" s="18" t="s">
+      <c r="J121" s="17" t="s">
         <v>1050</v>
       </c>
-      <c r="K121" s="17" t="s">
+      <c r="K121" s="16" t="s">
         <v>1052</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A122" s="17" t="s">
+      <c r="A122" s="16" t="s">
         <v>1055</v>
       </c>
-      <c r="B122" s="18" t="s">
+      <c r="B122" s="17" t="s">
         <v>1053</v>
       </c>
-      <c r="C122" s="18" t="s">
+      <c r="C122" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D122" s="18">
+      <c r="D122" s="17">
         <v>2400</v>
       </c>
-      <c r="E122" s="18">
+      <c r="E122" s="17">
         <v>2000</v>
       </c>
-      <c r="F122" s="18"/>
-      <c r="G122" s="8">
+      <c r="F122" s="17"/>
+      <c r="G122" s="7">
         <v>24</v>
       </c>
-      <c r="H122" s="18" t="s">
+      <c r="H122" s="17" t="s">
         <v>928</v>
       </c>
-      <c r="I122" s="18" t="s">
+      <c r="I122" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J122" s="18" t="s">
+      <c r="J122" s="17" t="s">
         <v>1054</v>
       </c>
-      <c r="K122" s="17" t="s">
+      <c r="K122" s="16" t="s">
         <v>1056</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A123" s="17" t="s">
+      <c r="A123" s="16" t="s">
         <v>1059</v>
       </c>
-      <c r="B123" s="18" t="s">
+      <c r="B123" s="17" t="s">
         <v>1057</v>
       </c>
-      <c r="C123" s="18" t="s">
+      <c r="C123" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D123" s="18">
+      <c r="D123" s="17">
         <v>2400</v>
       </c>
-      <c r="E123" s="18">
+      <c r="E123" s="17">
         <v>2000</v>
       </c>
-      <c r="F123" s="18"/>
-      <c r="G123" s="8">
+      <c r="F123" s="17"/>
+      <c r="G123" s="7">
         <v>25</v>
       </c>
-      <c r="H123" s="18" t="s">
+      <c r="H123" s="17" t="s">
         <v>928</v>
       </c>
-      <c r="I123" s="18" t="s">
+      <c r="I123" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J123" s="18" t="s">
+      <c r="J123" s="17" t="s">
         <v>1058</v>
       </c>
-      <c r="K123" s="17" t="s">
+      <c r="K123" s="16" t="s">
         <v>1060</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A124" s="17" t="s">
+      <c r="A124" s="16" t="s">
         <v>1063</v>
       </c>
-      <c r="B124" s="18" t="s">
+      <c r="B124" s="17" t="s">
         <v>1061</v>
       </c>
-      <c r="C124" s="18" t="s">
+      <c r="C124" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D124" s="18">
+      <c r="D124" s="17">
         <v>1500</v>
       </c>
-      <c r="E124" s="18">
+      <c r="E124" s="17">
         <v>1260</v>
       </c>
-      <c r="F124" s="18"/>
-      <c r="G124" s="8">
+      <c r="F124" s="17"/>
+      <c r="G124" s="7">
         <v>21</v>
       </c>
-      <c r="H124" s="18" t="s">
+      <c r="H124" s="17" t="s">
         <v>961</v>
       </c>
-      <c r="I124" s="18" t="s">
+      <c r="I124" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J124" s="18" t="s">
+      <c r="J124" s="17" t="s">
         <v>1062</v>
       </c>
-      <c r="K124" s="17" t="s">
+      <c r="K124" s="16" t="s">
         <v>1064</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A125" s="17" t="s">
+      <c r="A125" s="16" t="s">
         <v>1067</v>
       </c>
-      <c r="B125" s="18" t="s">
+      <c r="B125" s="17" t="s">
         <v>1065</v>
       </c>
-      <c r="C125" s="18" t="s">
+      <c r="C125" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D125" s="18">
+      <c r="D125" s="17">
         <v>1400</v>
       </c>
-      <c r="E125" s="18">
+      <c r="E125" s="17">
         <v>1220</v>
       </c>
-      <c r="F125" s="18"/>
-      <c r="G125" s="8">
+      <c r="F125" s="17"/>
+      <c r="G125" s="7">
         <v>25</v>
       </c>
-      <c r="H125" s="18" t="s">
+      <c r="H125" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="I125" s="18" t="s">
+      <c r="I125" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J125" s="18" t="s">
+      <c r="J125" s="17" t="s">
         <v>1066</v>
       </c>
-      <c r="K125" s="17" t="s">
+      <c r="K125" s="16" t="s">
         <v>1068</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A126" s="17" t="s">
+      <c r="A126" s="16" t="s">
         <v>1072</v>
       </c>
-      <c r="B126" s="18" t="s">
+      <c r="B126" s="17" t="s">
         <v>1069</v>
       </c>
-      <c r="C126" s="18" t="s">
+      <c r="C126" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D126" s="18">
+      <c r="D126" s="17">
         <v>1500</v>
       </c>
-      <c r="E126" s="18">
+      <c r="E126" s="17">
         <v>1300</v>
       </c>
-      <c r="F126" s="18"/>
-      <c r="G126" s="8">
+      <c r="F126" s="17"/>
+      <c r="G126" s="7">
         <v>21</v>
       </c>
-      <c r="H126" s="18" t="s">
+      <c r="H126" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="I126" s="18" t="s">
+      <c r="I126" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J126" s="18" t="s">
+      <c r="J126" s="17" t="s">
         <v>1070</v>
       </c>
-      <c r="K126" s="17" t="s">
+      <c r="K126" s="16" t="s">
         <v>1071</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A127" s="17" t="s">
+      <c r="A127" s="16" t="s">
         <v>1075</v>
       </c>
-      <c r="B127" s="18" t="s">
+      <c r="B127" s="17" t="s">
         <v>1073</v>
       </c>
-      <c r="C127" s="18" t="s">
+      <c r="C127" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D127" s="18">
+      <c r="D127" s="17">
         <v>1600</v>
       </c>
-      <c r="E127" s="18">
+      <c r="E127" s="17">
         <v>1440</v>
       </c>
-      <c r="F127" s="18"/>
-      <c r="G127" s="8">
+      <c r="F127" s="17"/>
+      <c r="G127" s="7">
         <v>15</v>
       </c>
-      <c r="H127" s="18" t="s">
+      <c r="H127" s="17" t="s">
         <v>971</v>
       </c>
-      <c r="I127" s="18" t="s">
+      <c r="I127" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J127" s="18" t="s">
+      <c r="J127" s="17" t="s">
         <v>1074</v>
       </c>
-      <c r="K127" s="17" t="s">
+      <c r="K127" s="16" t="s">
         <v>1076</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A128" s="17" t="s">
+      <c r="A128" s="16" t="s">
         <v>1079</v>
       </c>
-      <c r="B128" s="18" t="s">
+      <c r="B128" s="17" t="s">
         <v>1077</v>
       </c>
-      <c r="C128" s="18" t="s">
+      <c r="C128" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D128" s="18">
+      <c r="D128" s="17">
         <v>1100</v>
       </c>
-      <c r="E128" s="18">
+      <c r="E128" s="17">
         <v>750</v>
       </c>
-      <c r="F128" s="18"/>
-      <c r="G128" s="8">
+      <c r="F128" s="17"/>
+      <c r="G128" s="7">
         <v>18</v>
       </c>
-      <c r="H128" s="18" t="s">
+      <c r="H128" s="17" t="s">
         <v>932</v>
       </c>
-      <c r="I128" s="18" t="s">
+      <c r="I128" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J128" s="18" t="s">
+      <c r="J128" s="17" t="s">
         <v>1078</v>
       </c>
-      <c r="K128" s="17" t="s">
+      <c r="K128" s="16" t="s">
         <v>1080</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A129" s="17" t="s">
+      <c r="A129" s="16" t="s">
         <v>1083</v>
       </c>
-      <c r="B129" s="18" t="s">
+      <c r="B129" s="17" t="s">
         <v>1081</v>
       </c>
-      <c r="C129" s="18" t="s">
+      <c r="C129" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D129" s="18">
+      <c r="D129" s="17">
         <v>1600</v>
       </c>
-      <c r="E129" s="18">
+      <c r="E129" s="17">
         <v>1300</v>
       </c>
-      <c r="F129" s="18"/>
-      <c r="G129" s="8">
+      <c r="F129" s="17"/>
+      <c r="G129" s="7">
         <v>12</v>
       </c>
-      <c r="H129" s="18" t="s">
+      <c r="H129" s="17" t="s">
         <v>980</v>
       </c>
-      <c r="I129" s="18" t="s">
+      <c r="I129" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J129" s="18" t="s">
+      <c r="J129" s="17" t="s">
         <v>1082</v>
       </c>
-      <c r="K129" s="17" t="s">
+      <c r="K129" s="16" t="s">
         <v>1084</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A130" s="17" t="s">
+      <c r="A130" s="16" t="s">
         <v>1087</v>
       </c>
-      <c r="B130" s="18" t="s">
+      <c r="B130" s="17" t="s">
         <v>1085</v>
       </c>
-      <c r="C130" s="18" t="s">
+      <c r="C130" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D130" s="18">
+      <c r="D130" s="17">
         <v>1300</v>
       </c>
-      <c r="E130" s="18">
+      <c r="E130" s="17">
         <v>1140</v>
       </c>
-      <c r="F130" s="18"/>
-      <c r="G130" s="8">
+      <c r="F130" s="17"/>
+      <c r="G130" s="7">
         <v>15</v>
       </c>
-      <c r="H130" s="18" t="s">
+      <c r="H130" s="17" t="s">
         <v>971</v>
       </c>
-      <c r="I130" s="18" t="s">
+      <c r="I130" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J130" s="18" t="s">
+      <c r="J130" s="17" t="s">
         <v>1086</v>
       </c>
-      <c r="K130" s="17" t="s">
+      <c r="K130" s="16" t="s">
         <v>1088</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A131" s="17" t="s">
+      <c r="A131" s="16" t="s">
         <v>1091</v>
       </c>
-      <c r="B131" s="18" t="s">
+      <c r="B131" s="17" t="s">
         <v>1089</v>
       </c>
-      <c r="C131" s="18" t="s">
+      <c r="C131" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D131" s="18">
+      <c r="D131" s="17">
         <v>1400</v>
       </c>
-      <c r="E131" s="18">
+      <c r="E131" s="17">
         <v>1240</v>
       </c>
-      <c r="F131" s="18"/>
-      <c r="G131" s="8">
+      <c r="F131" s="17"/>
+      <c r="G131" s="7">
         <v>19</v>
       </c>
-      <c r="H131" s="18" t="s">
+      <c r="H131" s="17" t="s">
         <v>928</v>
       </c>
-      <c r="I131" s="18" t="s">
+      <c r="I131" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J131" s="18" t="s">
+      <c r="J131" s="17" t="s">
         <v>1090</v>
       </c>
-      <c r="K131" s="17" t="s">
+      <c r="K131" s="16" t="s">
         <v>1092</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A132" s="17" t="s">
+      <c r="A132" s="16" t="s">
         <v>1095</v>
       </c>
-      <c r="B132" s="18" t="s">
+      <c r="B132" s="17" t="s">
         <v>1093</v>
       </c>
-      <c r="C132" s="18" t="s">
+      <c r="C132" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D132" s="18">
+      <c r="D132" s="17">
         <v>2500</v>
       </c>
-      <c r="E132" s="18">
+      <c r="E132" s="17">
         <v>2200</v>
       </c>
-      <c r="F132" s="18"/>
-      <c r="G132" s="8">
+      <c r="F132" s="17"/>
+      <c r="G132" s="7">
         <v>25</v>
       </c>
-      <c r="H132" s="18" t="s">
+      <c r="H132" s="17" t="s">
         <v>928</v>
       </c>
-      <c r="I132" s="18" t="s">
+      <c r="I132" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J132" s="18" t="s">
+      <c r="J132" s="17" t="s">
         <v>1094</v>
       </c>
-      <c r="K132" s="17" t="s">
+      <c r="K132" s="16" t="s">
         <v>1096</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A133" s="17" t="s">
+      <c r="A133" s="16" t="s">
         <v>1099</v>
       </c>
-      <c r="B133" s="18" t="s">
+      <c r="B133" s="17" t="s">
         <v>1097</v>
       </c>
-      <c r="C133" s="18" t="s">
+      <c r="C133" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D133" s="18">
+      <c r="D133" s="17">
         <v>1800</v>
       </c>
-      <c r="E133" s="18">
+      <c r="E133" s="17">
         <v>1440</v>
       </c>
-      <c r="F133" s="18"/>
-      <c r="G133" s="8">
+      <c r="F133" s="17"/>
+      <c r="G133" s="7">
         <v>16</v>
       </c>
-      <c r="H133" s="18" t="s">
+      <c r="H133" s="17" t="s">
         <v>928</v>
       </c>
-      <c r="I133" s="18" t="s">
+      <c r="I133" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J133" s="18" t="s">
+      <c r="J133" s="17" t="s">
         <v>1098</v>
       </c>
-      <c r="K133" s="17" t="s">
+      <c r="K133" s="16" t="s">
         <v>1100</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A134" s="17"/>
-      <c r="B134" s="18"/>
-      <c r="C134" s="18" t="s">
+      <c r="A134" s="16" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B134" s="17" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C134" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D134" s="18"/>
-      <c r="E134" s="18"/>
-      <c r="F134" s="18"/>
-      <c r="G134" s="8"/>
-      <c r="H134" s="18"/>
-      <c r="I134" s="18" t="s">
+      <c r="D134" s="17">
+        <v>1600</v>
+      </c>
+      <c r="E134" s="17">
+        <v>1380</v>
+      </c>
+      <c r="F134" s="17"/>
+      <c r="G134" s="7">
+        <v>17</v>
+      </c>
+      <c r="H134" s="17" t="s">
+        <v>971</v>
+      </c>
+      <c r="I134" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J134" s="18"/>
-      <c r="K134" s="17"/>
+      <c r="J134" s="17" t="s">
+        <v>1102</v>
+      </c>
+      <c r="K134" s="16" t="s">
+        <v>1104</v>
+      </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A135" s="17"/>
-      <c r="B135" s="18"/>
-      <c r="C135" s="18" t="s">
+      <c r="A135" s="16" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B135" s="17" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C135" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D135" s="18"/>
-      <c r="E135" s="18"/>
-      <c r="F135" s="18"/>
-      <c r="G135" s="8"/>
-      <c r="H135" s="18"/>
-      <c r="I135" s="18" t="s">
+      <c r="D135" s="17">
+        <v>1350</v>
+      </c>
+      <c r="E135" s="17">
+        <v>1120</v>
+      </c>
+      <c r="F135" s="17"/>
+      <c r="G135" s="7">
+        <v>23</v>
+      </c>
+      <c r="H135" s="17" t="s">
+        <v>971</v>
+      </c>
+      <c r="I135" s="17" t="s">
         <v>657</v>
       </c>
-      <c r="J135" s="18"/>
-      <c r="K135" s="17"/>
+      <c r="J135" s="17" t="s">
+        <v>1106</v>
+      </c>
+      <c r="K135" s="16" t="s">
+        <v>1108</v>
+      </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A136" s="17"/>
-      <c r="B136" s="18"/>
-      <c r="C136" s="18" t="s">
+      <c r="A136" s="16" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B136" s="17" t="s">
+        <v>919</v>
+      </c>
+      <c r="C136" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D136" s="18"/>
-      <c r="E136" s="18"/>
-      <c r="F136" s="18"/>
-      <c r="G136" s="8"/>
-      <c r="H136" s="18"/>
-      <c r="I136" s="18"/>
-      <c r="J136" s="18"/>
-      <c r="K136" s="17"/>
+      <c r="D136" s="17">
+        <v>2300</v>
+      </c>
+      <c r="E136" s="17">
+        <v>2000</v>
+      </c>
+      <c r="F136" s="17"/>
+      <c r="G136" s="7">
+        <v>17</v>
+      </c>
+      <c r="H136" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I136" s="17" t="s">
+        <v>657</v>
+      </c>
+      <c r="J136" s="17" t="s">
+        <v>918</v>
+      </c>
+      <c r="K136" s="16" t="s">
+        <v>1110</v>
+      </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A137" s="17"/>
-      <c r="B137" s="18"/>
-      <c r="C137" s="18" t="s">
+      <c r="A137" s="16" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B137" s="17" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C137" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D137" s="18"/>
-      <c r="E137" s="18"/>
-      <c r="F137" s="18"/>
-      <c r="G137" s="8"/>
-      <c r="H137" s="18"/>
-      <c r="I137" s="18"/>
-      <c r="J137" s="18"/>
-      <c r="K137" s="17"/>
+      <c r="D137" s="17">
+        <v>650</v>
+      </c>
+      <c r="E137" s="17">
+        <v>550</v>
+      </c>
+      <c r="F137" s="17"/>
+      <c r="G137" s="7">
+        <v>15</v>
+      </c>
+      <c r="H137" s="17" t="s">
+        <v>998</v>
+      </c>
+      <c r="I137" s="17" t="s">
+        <v>657</v>
+      </c>
+      <c r="J137" s="17" t="s">
+        <v>1112</v>
+      </c>
+      <c r="K137" s="16" t="s">
+        <v>1114</v>
+      </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A138" s="17"/>
-      <c r="B138" s="18"/>
-      <c r="C138" s="18" t="s">
+      <c r="A138" s="16" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B138" s="17" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C138" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D138" s="18"/>
-      <c r="E138" s="18"/>
-      <c r="F138" s="18"/>
-      <c r="G138" s="8"/>
-      <c r="H138" s="18"/>
-      <c r="I138" s="18"/>
-      <c r="J138" s="18"/>
-      <c r="K138" s="17"/>
+      <c r="D138" s="17">
+        <v>850</v>
+      </c>
+      <c r="E138" s="17">
+        <v>620</v>
+      </c>
+      <c r="F138" s="17"/>
+      <c r="G138" s="7">
+        <v>17</v>
+      </c>
+      <c r="H138" s="17" t="s">
+        <v>672</v>
+      </c>
+      <c r="I138" s="17" t="s">
+        <v>657</v>
+      </c>
+      <c r="J138" s="17" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K138" s="16" t="s">
+        <v>1118</v>
+      </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A139" s="17"/>
-      <c r="B139" s="18"/>
-      <c r="C139" s="18" t="s">
+      <c r="A139" s="16" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B139" s="17" t="s">
+        <v>935</v>
+      </c>
+      <c r="C139" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D139" s="18"/>
-      <c r="E139" s="18"/>
-      <c r="F139" s="18"/>
-      <c r="G139" s="8"/>
-      <c r="H139" s="18"/>
-      <c r="I139" s="18"/>
-      <c r="J139" s="18"/>
-      <c r="K139" s="17"/>
+      <c r="D139" s="17">
+        <v>1800</v>
+      </c>
+      <c r="E139" s="17">
+        <v>1440</v>
+      </c>
+      <c r="F139" s="17"/>
+      <c r="G139" s="7">
+        <v>15</v>
+      </c>
+      <c r="H139" s="17" t="s">
+        <v>971</v>
+      </c>
+      <c r="I139" s="17" t="s">
+        <v>657</v>
+      </c>
+      <c r="J139" s="17" t="s">
+        <v>1119</v>
+      </c>
+      <c r="K139" s="16" t="s">
+        <v>1120</v>
+      </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A140" s="17"/>
-      <c r="B140" s="18"/>
-      <c r="C140" s="18" t="s">
+      <c r="A140" s="16" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B140" s="17" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C140" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D140" s="18"/>
-      <c r="E140" s="18"/>
-      <c r="F140" s="18"/>
-      <c r="G140" s="8"/>
-      <c r="H140" s="18"/>
-      <c r="I140" s="18"/>
-      <c r="J140" s="18"/>
-      <c r="K140" s="17"/>
+      <c r="D140" s="17">
+        <v>1500</v>
+      </c>
+      <c r="E140" s="17">
+        <v>1380</v>
+      </c>
+      <c r="F140" s="17"/>
+      <c r="G140" s="7">
+        <v>21</v>
+      </c>
+      <c r="H140" s="17" t="s">
+        <v>980</v>
+      </c>
+      <c r="I140" s="17" t="s">
+        <v>657</v>
+      </c>
+      <c r="J140" s="17" t="s">
+        <v>1123</v>
+      </c>
+      <c r="K140" s="16" t="s">
+        <v>1125</v>
+      </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A141" s="17"/>
-      <c r="B141" s="18"/>
-      <c r="C141" s="18" t="s">
+      <c r="A141" s="16" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B141" s="17" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C141" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D141" s="18"/>
-      <c r="E141" s="18"/>
-      <c r="F141" s="18"/>
-      <c r="G141" s="8"/>
-      <c r="H141" s="18"/>
-      <c r="I141" s="18"/>
-      <c r="J141" s="18"/>
-      <c r="K141" s="17"/>
+      <c r="D141" s="17">
+        <v>900</v>
+      </c>
+      <c r="E141" s="17">
+        <v>790</v>
+      </c>
+      <c r="F141" s="17"/>
+      <c r="G141" s="7">
+        <v>15</v>
+      </c>
+      <c r="H141" s="17" t="s">
+        <v>1127</v>
+      </c>
+      <c r="I141" s="17" t="s">
+        <v>657</v>
+      </c>
+      <c r="J141" s="17" t="s">
+        <v>1128</v>
+      </c>
+      <c r="K141" s="16" t="s">
+        <v>1130</v>
+      </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A142" s="17"/>
-      <c r="B142" s="18"/>
-      <c r="C142" s="18" t="s">
+      <c r="A142" s="16" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B142" s="17" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C142" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D142" s="18"/>
-      <c r="E142" s="18"/>
-      <c r="F142" s="18"/>
-      <c r="G142" s="8"/>
-      <c r="H142" s="18"/>
-      <c r="I142" s="18"/>
-      <c r="J142" s="18"/>
-      <c r="K142" s="17"/>
+      <c r="D142" s="17">
+        <v>1500</v>
+      </c>
+      <c r="E142" s="17">
+        <v>1360</v>
+      </c>
+      <c r="F142" s="17"/>
+      <c r="G142" s="7">
+        <v>15</v>
+      </c>
+      <c r="H142" s="17" t="s">
+        <v>1127</v>
+      </c>
+      <c r="I142" s="17" t="s">
+        <v>657</v>
+      </c>
+      <c r="J142" s="17" t="s">
+        <v>1132</v>
+      </c>
+      <c r="K142" s="16" t="s">
+        <v>1134</v>
+      </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A143" s="17"/>
-      <c r="B143" s="18"/>
-      <c r="C143" s="18" t="s">
+      <c r="A143" s="16" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B143" s="17" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C143" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D143" s="18"/>
-      <c r="E143" s="18"/>
-      <c r="F143" s="18"/>
-      <c r="G143" s="8"/>
-      <c r="H143" s="18"/>
-      <c r="I143" s="18"/>
-      <c r="J143" s="18"/>
-      <c r="K143" s="17"/>
+      <c r="D143" s="17">
+        <v>900</v>
+      </c>
+      <c r="E143" s="17">
+        <v>790</v>
+      </c>
+      <c r="F143" s="17"/>
+      <c r="G143" s="7">
+        <v>19</v>
+      </c>
+      <c r="H143" s="17" t="s">
+        <v>1127</v>
+      </c>
+      <c r="I143" s="17" t="s">
+        <v>657</v>
+      </c>
+      <c r="J143" s="17" t="s">
+        <v>1135</v>
+      </c>
+      <c r="K143" s="16" t="s">
+        <v>1137</v>
+      </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A144" s="17"/>
-      <c r="B144" s="18"/>
-      <c r="C144" s="18" t="s">
+      <c r="A144" s="16" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B144" s="17" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C144" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D144" s="18"/>
-      <c r="E144" s="18"/>
-      <c r="F144" s="18"/>
-      <c r="G144" s="8"/>
-      <c r="H144" s="18"/>
-      <c r="I144" s="18"/>
-      <c r="J144" s="18"/>
-      <c r="K144" s="17"/>
+      <c r="D144" s="17">
+        <v>900</v>
+      </c>
+      <c r="E144" s="17">
+        <v>790</v>
+      </c>
+      <c r="F144" s="17"/>
+      <c r="G144" s="7">
+        <v>23</v>
+      </c>
+      <c r="H144" s="17" t="s">
+        <v>1127</v>
+      </c>
+      <c r="I144" s="17" t="s">
+        <v>657</v>
+      </c>
+      <c r="J144" s="17" t="s">
+        <v>1140</v>
+      </c>
+      <c r="K144" s="16" t="s">
+        <v>1142</v>
+      </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A145" s="17"/>
-      <c r="B145" s="18"/>
-      <c r="C145" s="18" t="s">
+      <c r="A145" s="16" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B145" s="17" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C145" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D145" s="18"/>
-      <c r="E145" s="18"/>
-      <c r="F145" s="18"/>
-      <c r="G145" s="8"/>
-      <c r="H145" s="18"/>
-      <c r="I145" s="18"/>
-      <c r="J145" s="18"/>
-      <c r="K145" s="17"/>
+      <c r="D145" s="17">
+        <v>2600</v>
+      </c>
+      <c r="E145" s="17">
+        <v>2400</v>
+      </c>
+      <c r="F145" s="17"/>
+      <c r="G145" s="7">
+        <v>15</v>
+      </c>
+      <c r="H145" s="17" t="s">
+        <v>971</v>
+      </c>
+      <c r="I145" s="17" t="s">
+        <v>657</v>
+      </c>
+      <c r="J145" s="17" t="s">
+        <v>1144</v>
+      </c>
+      <c r="K145" s="16" t="s">
+        <v>1146</v>
+      </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A146" s="17"/>
-      <c r="B146" s="18"/>
-      <c r="C146" s="18" t="s">
+      <c r="A146" s="16" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B146" s="17" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C146" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D146" s="18"/>
-      <c r="E146" s="18"/>
-      <c r="F146" s="18"/>
-      <c r="G146" s="8"/>
-      <c r="H146" s="18"/>
-      <c r="I146" s="18"/>
-      <c r="J146" s="18"/>
-      <c r="K146" s="17"/>
+      <c r="D146" s="17">
+        <v>1700</v>
+      </c>
+      <c r="E146" s="17">
+        <v>1580</v>
+      </c>
+      <c r="F146" s="17"/>
+      <c r="G146" s="7">
+        <v>24</v>
+      </c>
+      <c r="H146" s="17" t="s">
+        <v>971</v>
+      </c>
+      <c r="I146" s="17" t="s">
+        <v>657</v>
+      </c>
+      <c r="J146" s="17" t="s">
+        <v>1148</v>
+      </c>
+      <c r="K146" s="16" t="s">
+        <v>1150</v>
+      </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A147" s="17"/>
-      <c r="B147" s="18"/>
-      <c r="C147" s="18" t="s">
+      <c r="A147" s="16" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B147" s="17" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C147" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="D147" s="18"/>
-      <c r="E147" s="18"/>
-      <c r="F147" s="18"/>
-      <c r="G147" s="8"/>
-      <c r="H147" s="18"/>
-      <c r="I147" s="18"/>
-      <c r="J147" s="18"/>
-      <c r="K147" s="17"/>
+      <c r="D147" s="17">
+        <v>2800</v>
+      </c>
+      <c r="E147" s="17">
+        <v>2500</v>
+      </c>
+      <c r="F147" s="17"/>
+      <c r="G147" s="7">
+        <v>14</v>
+      </c>
+      <c r="H147" s="17" t="s">
+        <v>971</v>
+      </c>
+      <c r="I147" s="17" t="s">
+        <v>657</v>
+      </c>
+      <c r="J147" s="17" t="s">
+        <v>1152</v>
+      </c>
+      <c r="K147" s="16" t="s">
+        <v>1154</v>
+      </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G148" s="8"/>
+      <c r="C148" s="15" t="s">
+        <v>653</v>
+      </c>
+      <c r="G148" s="7"/>
+      <c r="I148" s="15" t="s">
+        <v>657</v>
+      </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G149" s="8"/>
+      <c r="C149" s="15" t="s">
+        <v>653</v>
+      </c>
+      <c r="G149" s="7"/>
+      <c r="I149" s="15" t="s">
+        <v>657</v>
+      </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G150" s="8"/>
+      <c r="C150" s="15" t="s">
+        <v>653</v>
+      </c>
+      <c r="G150" s="7"/>
+      <c r="I150" s="15" t="s">
+        <v>657</v>
+      </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G151" s="8"/>
+      <c r="C151" s="15" t="s">
+        <v>653</v>
+      </c>
+      <c r="G151" s="7"/>
+      <c r="I151" s="15" t="s">
+        <v>657</v>
+      </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G152" s="8"/>
+      <c r="C152" s="15" t="s">
+        <v>653</v>
+      </c>
+      <c r="G152" s="7"/>
+      <c r="I152" s="15" t="s">
+        <v>657</v>
+      </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G153" s="8"/>
+      <c r="C153" s="15" t="s">
+        <v>653</v>
+      </c>
+      <c r="G153" s="7"/>
+      <c r="I153" s="15" t="s">
+        <v>657</v>
+      </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G154" s="8"/>
+      <c r="C154" s="15" t="s">
+        <v>653</v>
+      </c>
+      <c r="G154" s="7"/>
+      <c r="I154" s="15" t="s">
+        <v>657</v>
+      </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G155" s="8"/>
+      <c r="C155" s="15" t="s">
+        <v>653</v>
+      </c>
+      <c r="G155" s="7"/>
+      <c r="I155" s="15" t="s">
+        <v>657</v>
+      </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G156" s="8"/>
+      <c r="C156" s="15" t="s">
+        <v>653</v>
+      </c>
+      <c r="G156" s="7"/>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G157" s="8"/>
+      <c r="C157" s="15" t="s">
+        <v>653</v>
+      </c>
+      <c r="G157" s="7"/>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G158" s="8"/>
+      <c r="C158" s="15" t="s">
+        <v>653</v>
+      </c>
+      <c r="G158" s="7"/>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C159" s="15" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C160" s="15" t="s">
+        <v>653</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K93" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/price.xlsx
+++ b/price.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ПРОЕКТ AI\ЛИЧНЫЕ НАРАБОТКИ\AI Skin Lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FF1C87-B644-40C2-8199-42242411DEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84258969-3C80-4057-88E3-80AA2C0BB7BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-1512" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Зручна таблиця" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1594" uniqueCount="716">
   <si>
     <t>Артикул</t>
   </si>
@@ -77,6 +77,9 @@
   </si>
   <si>
     <t>50 мл</t>
+  </si>
+  <si>
+    <t>Україна</t>
   </si>
   <si>
     <t>002</t>
@@ -5952,8 +5955,974 @@
     <t>Комплексний очищуючий тонік Anna Logor Purifying Complex Toner (Art.302), 350 мл</t>
   </si>
   <si>
+    <t>AL302</t>
+  </si>
+  <si>
+    <t>Очищуюче молочко з екстрактом примули Anna Logor Vital Primrose Cleanser (Art.501), 350 мл</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor Vital Primrose Cleanser – ніжне очищення та догляд після 30! ✨
+🌿 Чому варто обрати це молочко:
+💧 Делікатно видаляє макіяж та забруднення, не порушуючи баланс шкіри
+🌸 Живить та заспокоює, дарує відчуття комфорту
+🛡️ Сприяє регенерації клітин та захищає від шкідливих бактерій
+⚡ Допомагає боротися з першими ознаками старіння
+🌟 Підтримує пружність та свіжість шкіри
+💚 Результат – доглянута, сяюча та м’яка шкіра щодня!
+📌 Активні компоненти:
+🌱 Вітаміни А та С – антиоксидантний захист та омолодження
+🍋 Лимонна кислота – м’яке відлущування та вирівнювання тону
+🌸 Екстракти розмарину, хвої, примули, хвоща та хмелю – живлення, тонізація та регенерація
+📌 Основні властивості:
+Баланс вологи та живлення
+Заспокійлива дія та стимуляція регенерації
+Приємний аромат
+Легке нанесення та змивання теплою водою
+Економне використання завдяки дозатору
+📌 Спосіб застосування:
+Нанести молочко на ватний диск.
+Протерти шкіру від центру до країв, уникаючи зони навколо очей.
+Змити теплою водою.
+Для максимального ефекту використати тонік Vital Primrose.
+✔️ Характеристики продукту:
+Тип: Очищуюче молочко
+Об’єм: 350 мл
+Вікова категорія: 30+, без обмежень
+Призначення: Очищення, живлення, регенерація
+Бренд: Anna Logor
+Країна виробництва: 🇺🇦 Україна
+🌟 Anna Logor Vital Primrose Cleanser – твій must-have для ніжного догляду та збереження молодості шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>AL501</t>
+  </si>
+  <si>
+    <t>Тональний сонцезахисний крем SPF-30 UVA,UVB Anna Logor (Art.1057), 115 мл</t>
+  </si>
+  <si>
+    <t>115 мл</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor Sunscreen SPF-30 – ідеальний тон та надійний захист! ✨
+🌿 Чому варто обрати цей крем:
+💧 Забезпечує рівний тон шкіри та тривале зволоження
+🌸 Захищає від UVA та UVB-променів, запобігаючи пігментації та зморшкам
+🛡️ Органічні, неорганічні та рослинні УФ-фільтри – ефективний захист від опіків і фотостаріння
+⚡ Сприяє регенерації клітин після пілінгу
+🌟 Гіпоалергенна формула, підходить навіть для жирної та комбінованої шкіри
+💚 Результат – свіжа, сяюча та захищена шкіра щодня!
+📌 Активні компоненти:
+🌱 Вітамін Е – антиоксидантний щит
+🌸 Екстракти мальви, бузини, огірка, плюща, настінниці лікарської, арніки – заспокоюють та відновлюють
+💧 Натуральні інгредієнти з вираженою регенеративною дією
+📌 Спосіб застосування:
+Очистіть шкіру обличчя та шиї за допомогою спеціального очищувача Anna Logor.
+Нанесіть крем рівномірним шаром перед виходом на сонце.
+Для тривалого ефекту повторюйте нанесення протягом дня.
+✔️ Характеристики продукту:
+Тип: Тональний сонцезахисний крем
+SPF: 30 (UVA/UVB)
+Об’єм: 115 мл · Туба з фліп-дозатором
+Призначення: Захист від сонця, вирівнювання тону, профілактика фотостаріння
+Тип шкіри: Усі типи, включно з жирною та комбінованою
+Бренд: Anna Logor
+Країна виробництва: 🇺🇦 Україна
+🌟 Anna Logor Sunscreen SPF-30 – твій must-have для рівного тону та бездоганного захисту від сонця! 🌟</t>
+  </si>
+  <si>
+    <t>AL1057</t>
+  </si>
+  <si>
+    <t>Тонік з екстрактом примули Anna Logor Vital Primrose Toner (Art.502), 350 мл</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor Vital Primrose Toner – ніжний догляд та відновлення після 30! ✨
+🌿 Чому варто обрати цей тонік:
+💧 Делікатно видаляє забруднення та надлишки себуму
+🌸 Відновлює природний баланс вологи та рН
+🛡️ Заспокоює, пом’якшує та живить шкіру
+⚡ Сприяє швидкій регенерації клітин
+🌟 Допомагає боротися з першими ознаками старіння
+💚 Результат – доглянута, пружна та сяюча шкіра щодня!
+📌 Активні компоненти:
+🌱 Вітамін В5 – живлення та регенерація
+🌸 Екстракти розмарину, польового хвоща, примули, хмелю, лимона та хвої – тонізація, антиоксидантний захист та відновлення
+📌 Спосіб застосування:
+Використовуйте щодня вранці та ввечері після очищення обличчя молочком Anna Logor Vital Primrose Cleanser.
+Нанесіть тонік на ватний диск і акуратно протирайте шкіру по масажних лініях від центру до країв, уникаючи зони навколо очей.
+Для максимального ефекту після процедури застосуйте Mezotherapy Serum, Mezotherapy Firming Moisturizer або Mezotherapy Night Cream.
+✔️ Переваги продукту:
+Без спирту, делікатна формула
+Натуральні екстракти
+Підходить для щоденного використання
+Зручний флакон з дозатором
+🌟 Anna Logor Vital Primrose Toner – твій must-have для щоденного догляду та збереження молодості шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>AL502</t>
+  </si>
+  <si>
+    <t>Сонцезахисний крем SPF-50 UVA,UVB DD Cream Anna Logor (Art.1058), 110 мл</t>
+  </si>
+  <si>
+    <t>110 мл</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor Sunscreen SPF-50 – максимальний захист та догляд! ✨
+🌿 Чому варто обрати цей крем:
+🛡️ Забезпечує надійний захист від UVA та UVB-променів
+💧 Запобігає фотостарінню та появі пігментації
+🌸 Інтенсивно зволожує та пом’якшує шкіру
+⚡ Сприяє відновленню клітин після впливу сонця чи косметологічних процедур
+🌟 Підходить для щоденного використання навіть на чутливій шкірі
+💚 Результат – свіжа, доглянута та захищена шкіра без відчуття жирності!
+📌 Активні компоненти:
+🌱 Аллантоїн – заспокоює та відновлює
+💧 Зволожуючий комплекс – підтримує баланс вологи
+🌸 Вітамін Е – антиоксидантний захист
+🌿 Екстракти мальви, плюща, постінниці лікарської, огірка, алое вера, бузини та арніки – живлення, тонізація та регенерація
+📌 Спосіб застосування:
+Очистіть шкіру обличчя та шиї за допомогою молочка чи пінного очищувача Anna Logor.
+Нанесіть невелику кількість крему круговими масажними рухами.
+Легкими дотиками пальців розподіліть до повного вбирання.
+✔️ Переваги продукту:
+Високий рівень захисту SPF-50
+Формула без подразнюючих компонентів
+Підходить для всіх типів шкіри, включно з чутливою
+Зручний флакон із дозатором для економного використання
+📦 Форма випуску:  
+Флакон із дозатором · 120 мл
+Формула: США · Виробництво: 🇺🇦 Україна
+🌟 Anna Logor Sunscreen SPF-50 – твій must-have для бездоганного захисту та здорової шкіри під сонцем! 🌟</t>
+  </si>
+  <si>
+    <t>AL1058</t>
+  </si>
+  <si>
+    <t>Очищуючий гель для жирної шкіри Anna Logor Oil Control Cleanser (Art.201), 350 мл</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor Oil Control Cleanser – професійне очищення для жирної шкіри! ✨
+🌿 Чому варто обрати цей гель:
+💧 Регулює роботу сальних залоз
+🌸 Зменшує жирність та дарує матовість
+🛡️ Нормалізує рівень pH
+⚡ Ефективно видаляє забруднення, ороговілі клітини та залишки макіяжу
+🌟 Готує шкіру до наступних етапів догляду
+💚 Результат – чиста, свіжа та доглянута шкіра без жирного блиску!
+📌 Активні компоненти:
+🌱 Карбонова, себацинова та гідроксидексанова кислоти – м’яке відлущування, антибактеріальна дія, покращення мікрофлори
+🌸 Екстракти кори білої верби, лимона, лопуха, крес-салату, шавлії та плюща – природне очищення, тонізація та регенерація
+📌 Спосіб застосування:
+Нанесіть гель на вологу шкіру обличчя.
+Легко помасажуйте.
+Ретельно змийте теплою водою.
+Для максимального ефекту використовуйте стабілізуючий тонік Oil Control Toner Anna Logor.
+✔️ Переваги продукту:
+Легка текстура та приємний аромат
+Підходить для щоденного застосування
+Натуральний склад
+Зручний флакон із дозатором · 350 мл
+🌟 Anna Logor Oil Control Cleanser – твій must-have для щоденного догляду за жирною шкірою! 🌟</t>
+  </si>
+  <si>
+    <t>AL201</t>
+  </si>
+  <si>
+    <t>Інтенсивний ліфтинг-відновлюючий денний крем Perfect Skin Ultimate Lifting Recovery (Art.43), 50 мл</t>
+  </si>
+  <si>
+    <t>Інтенсивний ліфтинг-крем для глибокого відновлення
+Цей крем — потужний коктейль активних компонентів, що забезпечує глибоке відновлення та видимий ліфтинг. Формула працює одразу в трьох напрямках: екстремальне зволоження, зміцнення структури шкіри та захист від передчасного старіння.
+Основна дія
+✨ Миттєвий ліфтинг і гладкість Поєднання пуллулану, альгіну та інноваційного пептиду Palmitoyl Tripeptide-28 (з частинками сапфіру для кращого проникнення) підтягує овал обличчя та стимулює синтез колагену.
+💧 Глибоке 4D-зволоження Комплекс із гіалуронової кислоти, сечовини, трегалози та серину створює невидиму «дихаючу» сітку, яка утримує вологу протягом усього дня.
+🌿 Вітамінне омолодження Вітамін А прискорює оновлення клітин, а вітамін Е та глутатіон — один із найсильніших антиоксидантів — нейтралізують дію вільних радикалів і повертають шкірі сяйво.
+🌸 Живлення цінними оліями Олії примули вечірньої відновлюють захисний бар’єр, усувають сухість і дарують шкірі оксамитовість.
+🍃 Рослинний детокс Екстракти арніки, плюща та бузини знімають набряки, зміцнюють судини та вирівнюють тон обличчя.
+Кому підійде
+Ідеальний для зрілої, сухої або втомленої шкіри, що втратила тонус. Легка текстура на основі сквалану та сучасних емолентів швидко вбирається, не залишаючи жирного блиску, і чудово підходить як база під макіяж.
+Результат
+Шкіра стає більш щільною та підтягнутою
+Дрібні зморшки розгладжуються
+Обличчя виглядає свіжим, живленим і сяючим
+Застосування
+Наносити щодня вранці на очищене обличчя, шию та зону декольте. Для максимального ефекту рекомендується комбінувати з Visage Cream Rich 44 як нічним доглядом та використовувати разом із сироваткою.
+Активні компоненти
+Трипептид-28, зволожуючий комплекс PatchH2O™, сквалан, олії примули, пікуї, каштану, малини та крамбе, вітаміни А й Е, екстракти мальви, плюща, постенніци лікарської, огірка, бузини та арніки.
+Відчуття на шкірі
+Освіжає, ніжно зволожує, дарує шовковистість.
+Текстура
+Ніжна, повітряна, легка, швидко вбирається.
+Аромат
+Делікатна зелено-квіткова композиція з легким фруктовим відтінком.</t>
+  </si>
+  <si>
+    <t>AL43</t>
+  </si>
+  <si>
+    <t>Цитрусова маска для жирної шкіри Anna Logor Oil Control Citrus Mask (Art.255), 250 мл</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor Oil Control Citrus Mask – свіжість та матовість для жирної шкіри! ✨
+🌿 Чому варто спробувати:
+💧 Регулює вироблення себуму
+🌸 Звужує пори та зменшує їх помітність
+🛡️ Знімає почервоніння та заспокоює шкіру
+⚡ Дарує матовий ефект і здоровий вигляд
+💚 Результат – чиста, доглянута та матова шкіра вже після першого застосування!
+📌 Активні компоненти:
+🌱 Себацинова та гідрокідеканова кислота – контроль себуму та м’яке відлущування
+🌸 Каолінова глина – очищення та матування
+🛡️ Органічна сірка – протизапальна дія
+🌿 Екстракти кресса водяного, лимона, гриба агарика, лопуха, плюща, шавлії – природне відновлення та захист
+🌟 Вітаміни А, Е, С – антиоксидантний комплекс
+📌 Консистенція та застосування:
+Ніжна пастоподібна текстура, легко наноситься та змивається
+Використовувати 1–2 рази на тиждень
+Нанести тонким шаром (1–2 мм) на очищену шкіру обличчя та шиї
+Через 15 хвилин змити прохолодною водою або видалити вологим рушником
+Для закріплення результату застосувати Oil Control Fluid Anna Logor
+✔️ Переваги продукту:
+Натуральний склад
+Швидкий ефект матування
+Приємний аромат
+Зручна форма випуску – баночка 250 мл · Art.255
+Вікова категорія: 16+
+🌟 Anna Logor Oil Control Citrus Mask – твій must-have для догляду за жирною шкірою та контролю себуму! 🌟</t>
+  </si>
+  <si>
+    <t>AL255</t>
+  </si>
+  <si>
+    <t>Живильний зміцнюючий нічний крем Perfect Skin Visage Cream Rich (Art.44), 50 мл</t>
+  </si>
+  <si>
+    <t>Нічний крем — «інтелектуальний відновлювач»
+Поки ви спите, крем працює над зміцненням каркаса шкіри, глибоким живленням та оновленням клітин. Вранці обличчя виглядає сяючим, свіжим і відпочилим.
+Основна дія
+✨ Пептидне моделювання (Drone Technology) Капсульована система доставки пептидів проникає у глибокі шари дерми, відновлює пошкоджені колагенові волокна, ущільнює шкіру та зменшує глибину зморшок.
+🌙 Нічний мікропілінг і сяйво Комплекс гліколевої, молочної та саліцилової кислот м’яко відлущує ороговілі клітини, вирівнює тон і текстуру, запобігаючи тьмяності.
+🌿 Ліпідне відновлення Олії жожоба та ши поповнюють дефіцит власних ліпідів, роблячи шкіру оксамитовою та насиченою до ранку.
+💧 Тривала гідратація (PatcH2O™) Молекулярна сітка з гіалуронової кислоти, сечовини та трегалози утримує вологу всередині клітин протягом усього циклу сну.
+🍃 Вітамінний детокс і зміцнення Вітаміни А та Е стимулюють клітинне оновлення, а екстракти хвоща, хмелю та розмарину знімають набряклість і зміцнюють судини.
+Кому підійде
+Для шкіри з втратою пружності, нерівним рельєфом та ознаками фотостаріння. Текстура насичена, але комфортна, швидко засвоюється протягом ночі.
+Результат
+Вранці обличчя виглядає підтягнутим і відпочилим
+Зникають дрібні зморшки
+Зміцнюється овал обличчя
+Відновлюється здоровий тургор
+Застосування
+Щодня ввечері наносити на очищене обличчя, шию та зону декольте. Для посилення ефекту використовувати разом із сироваткою. Ідеально поєднується з денним кремом Ultimate Lifting Recovery 43.
+Активні компоненти
+Пентапептид-35, протеїни сої, комплекс PatcH2O™, сквалан, олії ши, жожоба, примули, кави, пікуї та дині калаха, вітаміни А та Е, альфа-ліпоєва кислота, екстракти хмелю, розмарину, хвоща, хвої та лимона.
+Відчуття на шкірі
+Живлення, ніжне зволоження, шовковисто-оксамитовий ефект.
+Текстура
+Живильний крем, щільний, але легкий, швидко вбирається.
+Аромат
+Делікатна зелено-квіткова композиція з легким фруктовим відтінком.</t>
+  </si>
+  <si>
+    <t>AL44</t>
+  </si>
+  <si>
+    <t>Очищуюче молочко з трав'яними екстрактами Anna Logor Silky Herbal Cleanser (Art.401), 350 мл</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor Silky Herbal Cleanser – ніжне очищення та шовковиста шкіра! ✨
+🌿 Чому варто обрати це молочко:
+💧 Делікатно видаляє макіяж, забруднення та надлишки себуму
+🌸 Забезпечує комплексний догляд завдяки трав’яним екстрактам
+🛡️ Вирівнює рельєф шкіри та нейтралізує відчуття стягнутості
+⚡ Глибоко зволожує та пом’якшує
+🌟 Допомагає розгладити дрібні зморшки та дарує омолоджувальний ефект
+💚 Результат – чиста, доглянута та сяюча шкіра без сухості!
+📌 Активні компоненти:
+🌱 Оливкова олія – живлення та захист
+🌸 Вітаміни А, Е та С – антиоксидантна дія та омолодження
+🌿 Екстракти розмарину, хвої, лимона, хмелю, хвоща польового – тонізація, регенерація та відновлення
+📌 Особливості продукту:
+Приємний аромат та ніжна текстура
+Добре піниться та легко змивається
+Зручний флакон із дозатором – економне використання
+📌 Спосіб застосування:
+Нанести молочко на зволожену шкіру обличчя.
+Розподілити легкими рухами.
+Змити теплою водою.
+Для максимального ефекту використати тонік Silky Herbal Toner Anna Logor.
+✔️ Характеристики продукту:
+Тип: Очищувальне молочко з трав’яними екстрактами
+Об’єм: 350 мл
+Вікова категорія: 16+
+Тип шкіри: Суха та нормальна
+Бренд: Anna Logor
+Країна виробництва: 🇺🇦 Україна
+🌟 Anna Logor Silky Herbal Cleanser – твій must-have для ніжного очищення та збереження молодості шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>AL401</t>
+  </si>
+  <si>
+    <t>Комплексний очищуючий гель Anna Logor Purifying Complex Cleanser (Art.301), 350 мл</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor Purifying Complex Cleanser – ідеальний баланс для комбінованої шкіри! ✨
+🌿 Чому варто обрати цей гель:
+💧 Ефективно видаляє надлишки себуму та звужує пори
+🌸 Пом’якшує, глибоко зволожує та делікатно освітлює шкіру
+🛡️ Стимулює процеси клітинного відновлення
+⚡ Покращує структуру та колір обличчя
+🌟 Дарує природну матовість і відчуття свіжості
+💚 Результат – доглянута, чиста та сяюча шкіра без дискомфорту!
+📌 Активні компоненти:
+🌱 Екстракти водяного кресу, шавлії, лимона, лопуха та плюща – природне очищення та тонізація
+⚡ Гліколева, лимонна, яблучна та молочна кислоти – м’яке відлущування та регенерація
+📌 Спосіб застосування:
+Нанесіть достатню кількість гелю на зволожену шкіру обличчя.
+Розподіліть легкими рухами.
+Ретельно змийте теплою водою.
+Для закріплення ефекту використайте тонік Purifying Complex Toner Anna Logor.
+✔️ Особливості продукту:
+Приємний аромат
+Зручний флакон із дозатором
+Економне використання
+Об’єм: 350 мл · Art.301
+Вікова категорія: 16+
+Тип шкіри: комбінована
+🌟 Anna Logor Purifying Complex Cleanser – твій must-have для щоденного догляду за комбінованою шкірою! 🌟</t>
+  </si>
+  <si>
+    <t>AL301</t>
+  </si>
+  <si>
+    <t>Омолоджуючий зміцнюючий-зволожуючий денний крем Anna Logor Mezotherapy Firming Moisturizer (Art.521), 250 мл</t>
+  </si>
+  <si>
+    <t>✨ Mezotherapy Firming Moisturizer – професійний ліфтинг та зволоження щодня! ✨
+🌿 Чому варто обрати цей крем:
+💧 Натуральний склад – кераміди, масло ши, гіалуронова кислота, протеїни сої, екстракти хмелю та розмарину
+🌸 Боротьба зі зморшками – зменшує мімічні лінії, заломи та дрібні зморшки
+🛡️ Глибоке зволоження – нормалізує водний баланс, усуває сухість та чутливість
+⚡ Ліфтинг-ефект – підвищує пружність, робить овал обличчя чітким і виразним
+💚 Результат – підтягнута, сяюча та доглянута шкіра вже після кількох застосувань!
+📌 Активні компоненти:
+🌱 Кераміди – відновлення бар’єрних функцій
+🌸 Масло ши – живлення та пом’якшення
+💧 Гіалуронова кислота – інтенсивне зволоження
+🛡️ Протеїни сої – підвищення еластичності
+🌿 Екстракти хмелю та розмарину – антиоксидантна дія та тонізація
+✔️ Переваги продукту:
+Натуральна формула без шкідливих компонентів
+Професійний догляд у домашніх умовах
+Відчутний ефект ліфтингу та зволоження
+Підходить для щоденного використання
+🌟 Mezotherapy Firming Moisturizer – твій must-have для збереження молодості та краси шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>AL521</t>
+  </si>
+  <si>
+    <t>Живильний пептидний нічний крем Perfect Skin Peptide-Rich Cream (Art.54), 50 мл</t>
+  </si>
+  <si>
+    <t>Нічний крем з платиною та пептидами: Розкішна реновація вашої шкіри
+Цей нічний крем — справжня квінтесенція сучасної косметології, створена для бездоганного догляду за зрілою шкірою. Поки ви насолоджуєтеся сном, інноваційна формула на основі дорогоцінної платини та пептидів проводить глобальну «реновацію» клітин, повертаючи обличчю природну щільність, шовковисту гладкість та здорове внутрішнє сяйво.
+💎 Секрет ефективності: Як це працює?
+Платинове омолодження (Platinum Peptides): Ключовий актив (Acetyl Tetrapeptide-17) у синергії з частинками колоїдної платини діє як надпотужний клітинний регенератор. Платина гарантує максимальну стабільність пептиду, що дозволяє йому ефективно запускати синтез колагену та еластину — фундаментальних елементів молодості шкіри.
+Нічне мікрооновлення: Делікатний комплекс гліколевої, молочної та саліцилової кислот забезпечує м'яке, фізіологічне оновлення. Він усуває вікову гіперкератозність (огрубіння), вирівнює тон та готує шкіру до максимального засвоєння поживних речовин.
+Розумне зволоження PatcH2O™: Передова система на основі гіалуронової кислоти, трегалози та сечовини створює на шкірі захисну молекулярну мікросітку. Вона дозовано віддає вологу протягом усієї ночі, надійно запобігаючи ефекту «ранкової пом’ятості».
+Інтенсивний живильний коктейль: Розкішна база з олій примули вечірньої та жожоба глибоко насичує стоншену шкіру, реставрує її бар’єрні функції та миттєво усуває сухість.
+Тонус та антиоксидантний захист: Вітаміни молодості (А та Е) сприяють клітинному омолодженню, а екстракти хвоща, хмелю та сосни тонізують тканини і зміцнюють мікросудини.
+✨ Для кого створений цей крем?
+Ідеальний вибір для власниць зрілої шкіри (45+), яка потребує глибокого відновлення, інтенсивної корекції зморшок та ефективного усунення в’ялості.
+Ваш результат: Вже на ранок шкіра стає неймовірно м’якою, «наповненою» та пружною. За умови регулярного використання платинові пептиди забезпечують виражений ліфтинг-ефект: моделюється овал обличчя, а шкіра набуває того самого доглянутого, «дорогого» вигляду.
+🌸 Сенсорний досвід та характеристики
+Текстура: Живильна, щільна, але напрочуд легка — миттєво та комфортно вбирається.
+Відчуття на шкірі: Глибоке живлення, ніжне зволоження та розкішний шовковисто-оксамитовий фініш.
+Аромат: Вишуканий парфумований букет із витонченими квітково-пудровими мотивами.
+Активний склад: Пептидні комплекси (зокрема гептапептид-17), сквалан, гіалуронова та молочна кислоти, комплекс ПатчН2О™, цінні олії (ши, жожоба, примули, кави, дині калахарі, камелії), вітаміни А та Е, рослинні екстракти (хміль, розмарин, хвощ, хвоя, лимон).
+🌙 Ритуал краси (Застосування)
+Щовечора наносьте крем на попередньо очищену шкіру обличчя, шиї та зони декольте.
+Порада експерта: Для досягнення максимального омолоджувального ефекту використовуйте крем після нанесення сироватки. В якості денного догляду ідеальним доповненням стане крем Derma-Restructurant 53.</t>
+  </si>
+  <si>
+    <t>AL54</t>
+  </si>
+  <si>
+    <t>Пінний очищувач обличчя Anna Logor Foaming Facial Cleanser (Art.1003), 160 мл</t>
+  </si>
+  <si>
+    <t>160 мл</t>
+  </si>
+  <si>
+    <t>Anna Logor Foaming Facial Cleanser (150 мл, Art.1003)
+📌 Основні характеристики
+Тип засобу: Очищувальна пінка з помпою-піноутворювачем.
+Об'єм / Артикул: 150 мл / Art.1003.
+Вікова категорія: 18+ (без обмежень).
+Призначення: Для всіх типів шкіри, зокрема сухої, чутливої та тьмяної.
+🧪 Активні компоненти та їхня дія
+КомпонентДія на шкіруКомплекс AHA-кислот + ЛимонМ'яко відлущують змертвілі клітини, вирівнюють рельєф, вибілюють та освіжають тон.Гіалуронова кислотаГлибоко зволожує, запобігає втраті вологи та відчуттю стягнутості після вмивання.Екстракти хвоща, розмарину, хвої та хмелюНадають антисептичний ефект, дезінфікують, тонізують та сприяють детоксикації.
+💧 Спосіб застосування
+Нанесіть необхідну кількість пінки масажними круговими рухами на вологу шкіру обличчя та шиї (уникаючи ділянки навколо очей).
+Масажуйте до розчинення макіяжу та забруднень.
+Змийте великою кількістю теплої води.
+Завершіть процедуру тоніком Anna Logor для відновлення pH-балансу.
+💡 Примітка щодо використання: Оскільки засіб містить AHA-кислоти (навіть у м'якій концентрації), під час ранкового догляду рекомендовано додатково наносити сонцезахисний засіб (SPF), особливо для чутливої шкіри.</t>
+  </si>
+  <si>
+    <t>AL1003</t>
+  </si>
+  <si>
+    <t>Гідрогелева маска з ПДРН Miore Magic Wand PDRN Hydrogel Mask, 1 шт</t>
+  </si>
+  <si>
+    <t>1 шт</t>
+  </si>
+  <si>
+    <t>Miore Magic Wand PDRN Hydrogel Mask — це мультифункціональна гідрогелева маска з ПДРН, яка працює миттєво та має пролонговану дію від 3 до 5 днів.
+Зняти запалення після процедур чи за 20 хвилин підготувати шкіру до важливої події? Вона може все!
+Чому це фаворит косметологів та клієнтів:
+💧 Миттєвий SOS-ефект: швидко знімає почервоніння, набряки та гіперемію.
+✨ Ефект «вау-сяйва»: вирівнює тон, підвищує тургор і робить шкіру оксамитовою на дотик.
+🌿 Альтернатива ін'єкціям: при регулярному використанні дає результат, порівняний із біоревіталізацією та ботулінотерапією — без болю, синців і реабілітації.
+🛡️ Регенерація та захист: прискорює відновлення шкіри після пілінгів, лазера, ін'єкцій та чисток.
+Потужний склад для видимого результату:
+ПДРН (PDRN) — запускають глибинні процеси регенерації та омолодження клітин.
+Аргірелін (Argireline) — пептид із ботокс-ефектом, що м'яко розгладжує мімічні зморшки.
+Гіалуронова кислота + Бета-глюкан — забезпечують глибоке зволоження та зміцнюють захисний бар'єр.
+Комплекс із 12 рослинних екстрактів (алое, ромашка, розмарин, юзу, лаванда тощо) — чинять потужну протизапальну та заспокійливу дію.
+Універсальний засіб: підходить як для закриття професійних процедур у кабінеті косметолога, так і для домашнього догляду «на вихід» або підтримки салонного ефекту.</t>
+  </si>
+  <si>
+    <t>AL9001</t>
+  </si>
+  <si>
+    <t>Омолоджуюча сироватка з пептидами Perfect Skin Nutri-Peptide Serum (Art.55), 30 мл</t>
+  </si>
+  <si>
+    <t>✨ 55 Nutri-Peptide Serum – інтенсивна корекція вікових змін! ✨
+🌿 Чому варто обрати цю сироватку:
+💧 Створена спеціально для шкіри 35–45 років
+🌸 Синергетичний комплекс пептидів стимулює синтез колагену та еластину
+🛡️ Вирівнює мікрорельєф та покращує колір обличчя
+⚡ Забезпечує ліфтинг-ефект і моделює чіткіший овал
+🌟 Зменшує пігментацію та запобігає появі нових плям
+💚 Результат – пружна, сяюча та доглянута шкіра без ознак втоми!
+📌 Результати застосування:
+Ліфтинг та відновлення – підвищення тургору та пружності
+Корекція пігментації – зменшення вікових плям
+Ефект «м’якого фокусу» – миттєве маскування недосконалостей
+Захист та зволоження – протидія передчасному старінню
+📌 Активні компоненти:
+🌱 Тетрапептид-11, гептапептид-14, гептапептид-15 – стимуляція синтезу колагену
+🌸 Протеїни сої – підвищення еластичності
+🛡️ Альфа-ліпоєва кислота – антиоксидантний захист
+🌿 Екстракти хмелю, розмарину, хвоща, хвої та лимона – регенерація та тонізація
+📌 Спосіб застосування:
+Нанести кілька крапель на очищену шкіру обличчя, шиї та декольте.
+Легкими круговими рухами розподілити до повного поглинання.
+Використовувати як самостійний засіб, під крем або як базу під макіяж.
+✔️ Характеристики продукту:
+Тип: Омолоджувальна пептидна сироватка
+Об’єм: 30 мл
+Призначення: Проти зморшок, пігментації, сухості, ліфтинг
+Тип шкіри: Для всіх типів
+Вікова категорія: 35–45 років (35+)
+Клас косметики: Професійна
+Екотренди: Cruelty-free (не тестується на тваринах)
+Країна-виробник: 🇺🇸 США
+🌟 55 Nutri-Peptide Serum – твій must-have для інтенсивного омолодження та сяйва шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>AL55</t>
+  </si>
+  <si>
+    <t>Очищуючий гель для вмивання з AHA-кислотами Miore, 250 мл</t>
+  </si>
+  <si>
+    <t>AL9003</t>
+  </si>
+  <si>
+    <t>✨ Renewal AHA Cleanser – глибоке очищення та сяйво без стягнутості! ✨
+🌿 Чому цей гель стане улюбленцем у вашому догляді:
+💧 Ніжне оновлення та гладкість – м’яко відлущує відмерлі клітини, прискорює регенерацію, робить шкіру шовковистою вже після перших застосувань
+🌸 Матовий фініш та чисті пори – нормалізує виділення себуму, прибирає небажаний блиск у Т-зоні, візуально звужує пори
+🛡️ Чиста шкіра без запалень – чинить антибактеріальну та антисептичну дію, заспокоює почервоніння, запобігає новим висипанням
+⚡ Рівний тон та сяйво – поступово освітлює сліди постакне й пігментні плями, повертає свіжий та здоровий вигляд
+🌟 Підсилення догляду – готує шкіру до сироваток і кремів, підвищуючи їхню ефективність; рекомендований як етап підготовки до пілінгів
+💚 Результат – чиста, матова та сяюча шкіра без відчуття сухості!
+📌 Спосіб застосування:
+Спіньте невелику кількість гелю у вологих долонях.
+Нанесіть на вологу шкіру обличчя, м’яко помасажуйте вздовж масажних ліній, уникаючи ділянки навколо очей.
+Ретельно змийте теплою водою.
+💡 Б’юті-порада: оскільки засіб містить AHA-кислоти, обов’язково використовуйте сонцезахисний крем (SPF) протягом дня, щоб зберегти молодість та запобігти пігментації.
+✔️ Переваги продукту:
+Збалансований комплекс AHA-кислот
+Делікатна формула без пересушування
+Професійний догляд у домашніх умовах
+Підходить для щоденного використання
+🌟 Renewal AHA Cleanser – твій must-have для сяючої та здорової шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>Освітлюючий зволожуючий крем Anna Logor Lightening Moisturizer (Art.951), 250 мл</t>
+  </si>
+  <si>
+    <t>Освітлюючий зволожуючий крем для обличчя Anna Logor Lightening Moisturizer (250 мл)
+Мрієте про ідеально рівний, свіжий тон шкіри без пігментних плям та веснянок?
+Професійний крем Anna Logor Lightening Moisturizer — це комплексне рішення для освітлення шкіри, глибокого зволоження та надійного захисту від передчасного старіння. Завдяки високій концентрації активних компонентів крем блокує надмірну виробку меланіну та повертає обличчю природне сяйво.
+Чому цей крем стане вашим фаворитом?
+✨ Ефективне освітлення: Помітно зменшує вираженість пігментних плям, веснянок та слідів постакне, вирівнюючи мікрорельєф і колір шкіри.
+🛡️ Захист від сонця та фотостаріння: УФА/УФВ-фільтри затримують шкідливе випромінювання, а антиоксиданти нейтралізують вільні радикали, запобігаючи появі нових плям.
+💧 Глибоке зволоження та легка текстура: Швидко поглинається, не залишає липкої плівки чи жирного блиску, ідеально підходить як база під макіяж.
+👑 Професійний об'єм 250 мл: Ви отримуєте у 5 разів більше засобу, ніж у стандартних баночках (50 мл), що робить покупку максимально вигідною!
+🌿 Гігієнічність та економія: Вакуумна банка з зручним дозатором захищає крем від контакту з повітрям і бактеріями та забезпечує точне дозування.
+Сила природних компонентів
+Формула крему поєднує фітотерапію та вітамінний комплекс:
+Екстракти солодки, петрушки та кульбаби — потужні природні освітлювачі, які м'яко пригнічують синтез меланіну та заспокоюють шкіру.
+Вітаміни А і Е — стимулюють оновлення клітин, підвищують пружність та захищають від оксидативного стресу.
+Спосіб застосування та результат
+Нанесіть невелику кількість крему на попередньо очищену шкіру обличчя та шиї легкими круговими рухами.
+Використовуйте двічі на день — вранці та ввечері.
+⏱️ Результат: Перші стійкі зміни та помітне освітлення тону ви побачите вже через 4–6 тижнів регулярного використання.</t>
+  </si>
+  <si>
+    <t>AL951</t>
+  </si>
+  <si>
+    <t>Освітлююча маска Anna Logor Lightening Mask (Art.965), 250 мл</t>
+  </si>
+  <si>
+    <t>✨ Прощавай, пігментація: рівний тон шкіри за 15 хвилин на тиждень!
+Сонячні промені, вікові зміни та стрес часто залишають на шкірі небажані сліди. Якщо ви шукаєте засіб, який працює прицільно та швидко, зверніть увагу на нашу Інтенсивну освітлювальну маску.
+Чому вона стане вашим улюбленцем? — Працює локально, безпосередньо на проблемних ділянках. — Сповільнює вироблення меланіну та захищає від вільних радикалів. — Дарує шкірі матовість і рівний колір без ефекту «білої маски». — Підходить абсолютно для будь-якого типу шкіри!
+🌿 У складі — суперкоманда активів: гліколева та октадецендіоєва кислоти, сквалан, вітаміни А й Е, а також цінні CO₂-екстракти солодки, петрушки та кульбаби.
+Як використовувати: Нанесіть щільним шаром на очищене обличчя на 10–15 хвилин, змийте теплим вологим рушником і закрийте кремом Lightening Moisturizer. Повторюйте 1–2 рази на тиждень — і насолоджуйтеся ідеальним тоном!
+📍 Об'єм: 250 мл (вистачить на тривалий курс!).</t>
+  </si>
+  <si>
+    <t>AL965</t>
+  </si>
+  <si>
+    <t>Омолоджуюча сироватка з пептидами Anna Logor Mezotherapy Serum (Art.535), 50 мл</t>
+  </si>
+  <si>
+    <t>✨ Омолоджуюча сироватка з пептидами Anna Logor Mezotherapy Serum
+Для всіх типів шкіри | 50 мл | Код: 535 | Вік: 30+ 🌸
+💆‍♀️ Збережіть молодість та пружність шкіри без радикальних процедур
+Після 30 років шкіра починає потребувати більш точкового та високоактивного догляду. Сироватка Anna Logor Mezotherapy Serum — це ваш щоденний безін'єкційний догляд, розроблений за передовими технологіями індустрії краси. 💧
+Завдяки легкій безолійній текстурі сироватка миттєво вбирається, не залишає липкої плівки та діє в глибоких шарах епідермісу, ефективно борючись із першими ознаками старіння та мімічними зморшками. ✨
+🧬 Інноваційний склад для швидкого результату:
+🌿 Міоксінол™ (Myoxinol™): Натуральний рослинний аналог ботокса. Дбайливо розслабляє мімічні м'язи, розгладжує існуючі заломи та запобігає появі нових.
+🔬 Тетрапептид-11: Активізує виробіток власного колагену, підвищує щільність та пружність шкіри.
+⚡ Альфа-ліпоєва кислота: Потужний антиоксидант, який нейтралізує вільні радикали, покращує колір обличчя та вирівнює тон.
+🪡 Протеїни шовку та сої: Глибоко зволожують, роблять шкіру гладенькою, ніжною та оксамитовою на дотик.
+🍃 Фіто-комплекс (хвощ, хміль, хвоя, розмарин, лимон): Стимулює регенерацію, знімає запалення та тонізує.
+🎯 Що ви отримуєте від використання:
+💎 Помітний ліфтинг-ефект: Підтягнутий овал обличчя та чіткіші контури.
+🪞 Гладкий рельєф: Розгладження мімічних зморшок і тонких ліній.
+💦 Глибоке зволоження: Усунення відчуття стягнутості на увесь день.
+🌟 Свіжість та сяйво: Відновлення здорового, відпочилого кольору обличчя.
+🕊️ Комфорт у догляді: Легка консистенція з приємним ароматом, яка ідеально підходить під макіяж.
+📝 Спосіб застосування:
+Використовуйте сироватку щодня — вранці та ввечері ☀️🌙
+1️⃣ Очистіть шкіру за допомогою молочка Vital Primrose Cleanser та тоніка Vital Primrose Toner.
+2️⃣ Нанесіть невелику кількість сироватки Mezotherapy Serum на обличчя легкими масажними рухами до повного вбирання.
+3️⃣ Для максимального ефекту закрийте сироватку денним кремом Mezotherapy Firming Moisturizer або нічним Mezotherapy Night Cream.
+🛍️ Замовляйте Anna Logor Mezotherapy Serum та подаруйте своїй шкірі молодість, пружність і доглянутий вигляд щодня! ✨</t>
+  </si>
+  <si>
+    <t>AL535</t>
+  </si>
+  <si>
+    <t>Відновлювальний гель Perfect Skin Ultimate Repair Cleanser (Art.11), 200 мл</t>
+  </si>
+  <si>
+    <t>200 мл</t>
+  </si>
+  <si>
+    <t>AL11</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor 11 Ultimate Repair Cleanser – делікатне очищення та відновлення! ✨
+🌿 Чому варто обрати цей гель:
+💧 М’яке та ретельне очищення – легко розчиняє макіяж, себум та забруднення, не травмуючи епідерміс
+🛡️ Захист мікробіому та зволоження – зберігає природний баланс, запобігає сухості та лущенню
+🌸 Заспокійливий комплекс – натуральні екстракти миттєво знімають подразнення та почервоніння
+⚡ Відновлення та пружність – стимулює регенерацію, вирівнює тон та підвищує еластичність
+🌟 Максимальна ефективність догляду – готує шкіру до сироваток і кремів, підсилюючи їхню дію у 2 рази
+💚 Результат – чиста, доглянута та сяюча шкіра без відчуття стягнутості!
+📌 Особливості продукту:
+Ніжна гелева текстура перетворюється на м’яку піну
+SPA-ефект під час щоденного вмивання
+Підходить для всіх типів шкіри, включно з чутливою
+Ідеальний для вікової категорії 35+ та шкіри з ознаками сухості чи в’ялості
+📌 Б’юті-ритуал для ідеальної шкіри:
+Очищення: нанести невелику кількість гелю на вологе обличчя, помасажувати та змити теплою водою
+Тонізація: використати тонік Anna Logor 15 Perfect Skin для відновлення pH-балансу
+Основний догляд: нанести сироватку та крем за типом шкіри
+✔️ Характеристики продукту:
+Тип: Відновлювальний гель для вмивання
+Об’єм: 200 мл
+Призначення: Очищення, відновлення, захист мікробіому
+Тип шкіри: Усі типи (особливо чутлива та комбінована)
+Бренд: Anna Logor
+Країна виробництва: 🇺🇦 Україна
+🌟 Anna Logor 11 Ultimate Repair Cleanser – твій must-have для делікатного очищення та відновлення шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>Сироватка з вітаміном С Anna Logor Vitamin C Serum (Art.653), 120 мл</t>
+  </si>
+  <si>
+    <t>120 мл</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor Vitamin C Serum – сяйво, молодість та захист! ✨
+🌿 Чому варто обрати цю сироватку:
+💧 Вирівнює тон та додає сяйва – освітлює постакне, зменшує пігментацію, повертає свіжий вигляд
+🌸 Бореться з висипаннями – потужна протизапальна дія, пригнічує бактерії, що викликають акне
+🛡️ Зберігає молодість – стимулює синтез колагену, розгладжує дрібні зморшки, підвищує еластичність
+⚡ Захищає від фотостаріння – антиоксидантна дія, нейтралізація вільних радикалів, захист від УФ-променів
+🌟 Прискорює відновлення – допомагає швидкому загоєнню мікропошкоджень
+💚 Результат – свіжа, сяюча та доглянута шкіра без недосконалостей!
+📌 Активний компонент:
+🌱 Аскорбіл фосфат натрію – стабільна форма вітаміну С, ефективніша за аскорбінову кислоту, без подразнень, підходить навіть для чутливої шкіри
+📌 Текстура:
+Легка, невагома консистенція
+Миттєво вбирається без липкості та жирного блиску
+Ідеальна як база під крем чи макіяж
+✔️ Переваги продукту:
+Швидка доставка активних компонентів у глибокі шари епідермісу
+Професійний догляд у домашніх умовах
+Підходить для всіх типів шкіри, включно з чутливою
+Помітний результат вже після перших застосувань
+🌟 Anna Logor Vitamin C Serum – твій must-have для сяючої та молодої шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>AL653</t>
+  </si>
+  <si>
+    <t>Мультивітамінна гелева маска для чутливої шкіри Anna Logor Multivitamin Mask (Art.694), 250 мл</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor Multivitamin Mask – здоров’я та сяйво для чутливої шкіри! ✨
+🌿 Чому варто спробувати цю маску:
+🛡️ Антиоксидантний захист – нейтралізує дію вільних радикалів та запобігає фотостарінню
+💧 Глибоке зволоження та живлення – відновлює баланс вологи та насичує клітини мікроелементами
+🌸 Ліфтинг та пружність – вирівнює мікрорельєф, підвищує тонус та еластичність
+🩹 Експрес-відновлення – швидко заспокоює подразнення та прискорює регенерацію клітин
+💚 Результат – свіжа, доглянута та сяюча шкіра без почервонінь і сухості!
+📌 Активні компоненти:
+🍊 Вітамінний комплекс (A, B, C, E, F) – енергія клітин, стимуляція оновлення, захист від старіння
+🌼 Екстракти василька, липи, звіробою, ромашки та календули – зняття запалень, глибоке заспокоєння та пом’якшення
+📌 Особливості текстури та застосування:
+Легка гелева текстура – ідеальна для релакс-масажу (2–3 хвилини)
+Підсилює проникнення активних компонентів із маски та попередньо нанесених сироваток
+📌 Спосіб застосування:
+Нанести тонкий шар (1–2 мм) на очищену шкіру обличчя та шиї.
+Залишити на 10–15 хвилин (за бажанням – легкий масаж протягом перших 2–3 хвилин).
+Видалити залишки теплою вологою серветкою або рушником.
+✔️ Характеристики продукту:
+Тип: Мультивітамінна гелева маска
+Об’єм: 250 мл · Art.694
+Вікова категорія: 18+
+Тип шкіри: Чутлива
+Бренд: Anna Logor
+Країна виробництва: 🇺🇦 Україна
+🌟 Anna Logor Multivitamin Mask – твій must-have для чутливої шкіри, яка потребує ніжного догляду та сяйва! 🌟</t>
+  </si>
+  <si>
+    <t>AL694</t>
+  </si>
+  <si>
+    <t>Живильна маска з екстрактом примули Anna Logor Vital Primrose Mask (Art.551), 250 мл</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor Vital Primrose Mask – молодість та сяйво для сухої шкіри! ✨
+🌿 Чому варто спробувати цю маску:
+💧 Інтенсивне живлення та ліфтинг – розгладжує дрібні лінії та зменшує глибину зморшок
+🌸 Чіткий контур обличчя – підвищує пружність, відновлює еластичність та підтягує овал
+🛡️ Глибоке та тривале зволоження – регулює pH-баланс, захищає від пересихання
+⚡ Рівний рельєф та свіжий колір – вирівнює текстуру, дарує оксамитовість та сяйво
+💚 Результат – доглянута, підтягнута та сяюча шкіра вже після першого застосування!
+📌 Активні компоненти:
+🧬 Комплекс PatcH2O™ + Гіалуронова кислота – пролонговане глибоке зволоження
+🌱 Протеїни сої та лінолева кислота – регенерація та зміцнення бар’єру
+🌸 Олія насіння луффи та алантоїн – заспокоюють та пом’якшують
+🌟 Вітаміни А, Е, F – антиоксидантний захист від старіння
+🌿 Екстракти лимона, хвоща, хмелю та розмарину – тонізація та мікроциркуляція
+📌 Спосіб застосування:
+Нанесіть тонкий шар маски на очищену шкіру обличчя та шиї.
+Залиште на 10–15 хвилин для дії активних компонентів.
+Змийте теплою водою або видаліть залишки вологим рушником.
+💡 Використовуйте 1 раз на тиждень увечері перед сном.
+✔️ Характеристики продукту:
+Тип: Живильна антиейдж-маска
+Об’єм: 250 мл · Код: 551
+Вікова категорія: 25+
+Тип шкіри: Суха, виснажена, з першими ознаками старіння
+Бренд: Anna Logor
+Країна виробництва: 🇺🇦 Україна
+🌟 Anna Logor Vital Primrose Mask – твій must-have для глибокого живлення та збереження молодості шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>AL551</t>
+  </si>
+  <si>
+    <t>Маска для проблемної шкіри Anna Logor Blemish Control Mask (Art.155), 250 мл</t>
+  </si>
+  <si>
+    <t>AL155</t>
+  </si>
+  <si>
+    <t>🌿 Маска для проблемної шкіри Anna Logor Blemish Control Mask (250 мл)
+📌 Артикул: 155
+🧴 Тип шкіри: проблемна, жирна, схильна до висипань та акне
+👤 Вікова категорія: без обмежень
+📦 Форма випуску: баночка 250 мл
+✨ Чиста, матова та здорова шкіра — з першого застосування!
+Професійна пастоподібна маска Anna Logor Blemish Control Mask на основі глини — це інтенсивний догляд за шкірою, схильною до запалень, підліткових чи дорослих висипань та надмірного жирного блиску. Вона діє комплексно: не просто підсушує наявні елементи, а нормалізує роботу сальних залоз і запобігає появі нових недосконалостей.
+🔥 Чому ця маска стане вашим мастхевом:
+🎯 Регулює вироблення себуму: миттєво прибирає жирний блиск та робить шкіру матовою.
+🧘‍♀️ Швидкий заспокійливий ефект: знімає почервоніння, подразнення та локальні запалення.
+✨ Звужує пори та вирівнює тон: стимулює регенерацію шкіри, допомагає зменшити сліди постакне та пігментацію.
+🛡️ Антибактеріальний захист: пригнічує розвиток бактерій, що провокують акне та вугровий висип.
+🧪 Потужний активний склад:
+🏺 Природна глина — глибоко очищає пори, адсорбує надлишки себуму та токсини.
+💧 Себацинова та гидроксидеканова кислоти + органічна сірка — ефективно знижують гіперсекрецію сальних залоз та запобігають закупорюванню пор.
+🌿 Екстракт кори білої верби — природне джерело саліцинової кислоти, яка має протизапальну та антибактеріальну дію.
+💊 Вітаміни А та B5 (пантенол) — прискорюють загоєння мікротріщин, заспокоюють та підтримують захисний бар’єр шкіри.
+📝 Спосіб застосування:
+🧴 Нанесіть маску рівномірним шаром 1–2 мм на попередньо очищену шкіру обличчя та шиї, уникаючи зони навколо очей.
+⏱️ Залиште на 15 хвилин.
+🧽 Делікатно видаліть залишки теплим вологим рушником або спонжем.
+💡 Порада косметолога: Для досягнення максимального та тривалого ефекту завершуйте процедуру сироваткою або кремом із серії Anna Logor Blemish Control.</t>
+  </si>
+  <si>
+    <t>Очищуючий тонік для проблемної шкіри</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor Prebiotic Toner – чистота та баланс для проблемної шкіри! ✨
+🌿 Чому варто обрати цей тонік:
+💧 Пребіотик-технологія – усуває шкідливі бактерії та запобігає їх повторній появі
+🌸 Відновлення балансу – себацинова та гідрокідеканова кислоти нормалізують pH та регулюють роботу сальних залоз
+🛡️ Антибактеріальна дія – екстракт білої верби (природне джерело саліцилової кислоти) прискорює відлущування та бореться із запаленнями
+⚡ Звуження пор та профілактика акне – зменшує утворення комедонів, вирівнює текстуру шкіри
+🌟 Догляд та захист – зволожує, заспокоює та допомагає усунути застійні пігментні плями
+💚 Результат – чиста, матова та здорова шкіра без недоліків!
+📌 Активні компоненти:
+🌱 Гіалуронова кислота – глибоке зволоження
+🌸 Себацинова та гідрокідеканова кислоти – себорегуляція та очищення
+🛡️ Декандіол – антибактеріальний ефект
+🌿 Вітамін В5 – регенерація та заспокійливий догляд
+🌸 Екстракти кори дуба, квітів троянди, листя гамамелісу, яблука та білої верби – природний антисептик та тонізація
+📌 Спосіб застосування:
+Попередньо очистіть шкіру гелем.
+Нанесіть тонік на ватний диск.
+Протріть шкіру по масажних лініях від центру до країв, уникаючи зони навколо очей.
+✔️ Характеристики продукту:
+Тип: Тонік для обличчя
+Об’єм: 350 мл
+Вікова категорія: 18+
+Тип шкіри: Проблемна
+Класифікація: Професійна
+Бренд: Anna Logor
+Країна: США – Україна
+🌟 Anna Logor Prebiotic Toner – твій must-have для щоденного догляду та контролю акне! 🌟</t>
+  </si>
+  <si>
+    <t>AL102</t>
+  </si>
+  <si>
+    <t>Active Propolis Moisturizer. Активний крем с прополісом для проблемної шкіри</t>
+  </si>
+  <si>
+    <t>AL123</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor Anti-Acne Cream – чиста та здорова шкіра без недоліків! ✨
+🌿 Чому варто обрати цей крем:
+🛡️ Прополіс + кислоти – запобігають запаленням, зменшують секрецію сальних залоз та заспокоюють шкіру
+💧 Контроль пор та комедонів – не дає порам закупорюватися, усуває чорні точки
+🌸 Nordihydroguaiaretic Acid – регулює ріст клітин, запобігає гіперкератозу та новим висипанням
+⚡ Антиоксидантний захист – стабілізує структуру шкіри та уповільнює процеси старіння
+👶 Рекомендований при подразненнях у дітей та локалізованій підлітковій акне
+💚 Результат – рівна, матова та спокійна шкіра без жирного блиску!
+📌 Активні компоненти:
+🌱 Натуральний екстракт прополісу – протизапальна та антибактеріальна дія
+🌸 Олеанолова кислота – себорегуляція
+🛡️ Nordihydroguaiaretic Acid – профілактика гіперкератозу
+🌿 Екстракти кори білої верби, дуба, листя яблука, гамамелісу та квітів троянди – природне очищення та тонізація
+💧 Вітамін В5 – регенерація та зволоження
+📌 Спосіб застосування:
+Очистіть шкіру гелем або пінним засобом.
+Використайте тонік для відновлення pH-балансу.
+Нанесіть невелику кількість крему на обличчя круговими масажними рухами.
+Використовуйте 2 рази на день – вранці та ввечері.
+💡 Для максимального ефекту рекомендується попередньо застосовувати Anti Acne Serum.
+✔️ Характеристики продукту:
+Тип: Крем для проблемної шкіри
+Об’єм: 350 мл
+Вікова категорія: 18+, 25+, 30+
+Призначення: живлення, контроль жирного блиску, звуження пор, антибактеріальний та заспокійливий догляд
+Тип шкіри: жирна, проблемна
+Бренд: Anna Logor
+Країна: США – Україна
+🌟 Anna Logor Anti-Acne Cream – твій must-have у боротьбі з акне та недосконалостями! 🌟</t>
+  </si>
+  <si>
+    <t>AL123(1)</t>
+  </si>
+  <si>
+    <t>AL134</t>
+  </si>
+  <si>
+    <t>Anti Acne Serum. Сироватка для проблемної шкіри</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor Anti Acne Serum – інтенсивна дія проти акне та жирного блиску! ✨
+🌿 Чому варто обрати цю сироватку:
+💧 Висока концентрація саліцилової кислоти – ефективно впливає на бактеріальну мікрофлору та очищує пори
+🌸 Активний комплекс Ac.net™ + екстракт гриба агарика – зменшує запалення та підтримує здоровий баланс шкіри
+🛡️ Олеанолова кислота – контролює вироблення себуму, пригнічує ензим «5-альфа-редуктазу»
+⚡ Миттєвий ефект – відразу після нанесення зменшує розмір пор, дарує гладкість та здоровий вигляд
+🌟 Пролонгована дія – тривале зволоження та профілактика нових висипань
+💚 Результат – чиста, матова та доглянута шкіра без акне!
+📌 Активні компоненти:
+🌱 Саліцилова кислота – глибоке очищення та протизапальна дія
+🌸 Ac.net™ – сучасний комплекс для контролю акне
+🛡️ Екстракт гриба агарика – природний антисептик
+🌿 Олеанолова кислота – себорегуляція та профілактика жирного блиску
+📌 Особливості продукту:
+Легка та приємна текстура
+Інтенсивна та пролонгована дія
+Підходить для проблемної шкіри
+Унісекс-засіб
+✔️ Характеристики:
+Артикул: 387653074
+Тип: Сироватка для проблемної шкіри
+Аудиторія: Унісекс
+Бренд: Anna Logor
+Країна бренду: 🇺🇦 Україна
+Об’єм: стандартний флакон
+Призначення: контроль себуму, звуження пор, антибактеріальна дія, зволоження
+🌟 Anna Logor Anti Acne Serum – твій must-have у боротьбі з акне та недосконалостями! 🌟</t>
+  </si>
+  <si>
+    <t>Blemish Control Mask. Маска для проблемної шкіри (пастообразна)</t>
+  </si>
+  <si>
+    <t>AL155(1)</t>
+  </si>
+  <si>
+    <t>AL180</t>
+  </si>
+  <si>
+    <t>Blemish Cure. Лікувальний концетрат для проблемної шкіри</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor Blemish Cure – швидка допомога при акне! ✨
+🌿 Чому варто обрати цей концентрат:
+💧 Антибактеріальна дія – унікальна формула швидко знищує бактерії, що спричиняють акне
+🌸 Підсушує та лікує – ефективно зменшує прищі та запобігає їх повторній появі
+🛡️ Знімає запалення – усуває почервоніння, свербіж та дискомфорт
+⚡ Глибока дія – проникає в пори, ліквідуючи комедони та висипання
+💚 Результат – чиста, спокійна та здорова шкіра вже після перших застосувань!
+📌 Особливості продукту:
+Швидкодіючий антибактеріальний комплекс
+Професійна формула для проблемної шкіри
+Локальна дія на висипання
+Підходить для щоденного використання
+✔️ Характеристики:
+Тип: Лікувальний концентрат для проблемної шкіри
+Об’єм: стандартний флакон
+Тип шкіри: Проблемна
+Виробник: Anna Logor
+Країна виробництва: 🇺🇸 США
+🌟 Anna Logor Blemish Cure – твій SOS-засіб у боротьбі з акне та запаленнями! 🌟</t>
+  </si>
+  <si>
+    <t>AL223</t>
+  </si>
+  <si>
+    <t>AL234</t>
+  </si>
+  <si>
+    <t>Oil Control Fluid. Эмульсія стабілізуюча для жирної шкіри</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor Oil Control Fluid – контроль себуму та матовість шкіри! ✨
+🌿 Чому варто обрати цю емульсію:
+💧 Зволожує та зберігає природний баланс вологи
+🌸 Стягує пори та зменшує активність сальних залоз
+🛡️ Захищає від негативного впливу вільних радикалів
+⚡ Усуває запалення та почервоніння
+🌟 Дарує матовість і здоровий колір обличчя
+💚 Результат – чиста, доглянута та свіжа шкіра без жирного блиску!
+📌 Активні компоненти:
+🌱 Екстракти плюща, шавлії, лимона, кресса водяного, лопуха та гриба агарика – природне очищення та тонізація
+💧 Натуральна формула – безпечна та ефективна для щоденного використання
+📌 Спосіб застосування:
+Очистіть шкіру гелем та тоніком серії Oil Control.
+Нанесіть емульсію на обличчя вранці та ввечері перед сном.
+Використовуйте регулярно для стабільного результату.
+✔️ Характеристики продукту:
+Тип: Стабілізуюча емульсія для жирної шкіри
+Об’єм: 100 мл · Art.223
+Вікова категорія: без обмежень
+Форма випуску: вакуумний флакон із дозатором
+Бренд: Anna Logor
+Країна виробництва: 🇺🇦 Україна
+🌟 Anna Logor Oil Control Fluid – твій must-have для щоденного догляду за жирною шкірою! 🌟</t>
+  </si>
+  <si>
+    <t>Oil Control Serum. Сироватка стабілізуюча для жирної шкіри</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor Oil Control Serum – чиста та матова шкіра без компромісів! ✨
+🌿 Чому варто обрати цю сироватку:
+💧 Контроль себуму – регулює вироблення шкірного жиру, усуває блиск у Т-зоні
+🌸 Звуження пор – робить їх менш помітними, не «запечатує» шкіру, дозволяючи їй вільно дихати
+🛡️ Bix'Activ® – клінічно доведений актив, що зменшує запалення та нормалізує роботу сальних залоз
+⚡ Антибактеріальна дія – знижує кількість висипів та дефектів шкіри
+🌟 Матує та зволожує – дарує гладкість і здоровий вигляд
+💚 Результат після курсу – себум скорочується до 75%, пори стають менш помітними, а шкіра набуває рівного кольору та свіжості!
+📌 Активні компоненти:
+🧬 Bix'Activ® (екстракт насіння Bixa Orellana) – зменшує утворення себоцитів та запальних процесів
+🌱 Екстракт гриба Fomes Officinalis – в’яжуча та порозвужуюча дія
+🌿 Крес-салат – антибактеріальний ефект
+🌸 Корінь лопуха – регуляція себуму та боротьба із запаленнями
+🌼 Листя шавлії – антисептичний та матуючий ефект
+🍋 Лимон – освітлення та освіження шкіри
+🌱 Мильнянка лікарська – м’яке очищення
+🌿 Плющ звичайний – покращує мікроциркуляцію та звужує пори
+📌 Спосіб застосування:
+Нанесіть сироватку на очищену та тонізовану шкіру обличчя.
+Використовуйте вранці та ввечері, легкими круговими рухами до повного вбирання.
+Для максимального ефекту застосовуйте разом із Oil Control Fluid Anna Logor.
+✔️ Характеристики продукту:
+Тип: Сироватка для жирної та проблемної шкіри
+Об’єм: 50 мл
+Клас косметики: Професійна
+Сфера застосування: Обличчя
+Бренд: Anna Logor
+Країна-виробник: 🇺🇦 Україна
+🌟 Anna Logor Oil Control Serum – твій must-have для щоденного контролю жирності та здорової шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>Silver Plus Moisturizer. Зволожуючий крем з колоїдним сріблом для комбінованої шкіри</t>
+  </si>
+  <si>
+    <t>AL323</t>
+  </si>
+  <si>
+    <t>AL323(1)</t>
+  </si>
+  <si>
     <t>✨ Anna Logor Purifying Complex Toner – баланс та догляд для комбінованої шкіри! ✨
-🌿 Чому варто обрати цей тонік:
+🌿 Основні переваги тоніка:
 💧 Підтримує природний рівень зволоженості та нормалізує pH-баланс
 🌸 Активізує процеси оновлення клітин епідермісу
 🛡️ Стимулює синтез колагену та еластину
@@ -5982,7 +6951,468 @@
 🌟 Anna Logor Purifying Complex Toner – твій must-have для догляду за комбінованою шкірою! 🌟</t>
   </si>
   <si>
-    <t>AL302</t>
+    <t>✨ Anna Logor Silver Plus Moisturizer – ніжний догляд із силою колоїдного срібла! ✨
+🌿 Основні переваги крему:
+💧 Баланс зволоження – підтримує водно-жировий баланс, скорочує пори
+🛡️ Антисептична дія – колоїдне срібло захищає від бактерій та запалень
+🌸 Відновлення та захист – комплекс АНА-кислот та рослинні екстракти стимулюють оновлення клітин
+⚡ Протеїни сої та алантоїн – зміцнюють шкіру, знімають подразнення та запобігають віковим змінам
+🌟 Антиоксидантний ефект – вітамін Е та сквалан захищають від негативного впливу довкілля та гормонального старіння
+💚 Результат – здорова, сяюча та доглянута комбінована шкіра без акне та почервонінь!
+📌 Активні компоненти:
+Колоїдне срібло – антисептичний та протизапальний ефект
+АНА-комплекс кислот – м’яке оновлення клітин
+Екстракти: гриба агарика, лопуха, плюща, кресса водяного, лимону, шавлії
+Гідролізовані протеїни сої – зміцнення та захист
+Алантоїн, сквалан, вітамін Е – живлення та антиоксидантна дія
+📌 Спосіб застосування:
+Очистіть шкіру гелем або пінним засобом та тоніком.
+Нанесіть невелику кількість крему на обличчя.
+Розподіліть масажними рухами.
+Використовуйте 2 рази на день – вранці та ввечері.
+✔️ Характеристики продукту:
+Тип: Зволожуючий крем із колоїдним сріблом
+Об’єм: 50 мл
+Вікова категорія: 16+
+Тип шкіри: комбінована
+Призначення: зволоження, антисептичний захист, відновлення
+Клас косметики: професійна
+Бренд: Anna Logor
+Країна-виробник: 🇺🇦 Україна
+🌟 Anna Logor Silver Plus Moisturizer – твій must-have для щоденного догляду за комбінованою шкірою! 🌟</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor Silver Plus Moisturizer – ніжний догляд із силою колоїдного срібла! ✨
+🌿 Основні переваги крему:
+💧 Баланс зволоження – підтримує водно-жировий баланс, скорочує пори
+🛡️ Антисептична дія – колоїдне срібло захищає від бактерій та запалень
+🌸 Відновлення та захист – комплекс АНА-кислот та рослинні екстракти стимулюють оновлення клітин
+⚡ Протеїни сої та алантоїн – зміцнюють шкіру, знімають подразнення та запобігають віковим змінам
+🌟 Антиоксидантний ефект – вітамін Е та сквалан захищають від негативного впливу довкілля та гормонального старіння
+💚 Результат – здорова, сяюча та доглянута комбінована шкіра без акне та почервонінь!
+📌 Активні компоненти:
+Колоїдне срібло – антисептичний та протизапальний ефект
+АНА-комплекс кислот – м’яке оновлення клітин
+Екстракти: гриба агарика, лопуха, плюща, кресса водяного, лимону, шавлії
+Гідролізовані протеїни сої – зміцнення та захист
+Алантоїн, сквалан, вітамін Е – живлення та антиоксидантна дія
+📌 Спосіб застосування:
+Очистіть шкіру гелем або пінним засобом та тоніком.
+Нанесіть невелику кількість крему на обличчя.
+Розподіліть масажними рухами.
+Використовуйте 2 рази на день – вранці та ввечері.
+✔️ Характеристики продукту:
+Тип: Зволожуючий крем із колоїдним сріблом
+Об’єм: 250 мл
+Вікова категорія: 16+
+Тип шкіри: комбінована
+Призначення: зволоження, антисептичний захист, відновлення
+Клас косметики: професійна
+Бренд: Anna Logor
+Країна-виробник: 🇺🇦 Україна
+🌟 Anna Logor Silver Plus Moisturizer – твій must-have для щоденного догляду за комбінованою шкірою! 🌟</t>
+  </si>
+  <si>
+    <t>AL355</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor Purifying Complex Mask – детокс та баланс для комбінованої шкіри! ✨
+🌿 Основні переваги маски:
+💧 Глибоке очищення – жовта глина абсорбує надлишки себуму та токсини
+🌸 Регуляція жирності – контролює секрецію сальних залоз у проблемних ділянках, не порушуючи баланс інших зон
+🛡️ Антиоксидантний захист – нейтралізує дію вільних радикалів та запобігає пошкодженню клітин
+⚡ Протизапальна дія – зменшує активність бактерій, що викликають акне, та стимулює імунний захист
+🌟 Видимий результат – пори стають менш помітними, шкіра набуває свіжого та здорового вигляду
+💚 Результат – чиста, матова та доглянута шкіра без подразнень!
+📌 Активні компоненти:
+Жовта глина – природний сорбент із детокс-дією
+Рослинні екстракти – заспокоюють та відновлюють шкіру
+Комплекс проти акне – зменшує запалення та комедони
+📌 Спосіб застосування:
+Нанесіть маску тонким шаром на очищену шкіру.
+Залиште на 10–15 хвилин для дії активних компонентів.
+Змийте теплою водою або видаліть залишки вологою серветкою.
+💡 Використовуйте 1–2 рази на тиждень для підтримки здорового вигляду шкіри.
+✔️ Характеристики продукту:
+Тип: Очищуюча маска з жовтою глиною
+Об’єм: 250 мл · Art.AL355
+Вікова категорія: 16+
+Тип шкіри: комбінована, проблемна
+Бренд: Anna Logor
+Країна виробництва: 🇺🇸 США – 🇺🇦 Україна
+🌟 Anna Logor Purifying Complex Mask – твій must-have для глибокого очищення та детоксу шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>AL355(1)</t>
+  </si>
+  <si>
+    <t>Purifying Complex Mask. Комплексна очищуюча маска для комбінованої шкіри</t>
+  </si>
+  <si>
+    <t>AL402</t>
+  </si>
+  <si>
+    <t>Silky Herbal Toner. Тонік з трав'яними екстрактами</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor Silky Herbal Toner – завершальний штрих для сяючої шкіри! ✨
+🌿 Основні переваги тоніка:
+💧 Відновлює pH-баланс після очищення
+🌸 Забезпечує легкий тонізуючий та зволожуючий ефект
+🛡️ Готує шкіру до нанесення кремів та сироваток, підсилюючи їх дію
+⚡ Має антиоксидантний та регенеруючий вплив завдяки вітамінам та рослинним екстрактам
+🌟 Легка текстура та приємний аромат – ідеальний засіб перед макіяжем
+💚 Результат – свіжа, доглянута та пружна шкіра, готова до щоденного догляду чи салонних процедур!
+📌 Активні компоненти:
+🌱 Гіалуронова кислота – пружність та зволоження
+🛡️ Натрію L-піроглютамат – підтримка клітинного балансу
+🌸 Вітаміни С та В5 – антиоксидантний захист та регенерація
+🌿 Екстракти розмарину, хмелю, лимона, польового хвоща та хвої – тонізація та відновлення
+📌 Спосіб застосування:
+Очистіть шкіру молочком Silky Herbal Cleanser.
+Нанесіть тонік на ватний диск.
+Протріть обличчя від центру до країв, уникаючи зони навколо очей.
+Завершіть догляд гель-сироваткою Ultra Silk або кремами Copper Plus Moisturizer / Silky Protein.
+✔️ Характеристики продукту:
+Тип: Тонік із трав’яними екстрактами
+Об’єм: 350 мл
+Вікова категорія: 16+
+Тип шкіри: нормальна, комбінована
+Призначення: тонізація, зволоження, антиоксидантний захист
+Бренд: Anna Logor
+Країна-виробник: 🇺🇦 Україна
+🌟 Anna Logor Silky Herbal Toner – твій must-have для завершення щоденного очищення та підготовки шкіри до догляду! 🌟</t>
+  </si>
+  <si>
+    <t>AL423</t>
+  </si>
+  <si>
+    <t>AL423(1)</t>
+  </si>
+  <si>
+    <t>Copper Plus Moisturizer. Антиоксидантний, зволожуючий крем</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor Copper Plus Moisturizer – відновлення, сяйво та захист твоєї шкіри! ✨
+🌿 Основні переваги крему:
+💧 PatchH2O™ комплекс – пролонговане зволоження до 48 годин
+🌸 Гідролізовані протеїни сої та шовку – розгладжують зморшки та захищають від гормонального старіння
+⚡ DMAE – зміцнює структурний баланс шкіри та покращує контур обличчя
+🛡️ Антиоксидант нового покоління + УФ-захист SPF 15 – захист від фотостаріння та негативного впливу довкілля
+🌟 Фосфоліпіди та сквалан – живлення, м’якість та еластичність
+💚 Результат – пружна, сяюча та доглянута шкіра без сухості та тьмяності!
+📌 Активні компоненти:
+Гідролізовані протеїни сої та шовку
+Сквалан
+DMAE
+PatchH2O™
+Піроглютамат міді
+Фосфоліпіди
+Вітаміни А, Е, С
+Екстракти хвоща, хвої, розмарину, хмелю та лимона
+📌 Спосіб застосування:
+Очистіть шкіру молочком або пінним засобом та тоніком.
+Нанесіть невелику кількість крему на обличчя круговими масажними рухами.
+Використовуйте 1 раз на день – вранці.
+Увечері застосовуйте крем Silky Protein.
+💡 Для максимального ефекту попередньо використовуйте сироватки Vital Firming, Ultra Silk або Vitamin C.
+✔️ Характеристики продукту:
+Тип: Антиоксидантний зволожуючий крем
+Об’єм: стандартний флакон
+Вікова категорія: для всіх
+Тип шкіри: нормальна, суха, збезводнена
+Призначення: відновлення, живлення, зволоження, проти зморшок
+Бренд: Anna Logor
+Країна-виробник: 🇺🇦 Україна
+🌟 Anna Logor Copper Plus Moisturizer – твій must-have для сяючої та здорової шкіри щодня! 🌟</t>
+  </si>
+  <si>
+    <t>AL424</t>
+  </si>
+  <si>
+    <t>AL424(1)</t>
+  </si>
+  <si>
+    <t>Silky Protein Cream. Живильний крем з протеінами шовку</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor Silky Protein Cream – енергія шовку для молодості та пружності шкіри! ✨
+🌿 Основні переваги крему:
+💧 Насичує шкіру вологою та відновлює її еластичність
+🌸 Запобігає ранній появі зморшок, сприяє загоєнню та регенерації тканин
+🛡️ Стимулює синтез еластину та колагену, забезпечуючи гнучкість і рівновагу шкіри
+⚡ Моделює контур обличчя, нейтралізуючи «гравітаційний птоз»
+🌟 Дарує шкірі пружність, гладкість і сяйво
+💚 Результат – доглянута, підтягнута та сяюча шкіра вже після курсу застосування!
+📌 Активні компоненти:
+🧬 Дипептид-1 – стимулює утворення колагену та підвищує пружність
+🌸 Протеїни шовку та сої – утворюють тонку захисну плівку, що утримує вологу, живлять і загоюють
+💧 PatchH2O™ комплекс – пролонговане зволоження до 48 годин
+🌿 Молочна кислота, олія ши та жожоба – живлення, пом’якшення та відновлення
+⚡ DMAE – зміцнює структурний баланс та покращує контур обличчя
+🌟 Вітаміни А, С, Е, В5 – антиоксидантний захист та регенерація
+🌱 Екстракти хмелю, лимона, хвої, розмарину та хвоща – тонізація та відновлення
+📌 Спосіб застосування:
+Очистіть шкіру молочком або пінним засобом та тоніком.
+Нанесіть невелику кількість крему на обличчя.
+Розподіліть круговими масажними рухами до повного вбирання.
+Використовуйте щодня для максимального ефекту.
+✔️ Характеристики продукту:
+Тип: Поживний крем із протеїнами шовку
+Об’єм: стандартний флакон
+Вікова категорія: 18+
+Тип шкіри: нормальна, суха, комбінована
+Призначення: зволоження, живлення, відновлення, проти зморшок
+Бренд: Anna Logor
+Країна-виробник: 🇺🇦 Україна
+🌟 Anna Logor Silky Protein Cream – твій must-have для пружної та сяючої шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>AL435</t>
+  </si>
+  <si>
+    <t>Rosacea Control serum. Відновлююча сироватка</t>
+  </si>
+  <si>
+    <t>✨ Anna LOGOR Rosacea Control Serum – контроль почервоніння та догляд при розацеа! ✨
+🌿 Основні переваги сироватки:
+💧 Зменшує прояви почервоніння та подразнення
+🌸 Регулює фактори запалення шкіри
+🛡️ Контролює утворення нових кровоносних судин у процесі відновлення тканин
+⚡ Вирівнює тон шкіри та покращує її стан вже за 28 днів
+🌟 Допомагає при розацеа, даруючи комфорт та здоровий вигляд
+💚 Результат – спокійна, рівна та доглянута шкіра без надмірного почервоніння!
+📌 Активні компоненти:
+Унікальний фармацевтичний інгредієнт для контролю запалення та судинних змін
+Комплекс рослинних екстрактів для заспокійливого та відновлюючого ефекту
+Додаткові активи для вирівнювання тону та зміцнення бар’єрних функцій
+📌 Спосіб застосування:
+Очистіть шкіру за допомогою гелю або молочка.
+Нанесіть сироватку на обличчя.
+Через 5–10 хвилин використайте крем за типом шкіри.
+💡 Для максимального ефекту застосовуйте щодня.
+✔️ Характеристики продукту:
+Тип: Відновлююча сироватка для проблемної шкіри
+Об’єм: 50 мл · вакуумний флакон із дозатором
+Вікова категорія: 18+
+Призначення: контроль розацеа, зменшення почервоніння, відновлення тканин
+Бренд: Anna LOGOR
+Країна-виробник: 🇺🇸 США – 🇺🇦 Україна
+🌟 Anna LOGOR Rosacea Control Serum – твій must-have у боротьбі з розацеа та почервонінням! 🌟</t>
+  </si>
+  <si>
+    <t>AL455</t>
+  </si>
+  <si>
+    <t>AL455(1)</t>
+  </si>
+  <si>
+    <t>Silky Cranberry Mask. Шовкова зволожуюча маска з екстрактом журавлини (пастообразна)</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor Silky Cranberry Mask – інтенсивне зволоження та сяйво твоєї шкіри! ✨
+🌿 Основні переваги маски:
+💧 PatchH2O™ комплекс (гіалуронова кислота, альгінат, глюкан) – миттєве насичення вологою та її утримання до 48 годин
+🌸 Антиоксиданти високої інтенсивності – захист від вільних радикалів та фотостаріння
+🛡️ Протеїни шовку та сої – роблять шкіру м’якою, гладкою, допомагають розгладити дрібні зморшки
+⚡ Рослинні екстракти (хміль, лимон, хвощ, хвоя) – підвищують еластичність та відновлюють структуру шкіри
+🌟 Вітаміни А, С, Е, В5 + молочна кислота, олія ши та сквалан – живлення, регенерація та захист
+💚 Результат – доглянута, сяюча та зволожена шкіра без сухості та тьмяності!
+📌 Спосіб застосування:
+Очистіть шкіру обличчя.
+Нанесіть маску тонким шаром (до 2 мм).
+Залиште на 15 хвилин.
+Видаліть залишки теплою вологою серветкою або рушником.
+💡 Використовуйте 2 рази на тиждень. Для максимального ефекту застосовуйте разом із гель-сироваткою Ultra Silk, кремом Copper Plus Moisturizer або Silky Protein.
+✔️ Характеристики продукту:
+Тип: Зволожуюча маска з екстрактом журавлини
+Об’єм: 250 мл
+Вікова категорія: 18+
+Тип шкіри: суха, зневоднена, комбінована
+Призначення: зволоження, живлення, антиоксидантний захист
+Бренд: Anna Logor
+Країна-виробник: 🇺🇸 США – 🇺🇦 Україна
+🌟 Anna Logor Silky Cranberry Mask – твій must-have для інтенсивного зволоження та сяйва шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>AL521(1)</t>
+  </si>
+  <si>
+    <t>Омолоджуючий зміцнюючий-зволожуючий денний крем Anna Logor Mezotherapy Firming Moisturizer (Art.521), 50 мл</t>
+  </si>
+  <si>
+    <t>AL522</t>
+  </si>
+  <si>
+    <t>AL522(1)</t>
+  </si>
+  <si>
+    <t>Mezotherapy Night Crem. Омолоджуючий нічний крем</t>
+  </si>
+  <si>
+    <t>✨ Mezotherapy Night Cream – інноваційний нічний догляд для молодої та пружної шкіри! ✨
+🌿 Основні переваги крему:
+💧 Matrixyl™ – активізує синтез колагену, гіалуронової кислоти, ламініну та фібронектину, відновлює фотопошкоджену шкіру та зменшує глибину зморшок
+🌸 Idealift™ – стимулює синтез еластину, зменшує провисання шкіри, вирівнює рельєф та розгладжує дрібні зморшки
+🛡️ Альфа-ліпоєва кислота – потужний антиоксидант, що бореться з вільними радикалами, підвищує тонус та еластичність
+⚡ Молочна кислота – м’яко відлущує, вирівнює тон та покращує проникнення активних інгредієнтів
+🌟 Олія ши та жожоба – живлять, відновлюють та пом’якшують шкіру
+💚 Результат – відновлена, гладка та сяюча шкіра щоранку!
+📌 Активні компоненти:
+Matrixyl™ – стимуляція колагену та відновлення
+Idealift™ – підтяжка та еластичність
+Альфа-ліпоєва кислота – антиоксидантний захист
+Молочна кислота – м’яке оновлення клітин
+Олія ши та жожоба – живлення та регенерація
+📌 Спосіб застосування:
+Очистіть шкіру перед сном.
+Нанесіть невелику кількість крему на обличчя, шию та декольте.
+Розподіліть легкими масажними рухами до повного вбирання.
+Використовуйте щодня для максимального ефекту.
+✔️ Характеристики продукту:
+Тип: Омолоджувальний нічний крем
+Об’єм: стандартний флакон
+Вікова категорія: 25+
+Тип шкіри: нормальна, суха, комбінована
+Призначення: омолодження, відновлення, підтяжка, антиоксидантний захист
+Бренд: Mezotherapy
+Країна-виробник: 🇺🇦 Україна
+🌟 Mezotherapy Night Cream – твій must-have для нічного омолодження та сяйва шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>AL536</t>
+  </si>
+  <si>
+    <t>AL536(1)</t>
+  </si>
+  <si>
+    <t>Anti-aging Serum with Retinol. Сироватка з Ретинолом</t>
+  </si>
+  <si>
+    <t>✨ Retinol Face Serum – твій захист від фотостаріння та акне! ✨
+🌿 Основні переваги сироватки:
+💧 Vitaliss® (7% ретинолу) – захищає від ультрафіолету та фотостаріння
+🌸 Вирівнює рельєф шкіри, покращує її тонус та еластичність
+🛡️ Освітлює пігментацію та запобігає появі нових плям
+⚡ Має антиоксидантний ефект – протидіє вільним радикалам та уповільнює старіння
+🌟 Бореться з акне та постакне, діє як м’який хімічний пілінг
+💚 Результат – гладка, підтягнута та сяюча шкіра без зморшок, пігментації та висипів!
+📌 Активні властивості ретинолу:
+Проникає через ліпідний бар’єр у глибокі шари епідермісу
+Активізує поділ клітин та оновлення тканин
+Освітлює шрами від акне та постакне
+Інгібує активність сальних залоз, запобігаючи закупорці пор
+📌 Спосіб застосування:
+Очистіть та тонізуйте шкіру.
+Нанесіть кілька крапель сироватки на обличчя, розподіліть масажними рухами.
+Дочекайтеся повного вбирання.
+Ввечері нанесіть нічний крем, а вдень – денний крем із високим SPF.
+✔️ Характеристики продукту:
+Тип: Сироватка з ретинолом
+Об’єм: стандартний флакон
+Вікова категорія: для зрілої та вікової шкіри
+Тип шкіри: всі типи
+Призначення: захист від фотостаріння, освітлення пігментації, антиоксидантний ефект, боротьба з акне та постакне
+Бренд: Anna Logor
+Країна-виробник: 🇺🇦 Україна
+🌟 Retinol Face Serum – твій must-have для молодої, сяючої та здорової шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>AL537</t>
+  </si>
+  <si>
+    <t>Age Reversing Complex. Комплексна відновлююча сироватка</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor Age Reversing Complex – твій секрет молодої та сяючої шкіри! ✨
+🌿 Основні переваги сироватки:
+💧 Agefinity™ – рослинний актив, що відновлює енергопостачання клітин та активізує процеси гліколізу
+🌸 М6Р-комплекс – зміцнює та підтягує шкіру, розгладжує зморшки, зменшує пігментні плями
+🛡️ Neodermyl™ – стимулює синтез колагену й еластину, покращує текстуру та еластичність шкіри
+⚡ Видимий ефект – зменшення кількості та глибини зморшок вже після курсу застосування
+🌟 Легка текстура та зручний дозатор – економне використання та комфорт у щоденному догляді
+💚 Результат – підтягнута, гладка та сяюча шкіра без ознак передчасного старіння!
+📌 Спосіб застосування:
+Очистіть шкіру обличчя.
+Нанесіть сироватку круговими масажними рухами.
+Використовуйте двічі на день – вранці та ввечері.
+💡 Для максимального ефекту комбінуйте з іншими засобами серії Anna Logor.
+✔️ Характеристики продукту:
+Тип: Відновлююча антивікова сироватка
+Об’єм: 50 мл · Art.537
+Вікова категорія: 25+
+Призначення: зменшення зморшок, відновлення, підтяжка, боротьба з пігментацією
+Бренд: Anna Logor
+Країна-виробник: 🇺🇦 Україна
+Форма випуску: вакуумний флакон із дозатором
+🌟 Anna Logor Age Reversing Complex – твій must-have у боротьбі з першими зморшками! 🌟</t>
+  </si>
+  <si>
+    <t>AL551(1)</t>
+  </si>
+  <si>
+    <t>Живильна маска з екстрактом примули Anna Logor Vital Primrose Mask (Art.551), 50 мл</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor Vital Primrose Mask – молодість та сяйво для сухої шкіри! ✨
+🌿 Чому варто спробувати цю маску:
+💧 Інтенсивне живлення та ліфтинг – розгладжує дрібні лінії та зменшує глибину зморшок
+🌸 Чіткий контур обличчя – підвищує пружність, відновлює еластичність та підтягує овал
+🛡️ Глибоке та тривале зволоження – регулює pH-баланс, захищає від пересихання
+⚡ Рівний рельєф та свіжий колір – вирівнює текстуру, дарує оксамитовість та сяйво
+💚 Результат – доглянута, підтягнута та сяюча шкіра вже після першого застосування!
+📌 Активні компоненти:
+🧬 Комплекс PatcH2O™ + Гіалуронова кислота – пролонговане глибоке зволоження
+🌱 Протеїни сої та лінолева кислота – регенерація та зміцнення бар’єру
+🌸 Олія насіння луффи та алантоїн – заспокоюють та пом’якшують
+🌟 Вітаміни А, Е, F – антиоксидантний захист від старіння
+🌿 Екстракти лимона, хвоща, хмелю та розмарину – тонізація та мікроциркуляція
+📌 Спосіб застосування:
+Нанесіть тонкий шар маски на очищену шкіру обличчя та шиї.
+Залиште на 10–15 хвилин для дії активних компонентів.
+Змийте теплою водою або видаліть залишки вологим рушником.
+💡 Використовуйте 1 раз на тиждень увечері перед сном.
+✔️ Характеристики продукту:
+Тип: Живильна антиейдж-маска
+Об’єм: 50 мл · Код: 551
+Вікова категорія: 25+
+Тип шкіри: Суха, виснажена, з першими ознаками старіння
+Бренд: Anna Logor
+Країна виробництва: 🇺🇦 Україна
+🌟 Anna Logor Vital Primrose Mask – твій must-have для глибокого живлення та збереження молодості шкіри! 🌟</t>
+  </si>
+  <si>
+    <t>AL550</t>
+  </si>
+  <si>
+    <t>AL550(1)</t>
+  </si>
+  <si>
+    <t>Collagen Firming Mask. Денна маска з колагеном</t>
+  </si>
+  <si>
+    <t>✨ Anna Logor Vital Collagen Firming Mask – денний догляд для пружності та сяйва шкіри! ✨
+🌿 Основні переваги маски:
+💧 Колаген + протеїни – відновлюють та зміцнюють шкіру, розгладжують дрібні зморшки
+🌸 Гіалуронова кислота та PatchH2O™ – інтенсивне зволоження та утримання вологи
+🛡️ Антиоксиданти та вітамін Е – захист від вільних радикалів та фотостаріння
+⚡ Масло ши – живлення та пом’якшення
+🌟 Рослинні екстракти (хвоя, розмарин, хміль, лимон, хвощ) – тонізація, вирівнювання тону та боротьба з пігментацією
+💚 Результат – підтягнута, сяюча та доглянута шкіра без ознак втоми!
+📌 Спосіб застосування:
+Очистіть шкіру обличчя та шиї.
+Нанесіть маску тонким шаром, уникаючи зони навколо очей.
+Залиште на 10–15 хвилин.
+Змийте теплою водою або видаліть залишки вологим рушником.
+💡 Для максимального ефекту використовуйте разом із сироваткою Mezotherapy Serum та кремом Mezotherapy Firming Moisturizer.
+✔️ Характеристики продукту:
+Тип: Денна маска з колагеном
+Об’єм: 250 мл
+Вікова категорія: 25+
+Призначення: зволоження, підтяжка, відновлення, боротьба з пігментацією
+Бренд: Anna Logor
+Країна-виробник: 🇺🇦 Україна
+🌟 Anna Logor Vital Collagen Firming Mask – твій must-have для щоденного омолодження та сяйва шкіри! 🌟</t>
   </si>
 </sst>
 </file>
@@ -6720,20 +8150,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K166"/>
+  <dimension ref="A1:K255"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" style="9" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="9" customWidth="1"/>
     <col min="2" max="2" width="37.44140625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="16" style="10" customWidth="1"/>
+    <col min="3" max="3" width="14.21875" style="10" customWidth="1"/>
     <col min="4" max="4" width="14.88671875" style="10" customWidth="1"/>
     <col min="5" max="5" width="12.77734375" style="10" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" style="10" customWidth="1"/>
-    <col min="7" max="7" width="12" style="10" customWidth="1"/>
-    <col min="8" max="8" width="18.88671875" style="10" customWidth="1"/>
-    <col min="9" max="9" width="21.109375" style="10" customWidth="1"/>
-    <col min="10" max="10" width="56" style="10" customWidth="1"/>
-    <col min="11" max="11" width="18" style="9" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" style="10" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" style="10" customWidth="1"/>
+    <col min="8" max="8" width="19.109375" style="10" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" style="10" customWidth="1"/>
+    <col min="10" max="10" width="84.33203125" style="10" customWidth="1"/>
+    <col min="11" max="11" width="13.21875" style="9" customWidth="1"/>
     <col min="12" max="16384" width="8.88671875" style="10"/>
   </cols>
   <sheetData>
@@ -6774,13 +8204,13 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" s="2">
         <v>3500</v>
@@ -6793,27 +8223,27 @@
         <v>10</v>
       </c>
       <c r="H2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="K2" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>18</v>
-      </c>
       <c r="C3" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" s="2">
         <v>1400</v>
@@ -6829,24 +8259,24 @@
         <v>12</v>
       </c>
       <c r="I3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>20</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>22</v>
       </c>
       <c r="D4" s="2">
         <v>1350</v>
@@ -6862,24 +8292,24 @@
         <v>12</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" s="7" t="s">
         <v>25</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>26</v>
-      </c>
       <c r="C5" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" s="2">
         <v>1300</v>
@@ -6892,27 +8322,27 @@
         <v>31</v>
       </c>
       <c r="H5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" s="2">
         <v>1200</v>
@@ -6928,24 +8358,24 @@
         <v>12</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" s="2">
         <v>1000</v>
@@ -6956,27 +8386,27 @@
         <v>22</v>
       </c>
       <c r="H7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" s="2">
         <v>1000</v>
@@ -6987,27 +8417,27 @@
         <v>28</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K8" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" s="2">
         <v>1000</v>
@@ -7018,27 +8448,27 @@
         <v>26</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K9" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="C10" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" s="2">
         <v>1100</v>
@@ -7052,24 +8482,24 @@
         <v>12</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K10" s="8" t="s">
         <v>45</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="C11" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D11" s="2">
         <v>800</v>
@@ -7080,27 +8510,27 @@
         <v>22</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" s="8" t="s">
         <v>48</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12" s="2">
         <v>1100</v>
@@ -7111,27 +8541,27 @@
         <v>8</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="C13" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13" s="2">
         <v>1100</v>
@@ -7145,24 +8575,24 @@
         <v>12</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K13" s="8" t="s">
         <v>54</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D14" s="2">
         <v>1200</v>
@@ -7173,27 +8603,27 @@
         <v>22</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15" s="2">
         <v>700</v>
@@ -7204,27 +8634,27 @@
         <v>15</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K15" s="8" t="s">
         <v>61</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="C16" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D16" s="2">
         <v>1400</v>
@@ -7238,24 +8668,24 @@
         <v>12</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K16" s="8" t="s">
         <v>64</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="C17" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D17" s="2">
         <v>1400</v>
@@ -7269,24 +8699,24 @@
         <v>12</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="K17" s="8" t="s">
         <v>67</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="C18" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D18" s="2">
         <v>1100</v>
@@ -7300,24 +8730,24 @@
         <v>12</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K18" s="8" t="s">
         <v>70</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="C19" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D19" s="2">
         <v>1700</v>
@@ -7328,27 +8758,27 @@
         <v>24</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K19" s="8" t="s">
         <v>73</v>
-      </c>
-      <c r="K19" s="8" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D20" s="2">
         <v>1300</v>
@@ -7359,27 +8789,27 @@
         <v>22</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K20" s="8" t="s">
         <v>75</v>
-      </c>
-      <c r="K20" s="8" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="C21" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D21" s="2">
         <v>900</v>
@@ -7390,27 +8820,27 @@
         <v>20</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K21" s="8" t="s">
         <v>78</v>
-      </c>
-      <c r="K21" s="8" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D22" s="2">
         <v>1500</v>
@@ -7421,27 +8851,27 @@
         <v>23</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D23" s="2">
         <v>1200</v>
@@ -7452,27 +8882,27 @@
         <v>36</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="C24" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D24" s="2">
         <v>1200</v>
@@ -7486,24 +8916,24 @@
         <v>12</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K24" s="8" t="s">
         <v>87</v>
-      </c>
-      <c r="K24" s="8" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D25" s="2">
         <v>1200</v>
@@ -7517,24 +8947,24 @@
         <v>12</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="C26" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D26" s="2">
         <v>1200</v>
@@ -7548,24 +8978,24 @@
         <v>12</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K26" s="8" t="s">
         <v>93</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="C27" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D27" s="2">
         <v>1200</v>
@@ -7576,27 +9006,27 @@
         <v>16</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K27" s="8" t="s">
         <v>96</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="C28" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D28" s="2">
         <v>900</v>
@@ -7607,27 +9037,27 @@
         <v>25</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="K28" s="8" t="s">
         <v>99</v>
-      </c>
-      <c r="K28" s="8" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="C29" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D29" s="2">
         <v>800</v>
@@ -7638,27 +9068,27 @@
         <v>25</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="K29" s="8" t="s">
         <v>102</v>
-      </c>
-      <c r="K29" s="8" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D30" s="2">
         <v>2420</v>
@@ -7669,27 +9099,27 @@
         <v>16</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="C31" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D31" s="2">
         <v>2800</v>
@@ -7700,27 +9130,27 @@
         <v>14</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="K31" s="8" t="s">
         <v>108</v>
-      </c>
-      <c r="K31" s="8" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="C32" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D32" s="2">
         <v>900</v>
@@ -7734,24 +9164,24 @@
         <v>12</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="K32" s="8" t="s">
         <v>111</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="C33" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D33" s="2">
         <v>1100</v>
@@ -7762,27 +9192,27 @@
         <v>9</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="K33" s="8" t="s">
         <v>114</v>
-      </c>
-      <c r="K33" s="8" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D34" s="2">
         <v>4100</v>
@@ -7793,27 +9223,27 @@
         <v>17</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="C35" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D35" s="2">
         <v>680</v>
@@ -7824,27 +9254,27 @@
         <v>15</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="K35" s="8" t="s">
         <v>121</v>
-      </c>
-      <c r="K35" s="8" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D36" s="2">
         <v>1180</v>
@@ -7858,24 +9288,24 @@
         <v>12</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D37" s="2">
         <v>1100</v>
@@ -7889,24 +9319,24 @@
         <v>12</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D38" s="2">
         <v>920</v>
@@ -7920,24 +9350,24 @@
         <v>12</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="C39" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D39" s="2">
         <v>760</v>
@@ -7948,27 +9378,27 @@
         <v>24</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="K39" s="8" t="s">
         <v>133</v>
-      </c>
-      <c r="K39" s="8" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="C40" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D40" s="2">
         <v>880</v>
@@ -7982,24 +9412,24 @@
         <v>12</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="K40" s="8" t="s">
         <v>136</v>
-      </c>
-      <c r="K40" s="8" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="C41" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D41" s="2">
         <v>1720</v>
@@ -8013,24 +9443,24 @@
         <v>12</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K41" s="8" t="s">
         <v>139</v>
-      </c>
-      <c r="K41" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>140</v>
-      </c>
       <c r="C42" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D42" s="2">
         <v>860</v>
@@ -8041,27 +9471,27 @@
         <v>16</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="K42" s="8" t="s">
         <v>142</v>
-      </c>
-      <c r="K42" s="8" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D43" s="2">
         <v>740</v>
@@ -8075,24 +9505,24 @@
         <v>12</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D44" s="2">
         <v>540</v>
@@ -8103,27 +9533,27 @@
         <v>17</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K44" s="8" t="s">
         <v>149</v>
-      </c>
-      <c r="K44" s="8" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>150</v>
-      </c>
       <c r="C45" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D45" s="2">
         <v>740</v>
@@ -8137,24 +9567,24 @@
         <v>12</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="K45" s="8" t="s">
         <v>152</v>
-      </c>
-      <c r="K45" s="8" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D46" s="2">
         <v>640</v>
@@ -8168,24 +9598,24 @@
         <v>12</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D47" s="2">
         <v>1460</v>
@@ -8199,24 +9629,24 @@
         <v>12</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="K47" s="8" t="s">
         <v>156</v>
-      </c>
-      <c r="K47" s="8" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D48" s="2">
         <v>800</v>
@@ -8230,24 +9660,24 @@
         <v>12</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="K48" s="8" t="s">
         <v>161</v>
-      </c>
-      <c r="K48" s="8" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="C49" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D49" s="2">
         <v>860</v>
@@ -8258,27 +9688,27 @@
         <v>22</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K49" s="8" t="s">
         <v>164</v>
-      </c>
-      <c r="K49" s="8" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="C50" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D50" s="2">
         <v>800</v>
@@ -8289,27 +9719,27 @@
         <v>25</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="K50" s="8" t="s">
         <v>167</v>
-      </c>
-      <c r="K50" s="8" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="C51" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D51" s="2">
         <v>1400</v>
@@ -8323,24 +9753,24 @@
         <v>12</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="K51" s="8" t="s">
         <v>170</v>
-      </c>
-      <c r="K51" s="8" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D52" s="2">
         <v>1260</v>
@@ -8354,24 +9784,24 @@
         <v>12</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K52" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="C53" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D53" s="2">
         <v>800</v>
@@ -8382,27 +9812,27 @@
         <v>24</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J53" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="K53" s="8" t="s">
         <v>177</v>
-      </c>
-      <c r="K53" s="8" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D54" s="2">
         <v>1380</v>
@@ -8413,27 +9843,27 @@
         <v>17</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K54" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>181</v>
-      </c>
       <c r="C55" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D55" s="2">
         <v>840</v>
@@ -8447,24 +9877,24 @@
         <v>12</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J55" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="K55" s="8" t="s">
         <v>183</v>
-      </c>
-      <c r="K55" s="8" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D56" s="2">
         <v>1680</v>
@@ -8478,24 +9908,24 @@
         <v>12</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K56" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D57" s="2">
         <v>1200</v>
@@ -8509,24 +9939,24 @@
         <v>12</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K57" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D58" s="2">
         <v>1100</v>
@@ -8540,24 +9970,24 @@
         <v>12</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K58" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D59" s="2">
         <v>1700</v>
@@ -8571,24 +10001,24 @@
         <v>12</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K59" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D60" s="2">
         <v>1060</v>
@@ -8599,27 +10029,27 @@
         <v>14</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K60" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D61" s="2">
         <v>1200</v>
@@ -8630,27 +10060,27 @@
         <v>18</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K61" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>202</v>
-      </c>
       <c r="C62" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D62" s="2">
         <v>1440</v>
@@ -8664,24 +10094,24 @@
         <v>12</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J62" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="K62" s="8" t="s">
         <v>204</v>
-      </c>
-      <c r="K62" s="8" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D63" s="2">
         <v>1140</v>
@@ -8695,24 +10125,24 @@
         <v>12</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K63" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D64" s="2">
         <v>1000</v>
@@ -8723,27 +10153,27 @@
         <v>19</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K64" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D65" s="2">
         <v>780</v>
@@ -8754,27 +10184,27 @@
         <v>16</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K65" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D66" s="2">
         <v>1320</v>
@@ -8785,27 +10215,27 @@
         <v>19</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K66" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D67" s="2">
         <v>680</v>
@@ -8819,24 +10249,24 @@
         <v>12</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K67" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D68" s="2">
         <v>980</v>
@@ -8850,24 +10280,24 @@
         <v>12</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K68" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="C69" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D69" s="2">
         <v>1260</v>
@@ -8878,27 +10308,27 @@
         <v>21</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J69" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="K69" s="8" t="s">
         <v>226</v>
-      </c>
-      <c r="K69" s="8" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D70" s="2">
         <v>1020</v>
@@ -8912,24 +10342,24 @@
         <v>12</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K70" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B71" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="C71" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D71" s="2">
         <v>980</v>
@@ -8940,27 +10370,27 @@
         <v>16</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J71" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="K71" s="8" t="s">
         <v>232</v>
-      </c>
-      <c r="K71" s="8" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D72" s="2">
         <v>1220</v>
@@ -8974,24 +10404,24 @@
         <v>12</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K72" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D73" s="2">
         <v>1140</v>
@@ -9005,24 +10435,24 @@
         <v>12</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K73" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D74" s="2">
         <v>780</v>
@@ -9036,24 +10466,24 @@
         <v>12</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K74" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D75" s="2">
         <v>660</v>
@@ -9064,27 +10494,27 @@
         <v>13</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K75" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D76" s="2">
         <v>1000</v>
@@ -9098,24 +10528,24 @@
         <v>12</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K76" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D77" s="2">
         <v>1280</v>
@@ -9129,24 +10559,24 @@
         <v>12</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K77" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D78" s="2">
         <v>940</v>
@@ -9157,27 +10587,27 @@
         <v>26</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K78" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D79" s="2">
         <v>480</v>
@@ -9188,27 +10618,27 @@
         <v>15</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K79" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D80" s="2">
         <v>700</v>
@@ -9219,27 +10649,27 @@
         <v>12</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K80" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D81" s="2">
         <v>620</v>
@@ -9253,24 +10683,24 @@
         <v>12</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K81" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D82" s="2">
         <v>680</v>
@@ -9284,24 +10714,24 @@
         <v>12</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K82" s="8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D83" s="2">
         <v>700</v>
@@ -9315,24 +10745,24 @@
         <v>12</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K83" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>270</v>
-      </c>
       <c r="C84" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D84" s="2">
         <v>700</v>
@@ -9346,24 +10776,24 @@
         <v>12</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J84" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="K84" s="8" t="s">
         <v>272</v>
-      </c>
-      <c r="K84" s="8" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B85" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>273</v>
-      </c>
       <c r="C85" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D85" s="2">
         <v>860</v>
@@ -9374,27 +10804,27 @@
         <v>23</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J85" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K85" s="8" t="s">
         <v>275</v>
-      </c>
-      <c r="K85" s="8" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D86" s="2">
         <v>720</v>
@@ -9405,27 +10835,27 @@
         <v>24</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K86" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B87" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>280</v>
-      </c>
       <c r="C87" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D87" s="2">
         <v>1160</v>
@@ -9439,24 +10869,24 @@
         <v>12</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K87" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>283</v>
-      </c>
       <c r="C88" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D88" s="2">
         <v>680</v>
@@ -9470,24 +10900,24 @@
         <v>12</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K88" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>286</v>
-      </c>
       <c r="C89" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D89" s="2">
         <v>780</v>
@@ -9501,24 +10931,24 @@
         <v>12</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K89" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D90" s="2">
         <v>1100</v>
@@ -9532,24 +10962,24 @@
         <v>12</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K90" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D91" s="2">
         <v>1440</v>
@@ -9560,27 +10990,27 @@
         <v>16</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K91" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D92" s="2">
         <v>680</v>
@@ -9591,60 +11021,60 @@
         <v>17</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K92" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D93" s="2">
         <v>900</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G93" s="2">
         <v>19</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K93" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="B94" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="B94" s="12" t="s">
-        <v>302</v>
-      </c>
       <c r="C94" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D94" s="12">
         <v>480</v>
@@ -9655,27 +11085,27 @@
         <v>16</v>
       </c>
       <c r="H94" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J94" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="K94" s="11" t="s">
         <v>304</v>
-      </c>
-      <c r="K94" s="11" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="B95" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="B95" s="12" t="s">
-        <v>305</v>
-      </c>
       <c r="C95" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D95" s="12">
         <v>1060</v>
@@ -9689,24 +11119,24 @@
         <v>11</v>
       </c>
       <c r="I95" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J95" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="K95" s="11" t="s">
         <v>307</v>
-      </c>
-      <c r="K95" s="11" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D96" s="12">
         <v>1400</v>
@@ -9719,27 +11149,27 @@
         <v>25</v>
       </c>
       <c r="H96" s="12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I96" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J96" s="12" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K96" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D97" s="12">
         <v>2500</v>
@@ -9752,27 +11182,27 @@
         <v>15</v>
       </c>
       <c r="H97" s="12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I97" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J97" s="12" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K97" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="B98" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="B98" s="12" t="s">
-        <v>316</v>
-      </c>
       <c r="C98" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D98" s="12">
         <v>1600</v>
@@ -9785,27 +11215,27 @@
         <v>21</v>
       </c>
       <c r="H98" s="12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I98" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J98" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="K98" s="11" t="s">
         <v>319</v>
-      </c>
-      <c r="K98" s="11" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="B99" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="B99" s="12" t="s">
-        <v>320</v>
-      </c>
       <c r="C99" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D99" s="12">
         <v>1650</v>
@@ -9821,24 +11251,24 @@
         <v>11</v>
       </c>
       <c r="I99" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J99" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="K99" s="11" t="s">
         <v>323</v>
-      </c>
-      <c r="K99" s="11" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D100" s="12">
         <v>2300</v>
@@ -9851,27 +11281,27 @@
         <v>17</v>
       </c>
       <c r="H100" s="12" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I100" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J100" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="K100" s="11" t="s">
         <v>328</v>
-      </c>
-      <c r="K100" s="11" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D101" s="12">
         <v>600</v>
@@ -9884,27 +11314,27 @@
         <v>25</v>
       </c>
       <c r="H101" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I101" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J101" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="K101" s="11" t="s">
         <v>333</v>
-      </c>
-      <c r="K101" s="11" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D102" s="12">
         <v>1600</v>
@@ -9917,27 +11347,27 @@
         <v>26</v>
       </c>
       <c r="H102" s="12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I102" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J102" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="K102" s="11" t="s">
         <v>338</v>
-      </c>
-      <c r="K102" s="11" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D103" s="12">
         <v>1100</v>
@@ -9950,27 +11380,27 @@
         <v>17</v>
       </c>
       <c r="H103" s="12" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I103" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J103" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="K103" s="11" t="s">
         <v>343</v>
-      </c>
-      <c r="K103" s="11" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B104" s="12" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D104" s="12">
         <v>1980</v>
@@ -9983,27 +11413,27 @@
         <v>19</v>
       </c>
       <c r="H104" s="12" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I104" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J104" s="12" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K104" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B105" s="12" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D105" s="12">
         <v>2100</v>
@@ -10016,27 +11446,27 @@
         <v>25</v>
       </c>
       <c r="H105" s="12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I105" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J105" s="12" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K105" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B106" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D106" s="12">
         <v>2100</v>
@@ -10049,27 +11479,27 @@
         <v>18</v>
       </c>
       <c r="H106" s="12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I106" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J106" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K106" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B107" s="12" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D107" s="12">
         <v>2200</v>
@@ -10082,27 +11512,27 @@
         <v>9</v>
       </c>
       <c r="H107" s="12" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I107" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J107" s="12" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K107" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B108" s="12" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D108" s="12">
         <v>550</v>
@@ -10115,27 +11545,27 @@
         <v>26</v>
       </c>
       <c r="H108" s="12" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I108" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J108" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="K108" s="11" t="s">
         <v>365</v>
-      </c>
-      <c r="K108" s="11" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D109" s="12">
         <v>1500</v>
@@ -10148,27 +11578,27 @@
         <v>13</v>
       </c>
       <c r="H109" s="12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I109" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J109" s="12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K109" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D110" s="12">
         <v>1600</v>
@@ -10181,27 +11611,27 @@
         <v>18</v>
       </c>
       <c r="H110" s="12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I110" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J110" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K110" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D111" s="12">
         <v>2800</v>
@@ -10214,27 +11644,27 @@
         <v>16</v>
       </c>
       <c r="H111" s="12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I111" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J111" s="12" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K111" s="11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D112" s="12">
         <v>1600</v>
@@ -10250,24 +11680,24 @@
         <v>11</v>
       </c>
       <c r="I112" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J112" s="12" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K112" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D113" s="12">
         <v>3200</v>
@@ -10280,27 +11710,27 @@
         <v>21</v>
       </c>
       <c r="H113" s="12" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I113" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J113" s="12" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K113" s="11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D114" s="12">
         <v>3200</v>
@@ -10313,27 +11743,27 @@
         <v>18</v>
       </c>
       <c r="H114" s="12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I114" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J114" s="12" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K114" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D115" s="12">
         <v>3000</v>
@@ -10346,27 +11776,27 @@
         <v>21</v>
       </c>
       <c r="H115" s="12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I115" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J115" s="12" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K115" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D116" s="12">
         <v>2400</v>
@@ -10379,27 +11809,27 @@
         <v>21</v>
       </c>
       <c r="H116" s="12" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I116" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J116" s="12" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K116" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B117" s="12" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D117" s="12">
         <v>2100</v>
@@ -10415,24 +11845,24 @@
         <v>11</v>
       </c>
       <c r="I117" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J117" s="12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K117" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B118" s="12" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D118" s="12">
         <v>550</v>
@@ -10445,27 +11875,27 @@
         <v>16</v>
       </c>
       <c r="H118" s="12" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I118" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J118" s="12" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K118" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B119" s="12" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D119" s="12">
         <v>1900</v>
@@ -10478,27 +11908,27 @@
         <v>18</v>
       </c>
       <c r="H119" s="12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I119" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J119" s="12" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K119" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" s="11" t="s">
+        <v>411</v>
+      </c>
+      <c r="B120" s="12" t="s">
         <v>410</v>
       </c>
-      <c r="B120" s="12" t="s">
-        <v>409</v>
-      </c>
       <c r="C120" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D120" s="12">
         <v>1500</v>
@@ -10511,27 +11941,27 @@
         <v>17</v>
       </c>
       <c r="H120" s="12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I120" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J120" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="K120" s="11" t="s">
         <v>412</v>
-      </c>
-      <c r="K120" s="11" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B121" s="12" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D121" s="12">
         <v>1700</v>
@@ -10544,27 +11974,27 @@
         <v>15</v>
       </c>
       <c r="H121" s="12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I121" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J121" s="12" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K121" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" s="11" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D122" s="12">
         <v>2400</v>
@@ -10577,27 +12007,27 @@
         <v>24</v>
       </c>
       <c r="H122" s="12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I122" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J122" s="12" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K122" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B123" s="12" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D123" s="12">
         <v>2400</v>
@@ -10610,27 +12040,27 @@
         <v>25</v>
       </c>
       <c r="H123" s="12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I123" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J123" s="12" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K123" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D124" s="12">
         <v>1500</v>
@@ -10643,27 +12073,27 @@
         <v>21</v>
       </c>
       <c r="H124" s="12" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I124" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J124" s="12" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K124" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D125" s="12">
         <v>1400</v>
@@ -10679,24 +12109,24 @@
         <v>11</v>
       </c>
       <c r="I125" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J125" s="12" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K125" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" s="11" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B126" s="12" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D126" s="12">
         <v>1500</v>
@@ -10712,24 +12142,24 @@
         <v>11</v>
       </c>
       <c r="I126" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J126" s="12" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K126" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B127" s="12" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D127" s="12">
         <v>1600</v>
@@ -10742,27 +12172,27 @@
         <v>15</v>
       </c>
       <c r="H127" s="12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I127" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J127" s="12" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K127" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B128" s="12" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D128" s="12">
         <v>1100</v>
@@ -10775,27 +12205,27 @@
         <v>18</v>
       </c>
       <c r="H128" s="12" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I128" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J128" s="12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K128" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B129" s="12" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D129" s="12">
         <v>1600</v>
@@ -10808,27 +12238,27 @@
         <v>12</v>
       </c>
       <c r="H129" s="12" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I129" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J129" s="12" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K129" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B130" s="12" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D130" s="12">
         <v>1300</v>
@@ -10841,27 +12271,27 @@
         <v>15</v>
       </c>
       <c r="H130" s="12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I130" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J130" s="12" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K130" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B131" s="12" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D131" s="12">
         <v>1400</v>
@@ -10874,27 +12304,27 @@
         <v>19</v>
       </c>
       <c r="H131" s="12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I131" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J131" s="12" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K131" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B132" s="12" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D132" s="12">
         <v>2500</v>
@@ -10907,27 +12337,27 @@
         <v>25</v>
       </c>
       <c r="H132" s="12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I132" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J132" s="12" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K132" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B133" s="12" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D133" s="12">
         <v>1800</v>
@@ -10940,27 +12370,27 @@
         <v>16</v>
       </c>
       <c r="H133" s="12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I133" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J133" s="12" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="K133" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B134" s="12" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D134" s="12">
         <v>1600</v>
@@ -10973,27 +12403,27 @@
         <v>17</v>
       </c>
       <c r="H134" s="12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I134" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J134" s="12" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K134" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B135" s="12" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D135" s="12">
         <v>1350</v>
@@ -11006,27 +12436,27 @@
         <v>23</v>
       </c>
       <c r="H135" s="12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I135" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J135" s="12" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K135" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B136" s="12" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D136" s="12">
         <v>2300</v>
@@ -11042,24 +12472,24 @@
         <v>12</v>
       </c>
       <c r="I136" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J136" s="12" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K136" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B137" s="12" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D137" s="12">
         <v>650</v>
@@ -11072,27 +12502,27 @@
         <v>15</v>
       </c>
       <c r="H137" s="12" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I137" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J137" s="12" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K137" s="11" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B138" s="12" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D138" s="12">
         <v>850</v>
@@ -11105,27 +12535,27 @@
         <v>17</v>
       </c>
       <c r="H138" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I138" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J138" s="12" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K138" s="11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" s="11" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B139" s="12" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D139" s="12">
         <v>1800</v>
@@ -11138,27 +12568,27 @@
         <v>15</v>
       </c>
       <c r="H139" s="12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I139" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J139" s="12" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K139" s="11" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" s="11" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B140" s="12" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D140" s="12">
         <v>1500</v>
@@ -11171,27 +12601,27 @@
         <v>21</v>
       </c>
       <c r="H140" s="12" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I140" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J140" s="12" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K140" s="11" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" s="11" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B141" s="12" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D141" s="12">
         <v>900</v>
@@ -11204,27 +12634,27 @@
         <v>15</v>
       </c>
       <c r="H141" s="12" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="I141" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J141" s="12" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K141" s="11" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" s="11" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B142" s="12" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D142" s="12">
         <v>1500</v>
@@ -11237,27 +12667,27 @@
         <v>15</v>
       </c>
       <c r="H142" s="12" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="I142" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J142" s="12" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K142" s="11" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" s="11" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B143" s="12" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D143" s="12">
         <v>900</v>
@@ -11270,27 +12700,27 @@
         <v>19</v>
       </c>
       <c r="H143" s="12" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="I143" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J143" s="12" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="K143" s="11" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B144" s="12" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D144" s="12">
         <v>900</v>
@@ -11303,27 +12733,27 @@
         <v>23</v>
       </c>
       <c r="H144" s="12" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="I144" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J144" s="12" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K144" s="11" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145" s="11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B145" s="12" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D145" s="12">
         <v>2600</v>
@@ -11336,27 +12766,27 @@
         <v>15</v>
       </c>
       <c r="H145" s="12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I145" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J145" s="12" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K145" s="11" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" s="11" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B146" s="12" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D146" s="12">
         <v>1700</v>
@@ -11369,27 +12799,27 @@
         <v>24</v>
       </c>
       <c r="H146" s="12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I146" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J146" s="12" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K146" s="11" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147" s="11" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B147" s="12" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D147" s="12">
         <v>2800</v>
@@ -11402,480 +12832,2859 @@
         <v>14</v>
       </c>
       <c r="H147" s="12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I147" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J147" s="12" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="K147" s="11" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A148" s="9" t="s">
-        <v>521</v>
-      </c>
-      <c r="B148" s="10" t="s">
-        <v>519</v>
-      </c>
-      <c r="C148" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D148" s="10">
+      <c r="A148" s="11" t="s">
+        <v>522</v>
+      </c>
+      <c r="B148" s="12" t="s">
+        <v>520</v>
+      </c>
+      <c r="C148" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D148" s="12">
         <v>2400</v>
       </c>
-      <c r="E148" s="10">
+      <c r="E148" s="12">
         <v>2100</v>
       </c>
+      <c r="F148" s="12"/>
       <c r="G148" s="2">
         <v>24</v>
       </c>
-      <c r="H148" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="I148" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J148" s="10" t="s">
-        <v>520</v>
-      </c>
-      <c r="K148" s="9" t="s">
-        <v>522</v>
+      <c r="H148" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="I148" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J148" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="K148" s="11" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A149" s="9" t="s">
-        <v>525</v>
-      </c>
-      <c r="B149" s="10" t="s">
-        <v>523</v>
-      </c>
-      <c r="C149" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D149" s="10">
+      <c r="A149" s="11" t="s">
+        <v>526</v>
+      </c>
+      <c r="B149" s="12" t="s">
+        <v>524</v>
+      </c>
+      <c r="C149" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D149" s="12">
         <v>2400</v>
       </c>
-      <c r="E149" s="10">
+      <c r="E149" s="12">
         <v>2100</v>
       </c>
+      <c r="F149" s="12"/>
       <c r="G149" s="2">
         <v>15</v>
       </c>
-      <c r="H149" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="I149" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J149" s="10" t="s">
-        <v>524</v>
-      </c>
-      <c r="K149" s="9" t="s">
-        <v>526</v>
+      <c r="H149" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="I149" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J149" s="12" t="s">
+        <v>525</v>
+      </c>
+      <c r="K149" s="11" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A150" s="9" t="s">
-        <v>529</v>
-      </c>
-      <c r="B150" s="10" t="s">
-        <v>527</v>
-      </c>
-      <c r="C150" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D150" s="10">
+      <c r="A150" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="B150" s="12" t="s">
+        <v>528</v>
+      </c>
+      <c r="C150" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D150" s="12">
         <v>1400</v>
       </c>
-      <c r="E150" s="10">
+      <c r="E150" s="12">
         <v>1140</v>
       </c>
+      <c r="F150" s="12"/>
       <c r="G150" s="2">
         <v>23</v>
       </c>
-      <c r="H150" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="I150" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J150" s="10" t="s">
-        <v>528</v>
-      </c>
-      <c r="K150" s="9" t="s">
-        <v>530</v>
+      <c r="H150" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="I150" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J150" s="12" t="s">
+        <v>529</v>
+      </c>
+      <c r="K150" s="11" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A151" s="9" t="s">
-        <v>533</v>
-      </c>
-      <c r="B151" s="10" t="s">
-        <v>531</v>
-      </c>
-      <c r="C151" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D151" s="10">
+      <c r="A151" s="11" t="s">
+        <v>534</v>
+      </c>
+      <c r="B151" s="12" t="s">
+        <v>532</v>
+      </c>
+      <c r="C151" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D151" s="12">
         <v>1300</v>
       </c>
-      <c r="E151" s="10">
+      <c r="E151" s="12">
         <v>1000</v>
       </c>
+      <c r="F151" s="12"/>
       <c r="G151" s="2">
         <v>12</v>
       </c>
-      <c r="H151" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="I151" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J151" s="10" t="s">
-        <v>532</v>
-      </c>
-      <c r="K151" s="9" t="s">
-        <v>534</v>
+      <c r="H151" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="I151" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J151" s="12" t="s">
+        <v>533</v>
+      </c>
+      <c r="K151" s="11" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A152" s="9" t="s">
-        <v>537</v>
-      </c>
-      <c r="B152" s="10" t="s">
-        <v>535</v>
-      </c>
-      <c r="C152" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D152" s="10">
+      <c r="A152" s="11" t="s">
+        <v>538</v>
+      </c>
+      <c r="B152" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="C152" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D152" s="12">
         <v>2500</v>
       </c>
-      <c r="E152" s="10">
+      <c r="E152" s="12">
         <v>2200</v>
       </c>
+      <c r="F152" s="12"/>
       <c r="G152" s="2">
         <v>17</v>
       </c>
-      <c r="H152" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="I152" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J152" s="10" t="s">
-        <v>536</v>
-      </c>
-      <c r="K152" s="9" t="s">
-        <v>538</v>
+      <c r="H152" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="I152" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J152" s="12" t="s">
+        <v>537</v>
+      </c>
+      <c r="K152" s="11" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A153" s="9" t="s">
-        <v>541</v>
-      </c>
-      <c r="B153" s="10" t="s">
-        <v>539</v>
-      </c>
-      <c r="C153" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D153" s="10">
+      <c r="A153" s="11" t="s">
+        <v>542</v>
+      </c>
+      <c r="B153" s="12" t="s">
+        <v>540</v>
+      </c>
+      <c r="C153" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D153" s="12">
         <v>1100</v>
       </c>
-      <c r="E153" s="10">
+      <c r="E153" s="12">
         <v>980</v>
       </c>
+      <c r="F153" s="12"/>
       <c r="G153" s="2">
         <v>23</v>
       </c>
-      <c r="H153" s="10" t="s">
+      <c r="H153" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I153" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J153" s="10" t="s">
-        <v>540</v>
-      </c>
-      <c r="K153" s="9" t="s">
-        <v>542</v>
+      <c r="I153" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J153" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="K153" s="11" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A154" s="9" t="s">
-        <v>545</v>
-      </c>
-      <c r="B154" s="10" t="s">
-        <v>543</v>
-      </c>
-      <c r="C154" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D154" s="10">
+      <c r="A154" s="11" t="s">
+        <v>546</v>
+      </c>
+      <c r="B154" s="12" t="s">
+        <v>544</v>
+      </c>
+      <c r="C154" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D154" s="12">
         <v>2000</v>
       </c>
-      <c r="E154" s="10">
+      <c r="E154" s="12">
         <v>1700</v>
       </c>
+      <c r="F154" s="12"/>
       <c r="G154" s="2">
         <v>15</v>
       </c>
-      <c r="H154" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="I154" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J154" s="10" t="s">
-        <v>544</v>
-      </c>
-      <c r="K154" s="9" t="s">
-        <v>546</v>
+      <c r="H154" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="I154" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J154" s="12" t="s">
+        <v>545</v>
+      </c>
+      <c r="K154" s="11" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A155" s="9" t="s">
+      <c r="A155" s="11" t="s">
+        <v>550</v>
+      </c>
+      <c r="B155" s="12" t="s">
         <v>549</v>
       </c>
-      <c r="B155" s="10" t="s">
-        <v>548</v>
-      </c>
-      <c r="C155" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D155" s="10">
+      <c r="C155" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D155" s="12">
         <v>2100</v>
       </c>
-      <c r="E155" s="10">
+      <c r="E155" s="12">
         <v>1800</v>
       </c>
+      <c r="F155" s="12"/>
       <c r="G155" s="2">
         <v>19</v>
       </c>
-      <c r="H155" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="I155" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J155" s="10" t="s">
-        <v>547</v>
-      </c>
-      <c r="K155" s="9" t="s">
-        <v>553</v>
+      <c r="H155" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="I155" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J155" s="12" t="s">
+        <v>548</v>
+      </c>
+      <c r="K155" s="11" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A156" s="9" t="s">
+      <c r="A156" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="B156" s="12" t="s">
         <v>551</v>
       </c>
-      <c r="B156" s="10" t="s">
-        <v>550</v>
-      </c>
-      <c r="C156" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D156" s="10">
+      <c r="C156" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D156" s="12">
         <v>1650</v>
       </c>
-      <c r="E156" s="10">
+      <c r="E156" s="12">
         <v>1440</v>
       </c>
+      <c r="F156" s="12"/>
       <c r="G156" s="2">
         <v>23</v>
       </c>
-      <c r="H156" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="I156" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J156" s="10" t="s">
-        <v>552</v>
-      </c>
-      <c r="K156" s="9" t="s">
-        <v>554</v>
+      <c r="H156" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="I156" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J156" s="12" t="s">
+        <v>553</v>
+      </c>
+      <c r="K156" s="11" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A157" s="9" t="s">
+      <c r="A157" s="11" t="s">
+        <v>562</v>
+      </c>
+      <c r="B157" s="12" t="s">
+        <v>556</v>
+      </c>
+      <c r="C157" s="12" t="s">
         <v>561</v>
       </c>
-      <c r="B157" s="10" t="s">
-        <v>555</v>
-      </c>
-      <c r="C157" s="10" t="s">
-        <v>560</v>
-      </c>
-      <c r="D157" s="10">
+      <c r="D157" s="12">
         <v>1400</v>
       </c>
-      <c r="E157" s="10">
+      <c r="E157" s="12">
         <v>1290</v>
       </c>
+      <c r="F157" s="12"/>
       <c r="G157" s="2">
         <v>17</v>
       </c>
-      <c r="H157" s="10" t="s">
+      <c r="H157" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I157" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J157" s="10" t="s">
-        <v>556</v>
-      </c>
-      <c r="K157" s="9" t="s">
+      <c r="I157" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J157" s="12" t="s">
+        <v>557</v>
+      </c>
+      <c r="K157" s="11" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A158" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="B158" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="C158" s="12" t="s">
         <v>561</v>
       </c>
-    </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A158" s="9" t="s">
-        <v>562</v>
-      </c>
-      <c r="B158" s="10" t="s">
-        <v>557</v>
-      </c>
-      <c r="C158" s="10" t="s">
-        <v>560</v>
-      </c>
-      <c r="D158" s="10">
+      <c r="D158" s="12">
         <v>750</v>
       </c>
-      <c r="E158" s="10">
+      <c r="E158" s="12">
         <v>500</v>
       </c>
+      <c r="F158" s="12"/>
       <c r="G158" s="2">
         <v>12</v>
       </c>
-      <c r="H158" s="10" t="s">
-        <v>558</v>
-      </c>
-      <c r="I158" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J158" s="10" t="s">
+      <c r="H158" s="12" t="s">
         <v>559</v>
       </c>
-      <c r="K158" s="9" t="s">
-        <v>562</v>
+      <c r="I158" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J158" s="12" t="s">
+        <v>560</v>
+      </c>
+      <c r="K158" s="11" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A159" s="9" t="s">
-        <v>565</v>
-      </c>
-      <c r="B159" s="10" t="s">
-        <v>563</v>
-      </c>
-      <c r="C159" s="10" t="s">
+      <c r="A159" s="11" t="s">
+        <v>566</v>
+      </c>
+      <c r="B159" s="12" t="s">
+        <v>564</v>
+      </c>
+      <c r="C159" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D159" s="12">
+        <v>850</v>
+      </c>
+      <c r="E159" s="12">
         <v>560</v>
       </c>
-      <c r="D159" s="10">
-        <v>850</v>
-      </c>
-      <c r="E159" s="10">
-        <v>560</v>
-      </c>
+      <c r="F159" s="12"/>
       <c r="G159" s="2">
         <v>23</v>
       </c>
-      <c r="H159" s="10" t="s">
-        <v>558</v>
-      </c>
-      <c r="I159" s="10" t="s">
+      <c r="H159" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="I159" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J159" s="12" t="s">
+        <v>565</v>
+      </c>
+      <c r="K159" s="11" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A160" s="11" t="s">
+        <v>649</v>
+      </c>
+      <c r="B160" s="12" t="s">
+        <v>647</v>
+      </c>
+      <c r="C160" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D160" s="12">
+        <v>750</v>
+      </c>
+      <c r="E160" s="12">
+        <v>500</v>
+      </c>
+      <c r="F160" s="12"/>
+      <c r="G160" s="2">
+        <v>12</v>
+      </c>
+      <c r="H160" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="I160" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J160" s="12" t="s">
+        <v>648</v>
+      </c>
+      <c r="K160" s="11" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A161" s="11" t="s">
+        <v>651</v>
+      </c>
+      <c r="B161" s="12" t="s">
+        <v>650</v>
+      </c>
+      <c r="C161" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D161" s="12">
+        <v>1000</v>
+      </c>
+      <c r="E161" s="12">
+        <v>740</v>
+      </c>
+      <c r="F161" s="12"/>
+      <c r="G161" s="2">
+        <v>13</v>
+      </c>
+      <c r="H161" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="I161" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J161" s="12" t="s">
+        <v>652</v>
+      </c>
+      <c r="K161" s="11" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A162" s="11" t="s">
+        <v>653</v>
+      </c>
+      <c r="B162" s="12" t="s">
+        <v>650</v>
+      </c>
+      <c r="C162" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D162" s="12">
+        <v>750</v>
+      </c>
+      <c r="E162" s="12">
+        <v>540</v>
+      </c>
+      <c r="F162" s="12"/>
+      <c r="G162" s="2">
+        <v>16</v>
+      </c>
+      <c r="H162" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I162" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J162" s="12" t="s">
+        <v>652</v>
+      </c>
+      <c r="K162" s="11" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A163" s="11" t="s">
+        <v>654</v>
+      </c>
+      <c r="B163" s="12" t="s">
+        <v>655</v>
+      </c>
+      <c r="C163" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D163" s="12">
+        <v>850</v>
+      </c>
+      <c r="E163" s="12">
+        <v>590</v>
+      </c>
+      <c r="F163" s="12"/>
+      <c r="G163" s="2">
+        <v>15</v>
+      </c>
+      <c r="H163" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I163" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J163" s="12" t="s">
+        <v>656</v>
+      </c>
+      <c r="K163" s="11" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A164" s="11" t="s">
+        <v>658</v>
+      </c>
+      <c r="B164" s="12" t="s">
+        <v>657</v>
+      </c>
+      <c r="C164" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D164" s="12">
+        <v>670</v>
+      </c>
+      <c r="E164" s="12">
+        <v>490</v>
+      </c>
+      <c r="F164" s="12"/>
+      <c r="G164" s="2">
+        <v>24</v>
+      </c>
+      <c r="H164" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I164" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J164" s="12" t="s">
+        <v>646</v>
+      </c>
+      <c r="K164" s="11" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A165" s="11" t="s">
+        <v>659</v>
+      </c>
+      <c r="B165" s="12" t="s">
+        <v>660</v>
+      </c>
+      <c r="C165" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D165" s="12">
+        <v>550</v>
+      </c>
+      <c r="E165" s="12">
+        <v>340</v>
+      </c>
+      <c r="F165" s="12"/>
+      <c r="G165" s="2">
+        <v>13</v>
+      </c>
+      <c r="H165" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="I165" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J165" s="12" t="s">
+        <v>661</v>
+      </c>
+      <c r="K165" s="11" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A166" s="11" t="s">
+        <v>662</v>
+      </c>
+      <c r="B166" s="12" t="s">
+        <v>664</v>
+      </c>
+      <c r="C166" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D166" s="12">
+        <v>1100</v>
+      </c>
+      <c r="E166" s="12">
+        <v>730</v>
+      </c>
+      <c r="F166" s="12"/>
+      <c r="G166" s="2">
+        <v>25</v>
+      </c>
+      <c r="H166" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="I166" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J166" s="12" t="s">
+        <v>665</v>
+      </c>
+      <c r="K166" s="11" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A167" s="11" t="s">
+        <v>663</v>
+      </c>
+      <c r="B167" s="12" t="s">
+        <v>666</v>
+      </c>
+      <c r="C167" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D167" s="12">
+        <v>890</v>
+      </c>
+      <c r="E167" s="12">
+        <v>690</v>
+      </c>
+      <c r="F167" s="12"/>
+      <c r="G167" s="2">
+        <v>13</v>
+      </c>
+      <c r="H167" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I167" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J167" s="12" t="s">
+        <v>667</v>
+      </c>
+      <c r="K167" s="11" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A168" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="B168" s="12" t="s">
+        <v>567</v>
+      </c>
+      <c r="C168" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D168" s="12">
+        <v>700</v>
+      </c>
+      <c r="E168" s="12">
+        <v>500</v>
+      </c>
+      <c r="F168" s="12"/>
+      <c r="G168" s="2">
+        <v>22</v>
+      </c>
+      <c r="H168" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="I168" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J168" s="12" t="s">
+        <v>671</v>
+      </c>
+      <c r="K168" s="11" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="11" t="s">
+        <v>670</v>
+      </c>
+      <c r="B169" s="12" t="s">
+        <v>668</v>
+      </c>
+      <c r="C169" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D169" s="12">
+        <v>950</v>
+      </c>
+      <c r="E169" s="12">
+        <v>740</v>
+      </c>
+      <c r="F169" s="12"/>
+      <c r="G169" s="2">
+        <v>16</v>
+      </c>
+      <c r="H169" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I169" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J169" s="12" t="s">
+        <v>672</v>
+      </c>
+      <c r="K169" s="11" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A170" s="11" t="s">
+        <v>669</v>
+      </c>
+      <c r="B170" s="12" t="s">
+        <v>668</v>
+      </c>
+      <c r="C170" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D170" s="12">
+        <v>1250</v>
+      </c>
+      <c r="E170" s="12">
+        <v>1090</v>
+      </c>
+      <c r="F170" s="12"/>
+      <c r="G170" s="2">
+        <v>16</v>
+      </c>
+      <c r="H170" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I170" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J170" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="K170" s="11" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A171" s="11" t="s">
+        <v>571</v>
+      </c>
+      <c r="B171" s="12" t="s">
+        <v>569</v>
+      </c>
+      <c r="C171" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D171" s="12">
+        <v>850</v>
+      </c>
+      <c r="E171" s="12">
+        <v>560</v>
+      </c>
+      <c r="F171" s="12"/>
+      <c r="G171" s="2">
+        <v>11</v>
+      </c>
+      <c r="H171" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="I171" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J171" s="12" t="s">
+        <v>570</v>
+      </c>
+      <c r="K171" s="11" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A172" s="11" t="s">
+        <v>575</v>
+      </c>
+      <c r="B172" s="12" t="s">
+        <v>572</v>
+      </c>
+      <c r="C172" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D172" s="12">
+        <v>950</v>
+      </c>
+      <c r="E172" s="12">
+        <v>830</v>
+      </c>
+      <c r="F172" s="12"/>
+      <c r="G172" s="2">
+        <v>12</v>
+      </c>
+      <c r="H172" s="12" t="s">
+        <v>573</v>
+      </c>
+      <c r="I172" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J172" s="12" t="s">
+        <v>574</v>
+      </c>
+      <c r="K172" s="11" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A173" s="11" t="s">
+        <v>578</v>
+      </c>
+      <c r="B173" s="12" t="s">
+        <v>576</v>
+      </c>
+      <c r="C173" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D173" s="12">
+        <v>730</v>
+      </c>
+      <c r="E173" s="12">
+        <v>500</v>
+      </c>
+      <c r="F173" s="12"/>
+      <c r="G173" s="2">
+        <v>23</v>
+      </c>
+      <c r="H173" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="I173" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J173" s="12" t="s">
+        <v>577</v>
+      </c>
+      <c r="K173" s="11" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A174" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="B174" s="12" t="s">
+        <v>579</v>
+      </c>
+      <c r="C174" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D174" s="12">
+        <v>1350</v>
+      </c>
+      <c r="E174" s="12">
+        <v>1070</v>
+      </c>
+      <c r="F174" s="12"/>
+      <c r="G174" s="2">
+        <v>12</v>
+      </c>
+      <c r="H174" s="12" t="s">
+        <v>580</v>
+      </c>
+      <c r="I174" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J174" s="12" t="s">
+        <v>581</v>
+      </c>
+      <c r="K174" s="11" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A175" s="11" t="s">
+        <v>585</v>
+      </c>
+      <c r="B175" s="12" t="s">
+        <v>583</v>
+      </c>
+      <c r="C175" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D175" s="12">
+        <v>790</v>
+      </c>
+      <c r="E175" s="12">
+        <v>570</v>
+      </c>
+      <c r="F175" s="12"/>
+      <c r="G175" s="2">
+        <v>12</v>
+      </c>
+      <c r="H175" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="I175" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J175" s="12" t="s">
+        <v>584</v>
+      </c>
+      <c r="K175" s="11" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A176" s="11" t="s">
+        <v>588</v>
+      </c>
+      <c r="B176" s="12" t="s">
+        <v>586</v>
+      </c>
+      <c r="C176" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D176" s="12">
+        <v>1700</v>
+      </c>
+      <c r="E176" s="12">
+        <v>1430</v>
+      </c>
+      <c r="F176" s="12"/>
+      <c r="G176" s="2">
         <v>21</v>
       </c>
-      <c r="J159" s="10" t="s">
-        <v>564</v>
-      </c>
-      <c r="K159" s="9" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A160" s="9" t="s">
-        <v>568</v>
-      </c>
-      <c r="B160" s="10" t="s">
-        <v>566</v>
-      </c>
-      <c r="C160" s="10" t="s">
+      <c r="H176" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I176" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J176" s="12" t="s">
+        <v>587</v>
+      </c>
+      <c r="K176" s="11" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A177" s="11" t="s">
+        <v>591</v>
+      </c>
+      <c r="B177" s="12" t="s">
+        <v>589</v>
+      </c>
+      <c r="C177" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D177" s="12">
+        <v>1100</v>
+      </c>
+      <c r="E177" s="12">
+        <v>830</v>
+      </c>
+      <c r="F177" s="12"/>
+      <c r="G177" s="2">
+        <v>26</v>
+      </c>
+      <c r="H177" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I177" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J177" s="12" t="s">
+        <v>590</v>
+      </c>
+      <c r="K177" s="11" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A178" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="B178" s="12" t="s">
+        <v>592</v>
+      </c>
+      <c r="C178" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D178" s="12">
+        <v>1800</v>
+      </c>
+      <c r="E178" s="12">
+        <v>1510</v>
+      </c>
+      <c r="F178" s="12"/>
+      <c r="G178" s="2">
+        <v>23</v>
+      </c>
+      <c r="H178" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I178" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J178" s="12" t="s">
+        <v>593</v>
+      </c>
+      <c r="K178" s="11" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A179" s="11" t="s">
+        <v>597</v>
+      </c>
+      <c r="B179" s="12" t="s">
+        <v>595</v>
+      </c>
+      <c r="C179" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D179" s="12">
+        <v>750</v>
+      </c>
+      <c r="E179" s="12">
+        <v>590</v>
+      </c>
+      <c r="F179" s="12"/>
+      <c r="G179" s="2">
+        <v>22</v>
+      </c>
+      <c r="H179" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="I179" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J179" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="K179" s="11" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A180" s="11" t="s">
+        <v>678</v>
+      </c>
+      <c r="B180" s="12" t="s">
+        <v>679</v>
+      </c>
+      <c r="C180" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D180" s="12">
+        <v>750</v>
+      </c>
+      <c r="E180" s="12">
+        <v>500</v>
+      </c>
+      <c r="F180" s="12"/>
+      <c r="G180" s="2">
+        <v>24</v>
+      </c>
+      <c r="H180" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="I180" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J180" s="12" t="s">
+        <v>680</v>
+      </c>
+      <c r="K180" s="11" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A181" s="11" t="s">
+        <v>600</v>
+      </c>
+      <c r="B181" s="12" t="s">
+        <v>598</v>
+      </c>
+      <c r="C181" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D181" s="12">
+        <v>800</v>
+      </c>
+      <c r="E181" s="12">
         <v>560</v>
       </c>
-      <c r="D160" s="10">
+      <c r="F181" s="12"/>
+      <c r="G181" s="2">
+        <v>17</v>
+      </c>
+      <c r="H181" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="I181" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J181" s="12" t="s">
+        <v>599</v>
+      </c>
+      <c r="K181" s="11" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A182" s="11" t="s">
+        <v>603</v>
+      </c>
+      <c r="B182" s="12" t="s">
+        <v>601</v>
+      </c>
+      <c r="C182" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D182" s="12">
+        <v>2100</v>
+      </c>
+      <c r="E182" s="12">
+        <v>1720</v>
+      </c>
+      <c r="F182" s="12"/>
+      <c r="G182" s="2">
+        <v>21</v>
+      </c>
+      <c r="H182" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I182" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J182" s="12" t="s">
+        <v>602</v>
+      </c>
+      <c r="K182" s="11" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A183" s="11" t="s">
+        <v>696</v>
+      </c>
+      <c r="B183" s="12" t="s">
+        <v>697</v>
+      </c>
+      <c r="C183" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D183" s="12">
+        <v>1100</v>
+      </c>
+      <c r="E183" s="12">
+        <v>950</v>
+      </c>
+      <c r="F183" s="12"/>
+      <c r="G183" s="2">
+        <v>12</v>
+      </c>
+      <c r="H183" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I183" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J183" s="12" t="s">
+        <v>602</v>
+      </c>
+      <c r="K183" s="11" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A184" s="11" t="s">
+        <v>698</v>
+      </c>
+      <c r="B184" s="12" t="s">
         <v>700</v>
       </c>
-      <c r="E160" s="10">
-        <v>500</v>
-      </c>
-      <c r="G160" s="2">
-        <v>22</v>
-      </c>
-      <c r="H160" s="10" t="s">
-        <v>558</v>
-      </c>
-      <c r="I160" s="10" t="s">
+      <c r="C184" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D184" s="12">
+        <v>2200</v>
+      </c>
+      <c r="E184" s="12">
+        <v>1820</v>
+      </c>
+      <c r="F184" s="12"/>
+      <c r="G184" s="2">
+        <v>17</v>
+      </c>
+      <c r="H184" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I184" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J184" s="12" t="s">
+        <v>701</v>
+      </c>
+      <c r="K184" s="11" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A185" s="11" t="s">
+        <v>699</v>
+      </c>
+      <c r="B185" s="12" t="s">
+        <v>700</v>
+      </c>
+      <c r="C185" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D185" s="12">
+        <v>1300</v>
+      </c>
+      <c r="E185" s="12">
+        <v>990</v>
+      </c>
+      <c r="F185" s="12"/>
+      <c r="G185" s="2">
+        <v>18</v>
+      </c>
+      <c r="H185" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I185" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J185" s="12" t="s">
+        <v>701</v>
+      </c>
+      <c r="K185" s="11" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A186" s="11" t="s">
+        <v>606</v>
+      </c>
+      <c r="B186" s="12" t="s">
+        <v>604</v>
+      </c>
+      <c r="C186" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D186" s="12">
+        <v>1900</v>
+      </c>
+      <c r="E186" s="12">
+        <v>1670</v>
+      </c>
+      <c r="F186" s="12"/>
+      <c r="G186" s="2">
+        <v>25</v>
+      </c>
+      <c r="H186" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I186" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J186" s="12" t="s">
+        <v>605</v>
+      </c>
+      <c r="K186" s="11" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A187" s="11" t="s">
+        <v>610</v>
+      </c>
+      <c r="B187" s="12" t="s">
+        <v>607</v>
+      </c>
+      <c r="C187" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D187" s="12">
+        <v>730</v>
+      </c>
+      <c r="E187" s="12">
+        <v>540</v>
+      </c>
+      <c r="F187" s="12"/>
+      <c r="G187" s="2">
+        <v>15</v>
+      </c>
+      <c r="H187" s="12" t="s">
+        <v>608</v>
+      </c>
+      <c r="I187" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J187" s="12" t="s">
+        <v>609</v>
+      </c>
+      <c r="K187" s="11" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A188" s="11" t="s">
+        <v>614</v>
+      </c>
+      <c r="B188" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="C188" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D188" s="12">
+        <v>600</v>
+      </c>
+      <c r="E188" s="12">
+        <v>420</v>
+      </c>
+      <c r="F188" s="12"/>
+      <c r="G188" s="2">
+        <v>18</v>
+      </c>
+      <c r="H188" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="I188" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J188" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="K188" s="11" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A189" s="11" t="s">
+        <v>617</v>
+      </c>
+      <c r="B189" s="12" t="s">
+        <v>615</v>
+      </c>
+      <c r="C189" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D189" s="12">
+        <v>1800</v>
+      </c>
+      <c r="E189" s="12">
+        <v>1500</v>
+      </c>
+      <c r="F189" s="12"/>
+      <c r="G189" s="2">
         <v>21</v>
       </c>
-      <c r="J160" s="10" t="s">
-        <v>567</v>
-      </c>
-      <c r="K160" s="9" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="161" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C161" s="10" t="s">
-        <v>560</v>
-      </c>
-      <c r="G161" s="2"/>
-      <c r="I161" s="10" t="s">
+      <c r="H189" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="I189" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J189" s="12" t="s">
+        <v>616</v>
+      </c>
+      <c r="K189" s="11" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A190" s="11" t="s">
+        <v>619</v>
+      </c>
+      <c r="B190" s="12" t="s">
+        <v>618</v>
+      </c>
+      <c r="C190" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D190" s="12">
+        <v>650</v>
+      </c>
+      <c r="E190" s="12">
+        <v>450</v>
+      </c>
+      <c r="F190" s="12"/>
+      <c r="G190" s="2">
+        <v>25</v>
+      </c>
+      <c r="H190" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I190" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J190" s="12" t="s">
+        <v>620</v>
+      </c>
+      <c r="K190" s="11" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A191" s="11" t="s">
+        <v>623</v>
+      </c>
+      <c r="B191" s="12" t="s">
+        <v>621</v>
+      </c>
+      <c r="C191" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D191" s="12">
+        <v>1200</v>
+      </c>
+      <c r="E191" s="12">
+        <v>1000</v>
+      </c>
+      <c r="F191" s="12"/>
+      <c r="G191" s="2">
+        <v>24</v>
+      </c>
+      <c r="H191" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I191" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J191" s="12" t="s">
+        <v>622</v>
+      </c>
+      <c r="K191" s="11" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A192" s="11" t="s">
+        <v>626</v>
+      </c>
+      <c r="B192" s="12" t="s">
+        <v>624</v>
+      </c>
+      <c r="C192" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D192" s="12">
+        <v>1200</v>
+      </c>
+      <c r="E192" s="12">
+        <v>950</v>
+      </c>
+      <c r="F192" s="12"/>
+      <c r="G192" s="2">
+        <v>17</v>
+      </c>
+      <c r="H192" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I192" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J192" s="12" t="s">
+        <v>625</v>
+      </c>
+      <c r="K192" s="11" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A193" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="B193" s="12" t="s">
+        <v>627</v>
+      </c>
+      <c r="C193" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D193" s="12">
+        <v>1200</v>
+      </c>
+      <c r="E193" s="12">
+        <v>850</v>
+      </c>
+      <c r="F193" s="12"/>
+      <c r="G193" s="2">
+        <v>16</v>
+      </c>
+      <c r="H193" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I193" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J193" s="12" t="s">
+        <v>628</v>
+      </c>
+      <c r="K193" s="11" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A194" s="11" t="s">
+        <v>632</v>
+      </c>
+      <c r="B194" s="12" t="s">
+        <v>630</v>
+      </c>
+      <c r="C194" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D194" s="12">
+        <v>1100</v>
+      </c>
+      <c r="E194" s="12">
+        <v>760</v>
+      </c>
+      <c r="F194" s="12"/>
+      <c r="G194" s="2">
+        <v>18</v>
+      </c>
+      <c r="H194" s="12" t="s">
+        <v>631</v>
+      </c>
+      <c r="I194" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J194" s="12" t="s">
+        <v>633</v>
+      </c>
+      <c r="K194" s="11" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A195" s="11" t="s">
+        <v>637</v>
+      </c>
+      <c r="B195" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="C195" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D195" s="12">
+        <v>1100</v>
+      </c>
+      <c r="E195" s="12">
+        <v>860</v>
+      </c>
+      <c r="F195" s="12"/>
+      <c r="G195" s="2">
+        <v>12</v>
+      </c>
+      <c r="H195" s="12" t="s">
+        <v>635</v>
+      </c>
+      <c r="I195" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J195" s="12" t="s">
+        <v>636</v>
+      </c>
+      <c r="K195" s="11" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A196" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="B196" s="12" t="s">
+        <v>638</v>
+      </c>
+      <c r="C196" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D196" s="12">
+        <v>1300</v>
+      </c>
+      <c r="E196" s="12">
+        <v>1050</v>
+      </c>
+      <c r="F196" s="12"/>
+      <c r="G196" s="2">
+        <v>23</v>
+      </c>
+      <c r="H196" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I196" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J196" s="12" t="s">
+        <v>639</v>
+      </c>
+      <c r="K196" s="11" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A197" s="11" t="s">
+        <v>709</v>
+      </c>
+      <c r="B197" s="12" t="s">
+        <v>710</v>
+      </c>
+      <c r="C197" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D197" s="12">
+        <v>700</v>
+      </c>
+      <c r="E197" s="12">
+        <v>490</v>
+      </c>
+      <c r="F197" s="12"/>
+      <c r="G197" s="2">
+        <v>15</v>
+      </c>
+      <c r="H197" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I197" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J197" s="12" t="s">
+        <v>711</v>
+      </c>
+      <c r="K197" s="11" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A198" s="11" t="s">
+        <v>643</v>
+      </c>
+      <c r="B198" s="12" t="s">
+        <v>641</v>
+      </c>
+      <c r="C198" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D198" s="12">
+        <v>1320</v>
+      </c>
+      <c r="E198" s="12">
+        <v>1090</v>
+      </c>
+      <c r="F198" s="12"/>
+      <c r="G198" s="2">
+        <v>26</v>
+      </c>
+      <c r="H198" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I198" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J198" s="12" t="s">
+        <v>642</v>
+      </c>
+      <c r="K198" s="11" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A199" s="11" t="s">
+        <v>645</v>
+      </c>
+      <c r="B199" s="12" t="s">
+        <v>644</v>
+      </c>
+      <c r="C199" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D199" s="12">
+        <v>1200</v>
+      </c>
+      <c r="E199" s="12">
+        <v>920</v>
+      </c>
+      <c r="F199" s="12"/>
+      <c r="G199" s="2">
+        <v>8</v>
+      </c>
+      <c r="H199" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I199" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J199" s="12" t="s">
+        <v>646</v>
+      </c>
+      <c r="K199" s="11" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A200" s="11" t="s">
+        <v>674</v>
+      </c>
+      <c r="B200" s="12" t="s">
+        <v>677</v>
+      </c>
+      <c r="C200" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D200" s="12">
+        <v>1200</v>
+      </c>
+      <c r="E200" s="12">
+        <v>970</v>
+      </c>
+      <c r="F200" s="12"/>
+      <c r="G200" s="2">
+        <v>16</v>
+      </c>
+      <c r="H200" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I200" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J200" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="K200" s="11" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A201" s="11" t="s">
+        <v>676</v>
+      </c>
+      <c r="B201" s="12" t="s">
+        <v>677</v>
+      </c>
+      <c r="C201" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D201" s="12">
+        <v>750</v>
+      </c>
+      <c r="E201" s="12">
+        <v>490</v>
+      </c>
+      <c r="F201" s="12"/>
+      <c r="G201" s="2">
+        <v>14</v>
+      </c>
+      <c r="H201" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I201" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J201" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="K201" s="11" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A202" s="11" t="s">
+        <v>681</v>
+      </c>
+      <c r="B202" s="12" t="s">
+        <v>683</v>
+      </c>
+      <c r="C202" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D202" s="12">
+        <v>1500</v>
+      </c>
+      <c r="E202" s="12">
+        <v>1240</v>
+      </c>
+      <c r="F202" s="12"/>
+      <c r="G202" s="2">
+        <v>22</v>
+      </c>
+      <c r="H202" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I202" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J202" s="12" t="s">
+        <v>684</v>
+      </c>
+      <c r="K202" s="11" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A203" s="11" t="s">
+        <v>682</v>
+      </c>
+      <c r="B203" s="12" t="s">
+        <v>683</v>
+      </c>
+      <c r="C203" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D203" s="12">
+        <v>1000</v>
+      </c>
+      <c r="E203" s="12">
+        <v>830</v>
+      </c>
+      <c r="F203" s="12"/>
+      <c r="G203" s="2">
+        <v>22</v>
+      </c>
+      <c r="H203" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I203" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J203" s="12" t="s">
+        <v>684</v>
+      </c>
+      <c r="K203" s="11" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A204" s="11" t="s">
+        <v>685</v>
+      </c>
+      <c r="B204" s="12" t="s">
+        <v>687</v>
+      </c>
+      <c r="C204" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D204" s="12">
+        <v>1450</v>
+      </c>
+      <c r="E204" s="12">
+        <v>1240</v>
+      </c>
+      <c r="F204" s="12"/>
+      <c r="G204" s="2">
+        <v>15</v>
+      </c>
+      <c r="H204" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I204" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J204" s="12" t="s">
+        <v>688</v>
+      </c>
+      <c r="K204" s="11" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A205" s="11" t="s">
+        <v>686</v>
+      </c>
+      <c r="B205" s="12" t="s">
+        <v>687</v>
+      </c>
+      <c r="C205" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D205" s="12">
+        <v>950</v>
+      </c>
+      <c r="E205" s="12">
+        <v>830</v>
+      </c>
+      <c r="F205" s="12"/>
+      <c r="G205" s="2">
+        <v>16</v>
+      </c>
+      <c r="H205" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I205" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J205" s="12" t="s">
+        <v>688</v>
+      </c>
+      <c r="K205" s="11" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A206" s="11" t="s">
+        <v>689</v>
+      </c>
+      <c r="B206" s="12" t="s">
+        <v>690</v>
+      </c>
+      <c r="C206" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D206" s="12">
+        <v>1350</v>
+      </c>
+      <c r="E206" s="12">
+        <v>1140</v>
+      </c>
+      <c r="F206" s="12"/>
+      <c r="G206" s="2">
         <v>21</v>
       </c>
-    </row>
-    <row r="162" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C162" s="10" t="s">
-        <v>560</v>
-      </c>
-      <c r="G162" s="2"/>
-      <c r="I162" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="163" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C163" s="10" t="s">
-        <v>560</v>
-      </c>
-      <c r="G163" s="2"/>
-      <c r="I163" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="164" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C164" s="10" t="s">
-        <v>560</v>
-      </c>
-      <c r="G164" s="2"/>
-      <c r="I164" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="165" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C165" s="10" t="s">
-        <v>560</v>
-      </c>
-      <c r="G165" s="2"/>
-    </row>
-    <row r="166" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C166" s="10" t="s">
-        <v>560</v>
-      </c>
+      <c r="H206" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I206" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J206" s="12" t="s">
+        <v>691</v>
+      </c>
+      <c r="K206" s="11" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A207" s="11" t="s">
+        <v>692</v>
+      </c>
+      <c r="B207" s="12" t="s">
+        <v>694</v>
+      </c>
+      <c r="C207" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D207" s="12">
+        <v>1300</v>
+      </c>
+      <c r="E207" s="12">
+        <v>1180</v>
+      </c>
+      <c r="F207" s="12"/>
+      <c r="G207" s="2">
+        <v>12</v>
+      </c>
+      <c r="H207" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I207" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J207" s="12" t="s">
+        <v>695</v>
+      </c>
+      <c r="K207" s="11" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A208" s="11" t="s">
+        <v>693</v>
+      </c>
+      <c r="B208" s="12" t="s">
+        <v>694</v>
+      </c>
+      <c r="C208" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D208" s="12">
+        <v>700</v>
+      </c>
+      <c r="E208" s="12">
+        <v>490</v>
+      </c>
+      <c r="F208" s="12"/>
+      <c r="G208" s="2">
+        <v>11</v>
+      </c>
+      <c r="H208" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I208" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J208" s="12" t="s">
+        <v>695</v>
+      </c>
+      <c r="K208" s="11" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A209" s="11" t="s">
+        <v>702</v>
+      </c>
+      <c r="B209" s="12" t="s">
+        <v>704</v>
+      </c>
+      <c r="C209" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D209" s="12">
+        <v>1320</v>
+      </c>
+      <c r="E209" s="12">
+        <v>1140</v>
+      </c>
+      <c r="F209" s="12"/>
+      <c r="G209" s="2">
+        <v>16</v>
+      </c>
+      <c r="H209" s="12" t="s">
+        <v>635</v>
+      </c>
+      <c r="I209" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J209" s="12" t="s">
+        <v>705</v>
+      </c>
+      <c r="K209" s="11" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A210" s="11" t="s">
+        <v>703</v>
+      </c>
+      <c r="B210" s="12" t="s">
+        <v>704</v>
+      </c>
+      <c r="C210" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D210" s="12">
+        <v>980</v>
+      </c>
+      <c r="E210" s="12">
+        <v>870</v>
+      </c>
+      <c r="F210" s="12"/>
+      <c r="G210" s="2">
+        <v>18</v>
+      </c>
+      <c r="H210" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I210" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J210" s="12" t="s">
+        <v>705</v>
+      </c>
+      <c r="K210" s="11" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A211" s="11" t="s">
+        <v>706</v>
+      </c>
+      <c r="B211" s="12" t="s">
+        <v>707</v>
+      </c>
+      <c r="C211" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D211" s="12">
+        <v>1100</v>
+      </c>
+      <c r="E211" s="12">
+        <v>850</v>
+      </c>
+      <c r="F211" s="12"/>
+      <c r="G211" s="2">
+        <v>23</v>
+      </c>
+      <c r="H211" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I211" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J211" s="12" t="s">
+        <v>708</v>
+      </c>
+      <c r="K211" s="11" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A212" s="11" t="s">
+        <v>712</v>
+      </c>
+      <c r="B212" s="12" t="s">
+        <v>714</v>
+      </c>
+      <c r="C212" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D212" s="12">
+        <v>1200</v>
+      </c>
+      <c r="E212" s="12">
+        <v>1090</v>
+      </c>
+      <c r="F212" s="12"/>
+      <c r="G212" s="2">
+        <v>12</v>
+      </c>
+      <c r="H212" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I212" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J212" s="12" t="s">
+        <v>715</v>
+      </c>
+      <c r="K212" s="11" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A213" s="11" t="s">
+        <v>713</v>
+      </c>
+      <c r="B213" s="12" t="s">
+        <v>714</v>
+      </c>
+      <c r="C213" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D213" s="12">
+        <v>750</v>
+      </c>
+      <c r="E213" s="12">
+        <v>490</v>
+      </c>
+      <c r="F213" s="12"/>
+      <c r="G213" s="2">
+        <v>15</v>
+      </c>
+      <c r="H213" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I213" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J213" s="12" t="s">
+        <v>715</v>
+      </c>
+      <c r="K213" s="11" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A214" s="11"/>
+      <c r="B214" s="12"/>
+      <c r="C214" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D214" s="12"/>
+      <c r="E214" s="12"/>
+      <c r="F214" s="12"/>
+      <c r="G214" s="2"/>
+      <c r="H214" s="12"/>
+      <c r="I214" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J214" s="12"/>
+      <c r="K214" s="11"/>
+    </row>
+    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A215" s="11"/>
+      <c r="B215" s="12"/>
+      <c r="C215" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D215" s="12"/>
+      <c r="E215" s="12"/>
+      <c r="F215" s="12"/>
+      <c r="G215" s="2"/>
+      <c r="H215" s="12"/>
+      <c r="I215" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J215" s="12"/>
+      <c r="K215" s="11"/>
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A216" s="11"/>
+      <c r="B216" s="12"/>
+      <c r="C216" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D216" s="12"/>
+      <c r="E216" s="12"/>
+      <c r="F216" s="12"/>
+      <c r="G216" s="2"/>
+      <c r="H216" s="12"/>
+      <c r="I216" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J216" s="12"/>
+      <c r="K216" s="11"/>
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A217" s="11"/>
+      <c r="B217" s="12"/>
+      <c r="C217" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D217" s="12"/>
+      <c r="E217" s="12"/>
+      <c r="F217" s="12"/>
+      <c r="G217" s="2"/>
+      <c r="H217" s="12"/>
+      <c r="I217" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J217" s="12"/>
+      <c r="K217" s="11"/>
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A218" s="11"/>
+      <c r="B218" s="12"/>
+      <c r="C218" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D218" s="12"/>
+      <c r="E218" s="12"/>
+      <c r="F218" s="12"/>
+      <c r="G218" s="2"/>
+      <c r="H218" s="12"/>
+      <c r="I218" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J218" s="12"/>
+      <c r="K218" s="11"/>
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A219" s="11"/>
+      <c r="B219" s="12"/>
+      <c r="C219" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D219" s="12"/>
+      <c r="E219" s="12"/>
+      <c r="F219" s="12"/>
+      <c r="G219" s="2"/>
+      <c r="H219" s="12"/>
+      <c r="I219" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J219" s="12"/>
+      <c r="K219" s="11"/>
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A220" s="11"/>
+      <c r="B220" s="12"/>
+      <c r="C220" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D220" s="12"/>
+      <c r="E220" s="12"/>
+      <c r="F220" s="12"/>
+      <c r="G220" s="2"/>
+      <c r="H220" s="12"/>
+      <c r="I220" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J220" s="12"/>
+      <c r="K220" s="11"/>
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A221" s="11"/>
+      <c r="B221" s="12"/>
+      <c r="C221" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D221" s="12"/>
+      <c r="E221" s="12"/>
+      <c r="F221" s="12"/>
+      <c r="G221" s="2"/>
+      <c r="H221" s="12"/>
+      <c r="I221" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J221" s="12"/>
+      <c r="K221" s="11"/>
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A222" s="11"/>
+      <c r="B222" s="12"/>
+      <c r="C222" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D222" s="12"/>
+      <c r="E222" s="12"/>
+      <c r="F222" s="12"/>
+      <c r="G222" s="2"/>
+      <c r="H222" s="12"/>
+      <c r="I222" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J222" s="12"/>
+      <c r="K222" s="11"/>
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A223" s="11"/>
+      <c r="B223" s="12"/>
+      <c r="C223" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D223" s="12"/>
+      <c r="E223" s="12"/>
+      <c r="F223" s="12"/>
+      <c r="G223" s="2"/>
+      <c r="H223" s="12"/>
+      <c r="I223" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J223" s="12"/>
+      <c r="K223" s="11"/>
+    </row>
+    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A224" s="11"/>
+      <c r="B224" s="12"/>
+      <c r="C224" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D224" s="12"/>
+      <c r="E224" s="12"/>
+      <c r="F224" s="12"/>
+      <c r="G224" s="2"/>
+      <c r="H224" s="12"/>
+      <c r="I224" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J224" s="12"/>
+      <c r="K224" s="11"/>
+    </row>
+    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A225" s="11"/>
+      <c r="B225" s="12"/>
+      <c r="C225" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D225" s="12"/>
+      <c r="E225" s="12"/>
+      <c r="F225" s="12"/>
+      <c r="G225" s="2"/>
+      <c r="H225" s="12"/>
+      <c r="I225" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J225" s="12"/>
+      <c r="K225" s="11"/>
+    </row>
+    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A226" s="11"/>
+      <c r="B226" s="12"/>
+      <c r="C226" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D226" s="12"/>
+      <c r="E226" s="12"/>
+      <c r="F226" s="12"/>
+      <c r="G226" s="12"/>
+      <c r="H226" s="12"/>
+      <c r="I226" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J226" s="12"/>
+      <c r="K226" s="11"/>
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A227" s="11"/>
+      <c r="B227" s="12"/>
+      <c r="C227" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D227" s="12"/>
+      <c r="E227" s="12"/>
+      <c r="F227" s="12"/>
+      <c r="G227" s="12"/>
+      <c r="H227" s="12"/>
+      <c r="I227" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J227" s="12"/>
+      <c r="K227" s="11"/>
+    </row>
+    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A228" s="11"/>
+      <c r="B228" s="12"/>
+      <c r="C228" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D228" s="12"/>
+      <c r="E228" s="12"/>
+      <c r="F228" s="12"/>
+      <c r="G228" s="12"/>
+      <c r="H228" s="12"/>
+      <c r="I228" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J228" s="12"/>
+      <c r="K228" s="11"/>
+    </row>
+    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A229" s="11"/>
+      <c r="B229" s="12"/>
+      <c r="C229" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D229" s="12"/>
+      <c r="E229" s="12"/>
+      <c r="F229" s="12"/>
+      <c r="G229" s="12"/>
+      <c r="H229" s="12"/>
+      <c r="I229" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J229" s="12"/>
+      <c r="K229" s="11"/>
+    </row>
+    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A230" s="11"/>
+      <c r="B230" s="12"/>
+      <c r="C230" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D230" s="12"/>
+      <c r="E230" s="12"/>
+      <c r="F230" s="12"/>
+      <c r="G230" s="12"/>
+      <c r="H230" s="12"/>
+      <c r="I230" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J230" s="12"/>
+      <c r="K230" s="11"/>
+    </row>
+    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A231" s="11"/>
+      <c r="B231" s="12"/>
+      <c r="C231" s="12"/>
+      <c r="D231" s="12"/>
+      <c r="E231" s="12"/>
+      <c r="F231" s="12"/>
+      <c r="G231" s="12"/>
+      <c r="H231" s="12"/>
+      <c r="I231" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J231" s="12"/>
+      <c r="K231" s="11"/>
+    </row>
+    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A232" s="11"/>
+      <c r="B232" s="12"/>
+      <c r="C232" s="12"/>
+      <c r="D232" s="12"/>
+      <c r="E232" s="12"/>
+      <c r="F232" s="12"/>
+      <c r="G232" s="12"/>
+      <c r="H232" s="12"/>
+      <c r="I232" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J232" s="12"/>
+      <c r="K232" s="11"/>
+    </row>
+    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A233" s="11"/>
+      <c r="B233" s="12"/>
+      <c r="C233" s="12"/>
+      <c r="D233" s="12"/>
+      <c r="E233" s="12"/>
+      <c r="F233" s="12"/>
+      <c r="G233" s="12"/>
+      <c r="H233" s="12"/>
+      <c r="I233" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J233" s="12"/>
+      <c r="K233" s="11"/>
+    </row>
+    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A234" s="11"/>
+      <c r="B234" s="12"/>
+      <c r="C234" s="12"/>
+      <c r="D234" s="12"/>
+      <c r="E234" s="12"/>
+      <c r="F234" s="12"/>
+      <c r="G234" s="12"/>
+      <c r="H234" s="12"/>
+      <c r="I234" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J234" s="12"/>
+      <c r="K234" s="11"/>
+    </row>
+    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A235" s="11"/>
+      <c r="B235" s="12"/>
+      <c r="C235" s="12"/>
+      <c r="D235" s="12"/>
+      <c r="E235" s="12"/>
+      <c r="F235" s="12"/>
+      <c r="G235" s="12"/>
+      <c r="H235" s="12"/>
+      <c r="I235" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J235" s="12"/>
+      <c r="K235" s="11"/>
+    </row>
+    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A236" s="11"/>
+      <c r="B236" s="12"/>
+      <c r="C236" s="12"/>
+      <c r="D236" s="12"/>
+      <c r="E236" s="12"/>
+      <c r="F236" s="12"/>
+      <c r="G236" s="12"/>
+      <c r="H236" s="12"/>
+      <c r="I236" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J236" s="12"/>
+      <c r="K236" s="11"/>
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A237" s="11"/>
+      <c r="B237" s="12"/>
+      <c r="C237" s="12"/>
+      <c r="D237" s="12"/>
+      <c r="E237" s="12"/>
+      <c r="F237" s="12"/>
+      <c r="G237" s="12"/>
+      <c r="H237" s="12"/>
+      <c r="I237" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J237" s="12"/>
+      <c r="K237" s="11"/>
+    </row>
+    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A238" s="11"/>
+      <c r="B238" s="12"/>
+      <c r="C238" s="12"/>
+      <c r="D238" s="12"/>
+      <c r="E238" s="12"/>
+      <c r="F238" s="12"/>
+      <c r="G238" s="12"/>
+      <c r="H238" s="12"/>
+      <c r="I238" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J238" s="12"/>
+      <c r="K238" s="11"/>
+    </row>
+    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A239" s="11"/>
+      <c r="B239" s="12"/>
+      <c r="C239" s="12"/>
+      <c r="D239" s="12"/>
+      <c r="E239" s="12"/>
+      <c r="F239" s="12"/>
+      <c r="G239" s="12"/>
+      <c r="H239" s="12"/>
+      <c r="I239" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J239" s="12"/>
+      <c r="K239" s="11"/>
+    </row>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A240" s="11"/>
+      <c r="B240" s="12"/>
+      <c r="C240" s="12"/>
+      <c r="D240" s="12"/>
+      <c r="E240" s="12"/>
+      <c r="F240" s="12"/>
+      <c r="G240" s="12"/>
+      <c r="H240" s="12"/>
+      <c r="I240" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J240" s="12"/>
+      <c r="K240" s="11"/>
+    </row>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A241" s="11"/>
+      <c r="B241" s="12"/>
+      <c r="C241" s="12"/>
+      <c r="D241" s="12"/>
+      <c r="E241" s="12"/>
+      <c r="F241" s="12"/>
+      <c r="G241" s="12"/>
+      <c r="H241" s="12"/>
+      <c r="I241" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J241" s="12"/>
+      <c r="K241" s="11"/>
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A242" s="11"/>
+      <c r="B242" s="12"/>
+      <c r="C242" s="12"/>
+      <c r="D242" s="12"/>
+      <c r="E242" s="12"/>
+      <c r="F242" s="12"/>
+      <c r="G242" s="12"/>
+      <c r="H242" s="12"/>
+      <c r="I242" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J242" s="12"/>
+      <c r="K242" s="11"/>
+    </row>
+    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A243" s="11"/>
+      <c r="B243" s="12"/>
+      <c r="C243" s="12"/>
+      <c r="D243" s="12"/>
+      <c r="E243" s="12"/>
+      <c r="F243" s="12"/>
+      <c r="G243" s="12"/>
+      <c r="H243" s="12"/>
+      <c r="I243" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J243" s="12"/>
+      <c r="K243" s="11"/>
+    </row>
+    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A244" s="11"/>
+      <c r="B244" s="12"/>
+      <c r="C244" s="12"/>
+      <c r="D244" s="12"/>
+      <c r="E244" s="12"/>
+      <c r="F244" s="12"/>
+      <c r="G244" s="12"/>
+      <c r="H244" s="12"/>
+      <c r="I244" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J244" s="12"/>
+      <c r="K244" s="11"/>
+    </row>
+    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A245" s="11"/>
+      <c r="B245" s="12"/>
+      <c r="C245" s="12"/>
+      <c r="D245" s="12"/>
+      <c r="E245" s="12"/>
+      <c r="F245" s="12"/>
+      <c r="G245" s="12"/>
+      <c r="H245" s="12"/>
+      <c r="I245" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J245" s="12"/>
+      <c r="K245" s="11"/>
+    </row>
+    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A246" s="11"/>
+      <c r="B246" s="12"/>
+      <c r="C246" s="12"/>
+      <c r="D246" s="12"/>
+      <c r="E246" s="12"/>
+      <c r="F246" s="12"/>
+      <c r="G246" s="12"/>
+      <c r="H246" s="12"/>
+      <c r="I246" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J246" s="12"/>
+      <c r="K246" s="11"/>
+    </row>
+    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A247" s="11"/>
+      <c r="B247" s="12"/>
+      <c r="C247" s="12"/>
+      <c r="D247" s="12"/>
+      <c r="E247" s="12"/>
+      <c r="F247" s="12"/>
+      <c r="G247" s="12"/>
+      <c r="H247" s="12"/>
+      <c r="I247" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J247" s="12"/>
+      <c r="K247" s="11"/>
+    </row>
+    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A248" s="11"/>
+      <c r="B248" s="12"/>
+      <c r="C248" s="12"/>
+      <c r="D248" s="12"/>
+      <c r="E248" s="12"/>
+      <c r="F248" s="12"/>
+      <c r="G248" s="12"/>
+      <c r="H248" s="12"/>
+      <c r="I248" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J248" s="12"/>
+      <c r="K248" s="11"/>
+    </row>
+    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A249" s="11"/>
+      <c r="B249" s="12"/>
+      <c r="C249" s="12"/>
+      <c r="D249" s="12"/>
+      <c r="E249" s="12"/>
+      <c r="F249" s="12"/>
+      <c r="G249" s="12"/>
+      <c r="H249" s="12"/>
+      <c r="I249" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J249" s="12"/>
+      <c r="K249" s="11"/>
+    </row>
+    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A250" s="11"/>
+      <c r="B250" s="12"/>
+      <c r="C250" s="12"/>
+      <c r="D250" s="12"/>
+      <c r="E250" s="12"/>
+      <c r="F250" s="12"/>
+      <c r="G250" s="12"/>
+      <c r="H250" s="12"/>
+      <c r="I250" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J250" s="12"/>
+      <c r="K250" s="11"/>
+    </row>
+    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A251" s="11"/>
+      <c r="B251" s="12"/>
+      <c r="C251" s="12"/>
+      <c r="D251" s="12"/>
+      <c r="E251" s="12"/>
+      <c r="F251" s="12"/>
+      <c r="G251" s="12"/>
+      <c r="H251" s="12"/>
+      <c r="I251" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J251" s="12"/>
+      <c r="K251" s="11"/>
+    </row>
+    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A252" s="11"/>
+      <c r="B252" s="12"/>
+      <c r="C252" s="12"/>
+      <c r="D252" s="12"/>
+      <c r="E252" s="12"/>
+      <c r="F252" s="12"/>
+      <c r="G252" s="12"/>
+      <c r="H252" s="12"/>
+      <c r="I252" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J252" s="12"/>
+      <c r="K252" s="11"/>
+    </row>
+    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A253" s="11"/>
+      <c r="B253" s="12"/>
+      <c r="C253" s="12"/>
+      <c r="D253" s="12"/>
+      <c r="E253" s="12"/>
+      <c r="F253" s="12"/>
+      <c r="G253" s="12"/>
+      <c r="H253" s="12"/>
+      <c r="I253" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J253" s="12"/>
+      <c r="K253" s="11"/>
+    </row>
+    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A254" s="11"/>
+      <c r="B254" s="12"/>
+      <c r="C254" s="12"/>
+      <c r="D254" s="12"/>
+      <c r="E254" s="12"/>
+      <c r="F254" s="12"/>
+      <c r="G254" s="12"/>
+      <c r="H254" s="12"/>
+      <c r="I254" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J254" s="12"/>
+      <c r="K254" s="11"/>
+    </row>
+    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A255" s="11"/>
+      <c r="B255" s="12"/>
+      <c r="C255" s="12"/>
+      <c r="D255" s="12"/>
+      <c r="E255" s="12"/>
+      <c r="F255" s="12"/>
+      <c r="G255" s="12"/>
+      <c r="H255" s="12"/>
+      <c r="I255" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J255" s="12"/>
+      <c r="K255" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K93" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -11967,7 +15776,7 @@
       <formula>20</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G159">
+  <conditionalFormatting sqref="G159:G167">
     <cfRule type="cellIs" dxfId="17" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
@@ -11978,7 +15787,7 @@
       <formula>20</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G160">
+  <conditionalFormatting sqref="G168:G170">
     <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
       <formula>0</formula>
     </cfRule>
@@ -11989,7 +15798,7 @@
       <formula>20</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G161:G165">
+  <conditionalFormatting sqref="G171:G225">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
@@ -12047,13 +15856,13 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" s="2">
         <v>3500</v>
@@ -12066,27 +15875,27 @@
         <v>10</v>
       </c>
       <c r="H2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="K2" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="2">
         <v>2420</v>
@@ -12097,27 +15906,27 @@
         <v>16</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="2">
         <v>2800</v>
@@ -12128,27 +15937,27 @@
         <v>14</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="K4" s="8" t="s">
         <v>108</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2">
         <v>4100</v>
@@ -12159,16 +15968,16 @@
         <v>17</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/price.xlsx
+++ b/price.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ПРОЕКТ AI\ЛИЧНЫЕ НАРАБОТКИ\AI Skin Lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84258969-3C80-4057-88E3-80AA2C0BB7BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED556DBF-94AA-4499-AE67-7D5227448194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Зручна таблиця" sheetId="1" r:id="rId1"/>
